--- a/data/people.xlsx
+++ b/data/people.xlsx
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Y10" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_iii</t>
+          <t>chapter_1_iii; chapter_3_vi</t>
         </is>
       </c>
       <c r="Z10" s="14" t="inlineStr">

--- a/data/people.xlsx
+++ b/data/people.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник полей" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'База данных'!$A$3:$AB$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'База данных'!$A$3:$AC$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB85"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -490,16 +490,17 @@
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="60" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="22" customWidth="1" min="26" max="26"/>
     <col width="22" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,43 +526,44 @@
       </c>
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>БИОГРАФИЯ — МЕСТО</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="n"/>
       <c r="K2" s="7" t="n"/>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>АКАДЕМИЧЕСКАЯ КАРЬЕРА</t>
         </is>
       </c>
-      <c r="M2" s="9" t="n"/>
       <c r="N2" s="9" t="n"/>
       <c r="O2" s="9" t="n"/>
       <c r="P2" s="9" t="n"/>
       <c r="Q2" s="9" t="n"/>
-      <c r="R2" s="10" t="inlineStr">
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="10" t="inlineStr">
         <is>
           <t>НАУЧНЫЙ ПРОФИЛЬ</t>
         </is>
       </c>
-      <c r="S2" s="11" t="n"/>
       <c r="T2" s="11" t="n"/>
       <c r="U2" s="11" t="n"/>
       <c r="V2" s="11" t="n"/>
-      <c r="W2" s="12" t="inlineStr">
+      <c r="W2" s="11" t="n"/>
+      <c r="X2" s="12" t="inlineStr">
         <is>
           <t>КОНТЕКСТ КНИГИ УИЛСОНА</t>
         </is>
       </c>
-      <c r="X2" s="13" t="n"/>
       <c r="Y2" s="13" t="n"/>
       <c r="Z2" s="13" t="n"/>
       <c r="AA2" s="13" t="n"/>
       <c r="AB2" s="13" t="n"/>
+      <c r="AC2" s="13" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -599,107 +601,112 @@
           <t>Дата смерти</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Причина смерти</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Место рождения</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Координаты рождения</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Место смерти</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>Координаты смерти</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>Alma mater</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>Аффилиация</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>Учителя</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>Ученики</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>Коллеги</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>Награды и премии</t>
         </is>
       </c>
-      <c r="R3" s="10" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Области интересов</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Кто это</t>
         </is>
       </c>
-      <c r="T3" s="10" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>Основные труды / понятия</t>
         </is>
       </c>
-      <c r="U3" s="10" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>Ссылка SEP</t>
         </is>
       </c>
-      <c r="V3" s="10" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Ссылка Wikipedia (RU)</t>
         </is>
       </c>
-      <c r="W3" s="12" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
         <is>
           <t>Роль в книге</t>
         </is>
       </c>
-      <c r="X3" s="12" t="inlineStr">
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>Главы</t>
         </is>
       </c>
-      <c r="Y3" s="12" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>Разделы книги</t>
         </is>
       </c>
-      <c r="Z3" s="12" t="inlineStr">
+      <c r="AA3" s="12" t="inlineStr">
         <is>
           <t>Карточка</t>
         </is>
       </c>
-      <c r="AA3" s="12" t="inlineStr">
+      <c r="AB3" s="12" t="inlineStr">
         <is>
           <t>Данные проверены</t>
         </is>
       </c>
-      <c r="AB3" s="12" t="inlineStr">
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
@@ -741,79 +748,80 @@
           <t>1231-06-13</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Лиссабон, Португалия</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>38.7223, -9.1393</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>Арчелла близ Падуи, Италия</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>45.4064, 11.8768</t>
         </is>
       </c>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>Орден францисканцев</t>
         </is>
       </c>
-      <c r="N4" s="14" t="n"/>
       <c r="O4" s="14" t="n"/>
       <c r="P4" s="14" t="n"/>
       <c r="Q4" s="14" t="n"/>
-      <c r="R4" s="14" t="inlineStr">
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="inlineStr">
         <is>
           <t>богословие; проповедь</t>
         </is>
       </c>
-      <c r="S4" s="14" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>Католический священник-францисканец, один из самых известных проповедников Средневековья, канонизирован уже через год после смерти (1232), позже провозглашён Учителем Церкви. В агиографии закрепился сюжет «Проповеди рыбам» (восходит к «Цветочкам Франциска Ассизского», гл. 40): когда еретики Римини отказались его слушать, Антоний обратился с проповедью к рыбам в реке и море, и те якобы высунули головы из воды, чтобы внимать его словам.</t>
         </is>
       </c>
-      <c r="T4" s="14" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>- Легенда о «Проповеди рыбам» (Sermon to the Fish / Miracle of the Fishes) — эпизод из жития, впервые подробно изложен в «Цветочках Франциска Ассизского» (Fioretti), гл. 40 - Опосредованный источник: Paul Nahin, Oliver Heaviside (см. карточку p-j-nahin)</t>
         </is>
       </c>
-      <c r="U4" s="14" t="n"/>
       <c r="V4" s="14" t="n"/>
-      <c r="W4" s="14" t="inlineStr">
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="inlineStr">
         <is>
           <t>(вывод по цепочке цитирования, требует уточнения при чтении) Появляется не напрямую, а через двойное цитирование: Уилсон приводит эпизод со ссылкой на биографа Хевисайда — Пола Нахина, у которого Хевисайд сам обращается к этому сюжету. По всей видимости, Хевисайд использовал образ «проповеди рыбам» иронически по отношению к себе: как и Антоний, обращавшийся к рыбам, потому что люди (еретики) отказывались слушать, Хевисайд адресовал свои идеи практикам-инженерам, т.к. академическое математическое сообщество, их отвергало.</t>
         </is>
       </c>
-      <c r="X4" s="14" t="inlineStr">
+      <c r="Y4" s="14" t="inlineStr">
         <is>
           <t>предисловие</t>
         </is>
       </c>
-      <c r="Y4" s="14" t="inlineStr">
+      <c r="Z4" s="14" t="inlineStr">
         <is>
           <t>predislovie</t>
         </is>
       </c>
-      <c r="Z4" s="14" t="inlineStr">
+      <c r="AA4" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/anthony-of-padua</t>
         </is>
       </c>
-      <c r="AA4" s="14" t="inlineStr">
+      <c r="AB4" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB4" s="14" t="n"/>
+      <c r="AC4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -853,85 +861,90 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
+          <t>предположительно, чума</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
           <t>Оккам, Суррей, Англия</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>51.3000, -0.4500</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>Мюнхен</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>48.1351, 11.5820</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t>Оксфордский университет</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t>Орден францисканцев</t>
         </is>
       </c>
-      <c r="N5" s="14" t="n"/>
       <c r="O5" s="14" t="n"/>
       <c r="P5" s="14" t="n"/>
       <c r="Q5" s="14" t="n"/>
-      <c r="R5" s="14" t="inlineStr">
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="inlineStr">
         <is>
           <t>логика; номинализм; богословие</t>
         </is>
       </c>
-      <c r="S5" s="14" t="inlineStr">
+      <c r="T5" s="14" t="inlineStr">
         <is>
           <t>Английский философ-схоласт и францисканский монах (ок. 1287–1347), один из крупнейших представителей позднесредневекового номинализма (терминизма). Автор «Summa Logica», где разрабатывает учение о терминах и интенциях души; известен также принципом экономии мышления («бритва Оккама»).</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>- «Ockham's Theory of Terms» (Summa Logica I), пер. Michael J. Loux, University of Notre Dame Press, 1974, с. 7 - Понятие «интенции души» (intentio animae)</t>
         </is>
       </c>
-      <c r="U5" s="14" t="inlineStr">
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/ockham/</t>
         </is>
       </c>
-      <c r="V5" s="14" t="n"/>
-      <c r="W5" s="14" t="inlineStr">
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="inlineStr">
         <is>
           <t>Приводится Уилсоном как исторический представитель интенционально-обоснованной картины предикатной значимости — через прямую цитату из «Summa Logica»: «интенция души — это нечто в душе, способное означать что-то другое». Уилсон отмечает, что Оккам, как теологически мотивированный автор, был «на грани заключения», что эта особая означивающая активность демонстрирует духовную способность человека, ставящую его на более высокую ступень Великой Цепи Бытия, чем у «не имеющих способности к означению обезьян».</t>
         </is>
       </c>
-      <c r="X5" s="14" t="inlineStr">
+      <c r="Y5" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y5" s="14" t="inlineStr">
+      <c r="Z5" s="14" t="inlineStr">
         <is>
           <t>chapter_3_ii</t>
         </is>
       </c>
-      <c r="Z5" s="14" t="inlineStr">
+      <c r="AA5" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/uilyam-okkam</t>
         </is>
       </c>
-      <c r="AA5" s="14" t="inlineStr">
+      <c r="AB5" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB5" s="14" t="n"/>
+      <c r="AC5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -969,79 +982,80 @@
           <t>1637-09-08</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Берстед, Кент, Англия</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>51.2760, 0.5780</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t>Сент-Джонс-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M6" s="14" t="n"/>
       <c r="N6" s="14" t="n"/>
       <c r="O6" s="14" t="n"/>
       <c r="P6" s="14" t="n"/>
       <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="14" t="inlineStr">
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="inlineStr">
         <is>
           <t>медицина; герметизм; космология; теория музыки</t>
         </is>
       </c>
-      <c r="S6" s="14" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>Английский врач, астролог и мистик, видный представитель ренессансного эзотеризма и герметической традиции. Верил в корреляцию между музыкальной гармонией и космическим порядком (музыка сфер).</t>
         </is>
       </c>
-      <c r="T6" s="14" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>- Герметическая философия / музыка сфер - Пифагорейские представления о гармонии</t>
         </is>
       </c>
-      <c r="U6" s="14" t="n"/>
       <c r="V6" s="14" t="n"/>
-      <c r="W6" s="14" t="inlineStr">
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="inlineStr">
         <is>
           <t>Уилсон приводит Фладда как крайний пример объективистской модели музыкальных атрибутов. Фладд и его последователи верили, что выражение печали музыкально — это объективное свойство, встроенное в космический порядок (подобно магнетизму), и что человеческая душа должна пройти через духовное очищение, чтобы стать открытой для этой небесной музыки. Уилсон использует этот пример, чтобы показать, к каким абсурдным (и потенциально жестоким) практическим выводам ведёт объективистская модель: если бы Фладд был прав, то «благоговейное вслушивание в ужасную какофонию звуков стало бы настоящим духовным долгом».</t>
         </is>
       </c>
-      <c r="X6" s="14" t="inlineStr">
+      <c r="Y6" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y6" s="14" t="inlineStr">
+      <c r="Z6" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z6" s="14" t="inlineStr">
+      <c r="AA6" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-fludd</t>
         </is>
       </c>
-      <c r="AA6" s="14" t="inlineStr">
+      <c r="AB6" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB6" s="14" t="n"/>
+      <c r="AC6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -1081,81 +1095,86 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
+          <t>пневмония (по другой версии — отравление)</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
           <t>Лаэ (ныне Декарт), Турень, Франция</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>46.9700, 0.7000</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>Стокгольм, Швеция</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t>59.3293, 18.0686</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t>Коллегия Ла Флеш; Университет Пуатье</t>
         </is>
       </c>
-      <c r="M7" s="14" t="n"/>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n"/>
       <c r="P7" s="14" t="n"/>
       <c r="Q7" s="14" t="n"/>
-      <c r="R7" s="14" t="inlineStr">
+      <c r="R7" s="14" t="n"/>
+      <c r="S7" s="14" t="inlineStr">
         <is>
           <t>метафизика; эпистемология; математика; натурфилософия</t>
         </is>
       </c>
-      <c r="S7" s="14" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>Французский философ, математик и физик, родоначальник новоевропейского рационализма («Рассуждение о методе», «Размышления о первой философии»), создатель аналитической геометрии и механистической картины природы.</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>- Различение ясных и отчётливых / смутных («запутанных») идей - Способность понимания (intellectus) vs способность воображения (imaginatio)</t>
         </is>
       </c>
-      <c r="U7" s="14" t="inlineStr">
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/descartes/</t>
         </is>
       </c>
-      <c r="V7" s="14" t="n"/>
-      <c r="W7" s="14" t="inlineStr">
+      <c r="W7" s="14" t="n"/>
+      <c r="X7" s="14" t="inlineStr">
         <is>
           <t>«Красный» — запутанная идея. Декарт классифицирует «быть красным» как «запутанную идею» именно потому, что понятие инференциально непродуктивно: узнав, что кусок железа красный, мы узнаём о его воздействии на среду гораздо меньше, чем узнав, что это жёсткое зубчатое колесо (с. 163). См. inferentsialnaya-napravlennost. Не-образное постижение треугольника. Желание сохранить инференциальные привязки «зубчатого колеса» и «треугольника» привело Декарта к тому, чтобы считать их классификационные направленности (внешний вид, чертёж) относительно неважными: подлинное постижение треугольника в «способности понимания» «совершенно не-образно», а «способность воображения» Бог добавил в помощь нашему медлительному интеллекту (с. 163). Отсюда — традиция Якоба Штайнера, не включавшего иллюстрации в свои работы (с. 164). Твёрдость как ощущение. Как и краснота, твёрдость у Декарта классифицирует лишь наши ощущения сопротивления; связь с алмазами и наковальнями — производная (с. 167). Против этого возражает Рид.</t>
         </is>
       </c>
-      <c r="X7" s="14" t="inlineStr">
+      <c r="Y7" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y7" s="14" t="inlineStr">
+      <c r="Z7" s="14" t="inlineStr">
         <is>
           <t>chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z7" s="14" t="inlineStr">
+      <c r="AA7" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/rene-descartes</t>
         </is>
       </c>
-      <c r="AA7" s="14" t="inlineStr">
+      <c r="AB7" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB7" s="14" t="n"/>
+      <c r="AC7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -1193,79 +1212,80 @@
           <t>1682-10-19</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>Норидж, Англия</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>52.6309, 1.2974</t>
         </is>
       </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="M8" s="14" t="inlineStr">
         <is>
           <t>Пемброк-колледж, Оксфорд; университеты Монпелье, Падуи, Лейдена</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n"/>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
       <c r="P8" s="14" t="n"/>
       <c r="Q8" s="14" t="n"/>
-      <c r="R8" s="14" t="inlineStr">
+      <c r="R8" s="14" t="n"/>
+      <c r="S8" s="14" t="inlineStr">
         <is>
           <t>медицина; эссеистика; натурфилософия</t>
         </is>
       </c>
-      <c r="S8" s="14" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>Английский врач и писатель-полимат XVII века, известен прежде всего книгой «Religio Medici» («Вероисповедание врачевателей», написана ок. 1635, опубликована 1642–43) — духовно-философской автобиографией, исследующей соотношение веры и науки, знаменитой своим витиеватым, латинизированным стилем. Также автор «Pseudodoxia Epidemica» («Общепринятые заблуждения», 1646) — труда, опровергающего расхожие заблуждения эпохи, и «Hydriotaphia, Urn Burial» (1658) — размышления о смертности по случаю находки древних погребальных урн. Считается, что Браун ввёл в английский язык ряд слов, включая «electricity», «hallucination», «medical», «literary».</t>
         </is>
       </c>
-      <c r="T8" s="14" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>- «Religio Medici» (1642/43) — см. отдельную карточку religio-medici-tsitata про сам цитируемый пассаж</t>
         </is>
       </c>
-      <c r="U8" s="14" t="n"/>
       <c r="V8" s="14" t="n"/>
-      <c r="W8" s="14" t="inlineStr">
+      <c r="W8" s="14" t="n"/>
+      <c r="X8" s="14" t="inlineStr">
         <is>
           <t>Не цитируется и не обсуждается напрямую — фигурирует только как объект чужой критики, которую Уилсон заимствует у Чарльза Лэмба (см. charles-lamb): Лэмб упрекает Брауна в том, что тот, «вознёсшись на воздушные ходули абстракции» в рассуждениях о «Religio Medici», упустил из виду «дерзкие индивидуальности» конкретного человечества. Функция в тексте Уилсона — служить историческим прецедентом того же самого греха (чрезмерная абстракция за счёт конкретики), в котором он обвиняет современных философов концепций.</t>
         </is>
       </c>
-      <c r="X8" s="14" t="inlineStr">
+      <c r="Y8" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y8" s="14" t="inlineStr">
+      <c r="Z8" s="14" t="inlineStr">
         <is>
           <t>chapter_1_iv</t>
         </is>
       </c>
-      <c r="Z8" s="14" t="inlineStr">
+      <c r="AA8" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/thomas-browne</t>
         </is>
       </c>
-      <c r="AA8" s="14" t="inlineStr">
+      <c r="AB8" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB8" s="14" t="n"/>
+      <c r="AC8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -1303,91 +1323,92 @@
           <t>1691-12-31</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Лисмор, Уотерфорд, Ирландия</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>52.1367, -7.9309</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t>Итонский колледж</t>
         </is>
       </c>
-      <c r="M9" s="14" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t>Оксфорд; Королевское общество</t>
         </is>
       </c>
-      <c r="N9" s="14" t="n"/>
       <c r="O9" s="14" t="n"/>
-      <c r="P9" s="14" t="inlineStr">
+      <c r="P9" s="14" t="n"/>
+      <c r="Q9" s="14" t="inlineStr">
         <is>
           <t>Исаак Ньютон</t>
         </is>
       </c>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="14" t="inlineStr">
+      <c r="R9" s="14" t="n"/>
+      <c r="S9" s="14" t="inlineStr">
         <is>
           <t>химия; натурфилософия; механистическая философия</t>
         </is>
       </c>
-      <c r="S9" s="14" t="inlineStr">
+      <c r="T9" s="14" t="inlineStr">
         <is>
           <t>Англо-ирландский естествоиспытатель, один из основателей Королевского общества и современной химии (закон Бойля–Мариотта, «Скептический химик»). Ведущий защитник «механической гипотезы» — объяснения природы через материю и движение.</t>
         </is>
       </c>
-      <c r="T9" s="14" t="inlineStr">
+      <c r="U9" s="14" t="inlineStr">
         <is>
           <t>- Robert Boyle, “About the Excellency and Grounds of the Mechanical Hypothesis” // Selected Philosophical Papers of Robert Boyle (Indianapolis: Hackett, 1991), 153 — сноска 17.</t>
         </is>
       </c>
-      <c r="U9" s="14" t="inlineStr">
+      <c r="V9" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/boyle/</t>
         </is>
       </c>
-      <c r="V9" s="14" t="n"/>
-      <c r="W9" s="14" t="inlineStr">
+      <c r="W9" s="14" t="n"/>
+      <c r="X9" s="14" t="inlineStr">
         <is>
           <t>Бойль представляет эпоху механистической философии, когда любая физическая классификация, не понятая «в квази-геометрической манере быть зубчатым колесом», отвергалась как оккультная. Цитата (с. 162–163): принципы «материя, движение…, величина, форма, положение тела, порядок, текстура» настолько «просты, ясны и всеобъемлющи», что нематериальный агент лишь затруднил бы объяснение. Для Бойля ядро «быть зубчатым колесом» составляет сильный набор инференциальных направленностей — наше «глубокое понимание того, как работает механизм». На бойлевских основаниях сначала было отвергнуто как «оккультное» ньютоновское тяготение, действующее на расстоянии (с. 165); поздние «тёплые и нечёткие» требования к объяснению, против которых выступали Мах и Дюгем, «сходны с требованиями Бойля» (с. 166).</t>
         </is>
       </c>
-      <c r="X9" s="14" t="inlineStr">
+      <c r="Y9" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y9" s="14" t="inlineStr">
+      <c r="Z9" s="14" t="inlineStr">
         <is>
           <t>chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z9" s="14" t="inlineStr">
+      <c r="AA9" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-boyle</t>
         </is>
       </c>
-      <c r="AA9" s="14" t="inlineStr">
+      <c r="AB9" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB9" s="14" t="n"/>
+      <c r="AC9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -1425,87 +1446,88 @@
           <t>1727-03-31</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>Вулсторп, Линкольншир, Англия</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>52.8090, -0.6310</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t>Кенсингтон, Лондон</t>
         </is>
       </c>
-      <c r="K10" s="14" t="inlineStr">
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t>51.5000, -0.1900</t>
         </is>
       </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>Кембриджский университет; Королевский монетный двор; Королевское общество (президент с 1703)</t>
         </is>
       </c>
-      <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
       <c r="P10" s="14" t="n"/>
       <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="14" t="inlineStr">
+      <c r="R10" s="14" t="n"/>
+      <c r="S10" s="14" t="inlineStr">
         <is>
           <t>механика; оптика; математический анализ</t>
         </is>
       </c>
-      <c r="S10" s="14" t="inlineStr">
+      <c r="T10" s="14" t="inlineStr">
         <is>
           <t>Английский физик, математик и астроном, один из важнейших учёных в истории науки. Сформулировал законы движения и всемирного тяготения, разработал (наряду с Лейбницем) математический анализ, автор «Начал» (Principia, 1687) и «Оптики» (Opticks, 1704) — в последней, среди прочего, изложены его эксперименты с призмой по разложению света.</t>
         </is>
       </c>
-      <c r="T10" s="14" t="inlineStr">
+      <c r="U10" s="14" t="inlineStr">
         <is>
           <t>- «Оптика» (Opticks, 1704) — опыты с призмой, см. nyuton-issledovaniya-sveta - Классическая механика в целом — вероятный источник дальнейших примеров по ходу книги (понятие «силы»)</t>
         </is>
       </c>
-      <c r="U10" s="14" t="inlineStr">
+      <c r="V10" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/newton/</t>
         </is>
       </c>
-      <c r="V10" s="14" t="n"/>
-      <c r="W10" s="14" t="inlineStr">
+      <c r="W10" s="14" t="n"/>
+      <c r="X10" s="14" t="inlineStr">
         <is>
           <t>Здесь фигурирует конкретно как автор экспериментов с призмой (см. отдельную карточку nyuton-issledovaniya-sveta) — источник центральной аналогии подраздела (iii) о том, как упрощённая, технически неполная картина явления может долго служить рабочим практическим ориентиром. Отдельно стоит иметь в виду: сама механика Ньютона (в частности, понятие «силы») по договорённостям проекта уже отмечена как классический пример «блуждающего» понятия — см. запись в конвенциях (00-meta/konventsii.md) про случай с понятием силы как образцовый пример типа «пример-кейс». Возможно, при дальнейшем чтении эта more общая тема механики Ньютона потребует отдельной карточки, отличной от узкого эпизода с призмой.</t>
         </is>
       </c>
-      <c r="X10" s="14" t="inlineStr">
+      <c r="Y10" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y10" s="14" t="inlineStr">
+      <c r="Z10" s="14" t="inlineStr">
         <is>
           <t>chapter_1_iii; chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z10" s="14" t="inlineStr">
+      <c r="AA10" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/isaac-newton</t>
         </is>
       </c>
-      <c r="AA10" s="14" t="inlineStr">
+      <c r="AB10" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB10" s="14" t="inlineStr">
+      <c r="AC10" s="14" t="inlineStr">
         <is>
           <t>Даты по григорианскому календарю; по юлианскому — 25.12.1642 – 20.03.1726/27.</t>
         </is>
@@ -1547,79 +1569,80 @@
           <t>1719-06-17</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Милстон, Уилтшир, Англия</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>51.2400, -1.7700</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="K11" s="14" t="inlineStr">
         <is>
           <t>Холланд-Хаус, Кенсингтон, Лондон</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t>51.5023, -0.2045</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="M11" s="14" t="inlineStr">
         <is>
           <t>Куинз-колледж и Модлин-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M11" s="14" t="n"/>
       <c r="N11" s="14" t="n"/>
       <c r="O11" s="14" t="n"/>
       <c r="P11" s="14" t="n"/>
       <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="14" t="inlineStr">
+      <c r="R11" s="14" t="n"/>
+      <c r="S11" s="14" t="inlineStr">
         <is>
           <t>эссеистика; журналистика; драматургия</t>
         </is>
       </c>
-      <c r="S11" s="14" t="inlineStr">
+      <c r="T11" s="14" t="inlineStr">
         <is>
           <t>Английский писатель, эссеист и политический деятель. В цикле Pleasures of the Imagination развивал эстетику воображения и чувственного восприятия.</t>
         </is>
       </c>
-      <c r="T11" s="14" t="inlineStr">
+      <c r="U11" s="14" t="inlineStr">
         <is>
           <t>- Joseph Addison, “Pleasures of the Imagination”, no. 413 - The Works of Joseph Addison, vol. VI - Joseph Addison, “Criticism on Paradise Lost”, no. 267, Works, vi. 32. - Воображение и чувственное восприятие - Цвет как чувственное качество -</t>
         </is>
       </c>
-      <c r="U11" s="14" t="n"/>
       <c r="V11" s="14" t="n"/>
-      <c r="W11" s="14" t="inlineStr">
+      <c r="W11" s="14" t="n"/>
+      <c r="X11" s="14" t="inlineStr">
         <is>
           <t>Аддисон появляется в обсуждении «завесы восприятия». Уилсон отмечает, что Аддисон, подобно Хаксли, может признать физическую нереальность цвета, не делая из этого вывода, будто цветовой опыт лишён смысла или реальности для человеческой жизни.</t>
         </is>
       </c>
-      <c r="X11" s="14" t="inlineStr">
+      <c r="Y11" s="14" t="inlineStr">
         <is>
           <t>гл. 2; гл. 3</t>
         </is>
       </c>
-      <c r="Y11" s="14" t="inlineStr">
+      <c r="Z11" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi; chapter_3_i</t>
         </is>
       </c>
-      <c r="Z11" s="14" t="inlineStr">
+      <c r="AA11" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/joseph-addison</t>
         </is>
       </c>
-      <c r="AA11" s="14" t="inlineStr">
+      <c r="AB11" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB11" s="14" t="n"/>
+      <c r="AC11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -1659,85 +1682,90 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
+          <t>внезапная смерть (предположительно, инсульт)</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
           <t>Дайсарт близ Томастауна, Килкенни, Ирландия</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>52.5300, -7.1400</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="K12" s="14" t="inlineStr">
         <is>
           <t>Оксфорд, Англия</t>
         </is>
       </c>
-      <c r="K12" s="14" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>51.7520, -1.2577</t>
         </is>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="M12" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Дублин</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Дублин; епископ Клойнский (с 1734)</t>
         </is>
       </c>
-      <c r="N12" s="14" t="n"/>
       <c r="O12" s="14" t="n"/>
       <c r="P12" s="14" t="n"/>
       <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="14" t="inlineStr">
+      <c r="R12" s="14" t="n"/>
+      <c r="S12" s="14" t="inlineStr">
         <is>
           <t>эмпиризм; идеализм; теория зрения</t>
         </is>
       </c>
-      <c r="S12" s="14" t="inlineStr">
+      <c r="T12" s="14" t="inlineStr">
         <is>
           <t>Ирландский философ-эмпирик, епископ Клойнский (1685–1753). Основоположник субъективного идеализма («esse est percipi»); в «Трактате о принципах человеческого знания» отверг локковское учение об абстрактных общих идеях, настаивая, что общие имена не соответствуют никаким отдельным абстрактным сущностям в уме, а функционируют иначе — представляя произвольно выбранный частный случай в качестве представителя класса.</t>
         </is>
       </c>
-      <c r="T12" s="14" t="inlineStr">
+      <c r="U12" s="14" t="inlineStr">
         <is>
           <t>- Критика абстрактных общих идей (Introduction, «A Treatise Concerning the Principles of Human Knowledge») - Номинализм — отрицание самостоятельного существования концепций за пределами предикатов</t>
         </is>
       </c>
-      <c r="U12" s="14" t="inlineStr">
+      <c r="V12" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/berkeley/</t>
         </is>
       </c>
-      <c r="V12" s="14" t="n"/>
-      <c r="W12" s="14" t="inlineStr">
+      <c r="W12" s="14" t="n"/>
+      <c r="X12" s="14" t="inlineStr">
         <is>
           <t>Уилсон опирается на берклианский тезис как на вторую (наряду с перегрузкой концепций) причину тщательно исследовать предикатные выражения: абстрактные сущности вроде «концепций» и свойств обретают видимость онтологической респектабельности, «облачаясь» в общие имена — мы ошибочно предполагаем, что «исхищрение, называемое быть кроликом», существует просто потому, что умеем подводить кроликов под рубрику «есть кролик». На деле концепция — фиктивный посредник, псевдо-объяснение практики предикации; «концепции» лишь позаимствовали эрзац-субстанциальность у предикатов. Уилсон прямо дистанцируется от анти-концептуализма Беркли: сам он не питает враждебности к абстрактным объектам и намерен показать (со ссылкой на §5, vii), что обширные области атрибутов — надёжные компоненты физического ландшафта. Беркли вводится как радикальный (номиналистский) полюс дефляционизма, в противовес более мягкой куайновской версии, разбираемой в главе 5.</t>
         </is>
       </c>
-      <c r="X12" s="14" t="inlineStr">
+      <c r="Y12" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y12" s="14" t="inlineStr">
+      <c r="Z12" s="14" t="inlineStr">
         <is>
           <t>chapter_3_i</t>
         </is>
       </c>
-      <c r="Z12" s="14" t="inlineStr">
+      <c r="AA12" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/george-berkeley</t>
         </is>
       </c>
-      <c r="AA12" s="14" t="inlineStr">
+      <c r="AB12" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB12" s="14" t="n"/>
+      <c r="AC12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -1775,79 +1803,80 @@
           <t>1770-02-26</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Пирано, Истрия (Венецианская республика)</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>45.5280, 13.5680</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="K13" s="14" t="inlineStr">
         <is>
           <t>Падуя</t>
         </is>
       </c>
-      <c r="K13" s="14" t="inlineStr">
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>45.4064, 11.8768</t>
         </is>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="M13" s="14" t="inlineStr">
         <is>
           <t>Падуанский университет</t>
         </is>
       </c>
-      <c r="M13" s="14" t="n"/>
       <c r="N13" s="14" t="n"/>
       <c r="O13" s="14" t="n"/>
       <c r="P13" s="14" t="n"/>
       <c r="Q13" s="14" t="n"/>
-      <c r="R13" s="14" t="inlineStr">
+      <c r="R13" s="14" t="n"/>
+      <c r="S13" s="14" t="inlineStr">
         <is>
           <t>скрипка; композиция; теория музыки</t>
         </is>
       </c>
-      <c r="S13" s="14" t="inlineStr">
+      <c r="T13" s="14" t="inlineStr">
         <is>
           <t>Итальянский скрипач, композитор и музыкальный теоретик. Известен как автор сонаты для скрипки «Дьявольская трель» и как первооткрыватель (совместно с Зорге) комбинационных тонов — акустического феномена, возникающего во внутреннем ухе при одновременном звучании двух тонов.</t>
         </is>
       </c>
-      <c r="T13" s="14" t="inlineStr">
+      <c r="U13" s="14" t="inlineStr">
         <is>
           <t>- Комбинационные (тартиниевы) тоны — эффект возникновения дополнительных тонов во внутреннем ухе - Использование эффекта в конструкции органа для получения желаемых тонов без длинных труб</t>
         </is>
       </c>
-      <c r="U13" s="14" t="n"/>
       <c r="V13" s="14" t="n"/>
-      <c r="W13" s="14" t="inlineStr">
+      <c r="W13" s="14" t="n"/>
+      <c r="X13" s="14" t="inlineStr">
         <is>
           <t>Уилсон упоминает Тартини (вместе с Зорге) как первооткрывателя комбинационных тонов в середине XVIII века. Этот феномен — когда одновременное звучание нот «до» и «соль» вызывает в улитке уха ложные колебания, воспринимаемые как низкая нота «до», которой физически нет ни в инструменте, ни в воздухе — используется как аргумент против объективистской модели музыкальных атрибутов. Этот эффект, по словам Уилсона, «неизбежно окрашивает все наши слуховые ощущения» и показывает, что музыкальные свойства не могут быть просто приравнены к внешним акустическим паттернам.</t>
         </is>
       </c>
-      <c r="X13" s="14" t="inlineStr">
+      <c r="Y13" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y13" s="14" t="inlineStr">
+      <c r="Z13" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv; chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z13" s="14" t="inlineStr">
+      <c r="AA13" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/giuseppe-tartini</t>
         </is>
       </c>
-      <c r="AA13" s="14" t="inlineStr">
+      <c r="AB13" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB13" s="14" t="n"/>
+      <c r="AC13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -1885,79 +1914,80 @@
           <t>1748-08-27</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>Эднам, Роксбургшир, Шотландия</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>55.6200, -2.4200</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>Ричмонд, Суррей, Англия</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t>51.4610, -0.3030</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="M14" s="14" t="inlineStr">
         <is>
           <t>Эдинбургский университет</t>
         </is>
       </c>
-      <c r="M14" s="14" t="n"/>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
       <c r="P14" s="14" t="n"/>
       <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="14" t="inlineStr">
+      <c r="R14" s="14" t="n"/>
+      <c r="S14" s="14" t="inlineStr">
         <is>
           <t>поэзия</t>
         </is>
       </c>
-      <c r="S14" s="14" t="inlineStr">
+      <c r="T14" s="14" t="inlineStr">
         <is>
           <t>Шотландский поэт и драматург XVIII века, известен прежде всего масштабной поэмой «Времена года» (The Seasons, 1726–1730) — одним из самых влиятельных англоязычных поэтических произведений эпохи (переведена на несколько языков, ею восхищался Гёте). Также автор слов британской патриотической песни «Rule, Britannia!». Учился в Эдинбургском университете (латынь, греческий, философия), с 1725 года жил в Лондоне. Авторские права на «Времена года» позже стали предметом двух знаковых судебных процессов в истории копирайта — Millar v. Taylor и Donaldson v. Beckett.</t>
         </is>
       </c>
-      <c r="T14" s="14" t="inlineStr">
+      <c r="U14" s="14" t="inlineStr">
         <is>
           <t>- «Времена года» (The Seasons), часть «Spring» — конкретный процитированный пассаж (строка про радугу и обращение «awful Newton») также известен как отдельно антологируемое стихотворение «The Rainbow»; оба названия относятся к одному и тому же тексту.</t>
         </is>
       </c>
-      <c r="U14" s="14" t="n"/>
       <c r="V14" s="14" t="n"/>
-      <c r="W14" s="14" t="inlineStr">
+      <c r="W14" s="14" t="n"/>
+      <c r="X14" s="14" t="inlineStr">
         <is>
           <t>Источник цитаты, сопровождающей рассказ о ньютоновских опытах с призмой (см. nyuton-issledovaniya-sveta) — фрагмент из поэмы «Spring» (часть «Времён года»), где поэт прямо обращается к Ньютону, поэтически описывая разложение света радугой на цвета. Использован как иллюстрация того, насколько глубоко идеи Ньютона о свете проникли в культуру его эпохи — вплоть до поэтического языка.</t>
         </is>
       </c>
-      <c r="X14" s="14" t="inlineStr">
+      <c r="Y14" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y14" s="14" t="inlineStr">
+      <c r="Z14" s="14" t="inlineStr">
         <is>
           <t>chapter_1_iii</t>
         </is>
       </c>
-      <c r="Z14" s="14" t="inlineStr">
+      <c r="AA14" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/james-thomson</t>
         </is>
       </c>
-      <c r="AA14" s="14" t="inlineStr">
+      <c r="AB14" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB14" s="14" t="n"/>
+      <c r="AC14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1995,75 +2025,76 @@
           <t>1778-04-04</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>Мелленбах, Шварцбург</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>50.6000, 11.1000</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>Лобенштайн</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="L15" s="14" t="inlineStr">
         <is>
           <t>50.4500, 11.6400</t>
         </is>
       </c>
-      <c r="L15" s="14" t="n"/>
       <c r="M15" s="14" t="n"/>
       <c r="N15" s="14" t="n"/>
       <c r="O15" s="14" t="n"/>
       <c r="P15" s="14" t="n"/>
       <c r="Q15" s="14" t="n"/>
-      <c r="R15" s="14" t="inlineStr">
+      <c r="R15" s="14" t="n"/>
+      <c r="S15" s="14" t="inlineStr">
         <is>
           <t>органная музыка; теория музыки; акустика</t>
         </is>
       </c>
-      <c r="S15" s="14" t="inlineStr">
+      <c r="T15" s="14" t="inlineStr">
         <is>
           <t>Немецкий музыкант и теоретик музыки XVIII века. Совместно с Джузеппе Тартини открыл явление комбинационных тонов (также называемых тартиниевыми тонами) — нелинейных акустических эффектов, возникающих во внутреннем ухе при одновременном звучании двух нот.</t>
         </is>
       </c>
-      <c r="T15" s="14" t="inlineStr">
+      <c r="U15" s="14" t="inlineStr">
         <is>
           <t>- Комбинационные (тартиниевы) тоны — нелинейные вибрационные компоненты, возникающие во внутреннем ухе</t>
         </is>
       </c>
-      <c r="U15" s="14" t="n"/>
       <c r="V15" s="14" t="n"/>
-      <c r="W15" s="14" t="inlineStr">
+      <c r="W15" s="14" t="n"/>
+      <c r="X15" s="14" t="inlineStr">
         <is>
           <t>Упоминается в паре с Тартини как один из первооткрывателей комбинационных тонов в середине XVIII века. Это открытие используется Уилсоном для демонстрации того, что музыкальное восприятие не может быть сведено к простым объективным акустическим свойствам, поскольку в самом слуховом аппарате возникают дополнительные тоны, отсутствующие в звучащем инструменте или окружающем воздухе.</t>
         </is>
       </c>
-      <c r="X15" s="14" t="inlineStr">
+      <c r="Y15" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y15" s="14" t="inlineStr">
+      <c r="Z15" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z15" s="14" t="inlineStr">
+      <c r="AA15" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/w-a-sorge</t>
         </is>
       </c>
-      <c r="AA15" s="14" t="inlineStr">
+      <c r="AB15" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB15" s="14" t="n"/>
+      <c r="AC15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -2101,79 +2132,80 @@
           <t>1760-02-14</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Бертон-апон-Трент, Англия</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>52.8019, -1.6370</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="M16" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
       <c r="P16" s="14" t="n"/>
       <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="14" t="inlineStr">
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="inlineStr">
         <is>
           <t>поэзия; пародия</t>
         </is>
       </c>
-      <c r="S16" s="14" t="inlineStr">
+      <c r="T16" s="14" t="inlineStr">
         <is>
           <t>Английский поэт, эпиграмматист и политик-виг XVIII века (1705–1760), член парламента от Бриджнорта. Известен главным образом малой сатирической и эпиграмматической поэзией; наиболее цитируемая его строка — эпиграмма «On Seeing a Portrait of Miss Robinson, Painted by Mr. Highmore», опубликованная в антологии Генри Филипа Додда «The Epigrammists» (1870).</t>
         </is>
       </c>
-      <c r="T16" s="14" t="inlineStr">
+      <c r="U16" s="14" t="inlineStr">
         <is>
           <t>- «On Seeing a Portrait of Miss Robinson, Painted by Mr. Highmore» (эпиграмма) - Мотив «empty form» — пустой формы, привлекательной сама по себе, без «живого» содержания</t>
         </is>
       </c>
-      <c r="U16" s="14" t="n"/>
       <c r="V16" s="14" t="n"/>
-      <c r="W16" s="14" t="inlineStr">
+      <c r="W16" s="14" t="n"/>
+      <c r="X16" s="14" t="inlineStr">
         <is>
           <t>Уилсон ставит двустишие Брауна («I, whom no living beauty yet could warm, / Am now enamour'd of an empty form») эпиграфом к главе 3, задавая программную метафору всей главы: философ (или говорящий вообще), очарованный синтаксически опрятной, но содержательно пустой предикатной формой, подобен герою эпиграммы, влюблённому не в живую красоту, а в пустую форму портрета. Название главы — «Классический клей» — обыгрывает ту же идею: предикат работает как клей, скрепляющий разнородный опыт видимостью единой концепции.</t>
         </is>
       </c>
-      <c r="X16" s="14" t="inlineStr">
+      <c r="Y16" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y16" s="14" t="inlineStr">
+      <c r="Z16" s="14" t="inlineStr">
         <is>
           <t>chapter_3_i</t>
         </is>
       </c>
-      <c r="Z16" s="14" t="inlineStr">
+      <c r="AA16" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/isaac-hawkins-browne</t>
         </is>
       </c>
-      <c r="AA16" s="14" t="inlineStr">
+      <c r="AB16" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB16" s="14" t="n"/>
+      <c r="AC16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -2213,77 +2245,82 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
+          <t>кровоизлияние в мозг</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
           <t>Базель, Швейцария</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>47.5596, 7.5886</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>Санкт-Петербург</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>59.9311, 30.3609</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="M17" s="14" t="inlineStr">
         <is>
           <t>Базельский университет</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>Петербургская академия наук; Берлинская академия наук</t>
         </is>
       </c>
-      <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
       <c r="P17" s="14" t="n"/>
       <c r="Q17" s="14" t="n"/>
-      <c r="R17" s="14" t="inlineStr">
+      <c r="R17" s="14" t="n"/>
+      <c r="S17" s="14" t="inlineStr">
         <is>
           <t>математика; механика; астрономия</t>
         </is>
       </c>
-      <c r="S17" s="14" t="inlineStr">
+      <c r="T17" s="14" t="inlineStr">
         <is>
           <t>Швейцарский математик, один из самых продуктивных и влиятельных учёных в истории математики — фундаментальный вклад в математический анализ, теорию чисел, механику, оптику и множество других областей; автор формулы и тождества, носящих его имя.</t>
         </is>
       </c>
-      <c r="T17" s="14" t="n"/>
       <c r="U17" s="14" t="n"/>
       <c r="V17" s="14" t="n"/>
-      <c r="W17" s="14" t="inlineStr">
+      <c r="W17" s="14" t="n"/>
+      <c r="X17" s="14" t="inlineStr">
         <is>
           <t>Использован в гипотетическом примере преподавателя математического анализа: в лекции студентам тот же преподаватель, что двумя часами ранее в рекомендательном письме хвалил студентку Пенелопу за «полное владение» понятиями анализа, теперь говорит классу, что даже «великий Эйлер на самом деле не понимал собственно содержания» тех математических понятий, которыми блестяще манипулировал. Функция примера — показать, что стандарт «владения понятием» резко смещается в зависимости от контекста высказывания (см. chuvstvitelnost-k-kontekstu): по меркам второго высказывания, Пенелопа «владеет» понятиями анализа хуже Эйлера, хотя именно Эйлер был неизмеримо технически искуснее её.</t>
         </is>
       </c>
-      <c r="X17" s="14" t="inlineStr">
+      <c r="Y17" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y17" s="14" t="inlineStr">
+      <c r="Z17" s="14" t="inlineStr">
         <is>
           <t>chapter_1_vi</t>
         </is>
       </c>
-      <c r="Z17" s="14" t="inlineStr">
+      <c r="AA17" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/leonhard-euler</t>
         </is>
       </c>
-      <c r="AA17" s="14" t="inlineStr">
+      <c r="AB17" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB17" s="14" t="n"/>
+      <c r="AC17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -2321,87 +2358,88 @@
           <t>1796-10-07</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Стракан, Кинкардиншир, Шотландия</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>57.0200, -2.5200</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>Глазго, Шотландия</t>
         </is>
       </c>
-      <c r="K18" s="14" t="inlineStr">
+      <c r="L18" s="14" t="inlineStr">
         <is>
           <t>55.8642, -4.2518</t>
         </is>
       </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="M18" s="14" t="inlineStr">
         <is>
           <t>Маришал-колледж, Абердин</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>Кингз-колледж, Абердин; Университет Глазго</t>
         </is>
       </c>
-      <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
       <c r="P18" s="14" t="n"/>
       <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="14" t="inlineStr">
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="inlineStr">
         <is>
           <t>философия здравого смысла; философия восприятия</t>
         </is>
       </c>
-      <c r="S18" s="14" t="inlineStr">
+      <c r="T18" s="14" t="inlineStr">
         <is>
           <t>Шотландский философ XVIII века, основатель так называемой «шотландской школы здравого смысла» (Scottish Common Sense Realism). Критиковал «теорию идей» Локка и Юма, отстаивал прямой реализм в вопросах восприятия: мы воспринимаем сами вещи, а не посредующие «идеи» в сознании. Основные работы — «Исследование о человеческом уме на принципах здравого смысла» и «Опыты об интеллектуальных способностях человека».</t>
         </is>
       </c>
-      <c r="T18" s="14" t="inlineStr">
+      <c r="U18" s="14" t="inlineStr">
         <is>
           <t>- Прямой реализм восприятия (direct realism) — против «теории идей» - Принципы здравого смысла (common sense) как источник эпистемического оправдания - Thomas Reid, Essays on the Intellectual Powers of Man, 57–58 — цитата о твёрдости (сноска 21) - Понятие совершенной твёрдости как основа понятия твёрдого тела - (дозаполнить по мере чтения)</t>
         </is>
       </c>
-      <c r="U18" s="14" t="inlineStr">
+      <c r="V18" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/reid/</t>
         </is>
       </c>
-      <c r="V18" s="14" t="n"/>
-      <c r="W18" s="14" t="inlineStr">
+      <c r="W18" s="14" t="n"/>
+      <c r="X18" s="14" t="inlineStr">
         <is>
           <t>(гипотеза, требует проверки по тексту) Рид — вероятный союзник в вопросе доверия обыденным, «здравосмысленным» классификациям и практикам употребления понятий, в противовес скептическим и редукционистским программам (в духе Юма). Подтверждено в гл. 3, §(vi) (с. 167–168). Рид — главный оппонент Декарта в споре о том, что составляет ядро «есть твёрдый». Для Декарта твёрдость, как и краснота, классифицирует лишь наши ощущения сопротивления. Рид, «не желая отрывать наше постижение классификационных понятий от физического мира в манере завесы восприятия», «справедливо возражал»: истинное понятие твёрдости — прочное сцепление частей тела, и оно «внутренне вообще не связано» с ощущением прикосновения: «Прочное сцепление частей тела не более похоже на то ощущение… чем вибрация звучного тела похожа на звук, который я слышу». Словарь Webster тоже определяет твёрдость без упоминания ощущений. Но, замечает Уилсон, ридовская направленность указывает на молекулярный уровень, недоступный повседневной классификации (и к тому же «довольно ошибочна»). По сути Рид утверждает, что ребёнок начинает с картезианских, основанных на ощущениях направленностей (твёрдая резиновая уточка), а «где-то между шестью месяцами и шестнадцатью годами» говорящие сдвигают привязки «есть твёрдый» к экстернализированному классификатору. Уилсон сопоставляет это с картиной красноты у Хелен Келлер. Сам Рид отмечает, что понятие совершенной твёрдости важно для понятия твёрдого тела, а оно — основа инференциальных способностей «зубчатого колеса» (см. inferentsialnaya-napravlennost).</t>
         </is>
       </c>
-      <c r="X18" s="14" t="inlineStr">
+      <c r="Y18" s="14" t="inlineStr">
         <is>
           <t>предисловие; гл. 2; гл. 3</t>
         </is>
       </c>
-      <c r="Y18" s="14" t="inlineStr">
+      <c r="Z18" s="14" t="inlineStr">
         <is>
           <t>chapter_2_v; chapter_3_vi; predislovie</t>
         </is>
       </c>
-      <c r="Z18" s="14" t="inlineStr">
+      <c r="AA18" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/thomas-reid</t>
         </is>
       </c>
-      <c r="AA18" s="14" t="inlineStr">
+      <c r="AB18" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB18" s="14" t="n"/>
+      <c r="AC18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -2441,81 +2479,86 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
+          <t>рак (предположительно, кишечника или печени)</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
           <t>Эдинбург, Шотландия</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>55.9533, -3.1883</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="K19" s="14" t="inlineStr">
         <is>
           <t>Эдинбург, Шотландия</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr">
+      <c r="L19" s="14" t="inlineStr">
         <is>
           <t>55.9533, -3.1883</t>
         </is>
       </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="M19" s="14" t="inlineStr">
         <is>
           <t>Эдинбургский университет</t>
         </is>
       </c>
-      <c r="M19" s="14" t="n"/>
       <c r="N19" s="14" t="n"/>
       <c r="O19" s="14" t="n"/>
       <c r="P19" s="14" t="n"/>
       <c r="Q19" s="14" t="n"/>
-      <c r="R19" s="14" t="inlineStr">
+      <c r="R19" s="14" t="n"/>
+      <c r="S19" s="14" t="inlineStr">
         <is>
           <t>эмпиризм; скептицизм; этика; история</t>
         </is>
       </c>
-      <c r="S19" s="14" t="inlineStr">
+      <c r="T19" s="14" t="inlineStr">
         <is>
           <t>Шотландский философ, историк и экономист, ключевая фигура эмпиризма и скептицизма Нового времени. Среди основных работ — «Трактат о человеческой природе» и «Исследование о человеческом разумении» (An Enquiry Concerning Human Understanding), где разбираются вопросы причинности, индукции и границ человеческого познания.</t>
         </is>
       </c>
-      <c r="T19" s="14" t="inlineStr">
+      <c r="U19" s="14" t="inlineStr">
         <is>
           <t>- David Hume, An Enquiry Concerning Human Understanding (Indianapolis: Bobbs-Merrill, 1955), 169.</t>
         </is>
       </c>
-      <c r="U19" s="14" t="inlineStr">
+      <c r="V19" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/hume/</t>
         </is>
       </c>
-      <c r="V19" s="14" t="n"/>
-      <c r="W19" s="14" t="inlineStr">
+      <c r="W19" s="14" t="n"/>
+      <c r="X19" s="14" t="inlineStr">
         <is>
           <t>Процитирован дважды подряд в одном пассаже. Первая цитата (из «Enquiry», с. 169) — о «причудливом состоянии человечества», которое вынуждено «действовать, рассуждать и верить», даже не будучи в силах обосновать эти действия при самом тщательном исследовании. Уилсон соглашается с диагнозом Юма — мы вынуждены пользоваться понятиями задолго до того, как проясним их подлинные основания, — но явно отвергает то, что называет «вечным пессимизмом» Юма: там, где Юм полагал, что семантическая подоплёка большинства слов навсегда останется скрытой, Уилсон настаивает, что прояснить её вполне возможно, просто это требует времени и кропотливого исследования, а не кабинетных размышлений. Вторая цитата (там же) — о склонности большинства людей к «утвердительности и догматизму» в мнениях — используется Уилсоном как психологическое объяснение того, почему классическая картина концепций кажется нам интуитивно убедительной: мы систематически переоцениваем прочность собственного концептуального понимания.</t>
         </is>
       </c>
-      <c r="X19" s="14" t="inlineStr">
+      <c r="Y19" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 3</t>
         </is>
       </c>
-      <c r="Y19" s="14" t="inlineStr">
+      <c r="Z19" s="14" t="inlineStr">
         <is>
           <t>chapter_1_ix; chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z19" s="14" t="inlineStr">
+      <c r="AA19" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/david-hume</t>
         </is>
       </c>
-      <c r="AA19" s="14" t="inlineStr">
+      <c r="AB19" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB19" s="14" t="n"/>
+      <c r="AC19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -2553,87 +2596,88 @@
           <t>1804-02-12</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>Кёнигсберг, Пруссия</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>54.7104, 20.4522</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>Кёнигсберг, Пруссия</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="L20" s="14" t="inlineStr">
         <is>
           <t>54.7104, 20.4522</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="M20" s="14" t="inlineStr">
         <is>
           <t>Кёнигсбергский университет</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>Кёнигсбергский университет</t>
         </is>
       </c>
-      <c r="N20" s="14" t="n"/>
       <c r="O20" s="14" t="n"/>
       <c r="P20" s="14" t="n"/>
       <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="14" t="inlineStr">
+      <c r="R20" s="14" t="n"/>
+      <c r="S20" s="14" t="inlineStr">
         <is>
           <t>эпистемология; метафизика; этика; эстетика</t>
         </is>
       </c>
-      <c r="S20" s="14" t="inlineStr">
+      <c r="T20" s="14" t="inlineStr">
         <is>
           <t>Немецкий философ XVIII века, основатель критической философии.</t>
         </is>
       </c>
-      <c r="T20" s="14" t="inlineStr">
+      <c r="U20" s="14" t="inlineStr">
         <is>
           <t>- Трансцендентальная философия - Конструктивная роль субъекта - Амфиболизм - Различие субъективного и объективного</t>
         </is>
       </c>
-      <c r="U20" s="14" t="inlineStr">
+      <c r="V20" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/kant/</t>
         </is>
       </c>
-      <c r="V20" s="14" t="n"/>
-      <c r="W20" s="14" t="inlineStr">
+      <c r="W20" s="14" t="n"/>
+      <c r="X20" s="14" t="inlineStr">
         <is>
           <t>Кант служит исходной философской точкой для идеи, что содержание жизнеспособной концепции не может быть понято как простая регистрация независимого свойства внешнего мира: в концепции неизбежно участвуют конструктивные способности познающего субъекта.</t>
         </is>
       </c>
-      <c r="X20" s="14" t="inlineStr">
+      <c r="Y20" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y20" s="14" t="inlineStr">
+      <c r="Z20" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z20" s="14" t="inlineStr">
+      <c r="AA20" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/immanuel-kant</t>
         </is>
       </c>
-      <c r="AA20" s="14" t="inlineStr">
+      <c r="AB20" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB20" s="14" t="n"/>
+      <c r="AC20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -2673,69 +2717,74 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
+          <t>острая лихорадочная болезнь; точная причина неизвестна</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
           <t>Зальцбург</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>47.8095, 13.0550</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="K21" s="14" t="inlineStr">
         <is>
           <t>Вена</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>48.2082, 16.3738</t>
         </is>
       </c>
-      <c r="L21" s="14" t="n"/>
       <c r="M21" s="14" t="n"/>
       <c r="N21" s="14" t="n"/>
       <c r="O21" s="14" t="n"/>
       <c r="P21" s="14" t="n"/>
       <c r="Q21" s="14" t="n"/>
-      <c r="R21" s="14" t="inlineStr">
+      <c r="R21" s="14" t="n"/>
+      <c r="S21" s="14" t="inlineStr">
         <is>
           <t>композиция</t>
         </is>
       </c>
-      <c r="S21" s="14" t="inlineStr">
+      <c r="T21" s="14" t="inlineStr">
         <is>
           <t>Австрийский композитор, чья Симфония №40 соль минор служит Уилсону отправной точкой для разбора проблем музыкальной атрибуции в главе 2.</t>
         </is>
       </c>
-      <c r="T21" s="14" t="n"/>
       <c r="U21" s="14" t="n"/>
       <c r="V21" s="14" t="n"/>
-      <c r="W21" s="14" t="inlineStr">
+      <c r="W21" s="14" t="n"/>
+      <c r="X21" s="14" t="inlineStr">
         <is>
           <t>Моцарт как таковой биографически не разбирается; фигура важна исключительно через конкретное произведение — Симфонию №40, — на примере которой ставится вопрос о природе «постоянства» музыкального смысла.</t>
         </is>
       </c>
-      <c r="X21" s="14" t="inlineStr">
+      <c r="Y21" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y21" s="14" t="inlineStr">
+      <c r="Z21" s="14" t="inlineStr">
         <is>
           <t>chapter_2_i</t>
         </is>
       </c>
-      <c r="Z21" s="14" t="inlineStr">
+      <c r="AA21" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/wolfgang-amadeus-mozart</t>
         </is>
       </c>
-      <c r="AA21" s="14" t="inlineStr">
+      <c r="AB21" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB21" s="14" t="n"/>
+      <c r="AC21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -2775,85 +2824,90 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
+          <t>плеврит</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
           <t>Кокермут, Камберленд, Англия</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>54.6630, -3.3620</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="K22" s="14" t="inlineStr">
         <is>
           <t>Райдал-Маунт, Эмблсайд, Англия</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr">
+      <c r="L22" s="14" t="inlineStr">
         <is>
           <t>54.4500, -2.9800</t>
         </is>
       </c>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="M22" s="14" t="inlineStr">
         <is>
           <t>Сент-Джонс-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M22" s="14" t="n"/>
       <c r="N22" s="14" t="n"/>
       <c r="O22" s="14" t="n"/>
-      <c r="P22" s="14" t="inlineStr">
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="inlineStr">
         <is>
           <t>Сэмюэл Тейлор Кольридж; Роберт Саути; Чарльз Лэмб</t>
         </is>
       </c>
-      <c r="Q22" s="14" t="inlineStr">
+      <c r="R22" s="14" t="inlineStr">
         <is>
           <t>Поэт-лауреат Великобритании (1843)</t>
         </is>
       </c>
-      <c r="R22" s="14" t="inlineStr">
+      <c r="S22" s="14" t="inlineStr">
         <is>
           <t>поэзия</t>
         </is>
       </c>
-      <c r="S22" s="14" t="inlineStr">
+      <c r="T22" s="14" t="inlineStr">
         <is>
           <t>Английский поэт-романтик, один из основателей и центральных представителей Озёрной школы.</t>
         </is>
       </c>
-      <c r="T22" s="14" t="inlineStr">
+      <c r="U22" s="14" t="inlineStr">
         <is>
           <t>- William Wordsworth, The Excursion - William Wordsworth, Lyrical Ballads - Человек и природа - Восприятие - Амфиболическая связь</t>
         </is>
       </c>
-      <c r="U22" s="14" t="n"/>
       <c r="V22" s="14" t="n"/>
-      <c r="W22" s="14" t="inlineStr">
+      <c r="W22" s="14" t="n"/>
+      <c r="X22" s="14" t="inlineStr">
         <is>
           <t>Вордсворт даёт поэтическую формулу амфиболической связи: человек и природа не выступают как два полностью независимых объекта, а человеческий разум оказывается соотнесён с качествами природы. В «Прогулке» он также противопоставляет геометрическое восприятие окружения более насыщенному чувственному отношению к миру.</t>
         </is>
       </c>
-      <c r="X22" s="14" t="inlineStr">
+      <c r="Y22" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y22" s="14" t="inlineStr">
+      <c r="Z22" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z22" s="14" t="inlineStr">
+      <c r="AA22" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/william-wordsworth</t>
         </is>
       </c>
-      <c r="AA22" s="14" t="inlineStr">
+      <c r="AB22" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB22" s="14" t="n"/>
+      <c r="AC22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -2893,81 +2947,86 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
+          <t>сердечная недостаточность</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
           <t>Оттери-Сент-Мэри, Девон, Англия</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>50.7500, -3.2800</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>Хайгейт, Лондон</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>51.5700, -0.1500</t>
         </is>
       </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="M23" s="14" t="inlineStr">
         <is>
           <t>Джизус-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M23" s="14" t="n"/>
       <c r="N23" s="14" t="n"/>
       <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="inlineStr">
+      <c r="P23" s="14" t="n"/>
+      <c r="Q23" s="14" t="inlineStr">
         <is>
           <t>Уильям Вордсворт; Роберт Саути; Чарльз Лэмб; Уильям Хэзлитт</t>
         </is>
       </c>
-      <c r="Q23" s="14" t="n"/>
-      <c r="R23" s="14" t="inlineStr">
+      <c r="R23" s="14" t="n"/>
+      <c r="S23" s="14" t="inlineStr">
         <is>
           <t>поэзия; литературная критика; философия</t>
         </is>
       </c>
-      <c r="S23" s="14" t="inlineStr">
+      <c r="T23" s="14" t="inlineStr">
         <is>
           <t>Английский поэт, философ и критик, один из центральных представителей британского романтизма.</t>
         </is>
       </c>
-      <c r="T23" s="14" t="inlineStr">
+      <c r="U23" s="14" t="inlineStr">
         <is>
           <t>- S. T. Coleridge, Aids to Reflection - The Philosophical Lectures - Научная абстракция - Жизнь и дух Природы - Амфиболизм</t>
         </is>
       </c>
-      <c r="U23" s="14" t="n"/>
       <c r="V23" s="14" t="n"/>
-      <c r="W23" s="14" t="inlineStr">
+      <c r="W23" s="14" t="n"/>
+      <c r="X23" s="14" t="inlineStr">
         <is>
           <t>Кольридж формулирует опасение, что научная абстракция, будучи полезным инструментом, может превратиться в картину мира, выдающую собственные упрощения за саму реальность. Уилсон связывает это с амфиболизмом: научное описание выделяет определённые свойства, но не должно приниматься за исчерпывающую структуру мира.</t>
         </is>
       </c>
-      <c r="X23" s="14" t="inlineStr">
+      <c r="Y23" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y23" s="14" t="inlineStr">
+      <c r="Z23" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z23" s="14" t="inlineStr">
+      <c r="AA23" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/coleridge</t>
         </is>
       </c>
-      <c r="AA23" s="14" t="inlineStr">
+      <c r="AB23" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB23" s="14" t="n"/>
+      <c r="AC23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -3005,87 +3064,88 @@
           <t>1843-03-21</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Бристоль, Англия</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>51.4545, -2.5879</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="K24" s="14" t="inlineStr">
         <is>
           <t>Кесуик, Камберленд, Англия</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr">
+      <c r="L24" s="14" t="inlineStr">
         <is>
           <t>54.6013, -3.1347</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="M24" s="14" t="inlineStr">
         <is>
           <t>Баллиол-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
       <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="inlineStr">
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="inlineStr">
         <is>
           <t>Сэмюэл Тейлор Кольридж; Уильям Вордсворт</t>
         </is>
       </c>
-      <c r="Q24" s="14" t="inlineStr">
+      <c r="R24" s="14" t="inlineStr">
         <is>
           <t>Поэт-лауреат Великобритании (1813)</t>
         </is>
       </c>
-      <c r="R24" s="14" t="inlineStr">
+      <c r="S24" s="14" t="inlineStr">
         <is>
           <t>поэзия; историческая проза</t>
         </is>
       </c>
-      <c r="S24" s="14" t="inlineStr">
+      <c r="T24" s="14" t="inlineStr">
         <is>
           <t>Английский поэт-романтик и историк, один из трёх традиционно выделяемых представителей Озёрной школы наряду с Вордсвортом и Кольриджем.</t>
         </is>
       </c>
-      <c r="T24" s="14" t="inlineStr">
+      <c r="U24" s="14" t="inlineStr">
         <is>
           <t>- Озёрная школа - Романтизм - Философия природы - Амфиболическая связь субъекта и мира</t>
         </is>
       </c>
-      <c r="U24" s="14" t="n"/>
       <c r="V24" s="14" t="n"/>
-      <c r="W24" s="14" t="inlineStr">
+      <c r="W24" s="14" t="n"/>
+      <c r="X24" s="14" t="inlineStr">
         <is>
           <t>Саути упоминается как часть коллективного романтического ответа на проблему «завесы восприятия». В отличие от Кольриджа и Вордсворта, которым Уилсон приписывает конкретные формулировки, Саути здесь выполняет прежде всего роль представителя общего интеллектуального контекста.</t>
         </is>
       </c>
-      <c r="X24" s="14" t="inlineStr">
+      <c r="Y24" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y24" s="14" t="inlineStr">
+      <c r="Z24" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z24" s="14" t="inlineStr">
+      <c r="AA24" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/r-southey</t>
         </is>
       </c>
-      <c r="AA24" s="14" t="inlineStr">
+      <c r="AB24" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB24" s="14" t="n"/>
+      <c r="AC24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -3125,81 +3185,86 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
+          <t>рожистое воспаление после падения</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="K25" s="14" t="inlineStr">
         <is>
           <t>Эдмонтон, Лондон</t>
         </is>
       </c>
-      <c r="K25" s="14" t="inlineStr">
+      <c r="L25" s="14" t="inlineStr">
         <is>
           <t>51.6200, -0.0600</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="M25" s="14" t="inlineStr">
         <is>
           <t>школа Христова госпиталя, Лондон</t>
         </is>
       </c>
-      <c r="M25" s="14" t="n"/>
       <c r="N25" s="14" t="n"/>
       <c r="O25" s="14" t="n"/>
-      <c r="P25" s="14" t="inlineStr">
+      <c r="P25" s="14" t="n"/>
+      <c r="Q25" s="14" t="inlineStr">
         <is>
           <t>Сэмюэл Тейлор Кольридж; Уильям Хэзлитт; Уильям Вордсворт; Роберт Саути</t>
         </is>
       </c>
-      <c r="Q25" s="14" t="n"/>
-      <c r="R25" s="14" t="inlineStr">
+      <c r="R25" s="14" t="n"/>
+      <c r="S25" s="14" t="inlineStr">
         <is>
           <t>эссеистика; литературная критика</t>
         </is>
       </c>
-      <c r="S25" s="14" t="inlineStr">
+      <c r="T25" s="14" t="inlineStr">
         <is>
           <t>Английский эссеист и поэт эпохи романтизма, ближайший друг Кольриджа (учились вместе в школе Christ's Hospital) и Вордсворта. Известен прежде всего циклом эссе «Essays of Elia» (публиковались в London Magazine в 1820-х, изданы отдельной книгой в 1823-м; вторая серия — «Last Essays of Elia», 1833) под псевдонимом «Elia» — непринуждённых, личных, часто ироничных текстов. Также автор (совместно с сестрой Мэри Лэмб) «Tales from Shakespeare» (1807) — прозаических пересказов пьес Шекспира для детей. Биография Лэмба омрачена трагедией: в 1796 году его сестра Мэри в приступе психического расстройства убила их мать; Чарльз всю оставшуюся жизнь заботился о сестре, у которой сохранялись периодические рецидивы.</t>
         </is>
       </c>
-      <c r="T25" s="14" t="inlineStr">
+      <c r="U25" s="14" t="inlineStr">
         <is>
           <t>- Charles Lamb, Essays of Elia, том i (New York: G. P. Putnam's Sons, б/г), с. 122 — точная сноска Уилсона; конкретное эссе внутри сборника не названо, требует уточнения при желании найти точный первоисточник</t>
         </is>
       </c>
-      <c r="U25" s="14" t="n"/>
       <c r="V25" s="14" t="n"/>
-      <c r="W25" s="14" t="inlineStr">
+      <c r="W25" s="14" t="n"/>
+      <c r="X25" s="14" t="inlineStr">
         <is>
           <t>Источник цитаты (через эссе из «Essays of Elia»), которую Уилсон перефразирует как эпиграф к собственной мысли: жалоба Лэмба на сэра Томаса Брауна (см. thomas-browne) за то, что тот, вознёсшись на «воздушные ходули абстракции», упустил из виду «дерзкие индивидуальности» конкретного человечества. Уилсон использует эту цитату как модель для собственной критики: так же, как Браун (по мнению Лэмба) потерялся в метафизических высотах, упуская конкретику, так и многие философы теряют индивидуальные детали конкретных оценочных суждений, сгоняя их в общий «загон» абстрактных понятийных категорий.</t>
         </is>
       </c>
-      <c r="X25" s="14" t="inlineStr">
+      <c r="Y25" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y25" s="14" t="inlineStr">
+      <c r="Z25" s="14" t="inlineStr">
         <is>
           <t>chapter_1_iv</t>
         </is>
       </c>
-      <c r="Z25" s="14" t="inlineStr">
+      <c r="AA25" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/charles-lamb</t>
         </is>
       </c>
-      <c r="AA25" s="14" t="inlineStr">
+      <c r="AB25" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB25" s="14" t="n"/>
+      <c r="AC25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -3239,81 +3304,86 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
+          <t>рак желудка (предположительно)</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
           <t>Мейдстон, Кент, Англия</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>51.2704, 0.5227</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="K26" s="14" t="inlineStr">
         <is>
           <t>Сохо, Лондон</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="L26" s="14" t="inlineStr">
         <is>
           <t>51.5136, -0.1365</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="M26" s="14" t="inlineStr">
         <is>
           <t>Новый колледж в Хакни</t>
         </is>
       </c>
-      <c r="M26" s="14" t="n"/>
       <c r="N26" s="14" t="n"/>
       <c r="O26" s="14" t="n"/>
-      <c r="P26" s="14" t="inlineStr">
+      <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14" t="inlineStr">
         <is>
           <t>Чарльз Лэмб; Сэмюэл Тейлор Кольридж; Уильям Вордсворт</t>
         </is>
       </c>
-      <c r="Q26" s="14" t="n"/>
-      <c r="R26" s="14" t="inlineStr">
+      <c r="R26" s="14" t="n"/>
+      <c r="S26" s="14" t="inlineStr">
         <is>
           <t>эссеистика; литературная критика; живопись</t>
         </is>
       </c>
-      <c r="S26" s="14" t="inlineStr">
+      <c r="T26" s="14" t="inlineStr">
         <is>
           <t>Английский эссеист, критик и публицист эпохи романтизма, один из крупнейших мастеров английского эссе. Известен сборником коротких эссе «Table Talk» (1821–1822), сочетающих личные наблюдения, литературную критику и рассуждения о человеческой природе в непринуждённой, разговорной манере.</t>
         </is>
       </c>
-      <c r="T26" s="14" t="inlineStr">
+      <c r="U26" s="14" t="inlineStr">
         <is>
           <t>- «Table Talk» (1821–1822) — сборник эссе; конкретно эссе «On Thought and Action» и «On Genius and Common Sense» фигурируют позже в книге (см. таблицу выше), но пока не разобраны в контексте.</t>
         </is>
       </c>
-      <c r="U26" s="14" t="n"/>
       <c r="V26" s="14" t="n"/>
-      <c r="W26" s="14" t="inlineStr">
+      <c r="W26" s="14" t="n"/>
+      <c r="X26" s="14" t="inlineStr">
         <is>
           <t>Уилсон называет Хэзлитта (наряду с Юмом) как ориентир для оснований собственной книги: обсуждение временами должно читаться как «неправдоподобный гибрид старомодной медитации о человеческом уделе... и Ingenious Mechanisms for Inventors» — то есть смесь эссеистической, личной рефлексии о жизни и сухого инженерного любопытства к устройству механизмов языка.</t>
         </is>
       </c>
-      <c r="X26" s="14" t="inlineStr">
+      <c r="Y26" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y26" s="14" t="inlineStr">
+      <c r="Z26" s="14" t="inlineStr">
         <is>
           <t>chapter_1_xi</t>
         </is>
       </c>
-      <c r="Z26" s="14" t="inlineStr">
+      <c r="AA26" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/william-hazlitt</t>
         </is>
       </c>
-      <c r="AA26" s="14" t="inlineStr">
+      <c r="AB26" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB26" s="14" t="n"/>
+      <c r="AC26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -3351,79 +3421,80 @@
           <t>1857-05-23</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>Париж</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>48.8566, 2.3522</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="K27" s="14" t="inlineStr">
         <is>
           <t>Со, Франция</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
+      <c r="L27" s="14" t="inlineStr">
         <is>
           <t>48.7766, 2.2908</t>
         </is>
       </c>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="M27" s="14" t="inlineStr">
         <is>
           <t>Политехническая школа; Школа мостов и дорог</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr">
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>Политехническая школа; Коллеж де Франс; Парижский университет</t>
         </is>
       </c>
-      <c r="N27" s="14" t="n"/>
       <c r="O27" s="14" t="n"/>
       <c r="P27" s="14" t="n"/>
       <c r="Q27" s="14" t="n"/>
-      <c r="R27" s="14" t="inlineStr">
+      <c r="R27" s="14" t="n"/>
+      <c r="S27" s="14" t="inlineStr">
         <is>
           <t>математический анализ; механика сплошных сред</t>
         </is>
       </c>
-      <c r="S27" s="14" t="inlineStr">
+      <c r="T27" s="14" t="inlineStr">
         <is>
           <t>Французский математик (1789–1857), один из создателей строгого математического анализа. В контексте Уилсона важно его определение суммы бесконечного ряда как предела частичных сумм (справочно, «Cours d'analyse», 1821).</t>
         </is>
       </c>
-      <c r="T27" s="14" t="n"/>
       <c r="U27" s="14" t="n"/>
       <c r="V27" s="14" t="n"/>
-      <c r="W27" s="14" t="inlineStr">
+      <c r="W27" s="14" t="n"/>
+      <c r="X27" s="14" t="inlineStr">
         <is>
           <t>В цитате Харди «классическое определение Коши» служит точкой отсчёта: Харди ищет определение суммы, «гораздо более широко применимое». Кроме того, Коши для Харди рубеж, до которого математики не привыкли задавать вопрос «как определить?», а спрашивали «что это такое?».</t>
         </is>
       </c>
-      <c r="X27" s="14" t="inlineStr">
+      <c r="Y27" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y27" s="14" t="inlineStr">
+      <c r="Z27" s="14" t="inlineStr">
         <is>
           <t>chapter_3_iv</t>
         </is>
       </c>
-      <c r="Z27" s="14" t="inlineStr">
+      <c r="AA27" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/ogyusten-koshi</t>
         </is>
       </c>
-      <c r="AA27" s="14" t="inlineStr">
+      <c r="AB27" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB27" s="14" t="n"/>
+      <c r="AC27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -3463,73 +3534,78 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
+          <t>туберкулёз</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
           <t>Недстранн, Норвегия</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr">
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>59.3500, 5.8500</t>
         </is>
       </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="K28" s="14" t="inlineStr">
         <is>
           <t>Фроланд, Норвегия</t>
         </is>
       </c>
-      <c r="K28" s="14" t="inlineStr">
+      <c r="L28" s="14" t="inlineStr">
         <is>
           <t>58.5300, 8.6500</t>
         </is>
       </c>
-      <c r="L28" s="14" t="inlineStr">
+      <c r="M28" s="14" t="inlineStr">
         <is>
           <t>Университет Кристиании</t>
         </is>
       </c>
-      <c r="M28" s="14" t="n"/>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n"/>
       <c r="P28" s="14" t="n"/>
       <c r="Q28" s="14" t="n"/>
-      <c r="R28" s="14" t="inlineStr">
+      <c r="R28" s="14" t="n"/>
+      <c r="S28" s="14" t="inlineStr">
         <is>
           <t>алгебра; математический анализ</t>
         </is>
       </c>
-      <c r="S28" s="14" t="inlineStr">
+      <c r="T28" s="14" t="inlineStr">
         <is>
           <t>Норвежский математик (1802–1829), один из основателей строгого анализа. Уилсон вводит его одной репликой в скобках: «Расходящиеся ряды, – как однажды написал Абель, – это дьявол». Сноски к цитате нет.</t>
         </is>
       </c>
-      <c r="T28" s="14" t="n"/>
       <c r="U28" s="14" t="n"/>
       <c r="V28" s="14" t="n"/>
-      <c r="W28" s="14" t="inlineStr">
+      <c r="W28" s="14" t="n"/>
+      <c r="X28" s="14" t="inlineStr">
         <is>
           <t>Реплика показывает, как остро воспринималась проблема расходящихся рядов. Выражения без очевидного смысла давали математикам и физикам большие успехи, если делать вид, что смысл есть, и именно эту двусмысленность Абель называл делом дьявола. Тем самым Уилсон создаёт исторический фон для цитаты Харди о «привычке определять».</t>
         </is>
       </c>
-      <c r="X28" s="14" t="inlineStr">
+      <c r="Y28" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y28" s="14" t="inlineStr">
+      <c r="Z28" s="14" t="inlineStr">
         <is>
           <t>chapter_3_iv</t>
         </is>
       </c>
-      <c r="Z28" s="14" t="inlineStr">
+      <c r="AA28" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/nils-abel</t>
         </is>
       </c>
-      <c r="AA28" s="14" t="inlineStr">
+      <c r="AB28" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB28" s="14" t="n"/>
+      <c r="AC28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -3567,79 +3643,80 @@
           <t>1864-05-19</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Сейлем, Массачусетс, США</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>42.5195, -70.8967</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="K29" s="14" t="inlineStr">
         <is>
           <t>Плимут, Нью-Гэмпшир, США</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="L29" s="14" t="inlineStr">
         <is>
           <t>43.7570, -71.6881</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="M29" s="14" t="inlineStr">
         <is>
           <t>Боудин-колледж</t>
         </is>
       </c>
-      <c r="M29" s="14" t="n"/>
       <c r="N29" s="14" t="n"/>
       <c r="O29" s="14" t="n"/>
       <c r="P29" s="14" t="n"/>
       <c r="Q29" s="14" t="n"/>
-      <c r="R29" s="14" t="inlineStr">
+      <c r="R29" s="14" t="n"/>
+      <c r="S29" s="14" t="inlineStr">
         <is>
           <t>проза</t>
         </is>
       </c>
-      <c r="S29" s="14" t="inlineStr">
+      <c r="T29" s="14" t="inlineStr">
         <is>
           <t>Американский писатель XIX века, автор рассказа «The Snow Image» («Образ снега») из сборника Twice-Told Tales — истории о духе, таинственным образом оживляющем ледяную/снежную статую, и о недалёком «мистере Линдси», не способном признать это чудо.</t>
         </is>
       </c>
-      <c r="T29" s="14" t="inlineStr">
+      <c r="U29" s="14" t="inlineStr">
         <is>
           <t>- Nathaniel Hawthorne, «The Snow Image» // Twice-Told Tales (Norwalk, Conn.: Heritage, 1966), с. 20</t>
         </is>
       </c>
-      <c r="U29" s="14" t="n"/>
       <c r="V29" s="14" t="n"/>
-      <c r="W29" s="14" t="inlineStr">
+      <c r="W29" s="14" t="n"/>
+      <c r="X29" s="14" t="inlineStr">
         <is>
           <t>Уилсон цитирует отрывок из «The Snow Image», якобы обличающий узколобое самодовольство мистера Линдси, — но затем оборачивает ту же критику против самого Готорна. По мнению Уилсона, Готорн сам демонстрирует снисходительное самодовольство, покровительствуя «ограниченности научного интеллекта» через фигуру Линдси: «трансцендентная возможность» духа в снежной статуе, которую Линдси якобы упускает, на деле банальна и восходит к анимистическим представлениям, известным из сказок (ср. osyol-silvestr). Уилсон противопоставляет этому по-настоящему удивительные, неожиданные возможности, которые открывает клиническая нейропсихология повреждённого мозга</t>
         </is>
       </c>
-      <c r="X29" s="14" t="inlineStr">
+      <c r="Y29" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y29" s="14" t="inlineStr">
+      <c r="Z29" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iii</t>
         </is>
       </c>
-      <c r="Z29" s="14" t="inlineStr">
+      <c r="AA29" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/nataniel-gotorn</t>
         </is>
       </c>
-      <c r="AA29" s="14" t="inlineStr">
+      <c r="AB29" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB29" s="14" t="n"/>
+      <c r="AC29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -3677,83 +3754,84 @@
           <t>1887-09-14</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="inlineStr">
         <is>
           <t>Людвигсбург, Вюртемберг</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr">
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>48.8975, 9.1919</t>
         </is>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="K30" s="14" t="inlineStr">
         <is>
           <t>Гмунден, Австрия</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="L30" s="14" t="inlineStr">
         <is>
           <t>47.9180, 13.7990</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
+      <c r="M30" s="14" t="inlineStr">
         <is>
           <t>Тюбингенский университет</t>
         </is>
       </c>
-      <c r="M30" s="14" t="inlineStr">
+      <c r="N30" s="14" t="inlineStr">
         <is>
           <t>Тюбингенский университет; Цюрихский политехникум</t>
         </is>
       </c>
-      <c r="N30" s="14" t="n"/>
       <c r="O30" s="14" t="n"/>
       <c r="P30" s="14" t="n"/>
       <c r="Q30" s="14" t="n"/>
-      <c r="R30" s="14" t="inlineStr">
+      <c r="R30" s="14" t="n"/>
+      <c r="S30" s="14" t="inlineStr">
         <is>
           <t>эстетика; литература</t>
         </is>
       </c>
-      <c r="S30" s="14" t="inlineStr">
+      <c r="T30" s="14" t="inlineStr">
         <is>
           <t>Немецкий философ, эстетик и литературовед, связанный с немецким идеализмом и эстетикой XIX века.</t>
         </is>
       </c>
-      <c r="T30" s="14" t="inlineStr">
+      <c r="U30" s="14" t="inlineStr">
         <is>
           <t>- Музыкальная эстетика - Амфиболический характер - Фундаментальные детерминанты музыки - Партиципативное вовлечение</t>
         </is>
       </c>
-      <c r="U30" s="14" t="n"/>
       <c r="V30" s="14" t="n"/>
-      <c r="W30" s="14" t="inlineStr">
+      <c r="W30" s="14" t="n"/>
+      <c r="X30" s="14" t="inlineStr">
         <is>
           <t>Вишер переносит амфиболическую логику из общей философии в область музыки. Музыкальное произведение оказывается не только совокупностью внешне фиксируемых физических характеристик: его фундаментальные детерминанты дают ему особый, «амфиболический» характер.</t>
         </is>
       </c>
-      <c r="X30" s="14" t="inlineStr">
+      <c r="Y30" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y30" s="14" t="inlineStr">
+      <c r="Z30" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z30" s="14" t="inlineStr">
+      <c r="AA30" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/f-t-vischer</t>
         </is>
       </c>
-      <c r="AA30" s="14" t="inlineStr">
+      <c r="AB30" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB30" s="14" t="n"/>
+      <c r="AC30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -3791,79 +3869,80 @@
           <t>1892-10-06</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Сомерсби, Линкольншир, Англия</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>53.2500, 0.0100</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="K31" s="14" t="inlineStr">
         <is>
           <t>Олдуорт близ Хейзлмира, Англия</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
+      <c r="L31" s="14" t="inlineStr">
         <is>
           <t>51.0800, -0.7200</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="M31" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M31" s="14" t="n"/>
       <c r="N31" s="14" t="n"/>
       <c r="O31" s="14" t="n"/>
       <c r="P31" s="14" t="n"/>
-      <c r="Q31" s="14" t="inlineStr">
+      <c r="Q31" s="14" t="n"/>
+      <c r="R31" s="14" t="inlineStr">
         <is>
           <t>Поэт-лауреат Великобритании (1850)</t>
         </is>
       </c>
-      <c r="R31" s="14" t="inlineStr">
+      <c r="S31" s="14" t="inlineStr">
         <is>
           <t>поэзия</t>
         </is>
       </c>
-      <c r="S31" s="14" t="inlineStr">
+      <c r="T31" s="14" t="inlineStr">
         <is>
           <t>Английский поэт викторианской эпохи (1809–1892). У Уилсона в этом фрагменте упомянут только по имени.</t>
         </is>
       </c>
-      <c r="T31" s="14" t="n"/>
       <c r="U31" s="14" t="n"/>
       <c r="V31" s="14" t="n"/>
-      <c r="W31" s="14" t="inlineStr">
+      <c r="W31" s="14" t="n"/>
+      <c r="X31" s="14" t="inlineStr">
         <is>
           <t>Имя возникает в сравнении: снисходительность Харди к математикам XVIII века Уилсон считает столь же оскорбительной, как «самодовольство критика из предыдущей главы, упрекающего Дарвина в неспособности оценить Теннисона». Сам Теннисон в аргументе не участвует, он служит опорой для отсылки к примеру главы 2.</t>
         </is>
       </c>
-      <c r="X31" s="14" t="inlineStr">
+      <c r="Y31" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y31" s="14" t="inlineStr">
+      <c r="Z31" s="14" t="inlineStr">
         <is>
           <t>chapter_3_iv</t>
         </is>
       </c>
-      <c r="Z31" s="14" t="inlineStr">
+      <c r="AA31" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/alfred-tennison</t>
         </is>
       </c>
-      <c r="AA31" s="14" t="inlineStr">
+      <c r="AB31" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB31" s="14" t="n"/>
+      <c r="AC31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -3903,85 +3982,90 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
+          <t>болезнь сердца</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
           <t>Шрусбери, Англия</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr">
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>52.7073, -2.7553</t>
         </is>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="K32" s="14" t="inlineStr">
         <is>
           <t>Даун-Хаус, Даун, Кент, Англия</t>
         </is>
       </c>
-      <c r="K32" s="14" t="inlineStr">
+      <c r="L32" s="14" t="inlineStr">
         <is>
           <t>51.3300, 0.0500</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="M32" s="14" t="inlineStr">
         <is>
           <t>Эдинбургский университет; Крайст-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
       <c r="O32" s="14" t="n"/>
-      <c r="P32" s="14" t="inlineStr">
+      <c r="P32" s="14" t="n"/>
+      <c r="Q32" s="14" t="inlineStr">
         <is>
           <t>Томас Генри Хаксли</t>
         </is>
       </c>
-      <c r="Q32" s="14" t="inlineStr">
+      <c r="R32" s="14" t="inlineStr">
         <is>
           <t>Медаль Копли (1864)</t>
         </is>
       </c>
-      <c r="R32" s="14" t="inlineStr">
+      <c r="S32" s="14" t="inlineStr">
         <is>
           <t>естествознание; эволюционная биология; геология</t>
         </is>
       </c>
-      <c r="S32" s="14" t="inlineStr">
+      <c r="T32" s="14" t="inlineStr">
         <is>
           <t>Английский натуралист, автор теории естественного отбора («Происхождение видов»). В позднем возрасте написал небольшую монографию о роли дождевых червей в формировании почвы. В своей Автобиографии признавался, что к старости утратил способность получать удовольствие от поэзии и музыки.</t>
         </is>
       </c>
-      <c r="T32" s="14" t="inlineStr">
+      <c r="U32" s="14" t="inlineStr">
         <is>
           <t>- The Formation of Vegetable Mold through the Action of Worms (1896) — как пример ценности «малых идей» - Autobiography (изд. 1983) — свидетельство об утрате эстетической восприимчивости</t>
         </is>
       </c>
-      <c r="U32" s="14" t="n"/>
       <c r="V32" s="14" t="n"/>
-      <c r="W32" s="14" t="inlineStr">
+      <c r="W32" s="14" t="n"/>
+      <c r="X32" s="14" t="inlineStr">
         <is>
           <t>Центральный кейс подраздела (ii) «Объективный экстремизм». Уилсон разбирает случай, когда некий «специалист по этике» публично упрекал Дарвина за утрату интереса к искусству в пользу «макулатуры» вроде брошюры о червях, обвиняя его в недостатке «процветания человечества». Уилсон защищает Дарвина по двум линиям: (1) брошюра о червях — образец ценных «малых идей» против ложного культа «больших идей»; (2) собственное признание Дарвина в Автобиографии об утрате эстетического вкуса свидетельствует о физиологической, а не моральной природе этой утраты — неконтролируемом «атрофировании» части мозга с возрастом. Используется как опровержение картины, будто музыкальное/эстетическое содержание прямолинейно доступно вниманию и его утрата — вопрос небрежности.</t>
         </is>
       </c>
-      <c r="X32" s="14" t="inlineStr">
+      <c r="Y32" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y32" s="14" t="inlineStr">
+      <c r="Z32" s="14" t="inlineStr">
         <is>
           <t>chapter_2_ii</t>
         </is>
       </c>
-      <c r="Z32" s="14" t="inlineStr">
+      <c r="AA32" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/charles-darwin</t>
         </is>
       </c>
-      <c r="AA32" s="14" t="inlineStr">
+      <c r="AB32" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB32" s="14" t="n"/>
+      <c r="AC32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -4021,73 +4105,78 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
+          <t>сердечный приступ</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
           <t>Лейпциг, Саксония</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>51.3397, 12.3731</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="K33" s="14" t="inlineStr">
         <is>
           <t>Венеция, Италия</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
+      <c r="L33" s="14" t="inlineStr">
         <is>
           <t>45.4408, 12.3155</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="M33" s="14" t="inlineStr">
         <is>
           <t>Лейпцигский университет</t>
         </is>
       </c>
-      <c r="M33" s="14" t="n"/>
       <c r="N33" s="14" t="n"/>
       <c r="O33" s="14" t="n"/>
       <c r="P33" s="14" t="n"/>
       <c r="Q33" s="14" t="n"/>
-      <c r="R33" s="14" t="inlineStr">
+      <c r="R33" s="14" t="n"/>
+      <c r="S33" s="14" t="inlineStr">
         <is>
           <t>композиция; оперная драматургия</t>
         </is>
       </c>
-      <c r="S33" s="14" t="inlineStr">
+      <c r="T33" s="14" t="inlineStr">
         <is>
           <t>Немецкий композитор XIX века, автор оперных реформ.</t>
         </is>
       </c>
-      <c r="T33" s="14" t="n"/>
       <c r="U33" s="14" t="n"/>
       <c r="V33" s="14" t="n"/>
-      <c r="W33" s="14" t="inlineStr">
+      <c r="W33" s="14" t="n"/>
+      <c r="X33" s="14" t="inlineStr">
         <is>
           <t>Цитируется как автор восторженного отзыва о Моцарте — о том, как тот «насыщает мелодию» глубиной человеческого чувства, сравнимой с выразительностью человеческого голоса.</t>
         </is>
       </c>
-      <c r="X33" s="14" t="inlineStr">
+      <c r="Y33" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y33" s="14" t="inlineStr">
+      <c r="Z33" s="14" t="inlineStr">
         <is>
           <t>chapter_2_i</t>
         </is>
       </c>
-      <c r="Z33" s="14" t="inlineStr">
+      <c r="AA33" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/richard-vagner</t>
         </is>
       </c>
-      <c r="AA33" s="14" t="inlineStr">
+      <c r="AB33" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB33" s="14" t="n"/>
+      <c r="AC33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -4127,85 +4216,90 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
+          <t>кровоизлияние в мозг</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
           <t>Потсдам, Пруссия</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="J34" s="14" t="inlineStr">
         <is>
           <t>52.3906, 13.0645</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="K34" s="14" t="inlineStr">
         <is>
           <t>Шарлоттенбург (Берлин)</t>
         </is>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="L34" s="14" t="inlineStr">
         <is>
           <t>52.5167, 13.3000</t>
         </is>
       </c>
-      <c r="L34" s="14" t="inlineStr">
+      <c r="M34" s="14" t="inlineStr">
         <is>
           <t>Медико-хирургический институт Фридриха Вильгельма, Берлин</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr">
+      <c r="N34" s="14" t="inlineStr">
         <is>
           <t>Кёнигсбергский университет; Боннский университет; Гейдельбергский университет; Берлинский университет</t>
         </is>
       </c>
-      <c r="N34" s="14" t="n"/>
-      <c r="O34" s="14" t="inlineStr">
+      <c r="O34" s="14" t="n"/>
+      <c r="P34" s="14" t="inlineStr">
         <is>
           <t>Генрих Герц</t>
         </is>
       </c>
-      <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
-      <c r="R34" s="14" t="inlineStr">
+      <c r="R34" s="14" t="n"/>
+      <c r="S34" s="14" t="inlineStr">
         <is>
           <t>физиология; физика; физиологическая акустика и оптика</t>
         </is>
       </c>
-      <c r="S34" s="14" t="inlineStr">
+      <c r="T34" s="14" t="inlineStr">
         <is>
           <t>Немецкий физик, физиолог и философ науки. Один из первооткрывателей закона сохранения энергии, автор фундаментальных работ по физиологической оптике и акустике («Handbuch der physiologischen Optik»), а также эпистемологических работ о природе геометрических аксиом и о роли знаков/символов в восприятии («Die Tatsachen in der Wahrnehmung», 1878) — идея, что наши перцептивные и понятийные «образы» суть условные, практически выработанные знаки, а не прямые слепки с реальности.</t>
         </is>
       </c>
-      <c r="T34" s="14" t="inlineStr">
+      <c r="U34" s="14" t="inlineStr">
         <is>
           <t>- Ранний, «умеренный» холизм немецкой физики середины XIX века (без указания конкретного труда — требует уточнения по внутренней ссылке 4,iii) - (гипотеза, не подтверждена цитатой): возможна связь с концепцией Гельмгольца о знаках/символах восприятия как параллелью к идее Уилсона о «блуждании» значений понятий</t>
         </is>
       </c>
-      <c r="U34" s="14" t="n"/>
       <c r="V34" s="14" t="n"/>
-      <c r="W34" s="14" t="inlineStr">
+      <c r="W34" s="14" t="n"/>
+      <c r="X34" s="14" t="inlineStr">
         <is>
           <t>Назван (наряду с Генрихом Герцем) как пример «холизма» в его первоначальном, сдержанном виде — как он возникал в середине XIX века у немецких физиков в качестве умеренного отхода от «классической закостенелости», а не как радикальное учение. Уилсон противопоставляет эту раннюю, умеренную форму холизма её позднейшим «диким и разрушительным» крайностям XX века (кунианизм, пост-структурализм), от которых сам явно дистанцируется. Даёт внутреннюю отсылку «(4, iii)» — судя по всему, к месту в главе 4, где эта тема развёрнута подробнее; при чтении главы 4 стоит свериться.</t>
         </is>
       </c>
-      <c r="X34" s="14" t="inlineStr">
+      <c r="Y34" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y34" s="14" t="inlineStr">
+      <c r="Z34" s="14" t="inlineStr">
         <is>
           <t>chapter_1_ix</t>
         </is>
       </c>
-      <c r="Z34" s="14" t="inlineStr">
+      <c r="AA34" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/hermann-helmholtz</t>
         </is>
       </c>
-      <c r="AA34" s="14" t="inlineStr">
+      <c r="AB34" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB34" s="14" t="n"/>
+      <c r="AC34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -4245,89 +4339,94 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
+          <t>сердечный приступ</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
           <t>Илинг, Лондон</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>51.5130, -0.3089</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="K35" s="14" t="inlineStr">
         <is>
           <t>Истборн, Англия</t>
         </is>
       </c>
-      <c r="K35" s="14" t="inlineStr">
+      <c r="L35" s="14" t="inlineStr">
         <is>
           <t>50.7680, 0.2905</t>
         </is>
       </c>
-      <c r="L35" s="14" t="inlineStr">
+      <c r="M35" s="14" t="inlineStr">
         <is>
           <t>Медицинская школа больницы Чаринг-Кросс</t>
         </is>
       </c>
-      <c r="M35" s="14" t="inlineStr">
+      <c r="N35" s="14" t="inlineStr">
         <is>
           <t>Королевская горная школа, Лондон</t>
         </is>
       </c>
-      <c r="N35" s="14" t="n"/>
       <c r="O35" s="14" t="n"/>
-      <c r="P35" s="14" t="inlineStr">
+      <c r="P35" s="14" t="n"/>
+      <c r="Q35" s="14" t="inlineStr">
         <is>
           <t>Чарльз Дарвин</t>
         </is>
       </c>
-      <c r="Q35" s="14" t="inlineStr">
+      <c r="R35" s="14" t="inlineStr">
         <is>
           <t>Медаль Копли (1888)</t>
         </is>
       </c>
-      <c r="R35" s="14" t="inlineStr">
+      <c r="S35" s="14" t="inlineStr">
         <is>
           <t>сравнительная анатомия; эволюционная биология</t>
         </is>
       </c>
-      <c r="S35" s="14" t="inlineStr">
+      <c r="T35" s="14" t="inlineStr">
         <is>
           <t>Английский биолог, известен как «бульдог Дарвина» за энергичную публичную защиту теории эволюции (в том числе в знаменитых дебатах с епископом Сэмюэлем Уилберфорсом, 1860). Ввёл в обиход термин «агностик». Дед писателя Олдоса Хаксли и биолога Джулиана Хаксли. Автор эссе «On the Method of Zadig» (в сборнике «Science and Culture», 1882), откуда взята цитата у Уилсона.</t>
         </is>
       </c>
-      <c r="T35" s="14" t="inlineStr">
+      <c r="U35" s="14" t="inlineStr">
         <is>
           <t>- T. H. Huxley, "On the Method of Zadig" // Science and Culture (New York: D. Appleton, 1882) - T. H. Huxley, Hume, with Helps to the Study of Berkeley (1898) - Наука как «тренированный и организованный здравый смысл» - Метод Задиг / ретроспективное пророчество - Научное описание и обычные качества опыта Про само название эссе. Задиг — главный герой философской повести Вольтера «Задиг, или Судьба» (1747): по одним лишь следам на земле он точно описывает сбежавшую собаку королевы и лошадь короля, которых никогда не видел (сюжет, предвосхищающий метод Шерлока Холмса на век раньше). Эссе Хаксли (впервые 1880, Popular Science Monthly; переиздано в «Science and Culture», 1882) использует этот сюжет для тезиса о «ретроспективном пророчестве» — способности восстанавливать факты прошлого по наблюдаемым в настоящем следам, не мистическом даре, а методе, на котором строятся геология, палеонтология, археология. Эссе открывается эпиграфом из Кювье, который по зубам и челюсти ископаемого верно предсказал строение его таза — той же логикой, что и Задиг по следам копыт заключил о хвосте лошади. То есть отсылка у Хаксли не случайна: цитируемый Уилсоном тезис («наука — тренированный здравый смысл») в самом эссе Хаксли развёрнут именно на этом примере.</t>
         </is>
       </c>
-      <c r="U35" s="14" t="n"/>
       <c r="V35" s="14" t="n"/>
-      <c r="W35" s="14" t="inlineStr">
+      <c r="W35" s="14" t="n"/>
+      <c r="X35" s="14" t="inlineStr">
         <is>
           <t>Процитирован в связи с тезисом о том, что мир природы «редко благосклонен к дисциплинарному разделению» — даже изучение морских водорослей ведёт в химию, физику, математику и философию. Уилсон приводит афоризм Хаксли о том, что наука — это «не что иное, как тренированный и организованный здравый смысл», отличающийся от обычного здравого смысла лишь так, как ветеран отличается от новобранца, а его методы — лишь так, как фехтовальная техника гвардейца («cut and thrust» — рубящие и колющие удары) отличается от того, как дикарь орудует дубиной. ⚠️ Важное расхождение с переводом. В оригинале у Хаксли дубина — только у «дикаря»; у гвардейца — именно фехтовальная техника («cut and thrust», рубяще-колющие удары холодным оружием/штыком), а не дубина. Русский перевод («удары гвардейца отличаются от манеры дикаря владеть своей дубинкой») видоизменил конструкцию так, что дубинка читается как общий инструмент для обеих сравниваемых сторон. Возможно, в этом пассаже речь идёт об оружии австралийских аборигенов. В 1847 г. в ходе первой картографической экспедиции к Большому Барьерному рифу фрегат "Rattlesnake", на котором Хаксли служил хирургом и естествоиспытателем, бросил якорь у мыса Апстарт, и учёный получил возможность ознакомиться с бытом местных племён. Предположительно автор видел своими глазами боевое применение дубинки Лил-лил</t>
         </is>
       </c>
-      <c r="X35" s="14" t="inlineStr">
+      <c r="Y35" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 2</t>
         </is>
       </c>
-      <c r="Y35" s="14" t="inlineStr">
+      <c r="Z35" s="14" t="inlineStr">
         <is>
           <t>chapter_1_iv; chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z35" s="14" t="inlineStr">
+      <c r="AA35" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/t-h-huxley</t>
         </is>
       </c>
-      <c r="AA35" s="14" t="inlineStr">
+      <c r="AB35" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB35" s="14" t="n"/>
+      <c r="AC35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -4365,83 +4464,84 @@
           <t>1905-08-20</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="inlineStr">
         <is>
           <t>Эшвайлер, Пруссия</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>50.8172, 6.2650</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="K36" s="14" t="inlineStr">
         <is>
           <t>Берлин</t>
         </is>
       </c>
-      <c r="K36" s="14" t="inlineStr">
+      <c r="L36" s="14" t="inlineStr">
         <is>
           <t>52.5200, 13.4050</t>
         </is>
       </c>
-      <c r="L36" s="14" t="inlineStr">
+      <c r="M36" s="14" t="inlineStr">
         <is>
           <t>Политехникум Карлсруэ</t>
         </is>
       </c>
-      <c r="M36" s="14" t="inlineStr">
+      <c r="N36" s="14" t="inlineStr">
         <is>
           <t>Цюрихский политехникум; Королевская ремесленная академия (Технический университет Берлина)</t>
         </is>
       </c>
-      <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
-      <c r="R36" s="14" t="inlineStr">
+      <c r="R36" s="14" t="n"/>
+      <c r="S36" s="14" t="inlineStr">
         <is>
           <t>кинематика машин; машиноведение</t>
         </is>
       </c>
-      <c r="S36" s="14" t="inlineStr">
+      <c r="T36" s="14" t="inlineStr">
         <is>
           <t>Немецкий инженер-машиностроитель, профессор Королевской технической академии в Берлине, основатель кинематики машин как систематической дисциплины. В работе «Теоретическая кинематика: основы теории машиноведения» (1875) разработал строгую понятийную схему для описания механизмов в отрыве от их конкретного материального воплощения — систему классификации «кинематических пар» (типов соединений между звеньями машины), позволяющую абстрактно анализировать движение независимо от того, из чего механизм сделан.</t>
         </is>
       </c>
-      <c r="T36" s="14" t="inlineStr">
+      <c r="U36" s="14" t="inlineStr">
         <is>
           <t>- «Theoretische Kinematik» (1875) — систематическая теория машиноведения - Классификация «кинематических пар» — абстрактная понятийная схема для описания механизмов независимо от материального воплощения</t>
         </is>
       </c>
-      <c r="U36" s="14" t="n"/>
       <c r="V36" s="14" t="n"/>
-      <c r="W36" s="14" t="inlineStr">
+      <c r="W36" s="14" t="n"/>
+      <c r="X36" s="14" t="inlineStr">
         <is>
           <t>Указан Уилсоном в предисловии наравне с Хевисайдом и Адамаром как один из авторов, чьим трудам он «особенно обязан» — трое инженеров и прикладных математиков второй половины XIX века, чьи замечания о концептуальной неоднозначности вдохновили общий замысел книги. Наиболее вероятная содержательная связь: классификационная схема Рёло — образцовый пример того, как из инженерной практики (работы с конкретными механизмами) вырастает абстрактная понятийная система (кинематические пары), которая затем сама начинает жить самостоятельной жизнью и требует уточнения при переносе на новые типы механизмов. Это специфичный пример «блуждания» понятия в духе центрального тезиса книги.</t>
         </is>
       </c>
-      <c r="X36" s="14" t="inlineStr">
+      <c r="Y36" s="14" t="inlineStr">
         <is>
           <t>предисловие</t>
         </is>
       </c>
-      <c r="Y36" s="14" t="inlineStr">
+      <c r="Z36" s="14" t="inlineStr">
         <is>
           <t>predislovie</t>
         </is>
       </c>
-      <c r="Z36" s="14" t="inlineStr">
+      <c r="AA36" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/franz-reuleaux</t>
         </is>
       </c>
-      <c r="AA36" s="14" t="inlineStr">
+      <c r="AB36" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB36" s="14" t="n"/>
+      <c r="AC36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -4481,73 +4581,78 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
+          <t>сердечная недостаточность</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
           <t>Дрезден, Нью-Йорк, США</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>42.6840, -76.9570</t>
         </is>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="K37" s="14" t="inlineStr">
         <is>
           <t>Доббс-Ферри, Нью-Йорк, США</t>
         </is>
       </c>
-      <c r="K37" s="14" t="inlineStr">
+      <c r="L37" s="14" t="inlineStr">
         <is>
           <t>41.0145, -73.8726</t>
         </is>
       </c>
-      <c r="L37" s="14" t="n"/>
       <c r="M37" s="14" t="n"/>
       <c r="N37" s="14" t="n"/>
       <c r="O37" s="14" t="n"/>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
-      <c r="R37" s="14" t="inlineStr">
+      <c r="R37" s="14" t="n"/>
+      <c r="S37" s="14" t="inlineStr">
         <is>
           <t>ораторское искусство; агностицизм; право</t>
         </is>
       </c>
-      <c r="S37" s="14" t="inlineStr">
+      <c r="T37" s="14" t="inlineStr">
         <is>
           <t>Американский юрист, ветеран Гражданской войны и знаменитый оратор второй половины XIX века, прозванный «Великим Агностиком» (The Great Agnostic) — самый известный публичный критик религиозной догмы своего времени в США, прославился зажигательными скептическими речами против религиозной ортодоксии.</t>
         </is>
       </c>
-      <c r="T37" s="14" t="inlineStr">
+      <c r="U37" s="14" t="inlineStr">
         <is>
           <t>- Не применимо — используется как культурная аллюзия/типаж, а не как источник идей</t>
         </is>
       </c>
-      <c r="U37" s="14" t="n"/>
       <c r="V37" s="14" t="n"/>
-      <c r="W37" s="14" t="inlineStr">
+      <c r="W37" s="14" t="n"/>
+      <c r="X37" s="14" t="inlineStr">
         <is>
           <t>Использован как риторический типаж-сравнение: Уилсон пишет, что некоторые читатели-номиналисты, воодушевлённые собственным скептицизмом, могут почувствовать порыв стать «Робертом Ингерсоллом метафизических излишеств» — то есть крестоносцем, очищающим философский ландшафт от «гнили мистических универсалий», подобно тому как сам Ингерсолл боролся с религиозной догмой. Это литературная аллюзия для описания определённого психологического типа читателя, а не цитирование идей самого Ингерсолла.</t>
         </is>
       </c>
-      <c r="X37" s="14" t="inlineStr">
+      <c r="Y37" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y37" s="14" t="inlineStr">
+      <c r="Z37" s="14" t="inlineStr">
         <is>
           <t>chapter_1_ii</t>
         </is>
       </c>
-      <c r="Z37" s="14" t="inlineStr">
+      <c r="AA37" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-ingersoll</t>
         </is>
       </c>
-      <c r="AA37" s="14" t="inlineStr">
+      <c r="AB37" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB37" s="14" t="n"/>
+      <c r="AC37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -4585,87 +4690,88 @@
           <t>1916-02-19</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="inlineStr">
         <is>
           <t>Хирлиц (Хрлице) близ Брюнна, Моравия</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>49.1300, 16.6500</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="K38" s="14" t="inlineStr">
         <is>
           <t>Фатерштеттен близ Мюнхена, Германия</t>
         </is>
       </c>
-      <c r="K38" s="14" t="inlineStr">
+      <c r="L38" s="14" t="inlineStr">
         <is>
           <t>48.1050, 11.7690</t>
         </is>
       </c>
-      <c r="L38" s="14" t="inlineStr">
+      <c r="M38" s="14" t="inlineStr">
         <is>
           <t>Венский университет</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr">
+      <c r="N38" s="14" t="inlineStr">
         <is>
           <t>Грацский университет; Пражский (Карлов) университет; Венский университет</t>
         </is>
       </c>
-      <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
-      <c r="R38" s="14" t="inlineStr">
+      <c r="R38" s="14" t="n"/>
+      <c r="S38" s="14" t="inlineStr">
         <is>
           <t>физика; психофизика; философия науки</t>
         </is>
       </c>
-      <c r="S38" s="14" t="inlineStr">
+      <c r="T38" s="14" t="inlineStr">
         <is>
           <t>Австрийский физик и философ. Исследовал ударные волны (отсюда «число Маха»), психофизиологию ощущений; критиковал ньютоновские абсолютные пространство и время, что повлияло на Эйнштейна. Один из главных представителей позитивизма конца XIX века.</t>
         </is>
       </c>
-      <c r="T38" s="14" t="inlineStr">
+      <c r="U38" s="14" t="inlineStr">
         <is>
           <t>- Ernst Mach, Principles of Physical Optics (New York: Dover, n.d.), 1 — сноска 14.</t>
         </is>
       </c>
-      <c r="U38" s="14" t="inlineStr">
+      <c r="V38" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/ernst-mach/</t>
         </is>
       </c>
-      <c r="V38" s="14" t="n"/>
-      <c r="W38" s="14" t="inlineStr">
+      <c r="W38" s="14" t="n"/>
+      <c r="X38" s="14" t="inlineStr">
         <is>
           <t>Краснота как неописуемое. Мах — голос «известного взгляда», что постижение «быть красным» непосредственно и неразложимо: «Яркость, темнота, свет и цвет не поддаются описанию… могут быть только поименованы» (с. 159). Отсюда и вывод, что говорить об «ингредиентах» красноты ошибочно: понятие либо постигнуто полностью, либо его нет (с. 161). Против «тёплых и нечётких» требований. Вместе с Дюгемом и другими учёными 1880–1910 гг. Мах утверждал, что прогрессу физики мешает приверженность «тёплым и нечётким» требованиям к объяснению в духе Бойля. Уилсон признаёт, что «в своём критическом чутье Мах и Дюгем часто оказывались правы», но «как специалисты по семантической диагностике они перестарались»: многозначное выражение «теоретическое содержание» — наследие этих чрезмерных мнений (с. 166).</t>
         </is>
       </c>
-      <c r="X38" s="14" t="inlineStr">
+      <c r="Y38" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y38" s="14" t="inlineStr">
+      <c r="Z38" s="14" t="inlineStr">
         <is>
           <t>chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z38" s="14" t="inlineStr">
+      <c r="AA38" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/ernst-mach</t>
         </is>
       </c>
-      <c r="AA38" s="14" t="inlineStr">
+      <c r="AB38" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB38" s="14" t="n"/>
+      <c r="AC38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -4705,85 +4811,90 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
+          <t>сердечная недостаточность</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
           <t>Нью-Йорк, США</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>40.7128, -74.0060</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="K39" s="14" t="inlineStr">
         <is>
           <t>Чокоруа, Нью-Гэмпшир, США</t>
         </is>
       </c>
-      <c r="K39" s="14" t="inlineStr">
+      <c r="L39" s="14" t="inlineStr">
         <is>
           <t>43.8800, -71.2300</t>
         </is>
       </c>
-      <c r="L39" s="14" t="inlineStr">
+      <c r="M39" s="14" t="inlineStr">
         <is>
           <t>Гарвардская медицинская школа</t>
         </is>
       </c>
-      <c r="M39" s="14" t="inlineStr">
+      <c r="N39" s="14" t="inlineStr">
         <is>
           <t>Гарвардский университет</t>
         </is>
       </c>
-      <c r="N39" s="14" t="n"/>
       <c r="O39" s="14" t="n"/>
       <c r="P39" s="14" t="n"/>
       <c r="Q39" s="14" t="n"/>
-      <c r="R39" s="14" t="inlineStr">
+      <c r="R39" s="14" t="n"/>
+      <c r="S39" s="14" t="inlineStr">
         <is>
           <t>психология; прагматизм</t>
         </is>
       </c>
-      <c r="S39" s="14" t="inlineStr">
+      <c r="T39" s="14" t="inlineStr">
         <is>
           <t>Американский философ и психолог, один из основателей прагматизма, автор The Principles of Psychology. В данном фрагменте цитируется как свидетель радикальной изменчивости человеческого восприятия и вкуса на протяжении жизни.</t>
         </is>
       </c>
-      <c r="T39" s="14" t="inlineStr">
+      <c r="U39" s="14" t="inlineStr">
         <is>
           <t>- The Principles of Psychology (изд. 1983), с. 227–228 - Talks to Teachers on Psychology: and to Students of Some of Life's Ideals (1913), с. 71–73</t>
         </is>
       </c>
-      <c r="U39" s="14" t="inlineStr">
+      <c r="V39" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/james/</t>
         </is>
       </c>
-      <c r="V39" s="14" t="n"/>
-      <c r="W39" s="14" t="inlineStr">
+      <c r="W39" s="14" t="n"/>
+      <c r="X39" s="14" t="inlineStr">
         <is>
           <t>Уилсон приводит развёрнутую цитату Джеймса о том, как со временем меняется отношение к одним и тем же вещам — книги, люди, произведения искусства «тускнеют» независимо от воли человека. Цитата подкрепляет тезис Уилсона о том, что колебания эстетической восприимчивости — естественный, отчасти непредсказуемый аспект человеческого существования, а не повод для морального упрёка (как в случае с Дарвином). В сноске Уилсон отмечает иронию: в другой своей работе («Talks to Teachers on Psychology») сам Джеймс упрекал Дарвина за «неподходящие привычки», проявив то же морализаторство, которое сам же здесь и разоблачает.</t>
         </is>
       </c>
-      <c r="X39" s="14" t="inlineStr">
+      <c r="Y39" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y39" s="14" t="inlineStr">
+      <c r="Z39" s="14" t="inlineStr">
         <is>
           <t>chapter_2_ii</t>
         </is>
       </c>
-      <c r="Z39" s="14" t="inlineStr">
+      <c r="AA39" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/william-james</t>
         </is>
       </c>
-      <c r="AA39" s="14" t="inlineStr">
+      <c r="AB39" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB39" s="14" t="n"/>
+      <c r="AC39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -4817,83 +4928,84 @@
           <t>1923-02-08</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>Рок-Холл близ Алника, Нортумберленд, Англия</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>55.4500, -1.7000</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="K40" s="14" t="inlineStr">
         <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="K40" s="14" t="inlineStr">
+      <c r="L40" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="L40" s="14" t="inlineStr">
+      <c r="M40" s="14" t="inlineStr">
         <is>
           <t>Баллиол-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M40" s="14" t="inlineStr">
+      <c r="N40" s="14" t="inlineStr">
         <is>
           <t>Университетский колледж, Оксфорд; Сент-Эндрюсский университет</t>
         </is>
       </c>
-      <c r="N40" s="14" t="n"/>
       <c r="O40" s="14" t="n"/>
       <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
-      <c r="R40" s="14" t="inlineStr">
+      <c r="R40" s="14" t="n"/>
+      <c r="S40" s="14" t="inlineStr">
         <is>
           <t>абсолютный идеализм; эстетика; логика</t>
         </is>
       </c>
-      <c r="S40" s="14" t="inlineStr">
+      <c r="T40" s="14" t="inlineStr">
         <is>
           <t>Английский философ, представитель британского абсолютного идеализма. Автор The Essentials of Logic, откуда Уилсон цитирует формулу о «мире как идее».</t>
         </is>
       </c>
-      <c r="T40" s="14" t="inlineStr">
+      <c r="U40" s="14" t="inlineStr">
         <is>
           <t>- Bernard Bosanquet, The Essentials of Logic, p. 6 - «Мир как идея» - Партиципативный идеализм - Амфиболизм</t>
         </is>
       </c>
-      <c r="U40" s="14" t="n"/>
       <c r="V40" s="14" t="n"/>
-      <c r="W40" s="14" t="inlineStr">
+      <c r="W40" s="14" t="n"/>
+      <c r="X40" s="14" t="inlineStr">
         <is>
           <t>Бозанкет представляет самую сильную форму амфиболизма — партиципативный идеализм. Мир, общий для всех людей, в этой формулировке существует для каждого как нечто созданное в его собственном уме, связанном с собственным телом.</t>
         </is>
       </c>
-      <c r="X40" s="14" t="inlineStr">
+      <c r="Y40" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y40" s="14" t="inlineStr">
+      <c r="Z40" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z40" s="14" t="inlineStr">
+      <c r="AA40" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/bernard-bosanquet</t>
         </is>
       </c>
-      <c r="AA40" s="14" t="inlineStr">
+      <c r="AB40" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB40" s="14" t="n"/>
+      <c r="AC40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -4931,91 +5043,92 @@
           <t>1925-07-26</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>Висмар, Мекленбург</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="J41" s="14" t="inlineStr">
         <is>
           <t>53.8913, 11.4650</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="K41" s="14" t="inlineStr">
         <is>
           <t>Бад-Кляйнен, Мекленбург</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr">
+      <c r="L41" s="14" t="inlineStr">
         <is>
           <t>53.7700, 11.4700</t>
         </is>
       </c>
-      <c r="L41" s="14" t="inlineStr">
+      <c r="M41" s="14" t="inlineStr">
         <is>
           <t>Йенский университет; Гёттингенский университет</t>
         </is>
       </c>
-      <c r="M41" s="14" t="inlineStr">
+      <c r="N41" s="14" t="inlineStr">
         <is>
           <t>Йенский университет</t>
         </is>
       </c>
-      <c r="N41" s="14" t="n"/>
       <c r="O41" s="14" t="n"/>
-      <c r="P41" s="14" t="inlineStr">
+      <c r="P41" s="14" t="n"/>
+      <c r="Q41" s="14" t="inlineStr">
         <is>
           <t>Бертран Рассел; Людвиг Витгенштейн</t>
         </is>
       </c>
-      <c r="Q41" s="14" t="n"/>
-      <c r="R41" s="14" t="inlineStr">
+      <c r="R41" s="14" t="n"/>
+      <c r="S41" s="14" t="inlineStr">
         <is>
           <t>логика; философия математики; философия языка</t>
         </is>
       </c>
-      <c r="S41" s="14" t="inlineStr">
+      <c r="T41" s="14" t="inlineStr">
         <is>
           <t>Немецкий философ и логик XIX века, один из главных основоположников современной логики и аналитической традиции в философии. Автор «понятийного письма» (Begriffsschrift) — формальной логической системы, предвосхитившей современную символическую логику, различения смысла и значения (Sinn/Bedeutung), значительных работ в философии математики и логицизме.</t>
         </is>
       </c>
-      <c r="T41" s="14" t="inlineStr">
+      <c r="U41" s="14" t="inlineStr">
         <is>
           <t>- Учение о «третьей сфере» существования концепций/мыслей — из эссе «Мысль» («Der Gedanke», 1918), канонического источника этой доктрины у Фреге. -</t>
         </is>
       </c>
-      <c r="U41" s="14" t="inlineStr">
+      <c r="V41" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/frege/</t>
         </is>
       </c>
-      <c r="V41" s="14" t="n"/>
-      <c r="W41" s="14" t="inlineStr">
+      <c r="W41" s="14" t="n"/>
+      <c r="X41" s="14" t="inlineStr">
         <is>
           <t>Введён как фигура, с которой ассоциируется представление о гипотетической «третьей сфере» существования — не ментальной и не физической, — где, как считается, находится весь возможный запас концепций и мыслей. Уилсон явно отказывается от онтологического спора вокруг этого образа и предлагает прочитать содержательное ядро идеи Фреге на обычном языке — так рождается его термин klassicheskaya-kartina-kontseptsiy. Примечательно: хотя автор признаётся, что часто цитирует Фреге на протяжении книги, он прямо говорит, что более чистым представителем классической картины считает не его, а bertrand-russell — потому что у Фреге слишком много «эксцентричных» взглядов, не относящихся напрямую к обсуждаемой теме.</t>
         </is>
       </c>
-      <c r="X41" s="14" t="inlineStr">
+      <c r="Y41" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 3</t>
         </is>
       </c>
-      <c r="Y41" s="14" t="inlineStr">
+      <c r="Z41" s="14" t="inlineStr">
         <is>
           <t>chapter_1_ii; chapter_3_ii</t>
         </is>
       </c>
-      <c r="Z41" s="14" t="inlineStr">
+      <c r="AA41" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/gottlob-frege</t>
         </is>
       </c>
-      <c r="AA41" s="14" t="inlineStr">
+      <c r="AB41" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB41" s="14" t="n"/>
+      <c r="AC41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -5053,83 +5166,84 @@
           <t>1925-02-03</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="inlineStr">
         <is>
           <t>Кэмден-Таун, Лондон</t>
         </is>
       </c>
-      <c r="I42" s="14" t="inlineStr">
+      <c r="J42" s="14" t="inlineStr">
         <is>
           <t>51.5390, -0.1426</t>
         </is>
       </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="K42" s="14" t="inlineStr">
         <is>
           <t>Торки, Девон, Англия</t>
         </is>
       </c>
-      <c r="K42" s="14" t="inlineStr">
+      <c r="L42" s="14" t="inlineStr">
         <is>
           <t>50.4619, -3.5253</t>
         </is>
       </c>
-      <c r="L42" s="14" t="inlineStr">
+      <c r="M42" s="14" t="inlineStr">
         <is>
           <t>самоучка</t>
         </is>
       </c>
-      <c r="M42" s="14" t="n"/>
       <c r="N42" s="14" t="n"/>
       <c r="O42" s="14" t="n"/>
       <c r="P42" s="14" t="n"/>
-      <c r="Q42" s="14" t="inlineStr">
+      <c r="Q42" s="14" t="n"/>
+      <c r="R42" s="14" t="inlineStr">
         <is>
           <t>Медаль Фарадея (1922, первый лауреат)</t>
         </is>
       </c>
-      <c r="R42" s="14" t="inlineStr">
+      <c r="S42" s="14" t="inlineStr">
         <is>
           <t>электротехника; операционное исчисление; электродинамика</t>
         </is>
       </c>
-      <c r="S42" s="14" t="inlineStr">
+      <c r="T42" s="14" t="inlineStr">
         <is>
           <t>Английский физик-самоучка, математик и инженер-электрик. Не имел формального университетского образования, но переформулировал уравнения Максвелла в привычном сегодня векторном виде, разработал операционное исчисление, ввёл в обиход термины «импеданс», «индуктивность», «проводимость», предсказал существование ионосферы (позже названной слоем Хевисайда).</t>
         </is>
       </c>
-      <c r="T42" s="14" t="inlineStr">
+      <c r="U42" s="14" t="inlineStr">
         <is>
           <t>- Операционное исчисление (operational calculus) — метод, которым Хевисайд пользовался без строгого математического обоснования, что вызвало споры с академическими математиками его времени - Векторная переформулировка уравнений Максвелла - Телеграфные уравнения (theory of transmission lines)</t>
         </is>
       </c>
-      <c r="U42" s="14" t="n"/>
       <c r="V42" s="14" t="n"/>
-      <c r="W42" s="14" t="inlineStr">
+      <c r="W42" s="14" t="n"/>
+      <c r="X42" s="14" t="inlineStr">
         <is>
           <t>Вторая ключевая фигура после Куайна, упомянутая уже в предисловии. Уилсон ссылается на него в контексте собственного проекта «Классическая механика сто лет спустя», нацеленного на то, чтобы проследить эволюцию значений базовых понятий классической физики. Для Уилсона Хевисайд — пример практика, который самозабвенно боролся с теоретическими догмами через саму практику, а не через формальное философское обоснование — то есть иллюстрация того, что понятия могут развиваться и уточняться «снизу», в ходе инженерной и вычислительной работы, опережая их строгое теоретическое осмысление.</t>
         </is>
       </c>
-      <c r="X42" s="14" t="inlineStr">
+      <c r="Y42" s="14" t="inlineStr">
         <is>
           <t>предисловие; гл. 3</t>
         </is>
       </c>
-      <c r="Y42" s="14" t="inlineStr">
+      <c r="Z42" s="14" t="inlineStr">
         <is>
           <t>chapter_3_v; predislovie</t>
         </is>
       </c>
-      <c r="Z42" s="14" t="inlineStr">
+      <c r="AA42" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/oliver-heaviside</t>
         </is>
       </c>
-      <c r="AA42" s="14" t="inlineStr">
+      <c r="AB42" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB42" s="14" t="n"/>
+      <c r="AC42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -5169,85 +5283,90 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
+          <t>гранулематоз с полиангиитом (предположительно)</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
           <t>Гамбург</t>
         </is>
       </c>
-      <c r="I43" s="14" t="inlineStr">
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>53.5511, 9.9937</t>
         </is>
       </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="K43" s="14" t="inlineStr">
         <is>
           <t>Бонн</t>
         </is>
       </c>
-      <c r="K43" s="14" t="inlineStr">
+      <c r="L43" s="14" t="inlineStr">
         <is>
           <t>50.7374, 7.0982</t>
         </is>
       </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="M43" s="14" t="inlineStr">
         <is>
           <t>Берлинский университет</t>
         </is>
       </c>
-      <c r="M43" s="14" t="inlineStr">
+      <c r="N43" s="14" t="inlineStr">
         <is>
           <t>Кильский университет; Политехникум Карлсруэ; Боннский университет</t>
         </is>
       </c>
-      <c r="N43" s="14" t="inlineStr">
+      <c r="O43" s="14" t="inlineStr">
         <is>
           <t>Герман фон Гельмгольц</t>
         </is>
       </c>
-      <c r="O43" s="14" t="n"/>
       <c r="P43" s="14" t="n"/>
       <c r="Q43" s="14" t="n"/>
-      <c r="R43" s="14" t="inlineStr">
+      <c r="R43" s="14" t="n"/>
+      <c r="S43" s="14" t="inlineStr">
         <is>
           <t>физика; электродинамика; механика</t>
         </is>
       </c>
-      <c r="S43" s="14" t="inlineStr">
+      <c r="T43" s="14" t="inlineStr">
         <is>
           <t>Немецкий физик, экспериментально подтвердивший существование электромагнитных волн, предсказанных теорией Максвелла (1886–1889) — единица частоты названа в его честь. В конце жизни написал философски значимый труд «Die Prinzipien der Mechanik» («Принципы механики», опубликован посмертно в 1894 году), где предложил переформулировать классическую механику без понятия силы как примитивного, взяв вместо этого за основу массу, пространство и время — и явно оговорил, что физические теории следует оценивать не как «истинные копии» реальности, а как более или менее «допустимые», «правильные» и «целесообразные» изображения (zulässige, richtige, zweckmäßige Bilder).</t>
         </is>
       </c>
-      <c r="T43" s="14" t="inlineStr">
+      <c r="U43" s="14" t="inlineStr">
         <is>
           <t>- «Die Prinzipien der Mechanik» (1894) — переформулировка механики без силы как примитивного понятия, концепция теорий как «допустимых изображений» (zulässige Bilder)</t>
         </is>
       </c>
-      <c r="U43" s="14" t="n"/>
       <c r="V43" s="14" t="n"/>
-      <c r="W43" s="14" t="inlineStr">
+      <c r="W43" s="14" t="n"/>
+      <c r="X43" s="14" t="inlineStr">
         <is>
           <t>Назван вместе с Гельмгольцем как пример раннего, «сдержанного» холизма XIX века — умеренного отступления от классической ортодоксии, в противовес позднейшим крайним формам (кунианизм, пост-структурализм). (Гипотеза, требует проверки): учитывая, что вся книга Уилсона посвящена именно понятиям классической механики и их «блужданию», герцевская идея теорий-как-допустимых-изображений (Bilder) — вероятно, не случайное совпадение, а содержательно значимая точка соприкосновения, которая может всплыть в других главах книги, посвящённых механике напрямую.</t>
         </is>
       </c>
-      <c r="X43" s="14" t="inlineStr">
+      <c r="Y43" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y43" s="14" t="inlineStr">
+      <c r="Z43" s="14" t="inlineStr">
         <is>
           <t>chapter_1_ix</t>
         </is>
       </c>
-      <c r="Z43" s="14" t="inlineStr">
+      <c r="AA43" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/heinrich-hertz</t>
         </is>
       </c>
-      <c r="AA43" s="14" t="inlineStr">
+      <c r="AB43" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB43" s="14" t="n"/>
+      <c r="AC43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -5287,85 +5406,90 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
+          <t>пневмония</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
           <t>Берлингтон, Вермонт, США</t>
         </is>
       </c>
-      <c r="I44" s="14" t="inlineStr">
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>44.4759, -73.2121</t>
         </is>
       </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="K44" s="14" t="inlineStr">
         <is>
           <t>Нью-Йорк, США</t>
         </is>
       </c>
-      <c r="K44" s="14" t="inlineStr">
+      <c r="L44" s="14" t="inlineStr">
         <is>
           <t>40.7128, -74.0060</t>
         </is>
       </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="M44" s="14" t="inlineStr">
         <is>
           <t>Вермонтский университет; Университет Джонса Хопкинса</t>
         </is>
       </c>
-      <c r="M44" s="14" t="inlineStr">
+      <c r="N44" s="14" t="inlineStr">
         <is>
           <t>Чикагский университет; Колумбийский университет</t>
         </is>
       </c>
-      <c r="N44" s="14" t="n"/>
       <c r="O44" s="14" t="n"/>
       <c r="P44" s="14" t="n"/>
       <c r="Q44" s="14" t="n"/>
-      <c r="R44" s="14" t="inlineStr">
+      <c r="R44" s="14" t="n"/>
+      <c r="S44" s="14" t="inlineStr">
         <is>
           <t>прагматизм; философия образования; эпистемология</t>
         </is>
       </c>
-      <c r="S44" s="14" t="inlineStr">
+      <c r="T44" s="14" t="inlineStr">
         <is>
           <t>Американский философ, психолог и реформатор образования, один из центральных представителей американского прагматизма (наряду с Пирсом и Джеймсом). Автор работ по логике как теории исследования, философии опыта и природы, а также обширных трудов по реформе образования.</t>
         </is>
       </c>
-      <c r="T44" s="14" t="inlineStr">
+      <c r="U44" s="14" t="inlineStr">
         <is>
           <t>John Dewey, Logic: The Theory of Inquiry (New York: Holt, Rinehart and Win- ston, 1938).</t>
         </is>
       </c>
-      <c r="U44" s="14" t="inlineStr">
+      <c r="V44" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/dewey/</t>
         </is>
       </c>
-      <c r="V44" s="14" t="n"/>
-      <c r="W44" s="14" t="inlineStr">
+      <c r="W44" s="14" t="n"/>
+      <c r="X44" s="14" t="inlineStr">
         <is>
           <t>(пока минимальный текстовой материал) Упомянут вскользь, одним именем, в пункте (11) подраздела (iii) — как более ранний мыслитель, независимо от Витгенштейна обеспокоенный «полным классическим попурри» в отношении концепций. То есть назван как ещё один, отдельный от витгенштейновской линии, источник скепсиса по отношению к klassicheskaya-kartina-kontseptsiy. Никаких конкретных работ или тезисов Дьюи не названо.</t>
         </is>
       </c>
-      <c r="X44" s="14" t="inlineStr">
+      <c r="Y44" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 2; гл. 3</t>
         </is>
       </c>
-      <c r="Y44" s="14" t="inlineStr">
+      <c r="Z44" s="14" t="inlineStr">
         <is>
           <t>chapter_1_iv; chapter_2_iv; chapter_3_ii</t>
         </is>
       </c>
-      <c r="Z44" s="14" t="inlineStr">
+      <c r="AA44" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/john-dewey</t>
         </is>
       </c>
-      <c r="AA44" s="14" t="inlineStr">
+      <c r="AB44" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB44" s="14" t="n"/>
+      <c r="AC44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -5399,91 +5523,92 @@
           <t>1947-12-30</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>Рамсгит, Англия</t>
         </is>
       </c>
-      <c r="I45" s="14" t="inlineStr">
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>51.3350, 1.4190</t>
         </is>
       </c>
-      <c r="J45" s="14" t="inlineStr">
+      <c r="K45" s="14" t="inlineStr">
         <is>
           <t>Кембридж, Массачусетс, США</t>
         </is>
       </c>
-      <c r="K45" s="14" t="inlineStr">
+      <c r="L45" s="14" t="inlineStr">
         <is>
           <t>42.3736, -71.1097</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="M45" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr">
+      <c r="N45" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж; Имперский колледж, Лондон; Гарвардский университет</t>
         </is>
       </c>
-      <c r="N45" s="14" t="n"/>
-      <c r="O45" s="14" t="inlineStr">
+      <c r="O45" s="14" t="n"/>
+      <c r="P45" s="14" t="inlineStr">
         <is>
           <t>Бертран Рассел; Уиллард Куайн</t>
         </is>
       </c>
-      <c r="P45" s="14" t="n"/>
       <c r="Q45" s="14" t="n"/>
-      <c r="R45" s="14" t="inlineStr">
+      <c r="R45" s="14" t="n"/>
+      <c r="S45" s="14" t="inlineStr">
         <is>
           <t>математика; логика; философия процесса</t>
         </is>
       </c>
-      <c r="S45" s="14" t="inlineStr">
+      <c r="T45" s="14" t="inlineStr">
         <is>
           <t>Английский математик и философ, один из создателей процессуальной философии.</t>
         </is>
       </c>
-      <c r="T45" s="14" t="inlineStr">
+      <c r="U45" s="14" t="inlineStr">
         <is>
           <t>- Alfred North Whitehead, The Concept of Nature, p. 29 - Научная абстракция - Природа - Геометризация физических объектов</t>
         </is>
       </c>
-      <c r="U45" s="14" t="inlineStr">
+      <c r="V45" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/whitehead/</t>
         </is>
       </c>
-      <c r="V45" s="14" t="n"/>
-      <c r="W45" s="14" t="inlineStr">
+      <c r="W45" s="14" t="n"/>
+      <c r="X45" s="14" t="inlineStr">
         <is>
           <t>Уайтхед используется как источник мысли о том, что научное описание неизбежно выбирает определённые аспекты природы. Физико-геометрическая схема может быть исключительно полезной, но это не делает её полным описанием всех свойств реально существующего мира.</t>
         </is>
       </c>
-      <c r="X45" s="14" t="inlineStr">
+      <c r="Y45" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y45" s="14" t="inlineStr">
+      <c r="Z45" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z45" s="14" t="inlineStr">
+      <c r="AA45" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/alfred-north-whitehead</t>
         </is>
       </c>
-      <c r="AA45" s="14" t="inlineStr">
+      <c r="AB45" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB45" s="14" t="n"/>
+      <c r="AC45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -5523,85 +5648,90 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
+          <t>сердечный приступ</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
           <t>Париж</t>
         </is>
       </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>48.8566, 2.3522</t>
         </is>
       </c>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="K46" s="14" t="inlineStr">
         <is>
           <t>Кабреспин, Франция</t>
         </is>
       </c>
-      <c r="K46" s="14" t="inlineStr">
+      <c r="L46" s="14" t="inlineStr">
         <is>
           <t>43.3700, 2.4500</t>
         </is>
       </c>
-      <c r="L46" s="14" t="inlineStr">
+      <c r="M46" s="14" t="inlineStr">
         <is>
           <t>Высшая нормальная школа</t>
         </is>
       </c>
-      <c r="M46" s="14" t="inlineStr">
+      <c r="N46" s="14" t="inlineStr">
         <is>
           <t>Лилльский университет; Реннский университет; Университет Бордо</t>
         </is>
       </c>
-      <c r="N46" s="14" t="n"/>
       <c r="O46" s="14" t="n"/>
       <c r="P46" s="14" t="n"/>
       <c r="Q46" s="14" t="n"/>
-      <c r="R46" s="14" t="inlineStr">
+      <c r="R46" s="14" t="n"/>
+      <c r="S46" s="14" t="inlineStr">
         <is>
           <t>термодинамика; философия науки; история науки</t>
         </is>
       </c>
-      <c r="S46" s="14" t="inlineStr">
+      <c r="T46" s="14" t="inlineStr">
         <is>
           <t>Французский физик (термодинамика), историк и философ науки. В книге «Физическая теория, её цель и строение» (1906) показал, что гипотезу нельзя проверить изолированно — только вместе с вспомогательными допущениями (позже — тезис Дюэма–Куайна). Открыл для истории науки средневековую физику.</t>
         </is>
       </c>
-      <c r="T46" s="14" t="inlineStr">
+      <c r="U46" s="14" t="inlineStr">
         <is>
           <t>- Тезис о холизме проверки (Дюэма–Куайна) — у Уилсона в этом месте не назван, но ср. willard-quine.</t>
         </is>
       </c>
-      <c r="U46" s="14" t="inlineStr">
+      <c r="V46" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/duhem/</t>
         </is>
       </c>
-      <c r="V46" s="14" t="n"/>
-      <c r="W46" s="14" t="inlineStr">
+      <c r="W46" s="14" t="n"/>
+      <c r="X46" s="14" t="inlineStr">
         <is>
           <t>Вместе с Махом и другими учёными 1880–1910 гг. Дюгем утверждал, что прогрессу физики мешает приверженность «тёплым и нечётким» требованиям к объяснению, сходным с бойлевскими (ср. robert-boyle). Именно на этом выражение «теоретическое содержание» впервые приобрело философское значение: как способ сказать, что науке не нужны «тёплые и нечёткие» качества в объяснениях. Уилсон признаёт, что «в своём критическом чутье Мах и Дюгем часто оказывались правы», но «как специалисты по семантической диагностике они перестарались» (с. 166).</t>
         </is>
       </c>
-      <c r="X46" s="14" t="inlineStr">
+      <c r="Y46" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y46" s="14" t="inlineStr">
+      <c r="Z46" s="14" t="inlineStr">
         <is>
           <t>chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z46" s="14" t="inlineStr">
+      <c r="AA46" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/pierre-duhem</t>
         </is>
       </c>
-      <c r="AA46" s="14" t="inlineStr">
+      <c r="AB46" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB46" s="14" t="n"/>
+      <c r="AC46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -5639,83 +5769,84 @@
           <t>1963-10-17</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H47" s="14" t="n"/>
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Версаль, Франция</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>48.8049, 2.1204</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="K47" s="14" t="inlineStr">
         <is>
           <t>Париж</t>
         </is>
       </c>
-      <c r="K47" s="14" t="inlineStr">
+      <c r="L47" s="14" t="inlineStr">
         <is>
           <t>48.8566, 2.3522</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
+      <c r="M47" s="14" t="inlineStr">
         <is>
           <t>Высшая нормальная школа</t>
         </is>
       </c>
-      <c r="M47" s="14" t="inlineStr">
+      <c r="N47" s="14" t="inlineStr">
         <is>
           <t>Коллеж де Франс; Политехническая школа; Парижский университет</t>
         </is>
       </c>
-      <c r="N47" s="14" t="n"/>
       <c r="O47" s="14" t="n"/>
       <c r="P47" s="14" t="n"/>
       <c r="Q47" s="14" t="n"/>
-      <c r="R47" s="14" t="inlineStr">
+      <c r="R47" s="14" t="n"/>
+      <c r="S47" s="14" t="inlineStr">
         <is>
           <t>математический анализ; теория чисел; дифференциальные уравнения</t>
         </is>
       </c>
-      <c r="S47" s="14" t="inlineStr">
+      <c r="T47" s="14" t="inlineStr">
         <is>
           <t>Французский математик, один из крупнейших математиков рубежа XIX–XX веков. Доказал теорему о распределении простых чисел (1896, независимо от де ла Валле-Пуссена), внёс фундаментальный вклад в комплексный анализ, теорию дифференциальных уравнений в частных производных и вариационное исчисление. Ввёл понятие «корректно поставленной задачи» (well-posed problem) — задачи, для которой решение существует, единственно и непрерывно зависит от исходных данных; это понятие стало основополагающим для математической физики. Также автор известной работы о психологии математического творчества («Психология изобретения в области математики»).</t>
         </is>
       </c>
-      <c r="T47" s="14" t="inlineStr">
+      <c r="U47" s="14" t="inlineStr">
         <is>
           <t>- Понятие «корректно поставленной задачи» (well-posed problem) — существование, единственность и устойчивость решения относительно исходных данных - Практика исследования моделей как семейств условий (начальные/граничные значения), а не изолированных случаев</t>
         </is>
       </c>
-      <c r="U47" s="14" t="n"/>
       <c r="V47" s="14" t="n"/>
-      <c r="W47" s="14" t="inlineStr">
+      <c r="W47" s="14" t="n"/>
+      <c r="X47" s="14" t="inlineStr">
         <is>
           <t>Указан Уилсоном в предисловии наравне с Хевисайдом и Рёло как один из авторов, чьим трудам он «особенно обязан» — трое инженеров и прикладных математиков второй половины XIX века, чьи замечания о концептуальной неоднозначности вдохновили общий замысел книги: демонстрация того, что понятия (в частности, используемые в механике) меняют своё значение при переносе в разные среды применения. Ключевая содержательная связь, судя по вторичной литературе о книге: концепция Адамара о «корректно поставленной задаче» — идея, что прикладные математики работают не с единичным случаем, а с целым семейством условий, варьируемых по начальным и граничным значениям — используется Уилсоном как модель того, как понятия должны пониматься через диапазон применения, а не через одно фиксированное значение. Это прямо перекликается с центральной темой книги — blujdayushee-kachestvo.</t>
         </is>
       </c>
-      <c r="X47" s="14" t="inlineStr">
+      <c r="Y47" s="14" t="inlineStr">
         <is>
           <t>предисловие</t>
         </is>
       </c>
-      <c r="Y47" s="14" t="inlineStr">
+      <c r="Z47" s="14" t="inlineStr">
         <is>
           <t>predislovie</t>
         </is>
       </c>
-      <c r="Z47" s="14" t="inlineStr">
+      <c r="AA47" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/jacques-hadamard</t>
         </is>
       </c>
-      <c r="AA47" s="14" t="inlineStr">
+      <c r="AB47" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB47" s="14" t="n"/>
+      <c r="AC47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -5755,77 +5886,82 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
+          <t>ожоги и шок после падения в камин</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
           <t>Ла-Сель-Сен-Клу, Франция</t>
         </is>
       </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>48.8500, 2.1300</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="K48" s="14" t="inlineStr">
         <is>
           <t>Гилфорд, Англия</t>
         </is>
       </c>
-      <c r="K48" s="14" t="inlineStr">
+      <c r="L48" s="14" t="inlineStr">
         <is>
           <t>51.2362, -0.5704</t>
         </is>
       </c>
-      <c r="L48" s="14" t="inlineStr">
+      <c r="M48" s="14" t="inlineStr">
         <is>
           <t>Баллиол-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M48" s="14" t="n"/>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n"/>
       <c r="P48" s="14" t="n"/>
       <c r="Q48" s="14" t="n"/>
-      <c r="R48" s="14" t="inlineStr">
+      <c r="R48" s="14" t="n"/>
+      <c r="S48" s="14" t="inlineStr">
         <is>
           <t>поэзия; эссеистика; история</t>
         </is>
       </c>
-      <c r="S48" s="14" t="inlineStr">
+      <c r="T48" s="14" t="inlineStr">
         <is>
           <t>Англо-французский писатель, поэт, эссеист, историк и политик (член парламента от Солфорда, 1906–1910), близкий друг и соавтор Г. К. Честертона. Наиболее известен циклом иронично-нравоучительных детских стихов «Cautionary Tales for Children» и родственными сборниками вроде «Cautionary Verses» — сатирическими баснями о детях, которых постигает нелепая, преувеличенно жестокая кара за шалости.</t>
         </is>
       </c>
-      <c r="T48" s="14" t="inlineStr">
+      <c r="U48" s="14" t="inlineStr">
         <is>
           <t>- Hilaire Belloc, «Jim, Who Ran Away from his Nurse, and was Eaten by a Lion», в сб. «Cautionary Verses» (New York: Alfred A. Knopf, 1976), 12.</t>
         </is>
       </c>
-      <c r="U48" s="14" t="n"/>
       <c r="V48" s="14" t="n"/>
-      <c r="W48" s="14" t="inlineStr">
+      <c r="W48" s="14" t="n"/>
+      <c r="X48" s="14" t="inlineStr">
         <is>
           <t>Процитировано двустишие из стихотворения «Jim, Who Ran Away from His Nurse, and Was Eaten by a Lion» («Джим, который сбежал от няни и был съеден львом», сб. «Cautionary Verses», 1976): совет «всегда держись близ медсестры / из страха встрять во что похуже». Уилсон приводит эти строки иронически — как образ психологии чрезмерной осторожности, к которой сводится один из возможных ответов на дилемму «классицизм vs. дикие анти-классические крайности»: если единственная альтернатива классическому мышлению — кунианизм и пост-структурализм, разумнее держаться классицизма из страха перед худшим. Уилсон сразу же дистанцируется от такой позиции, называя собственную оценку анти-классицизма «значительно более сдержанной».</t>
         </is>
       </c>
-      <c r="X48" s="14" t="inlineStr">
+      <c r="Y48" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y48" s="14" t="inlineStr">
+      <c r="Z48" s="14" t="inlineStr">
         <is>
           <t>chapter_1_ix</t>
         </is>
       </c>
-      <c r="Z48" s="14" t="inlineStr">
+      <c r="AA48" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/hilaire-belloc</t>
         </is>
       </c>
-      <c r="AA48" s="14" t="inlineStr">
+      <c r="AB48" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB48" s="14" t="n"/>
+      <c r="AC48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -5865,101 +6001,106 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
+          <t>грипп</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
           <t>Треллек, Уэльс</t>
         </is>
       </c>
-      <c r="I49" s="14" t="inlineStr">
+      <c r="J49" s="14" t="inlineStr">
         <is>
           <t>51.7500, -2.7800</t>
         </is>
       </c>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="K49" s="14" t="inlineStr">
         <is>
           <t>Пенриндейдрайт, Уэльс</t>
         </is>
       </c>
-      <c r="K49" s="14" t="inlineStr">
+      <c r="L49" s="14" t="inlineStr">
         <is>
           <t>52.9300, -4.0700</t>
         </is>
       </c>
-      <c r="L49" s="14" t="inlineStr">
+      <c r="M49" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M49" s="14" t="inlineStr">
+      <c r="N49" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж; Чикагский университет; Калифорнийский университет в Лос-Анджелесе</t>
         </is>
       </c>
-      <c r="N49" s="14" t="inlineStr">
+      <c r="O49" s="14" t="inlineStr">
         <is>
           <t>Альфред Норт Уайтхед</t>
         </is>
       </c>
-      <c r="O49" s="14" t="inlineStr">
+      <c r="P49" s="14" t="inlineStr">
         <is>
           <t>Людвиг Витгенштейн</t>
         </is>
       </c>
-      <c r="P49" s="14" t="inlineStr">
+      <c r="Q49" s="14" t="inlineStr">
         <is>
           <t>Готлоб Фреге; Годфри Харольд Харди</t>
         </is>
       </c>
-      <c r="Q49" s="14" t="inlineStr">
+      <c r="R49" s="14" t="inlineStr">
         <is>
           <t>Нобелевская премия по литературе (1950)</t>
         </is>
       </c>
-      <c r="R49" s="14" t="inlineStr">
+      <c r="S49" s="14" t="inlineStr">
         <is>
           <t>математическая логика; аналитическая философия; эпистемология</t>
         </is>
       </c>
-      <c r="S49" s="14" t="inlineStr">
+      <c r="T49" s="14" t="inlineStr">
         <is>
           <t>Британский философ, логик и математик, один из основателей аналитической философии. Соавтор (вместе с Уайтхедом) «Principia Mathematica» — попытки свести математику к логике. Автор теории дескрипций, логического атомизма; лауреат Нобелевской премии по литературе (1950).</t>
         </is>
       </c>
-      <c r="T49" s="14" t="inlineStr">
+      <c r="U49" s="14" t="inlineStr">
         <is>
           <t>- Логический атомизм / программа сведения математики к логике («Principia Mathematica») - «Проблемы философии» (The Problems of Philosophy, 1912) — основной каркас для систематизации klassicheskaya-kartina-kontseptsiy, см. отдельную карточку problemy-filosofii-1912</t>
         </is>
       </c>
-      <c r="U49" s="14" t="inlineStr">
+      <c r="V49" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/russell/</t>
         </is>
       </c>
-      <c r="V49" s="14" t="n"/>
-      <c r="W49" s="14" t="inlineStr">
+      <c r="W49" s="14" t="n"/>
+      <c r="X49" s="14" t="inlineStr">
         <is>
           <t>Уилсон прямо пишет в предисловии, что на философской стороне Рассел и Куайн долгое время служили для него «опорами», между которыми он старался прокладывать курс в вопросах, касающихся концепций, предикатов и работы с понятиями (см. также willard-quine — второй полюс той же пары). Гораздо более весомая роль обнаружилась в главе 1. Хотя Уилсон чаще цитирует Фреге (см. gottlob-frege), он прямо заявляет, что именно Рассел — более чистый, показательный представитель того, что он называет klassicheskaya-kartina-kontseptsiy («классическая картина концепций»): у Фреге слишком много «эксцентричных» побочных взглядов, а Рассел даёт более чистый случай. Работа «Проблемы философии» (1912) названа «основным каркасом», из которого Уилсон выводит систематизированный список тезисов классической картины (полностью — в приложении к главе 3, см. problemy-filosofii-1912).</t>
         </is>
       </c>
-      <c r="X49" s="14" t="inlineStr">
+      <c r="Y49" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 2; гл. 3</t>
         </is>
       </c>
-      <c r="Y49" s="14" t="inlineStr">
+      <c r="Z49" s="14" t="inlineStr">
         <is>
           <t>chapter_1_ii; chapter_2_vi; chapter_3_iii</t>
         </is>
       </c>
-      <c r="Z49" s="14" t="inlineStr">
+      <c r="AA49" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/bertrand-russell</t>
         </is>
       </c>
-      <c r="AA49" s="14" t="inlineStr">
+      <c r="AB49" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB49" s="14" t="n"/>
+      <c r="AC49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
@@ -5997,87 +6138,88 @@
           <t>1947-12-01</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H50" s="14" t="n"/>
+      <c r="I50" s="14" t="inlineStr">
         <is>
           <t>Кранли, Суррей, Англия</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>51.1410, -0.4880</t>
         </is>
       </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="K50" s="14" t="inlineStr">
         <is>
           <t>Кембридж, Англия</t>
         </is>
       </c>
-      <c r="K50" s="14" t="inlineStr">
+      <c r="L50" s="14" t="inlineStr">
         <is>
           <t>52.2053, 0.1218</t>
         </is>
       </c>
-      <c r="L50" s="14" t="inlineStr">
+      <c r="M50" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M50" s="14" t="inlineStr">
+      <c r="N50" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж; Нью-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
-      <c r="P50" s="14" t="inlineStr">
+      <c r="P50" s="14" t="n"/>
+      <c r="Q50" s="14" t="inlineStr">
         <is>
           <t>Бертран Рассел</t>
         </is>
       </c>
-      <c r="Q50" s="14" t="n"/>
-      <c r="R50" s="14" t="inlineStr">
+      <c r="R50" s="14" t="n"/>
+      <c r="S50" s="14" t="inlineStr">
         <is>
           <t>теория чисел; математический анализ</t>
         </is>
       </c>
-      <c r="S50" s="14" t="inlineStr">
+      <c r="T50" s="14" t="inlineStr">
         <is>
           <t>Английский математик (1877–1947), работал в Кембридже в области теории чисел и анализа. Автор книги «Divergent Series» (Oxford, 1949, вышла посмертно), посвящённой методам суммирования расходящихся рядов. Уилсон представляет его как друга Рассела.</t>
         </is>
       </c>
-      <c r="T50" s="14" t="inlineStr">
+      <c r="U50" s="14" t="inlineStr">
         <is>
           <t>- G. H. Hardy, Divergent Series (Oxford UP, 1949), с. 5–6 - Определение суммы ряда как задача выбора, а не открытия</t>
         </is>
       </c>
-      <c r="U50" s="14" t="n"/>
       <c r="V50" s="14" t="n"/>
-      <c r="W50" s="14" t="inlineStr">
+      <c r="W50" s="14" t="n"/>
+      <c r="X50" s="14" t="inlineStr">
         <is>
           <t>Харди служит примером «улучшения состояния ума» в математике, то есть того, как методологический совет «сначала определим термины» действительно помогает. Он даёт более широкое определение «суммы» бесконечного ряда, чем классическое определение Коши. Харди утверждает, что математики XVIII века спрашивали «что такое 1 – 1 + 1 …?», а не «как нам определить 1 – 1 + 1 …?», и потому попадали в чисто вербальные споры. Уилсон признаёт вклад Харди, но слышит в формуле «у них не было привычки давать определения» нотку незаслуженного превосходства. Его возражение: вершины, на которых стоит сам Харди, не радикально выше прежних, и его открытия так же подвержены случайностям, поскольку недоумение и противоречия остаются постоянными атрибутами человеческого положения. Уилсон сравнивает эту снисходительность с самодовольством критика из главы 2, упрекавшего Дарвина в неспособности оценить Теннисона. Кроме того, Харди, сам того не желая, расплывчат в том, что такое «установление определения». К этому Уилсон обещает вернуться в следующей главе.</t>
         </is>
       </c>
-      <c r="X50" s="14" t="inlineStr">
+      <c r="Y50" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y50" s="14" t="inlineStr">
+      <c r="Z50" s="14" t="inlineStr">
         <is>
           <t>chapter_3_iv</t>
         </is>
       </c>
-      <c r="Z50" s="14" t="inlineStr">
+      <c r="AA50" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/godfri-kharold-khardi</t>
         </is>
       </c>
-      <c r="AA50" s="14" t="inlineStr">
+      <c r="AB50" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB50" s="14" t="n"/>
+      <c r="AC50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -6117,81 +6259,86 @@
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
+          <t>последствия инсультов</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
           <t>Таскамбия, Алабама, США</t>
         </is>
       </c>
-      <c r="I51" s="14" t="inlineStr">
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>34.7309, -87.7025</t>
         </is>
       </c>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="K51" s="14" t="inlineStr">
         <is>
           <t>Истон, Коннектикут, США</t>
         </is>
       </c>
-      <c r="K51" s="14" t="inlineStr">
+      <c r="L51" s="14" t="inlineStr">
         <is>
           <t>41.2500, -73.3000</t>
         </is>
       </c>
-      <c r="L51" s="14" t="inlineStr">
+      <c r="M51" s="14" t="inlineStr">
         <is>
           <t>Рэдклифф-колледж</t>
         </is>
       </c>
-      <c r="M51" s="14" t="n"/>
       <c r="N51" s="14" t="n"/>
       <c r="O51" s="14" t="n"/>
       <c r="P51" s="14" t="n"/>
-      <c r="Q51" s="14" t="inlineStr">
+      <c r="Q51" s="14" t="n"/>
+      <c r="R51" s="14" t="inlineStr">
         <is>
           <t>Президентская медаль Свободы (1964)</t>
         </is>
       </c>
-      <c r="R51" s="14" t="inlineStr">
+      <c r="S51" s="14" t="inlineStr">
         <is>
           <t>литература; общественная деятельность</t>
         </is>
       </c>
-      <c r="S51" s="14" t="inlineStr">
+      <c r="T51" s="14" t="inlineStr">
         <is>
           <t>Американская писательница и общественный деятель, с полутора лет слепая и глухая. Научилась общаться и читать с помощью учительницы Энн Салливан, окончила Рэдклифф-колледж; автор нескольких автобиографических книг.</t>
         </is>
       </c>
-      <c r="T51" s="14" t="inlineStr">
+      <c r="U51" s="14" t="inlineStr">
         <is>
           <t>- Helen Keller, The World I Live In (New York: The Century Company, 1908), 105 — сноска 16.</t>
         </is>
       </c>
-      <c r="U51" s="14" t="n"/>
       <c r="V51" s="14" t="n"/>
-      <c r="W51" s="14" t="inlineStr">
+      <c r="W51" s="14" t="n"/>
+      <c r="X51" s="14" t="inlineStr">
         <is>
           <t>Главное «возражение» против взгляда Маха и Локка, что краснота постигается только через ощущение. Келлер утверждает, что постигает понятие красноты вопреки сенсорным ограничениям: «Я понимаю, чем отличается алый цвет от малинового, потому что знаю, что запах апельсина отличается от запаха грейпфрута… красный говорит о любви, стыде или силе» (с. 160). Уилсон видит здесь упор на инференциальную направленность «есть красный». Ортодоксия отвечает, что это лишь «структурные сопутствующие обстоятельства»: даже если бы Келлер знала физику красителей лучше нас, ей всё равно недоставало бы «основных ингредиентов» красноты (с. 161). При этом сторонники «публичной» точки зрения (ядро — согласие с классификациями сообщества) не готовы последовать её примеру: «она не может классифицировать розы и пожарные машины так же быстро и непосредственно, как остальные из нас» (с. 162). На с. 168 Уилсон сопоставляет её картину красноты с картиной твёрдости у Рида: может ли говорящий «где-то между 6 месяцами и 16 годами» незаметно сдвинуть содержание «есть красный» к такому признаку?</t>
         </is>
       </c>
-      <c r="X51" s="14" t="inlineStr">
+      <c r="Y51" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y51" s="14" t="inlineStr">
+      <c r="Z51" s="14" t="inlineStr">
         <is>
           <t>chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z51" s="14" t="inlineStr">
+      <c r="AA51" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/helen-keller</t>
         </is>
       </c>
-      <c r="AA51" s="14" t="inlineStr">
+      <c r="AB51" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB51" s="14" t="n"/>
+      <c r="AC51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
@@ -6231,85 +6378,90 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
+          <t>сердечный приступ</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
           <t>Вена, Австро-Венгрия</t>
         </is>
       </c>
-      <c r="I52" s="14" t="inlineStr">
+      <c r="J52" s="14" t="inlineStr">
         <is>
           <t>48.2082, 16.3738</t>
         </is>
       </c>
-      <c r="J52" s="14" t="inlineStr">
+      <c r="K52" s="14" t="inlineStr">
         <is>
           <t>Оксфорд, Англия</t>
         </is>
       </c>
-      <c r="K52" s="14" t="inlineStr">
+      <c r="L52" s="14" t="inlineStr">
         <is>
           <t>51.7520, -1.2577</t>
         </is>
       </c>
-      <c r="L52" s="14" t="inlineStr">
+      <c r="M52" s="14" t="inlineStr">
         <is>
           <t>Берлинский университет</t>
         </is>
       </c>
-      <c r="M52" s="14" t="inlineStr">
+      <c r="N52" s="14" t="inlineStr">
         <is>
           <t>Венский кружок; Музей общества и экономики, Вена; Институт ISOTYPE</t>
         </is>
       </c>
-      <c r="N52" s="14" t="n"/>
       <c r="O52" s="14" t="n"/>
       <c r="P52" s="14" t="n"/>
       <c r="Q52" s="14" t="n"/>
-      <c r="R52" s="14" t="inlineStr">
+      <c r="R52" s="14" t="n"/>
+      <c r="S52" s="14" t="inlineStr">
         <is>
           <t>философия науки; социология; политэкономия; визуальная статистика</t>
         </is>
       </c>
-      <c r="S52" s="14" t="inlineStr">
+      <c r="T52" s="14" t="inlineStr">
         <is>
           <t>Австрийский философ и социолог, один из ведущих участников Венского кружка (Wiener Kreis) — интеллектуального сообщества логических позитивистов, сформировавшегося в Вене в 1920–30-х годах вокруг Морица Шлика. Нейрат был одним из авторов манифеста Венского кружка «Научное миропонимание» (1929). Помимо философии науки, известен работами по политэкономии, социологии и созданию системы визуальных знаков ISOTYPE — универсального изобразительного языка для представления статистики и социальных данных, оказавшего заметное влияние на современный информационный дизайн. После аншлюса эмигрировал из Австрии, работал в Нидерландах, затем в Великобритании, где и умер в 1945 году.</t>
         </is>
       </c>
-      <c r="T52" s="14" t="inlineStr">
+      <c r="U52" s="14" t="inlineStr">
         <is>
           <t>- Метафора корабля Нейрата (в русской традиции чаще «корабль Нейрата» или «корабль Нойрата») — образ, впервые чётко сформулированный Нейратом ок. 1913 года, затем неоднократно повторённый им в статьях о протокольных предложениях и научном методе. У Уилсона фигурирует опосредованно, через цитату Куайна из Word and Object (Cambridge, Mass.: MIT Press, 1960), с. 124.</t>
         </is>
       </c>
-      <c r="U52" s="14" t="inlineStr">
+      <c r="V52" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/neurath/</t>
         </is>
       </c>
-      <c r="V52" s="14" t="n"/>
-      <c r="W52" s="14" t="inlineStr">
+      <c r="W52" s="14" t="n"/>
+      <c r="X52" s="14" t="inlineStr">
         <is>
           <t>Появляется в подразделе (vii) как автор одной из центральных методологических метафор всей книги — корабля, который приходится ремонтировать в открытом море, не сходя на берег (см. metafora-morskogo-puteshestviya). Сам Нейрат заимствовал этот образ из античной темы «корабля Тесея», а Куайн (см. willard-quine) перенял его у Нейрата и сделал одной из своих любимых философских метафор (Уилсон приводит цитату из «Word and Object», 1960, с. 124). Уилсон принимает эту метафору, но добавляет собственную мягкую оговорку: он допускает, что в конечном итоге может наступить день, когда «наш корабль будет достроен» и мы поймём, как его части подходят друг к другу, — то есть смягчает жёсткую куайновскую версию о том, что человечество навсегда обречено жить внутри незавершённого концептуального языка.</t>
         </is>
       </c>
-      <c r="X52" s="14" t="inlineStr">
+      <c r="Y52" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 3</t>
         </is>
       </c>
-      <c r="Y52" s="14" t="inlineStr">
+      <c r="Z52" s="14" t="inlineStr">
         <is>
           <t>chapter_1_vii; chapter_3_v</t>
         </is>
       </c>
-      <c r="Z52" s="14" t="inlineStr">
+      <c r="AA52" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/otto-neurath</t>
         </is>
       </c>
-      <c r="AA52" s="14" t="inlineStr">
+      <c r="AB52" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB52" s="14" t="n"/>
+      <c r="AC52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -6349,81 +6501,86 @@
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
+          <t>рак</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
           <t>Уимблдон, Лондон</t>
         </is>
       </c>
-      <c r="I53" s="14" t="inlineStr">
+      <c r="J53" s="14" t="inlineStr">
         <is>
           <t>51.4214, -0.2064</t>
         </is>
       </c>
-      <c r="J53" s="14" t="inlineStr">
+      <c r="K53" s="14" t="inlineStr">
         <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="K53" s="14" t="inlineStr">
+      <c r="L53" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="L53" s="14" t="inlineStr">
+      <c r="M53" s="14" t="inlineStr">
         <is>
           <t>Гиртон-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M53" s="14" t="inlineStr">
+      <c r="N53" s="14" t="inlineStr">
         <is>
           <t>Бедфорд-колледж, Лондонский университет</t>
         </is>
       </c>
-      <c r="N53" s="14" t="n"/>
       <c r="O53" s="14" t="n"/>
       <c r="P53" s="14" t="n"/>
       <c r="Q53" s="14" t="n"/>
-      <c r="R53" s="14" t="inlineStr">
+      <c r="R53" s="14" t="n"/>
+      <c r="S53" s="14" t="inlineStr">
         <is>
           <t>логика; аналитическая философия; критическое мышление</t>
         </is>
       </c>
-      <c r="S53" s="14" t="inlineStr">
+      <c r="T53" s="14" t="inlineStr">
         <is>
           <t>Британский философ и логик, одна из первых женщин-профессоров философии в Великобритании. Автор Philosophy and the Physicists (1937).</t>
         </is>
       </c>
-      <c r="T53" s="14" t="inlineStr">
+      <c r="U53" s="14" t="inlineStr">
         <is>
           <t>- L. Susan Stebbing, Philosophy and the Physicists (1937), p. 64 - Метод и метафизика - Цвет - Физическое описание</t>
         </is>
       </c>
-      <c r="U53" s="14" t="n"/>
       <c r="V53" s="14" t="n"/>
-      <c r="W53" s="14" t="inlineStr">
+      <c r="W53" s="14" t="n"/>
+      <c r="X53" s="14" t="inlineStr">
         <is>
           <t>Стеббинг помогает Уилсону показать, как физическое описание цвета может быть ошибочно превращено в метафизический тезис. По её замечанию, отрицатели объективности цвета сделали из метода физики метафизику, забыв, что этот метод разрабатывался для определённых исследовательских целей.</t>
         </is>
       </c>
-      <c r="X53" s="14" t="inlineStr">
+      <c r="Y53" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y53" s="14" t="inlineStr">
+      <c r="Z53" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z53" s="14" t="inlineStr">
+      <c r="AA53" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/l-susan-stebbing</t>
         </is>
       </c>
-      <c r="AA53" s="14" t="inlineStr">
+      <c r="AB53" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB53" s="14" t="n"/>
+      <c r="AC53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
@@ -6463,93 +6620,98 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
+          <t>рак простаты</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
           <t>Вена, Австро-Венгрия</t>
         </is>
       </c>
-      <c r="I54" s="14" t="inlineStr">
+      <c r="J54" s="14" t="inlineStr">
         <is>
           <t>48.2082, 16.3738</t>
         </is>
       </c>
-      <c r="J54" s="14" t="inlineStr">
+      <c r="K54" s="14" t="inlineStr">
         <is>
           <t>Кембридж, Англия</t>
         </is>
       </c>
-      <c r="K54" s="14" t="inlineStr">
+      <c r="L54" s="14" t="inlineStr">
         <is>
           <t>52.2053, 0.1218</t>
         </is>
       </c>
-      <c r="L54" s="14" t="inlineStr">
+      <c r="M54" s="14" t="inlineStr">
         <is>
           <t>Высшая техническая школа Шарлоттенбурга; Манчестерский университет; Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="M54" s="14" t="inlineStr">
+      <c r="N54" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
-      <c r="N54" s="14" t="inlineStr">
+      <c r="O54" s="14" t="inlineStr">
         <is>
           <t>Бертран Рассел</t>
         </is>
       </c>
-      <c r="O54" s="14" t="n"/>
-      <c r="P54" s="14" t="inlineStr">
+      <c r="P54" s="14" t="n"/>
+      <c r="Q54" s="14" t="inlineStr">
         <is>
           <t>Готлоб Фреге</t>
         </is>
       </c>
-      <c r="Q54" s="14" t="n"/>
-      <c r="R54" s="14" t="inlineStr">
+      <c r="R54" s="14" t="n"/>
+      <c r="S54" s="14" t="inlineStr">
         <is>
           <t>философия языка; философия логики; философия математики</t>
         </is>
       </c>
-      <c r="S54" s="14" t="inlineStr">
+      <c r="T54" s="14" t="inlineStr">
         <is>
           <t>Австрийско-британский философ, один из самых влиятельных мыслителей XX века в философии языка. Условно разделяется на «раннего» (логический атомизм, «Логико-философский трактат», идея языка как картины мира) и «позднего» (философия обыденного языка, «Философские исследования», идея значения как употребления, языковые игры). Рецензенты считают, что «Блуждающие значения» сохраняют дух позднего Витгенштейна. Показательно, что в самой книге Уилсона фигурируют оба периода в диаметрально противоположных ролях (см. раздел «Ранний и поздний Витгенштейн в аргументации Уилсона» ниже).</t>
         </is>
       </c>
-      <c r="T54" s="14" t="inlineStr">
+      <c r="U54" s="14" t="inlineStr">
         <is>
           <t>- Поздний Витгенштейн: значение как употребление, языковые игры («Философские исследования», см. отдельную карточку filosofskie-issledovaniya-vitgenshteyna) - «Философские исследования», §18 — метафора языка как старого города (лабиринт узких улиц и площадей разных эпох плюс новые районы с регулярной планировкой) - Ранний Витгенштейн: «Логико-философский трактат» (1921) — идея Души, проецирующей значение на символы через интенцию (см. logiko-filosofsky-traktat) - (дозаполнить по мере чтения — само название книги, «Блуждающие значения», возможно, перекликается с образом «блуждания» по темам, о котором пишет Уилсон в этом же фрагменте предисловия)</t>
         </is>
       </c>
-      <c r="U54" s="14" t="inlineStr">
+      <c r="V54" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/wittgenstein/</t>
         </is>
       </c>
-      <c r="V54" s="14" t="n"/>
-      <c r="W54" s="14" t="inlineStr">
+      <c r="W54" s="14" t="n"/>
+      <c r="X54" s="14" t="inlineStr">
         <is>
           <t>Уилсон в предисловии пишет, что несколько рецензентов охарактеризовали высказанные в книге взгляды как «витгенштейнианские» — и он, возможно, с этим согласен. В юности он много читал Витгенштейна под руководством своего учителя Чарльза Маркса и находит примечательным, что они с Витгенштейном часто «блуждают» по схожим темам в своих философских странствиях. В главе 1 (раздел «Смягчённый скептицизм») Витгенштейн появляется ещё раз как источник альтернативной метафоры. Разбирая, как в языке возникают локальные «карманы» нового словоупотребления рядом со старым, Уилсон сперва предлагает собственный образ («поликристаллическая» структура значения слова, зарождение новых «зёрен»-употреблений по краям старых — метафора из материаловедения, эпитаксиальный рост кристаллов), а затем прямо предлагает витгенштейновскую метафору города как альтернативу или дополнение к своей: язык — это старинный город, лабиринт узких улиц и площадей вперемешку с домами разных эпох, окружённый новыми районами с прямой, регулярной планировкой. Источник — «Философские исследования», §18 (в тексте сноска дана как «Investigations, x18», по всей видимости — опечатка). ### Ранний и поздний Витгенштейн в аргументации Уилсона В главе 3, §(ii) («Классический клей») Витгенштейн появляется в третий раз — но уже как ранний Витгенштейн периода Трактата, и в роли, прямо противоположной главе 1. Уилсон приводит его идею Души как невидимого присутствия, «оживляющего» обычные символы через акт интенционального проецирования — иллюстрируя это бытовым образом кухонной утвари на столе, которая символизирует Битву при Энтитеме (Antietam) потому, что дед рассказчика пожелал реализовать эту связь. Этот ранний Витгенштейн вводится Уилсоном как исторический представитель интенционально-обоснованной картины предикатной значимости — картины, которую Уилсон явно отграничивает от защищаемого им классического склеивания Рассела, и которая, доведённая до крайности, граничит с «оккультной». Таким образом, один и тот же философ у Уилсона фигурирует дважды в противоположных функциях: ранний Витгенштейн (гл. 3) иллюстрирует почти магическую, интенционально-волевую картину языка, которую Уилсон скорее дистанцирует от собственной позиции; поздний Витгенштейн (гл. 1, предисловие) назван важнейшим анти-классическим событием и источником дружественной, созвучной Уилсону метафоры города.</t>
         </is>
       </c>
-      <c r="X54" s="14" t="inlineStr">
+      <c r="Y54" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 3</t>
         </is>
       </c>
-      <c r="Y54" s="14" t="inlineStr">
+      <c r="Z54" s="14" t="inlineStr">
         <is>
           <t>chapter_1_iii; chapter_1_ix; chapter_3_ii</t>
         </is>
       </c>
-      <c r="Z54" s="14" t="inlineStr">
+      <c r="AA54" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/ludwig-wittgenstein</t>
         </is>
       </c>
-      <c r="AA54" s="14" t="inlineStr">
+      <c r="AB54" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB54" s="14" t="n"/>
+      <c r="AC54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -6589,73 +6751,78 @@
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
+          <t>рак лёгких</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
           <t>Пикуа, Канзас, США</t>
         </is>
       </c>
-      <c r="I55" s="14" t="inlineStr">
+      <c r="J55" s="14" t="inlineStr">
         <is>
           <t>37.9200, -95.5300</t>
         </is>
       </c>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="K55" s="14" t="inlineStr">
         <is>
           <t>Вудленд-Хиллз, Лос-Анджелес, США</t>
         </is>
       </c>
-      <c r="K55" s="14" t="inlineStr">
+      <c r="L55" s="14" t="inlineStr">
         <is>
           <t>34.1680, -118.6050</t>
         </is>
       </c>
-      <c r="L55" s="14" t="n"/>
       <c r="M55" s="14" t="n"/>
       <c r="N55" s="14" t="n"/>
       <c r="O55" s="14" t="n"/>
       <c r="P55" s="14" t="n"/>
-      <c r="Q55" s="14" t="inlineStr">
+      <c r="Q55" s="14" t="n"/>
+      <c r="R55" s="14" t="inlineStr">
         <is>
           <t>Почётный «Оскар» (1960)</t>
         </is>
       </c>
-      <c r="R55" s="14" t="inlineStr">
+      <c r="S55" s="14" t="inlineStr">
         <is>
           <t>кино; комедия</t>
         </is>
       </c>
-      <c r="S55" s="14" t="inlineStr">
+      <c r="T55" s="14" t="inlineStr">
         <is>
           <t>Американский комик и режиссёр немого кино, «Великий Каменное Лицо»: «Генерал», «Шерлок-младший», «Пароходный Билл-младший».</t>
         </is>
       </c>
-      <c r="T55" s="14" t="n"/>
       <c r="U55" s="14" t="n"/>
       <c r="V55" s="14" t="n"/>
-      <c r="W55" s="14" t="inlineStr">
+      <c r="W55" s="14" t="n"/>
+      <c r="X55" s="14" t="inlineStr">
         <is>
           <t>В честь фильма Китона «Шерлок-младший» (Sherlock Jr., 1924) Уилсон называет юмовские рассуждения «аргументами Шерлока-младшего» (с. 165). В фильме киномеханик во сне входит в экран, и монтаж мгновенно меняет вокруг него обстановку. Так и юмовский аргумент утверждает, что «кинематографический монтаж реального жизненного опыта» можно отредактировать любым нестандартным способом: зубчатое колесо в железном корпусе последовательно заменяется зубчатым колесом с крылышками. Мы всё равно классифицировали бы предмет в каждом кадре как «зубчатое колесо» — значит, понятие не может содержать богатый набор инференциальных ассоциаций как часть инвариантного содержания.</t>
         </is>
       </c>
-      <c r="X55" s="14" t="inlineStr">
+      <c r="Y55" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y55" s="14" t="inlineStr">
+      <c r="Z55" s="14" t="inlineStr">
         <is>
           <t>chapter_3_vi</t>
         </is>
       </c>
-      <c r="Z55" s="14" t="inlineStr">
+      <c r="AA55" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/buster-keaton</t>
         </is>
       </c>
-      <c r="AA55" s="14" t="inlineStr">
+      <c r="AB55" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB55" s="14" t="n"/>
+      <c r="AC55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
@@ -6695,81 +6862,86 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
+          <t>острый панкреатит</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
           <t>Ханау, Германия</t>
         </is>
       </c>
-      <c r="I56" s="14" t="inlineStr">
+      <c r="J56" s="14" t="inlineStr">
         <is>
           <t>50.1264, 8.9283</t>
         </is>
       </c>
-      <c r="J56" s="14" t="inlineStr">
+      <c r="K56" s="14" t="inlineStr">
         <is>
           <t>Франкфурт-на-Майне, Германия</t>
         </is>
       </c>
-      <c r="K56" s="14" t="inlineStr">
+      <c r="L56" s="14" t="inlineStr">
         <is>
           <t>50.1109, 8.6821</t>
         </is>
       </c>
-      <c r="L56" s="14" t="inlineStr">
+      <c r="M56" s="14" t="inlineStr">
         <is>
           <t>Консерватория Хоха, Франкфурт</t>
         </is>
       </c>
-      <c r="M56" s="14" t="inlineStr">
+      <c r="N56" s="14" t="inlineStr">
         <is>
           <t>Берлинская высшая школа музыки; Йельский университет</t>
         </is>
       </c>
-      <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n"/>
       <c r="P56" s="14" t="n"/>
       <c r="Q56" s="14" t="n"/>
-      <c r="R56" s="14" t="inlineStr">
+      <c r="R56" s="14" t="n"/>
+      <c r="S56" s="14" t="inlineStr">
         <is>
           <t>композиция; теория музыки</t>
         </is>
       </c>
-      <c r="S56" s="14" t="inlineStr">
+      <c r="T56" s="14" t="inlineStr">
         <is>
           <t>Немецкий композитор, дирижёр и музыкальный теоретик, один из крупнейших музыкантов XX века. Автор оперы «Художник Матис» и теоретических трудов по музыкальной композиции.</t>
         </is>
       </c>
-      <c r="T56" s="14" t="inlineStr">
+      <c r="U56" s="14" t="inlineStr">
         <is>
           <t>- Комбинационные тоны как необходимое условие музыкального восприятия</t>
         </is>
       </c>
-      <c r="U56" s="14" t="n"/>
       <c r="V56" s="14" t="n"/>
-      <c r="W56" s="14" t="inlineStr">
+      <c r="W56" s="14" t="n"/>
+      <c r="X56" s="14" t="inlineStr">
         <is>
           <t>Уилсон цитирует Хиндемита как авторитетного музыканта, подтверждающего фундаментальную роль комбинационных тонов в музыкальном восприятии. Хиндемит заявляет: «Интервал без комбинационных тонов был бы абстрактным понятием, не имеющим бытия». Эта цитата используется для усиления аргумента о том, что музыкальное восприятие неразрывно связано с субъективными процессами в слуховом аппарате.</t>
         </is>
       </c>
-      <c r="X56" s="14" t="inlineStr">
+      <c r="Y56" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y56" s="14" t="inlineStr">
+      <c r="Z56" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z56" s="14" t="inlineStr">
+      <c r="AA56" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/paul-hindemith</t>
         </is>
       </c>
-      <c r="AA56" s="14" t="inlineStr">
+      <c r="AB56" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB56" s="14" t="n"/>
+      <c r="AC56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
@@ -6807,83 +6979,84 @@
           <t>1980-09-16</t>
         </is>
       </c>
-      <c r="H57" s="14" t="inlineStr">
+      <c r="H57" s="14" t="n"/>
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Невшатель, Швейцария</t>
         </is>
       </c>
-      <c r="I57" s="14" t="inlineStr">
+      <c r="J57" s="14" t="inlineStr">
         <is>
           <t>46.9900, 6.9300</t>
         </is>
       </c>
-      <c r="J57" s="14" t="inlineStr">
+      <c r="K57" s="14" t="inlineStr">
         <is>
           <t>Женева, Швейцария</t>
         </is>
       </c>
-      <c r="K57" s="14" t="inlineStr">
+      <c r="L57" s="14" t="inlineStr">
         <is>
           <t>46.2044, 6.1432</t>
         </is>
       </c>
-      <c r="L57" s="14" t="inlineStr">
+      <c r="M57" s="14" t="inlineStr">
         <is>
           <t>Невшательский университет</t>
         </is>
       </c>
-      <c r="M57" s="14" t="inlineStr">
+      <c r="N57" s="14" t="inlineStr">
         <is>
           <t>Женевский университет; Институт Жан-Жака Руссо</t>
         </is>
       </c>
-      <c r="N57" s="14" t="n"/>
       <c r="O57" s="14" t="n"/>
       <c r="P57" s="14" t="n"/>
       <c r="Q57" s="14" t="n"/>
-      <c r="R57" s="14" t="inlineStr">
+      <c r="R57" s="14" t="n"/>
+      <c r="S57" s="14" t="inlineStr">
         <is>
           <t>психология развития; генетическая эпистемология</t>
         </is>
       </c>
-      <c r="S57" s="14" t="inlineStr">
+      <c r="T57" s="14" t="inlineStr">
         <is>
           <t>Швейцарский психолог, основоположник теории когнитивного развития ребёнка — описал стадии, через которые проходит детское мышление на пути к взрослому пониманию мира, включая представления о причинности, постоянстве объектов и логических операциях.</t>
         </is>
       </c>
-      <c r="T57" s="14" t="inlineStr">
+      <c r="U57" s="14" t="inlineStr">
         <is>
           <t>- Не применимо — используется как имя-маркер авторитета, а не как содержательный источник</t>
         </is>
       </c>
-      <c r="U57" s="14" t="n"/>
       <c r="V57" s="14" t="n"/>
-      <c r="W57" s="14" t="inlineStr">
+      <c r="W57" s="14" t="n"/>
+      <c r="X57" s="14" t="inlineStr">
         <is>
           <t>Упомянут как источник стандартной, узнаваемой мерки для оценки уровня концептуального развития — в шуточных примерах про Джона, Хьюи, Дьюи и Луи, оценивающих их понимание «радуги» через фразы вроде «не достиг требуемого Пиаже уровня понимания причинных связей с материальными объектами».</t>
         </is>
       </c>
-      <c r="X57" s="14" t="inlineStr">
+      <c r="Y57" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y57" s="14" t="inlineStr">
+      <c r="Z57" s="14" t="inlineStr">
         <is>
           <t>chapter_1_vi</t>
         </is>
       </c>
-      <c r="Z57" s="14" t="inlineStr">
+      <c r="AA57" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/jean-piaget</t>
         </is>
       </c>
-      <c r="AA57" s="14" t="inlineStr">
+      <c r="AB57" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB57" s="14" t="n"/>
+      <c r="AC57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
@@ -6921,83 +7094,84 @@
           <t>1988-10-31</t>
         </is>
       </c>
-      <c r="H58" s="14" t="inlineStr">
+      <c r="H58" s="14" t="n"/>
+      <c r="I58" s="14" t="inlineStr">
         <is>
           <t>Флоренция</t>
         </is>
       </c>
-      <c r="I58" s="14" t="inlineStr">
+      <c r="J58" s="14" t="inlineStr">
         <is>
           <t>43.7696, 11.2558</t>
         </is>
       </c>
-      <c r="J58" s="14" t="inlineStr">
+      <c r="K58" s="14" t="inlineStr">
         <is>
           <t>Флоренция</t>
         </is>
       </c>
-      <c r="K58" s="14" t="inlineStr">
+      <c r="L58" s="14" t="inlineStr">
         <is>
           <t>43.7696, 11.2558</t>
         </is>
       </c>
-      <c r="L58" s="14" t="inlineStr">
+      <c r="M58" s="14" t="inlineStr">
         <is>
           <t>Высшая нормальная школа, Пиза</t>
         </is>
       </c>
-      <c r="M58" s="14" t="inlineStr">
+      <c r="N58" s="14" t="inlineStr">
         <is>
           <t>Национальный институт оптики, Флоренция</t>
         </is>
       </c>
-      <c r="N58" s="14" t="n"/>
       <c r="O58" s="14" t="n"/>
       <c r="P58" s="14" t="n"/>
       <c r="Q58" s="14" t="n"/>
-      <c r="R58" s="14" t="inlineStr">
+      <c r="R58" s="14" t="n"/>
+      <c r="S58" s="14" t="inlineStr">
         <is>
           <t>оптика; история оптики</t>
         </is>
       </c>
-      <c r="S58" s="14" t="inlineStr">
+      <c r="T58" s="14" t="inlineStr">
         <is>
           <t>Итальянский физик и историк науки, специалист в области оптики и теории зрения. Автор книги «Оптика: наука о зрении» (Optics: The Science of Vision).</t>
         </is>
       </c>
-      <c r="T58" s="14" t="inlineStr">
+      <c r="U58" s="14" t="inlineStr">
         <is>
           <t>- Optics: The Science of Vision (1991) — цитата о субъективной природе звука</t>
         </is>
       </c>
-      <c r="U58" s="14" t="n"/>
       <c r="V58" s="14" t="n"/>
-      <c r="W58" s="14" t="inlineStr">
+      <c r="W58" s="14" t="n"/>
+      <c r="X58" s="14" t="inlineStr">
         <is>
           <t>Уилсон цитирует Рончи как пример «совершенно оголтелой» формы субъективизма, характерной для практических руководств (в отличие от философской литературы, которая обычно пытается смягчить радикальность субъективации). Рончи утверждает, что звук — это сугубо ментальный феномен, а физические вибрации существуют вне сознания; отождествление акустических колебаний со звуком ведёт к опасному недоразумению. Уилсон иронически замечает, что такой подход приводит к парадоксальному выводу: если в лесу падает дерево, звука не возникает. Этот пример служит иллюстрацией субъективистской модели музыкальных атрибутов, которую Уилсон также отвергает.</t>
         </is>
       </c>
-      <c r="X58" s="14" t="inlineStr">
+      <c r="Y58" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y58" s="14" t="inlineStr">
+      <c r="Z58" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z58" s="14" t="inlineStr">
+      <c r="AA58" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/vasco-ronchi</t>
         </is>
       </c>
-      <c r="AA58" s="14" t="inlineStr">
+      <c r="AB58" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB58" s="14" t="n"/>
+      <c r="AC58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
@@ -7037,49 +7211,50 @@
       <c r="O59" s="14" t="n"/>
       <c r="P59" s="14" t="n"/>
       <c r="Q59" s="14" t="n"/>
-      <c r="R59" s="14" t="inlineStr">
+      <c r="R59" s="14" t="n"/>
+      <c r="S59" s="14" t="inlineStr">
         <is>
           <t>фольклористика; полевые записи</t>
         </is>
       </c>
-      <c r="S59" s="14" t="inlineStr">
+      <c r="T59" s="14" t="inlineStr">
         <is>
           <t>Американские собиратели, исполнители и исследователи традиционной народной музыки. С конца 1930-х годов Фрэнк и Энн Уорнер во время поездок по восточным районам США записывали песни и рассказы традиционных исполнителей, формируя коллекцию, насчитывающую более тысячи песен и историй. Их деятельность охватывала Аппалачи, Северную Каролину, Внешние отмели, Вирджинию, Новую Англию и север штата Нью-Йорк. Фрэнк выступал как певец и музыкант, а Энн занималась документированием материала, расшифровкой записей и подготовкой текстов. При нехватке носителей они нередко записывали только часть песни, после чего Энн восстанавливала остальной текст по стенографической записи.</t>
         </is>
       </c>
-      <c r="T59" s="14" t="inlineStr">
+      <c r="U59" s="14" t="inlineStr">
         <is>
           <t>- Anne and Frank Warner Collection — собрание полевых записей традиционной американской музыки. - Her Bright Smile Haunts Me Still, Appleseed APR CD 1035 (2000). - Полевое собирание фольклора. - Документирование традиционной музыки. - Сохранение музыкального содержания. - Исполнение как форма продолжения традиции. - Противопоставление записи и живого музыкального опыта.</t>
         </is>
       </c>
-      <c r="U59" s="14" t="n"/>
       <c r="V59" s="14" t="n"/>
-      <c r="W59" s="14" t="inlineStr">
+      <c r="W59" s="14" t="n"/>
+      <c r="X59" s="14" t="inlineStr">
         <is>
           <t>Уилсон вводит Уорнеров как собирателей 1940-х годов, чьи полевые записи становятся объектом последующего рассуждения о сохранении музыкального содержания. Непосредственно философскую позицию, связанную с этими записями, выражает Тим Эриксон в сопроводительных заметках к переизданию их полевых записей Her Bright Smile Haunts Me Still (2000). Эриксон утверждает, что ценность записанной музыки не существует вне восприятия и опыта и что надёжный способ сохранить музыку «живой» состоит в её исполнении и проживании. Таким образом, Уорнеры занимают в аргументе Уилсона особое положение: их записи представляют объект сохранения, а рассуждения Эриксона превращают этот объект в повод для критики партиципативного понимания сохранения. Уилсон противопоставляет этой позиции идею сохранения посредством записи: если музыкальное содержание уже зафиксировано на носителе, дополнительное участие исполнителя может не только поддерживать традицию, но и изменять или даже разрушать особенности первоначального исполнения.</t>
         </is>
       </c>
-      <c r="X59" s="14" t="inlineStr">
+      <c r="Y59" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y59" s="14" t="inlineStr">
+      <c r="Z59" s="14" t="inlineStr">
         <is>
           <t>chapter_2_v</t>
         </is>
       </c>
-      <c r="Z59" s="14" t="inlineStr">
+      <c r="AA59" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/frank-and-anne-warner</t>
         </is>
       </c>
-      <c r="AA59" s="14" t="inlineStr">
+      <c r="AB59" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB59" s="14" t="n"/>
+      <c r="AC59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -7119,73 +7294,78 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
+          <t>инсульт</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
           <t>Бристоль, Англия</t>
         </is>
       </c>
-      <c r="I60" s="14" t="inlineStr">
+      <c r="J60" s="14" t="inlineStr">
         <is>
           <t>51.4545, -2.5879</t>
         </is>
       </c>
-      <c r="J60" s="14" t="inlineStr">
+      <c r="K60" s="14" t="inlineStr">
         <is>
           <t>Дэвенпорт, Айова, США</t>
         </is>
       </c>
-      <c r="K60" s="14" t="inlineStr">
+      <c r="L60" s="14" t="inlineStr">
         <is>
           <t>41.5236, -90.5776</t>
         </is>
       </c>
-      <c r="L60" s="14" t="n"/>
       <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
-      <c r="Q60" s="14" t="inlineStr">
+      <c r="Q60" s="14" t="n"/>
+      <c r="R60" s="14" t="inlineStr">
         <is>
           <t>Почётный «Оскар» (1970)</t>
         </is>
       </c>
-      <c r="R60" s="14" t="inlineStr">
+      <c r="S60" s="14" t="inlineStr">
         <is>
           <t>кино</t>
         </is>
       </c>
-      <c r="S60" s="14" t="inlineStr">
+      <c r="T60" s="14" t="inlineStr">
         <is>
           <t>Британско-американский киноактёр (настоящее имя — Арчибальд Александер Лич), одна из главных звёзд классического Голливуда: «Воспитание крошки», «Филадельфийская история», «Дурная слава», «К северу через северо-запад».</t>
         </is>
       </c>
-      <c r="T60" s="14" t="n"/>
       <c r="U60" s="14" t="n"/>
       <c r="V60" s="14" t="n"/>
-      <c r="W60" s="14" t="inlineStr">
+      <c r="W60" s="14" t="n"/>
+      <c r="X60" s="14" t="inlineStr">
         <is>
           <t>Возникает в одном примере. Уилсон показывает, что некоторые «паттерны руководства» легко подчиняются нашему сознательному контролю: речь можно подчинить алгоритму или схеме аксиом («Прибавьте „2“ к цифре, которая у вас уже есть») — или инструкции, опирающейся на непосредственное впечатление: «Помечайте знаком „Х“ любого человека, который напоминает вам Кэри Гранта». Решительное следование таким инструкциям Уилсон называет лично навязанными направленностями. Именно на них, по Уилсону, Куайн чрезмерно полагается в своей картине «правильной лингвистической навигации» (см. willard-quine).</t>
         </is>
       </c>
-      <c r="X60" s="14" t="inlineStr">
+      <c r="Y60" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y60" s="14" t="inlineStr">
+      <c r="Z60" s="14" t="inlineStr">
         <is>
           <t>chapter_3_v</t>
         </is>
       </c>
-      <c r="Z60" s="14" t="inlineStr">
+      <c r="AA60" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/cary-grant</t>
         </is>
       </c>
-      <c r="AA60" s="14" t="inlineStr">
+      <c r="AB60" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB60" s="14" t="n"/>
+      <c r="AC60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
@@ -7225,81 +7405,86 @@
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
+          <t>рак ротовой полости</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
           <t>Спрингфилд, Массачусетс, США</t>
         </is>
       </c>
-      <c r="I61" s="14" t="inlineStr">
+      <c r="J61" s="14" t="inlineStr">
         <is>
           <t>42.1015, -72.5898</t>
         </is>
       </c>
-      <c r="J61" s="14" t="inlineStr">
+      <c r="K61" s="14" t="inlineStr">
         <is>
           <t>Ла-Холья, Калифорния, США</t>
         </is>
       </c>
-      <c r="K61" s="14" t="inlineStr">
+      <c r="L61" s="14" t="inlineStr">
         <is>
           <t>32.8328, -117.2713</t>
         </is>
       </c>
-      <c r="L61" s="14" t="inlineStr">
+      <c r="M61" s="14" t="inlineStr">
         <is>
           <t>Дартмутский колледж; Линкольн-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M61" s="14" t="n"/>
       <c r="N61" s="14" t="n"/>
       <c r="O61" s="14" t="n"/>
       <c r="P61" s="14" t="n"/>
-      <c r="Q61" s="14" t="inlineStr">
+      <c r="Q61" s="14" t="n"/>
+      <c r="R61" s="14" t="inlineStr">
         <is>
           <t>Специальная Пулитцеровская премия (1984)</t>
         </is>
       </c>
-      <c r="R61" s="14" t="inlineStr">
+      <c r="S61" s="14" t="inlineStr">
         <is>
           <t>детская литература; иллюстрация</t>
         </is>
       </c>
-      <c r="S61" s="14" t="inlineStr">
+      <c r="T61" s="14" t="inlineStr">
         <is>
           <t>Псевдоним Теодора Сьюза Гайзеля, американского детского писателя и иллюстратора, автора «The Cat in the Hat», «Green Eggs and Ham», «How the Grinch Stole Christmas!» и десятков других книг, отличающихся характерным ритмизованным, изобретательным словотворчеством. Здесь цитируется его алфавитная книга «Dr. Seuss's ABC» (1963). (Примечание по транслитерации: в русском переводе фрагмента имя передано как «доктор Зойс» — нестандартный вариант против общепринятого в русскоязычной традиции «Доктор Сьюз»; возможно, стоит унифицировать при редактуре.)</t>
         </is>
       </c>
-      <c r="T61" s="14" t="inlineStr">
+      <c r="U61" s="14" t="inlineStr">
         <is>
           <t>- Dr. Seuss, Dr. Seuss's ABC (New York: Random House, 1963), 34</t>
         </is>
       </c>
-      <c r="U61" s="14" t="n"/>
       <c r="V61" s="14" t="n"/>
-      <c r="W61" s="14" t="inlineStr">
+      <c r="W61" s="14" t="n"/>
+      <c r="X61" s="14" t="inlineStr">
         <is>
           <t>Использован как шутливая, но точная иллюстрация тезиса о «креативности языка»: строчка про букву «O» («Oscar's only ostrich oiled an orange owl today») — искусственное предложение, которое почти наверняка никто, кроме самого Доктора Сьюза (и производных от него комментаторов вроде самого Уилсона), никогда не произнёс бы, но которое, тем не менее, мгновенно и полностью понятно любому носителю языка. Это доводит до абсурда — и тем самым иллюстрирует — довод Джекендоффа о том, что понимание бесконечного числа новых предложений требует конечного набора полностью усвоенных примитивов.</t>
         </is>
       </c>
-      <c r="X61" s="14" t="inlineStr">
+      <c r="Y61" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y61" s="14" t="inlineStr">
+      <c r="Z61" s="14" t="inlineStr">
         <is>
           <t>chapter_1_vi</t>
         </is>
       </c>
-      <c r="Z61" s="14" t="inlineStr">
+      <c r="AA61" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/doctor-seuss</t>
         </is>
       </c>
-      <c r="AA61" s="14" t="inlineStr">
+      <c r="AB61" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB61" s="14" t="n"/>
+      <c r="AC61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
@@ -7347,49 +7532,50 @@
       <c r="O62" s="14" t="n"/>
       <c r="P62" s="14" t="n"/>
       <c r="Q62" s="14" t="n"/>
-      <c r="R62" s="14" t="inlineStr">
+      <c r="R62" s="14" t="n"/>
+      <c r="S62" s="14" t="inlineStr">
         <is>
           <t>калипсо</t>
         </is>
       </c>
-      <c r="S62" s="14" t="inlineStr">
+      <c r="T62" s="14" t="inlineStr">
         <is>
           <t>Настоящее имя — Сесил Андерсон (Cecil Anderson), калипсонье (исполнитель калипсо), уроженец Порт-оф-Спейна, Тринидад. В 1923 году переехал с семьёй в Нью-Йорк, где и сделал основную карьеру — один из самых популярных исполнителей калипсо в США 1930–1960-х годов, известен чёткой дикцией и умением ясно доносить английский текст до американской аудитории (в отличие от многих коллег с более выраженным креольским произношением), а также озорным, фривольным юмором в текстах. Десятимесячная резидентура в нью-йоркском Village Vanguard (1940-е), выступления в Carnegie Hall и Apollo Theater, участие в легендарном концерте «Calypso at Midnight» Алана Ломакса (Town Hall, декабрь 1946), роль в фильме «Calypso Joe» (1957) с Энджи Дикинсон. Среди самых известных вещей — «The Big Bamboo» (культовая фривольная классика жанра) и, что любопытно для этого путеводителя, собственная запись той же песни «Marry a Woman Uglier Than You» — того самого источника, вокруг авторства которого разворачивается путаница в примечании Уилсона (см. карточку roaring-lion).</t>
         </is>
       </c>
-      <c r="T62" s="14" t="inlineStr">
+      <c r="U62" s="14" t="inlineStr">
         <is>
           <t>- «Wide Screen» (Monogram Record M-934) — источник эпиграфа, установлено по авторской сноске</t>
         </is>
       </c>
-      <c r="U62" s="14" t="n"/>
       <c r="V62" s="14" t="n"/>
-      <c r="W62" s="14" t="inlineStr">
+      <c r="W62" s="14" t="n"/>
+      <c r="X62" s="14" t="inlineStr">
         <is>
           <t>Использован как источник эпиграфа к главе 1 («Широкий экран»/Wide Screen) — двустишие про очки и возможность видеть «любой экран, прибывший в Тринидад» (по содержанию соответствует русскому переводу; дословно не воспроизвожу — это лирика песни, а не проза Уилсона). Источник установлен точно по сноске самого автора: песня называется «Wide Screen», пластинка Monogram Record M-934. Главы книги открываются калипсо-эпиграфами, что задаёт неформальный, игривый тон изложения даже там, где обсуждаются сложные технические вопросы. Не удалось найти первоисточник всего текста песни.</t>
         </is>
       </c>
-      <c r="X62" s="14" t="inlineStr">
+      <c r="Y62" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y62" s="14" t="inlineStr">
+      <c r="Z62" s="14" t="inlineStr">
         <is>
           <t>chapter_1_i</t>
         </is>
       </c>
-      <c r="Z62" s="14" t="inlineStr">
+      <c r="AA62" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/duke-of-iron</t>
         </is>
       </c>
-      <c r="AA62" s="14" t="inlineStr">
+      <c r="AB62" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB62" s="14" t="n"/>
+      <c r="AC62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
@@ -7432,58 +7618,59 @@
       <c r="J63" s="14" t="n"/>
       <c r="K63" s="14" t="n"/>
       <c r="L63" s="14" t="n"/>
-      <c r="M63" s="14" t="inlineStr">
+      <c r="M63" s="14" t="n"/>
+      <c r="N63" s="14" t="inlineStr">
         <is>
           <t>Технический университет Берлина</t>
         </is>
       </c>
-      <c r="N63" s="14" t="n"/>
       <c r="O63" s="14" t="n"/>
       <c r="P63" s="14" t="n"/>
       <c r="Q63" s="14" t="n"/>
-      <c r="R63" s="14" t="inlineStr">
+      <c r="R63" s="14" t="n"/>
+      <c r="S63" s="14" t="inlineStr">
         <is>
           <t>акустика; музыкальная психоакустика</t>
         </is>
       </c>
-      <c r="S63" s="14" t="inlineStr">
+      <c r="T63" s="14" t="inlineStr">
         <is>
           <t>Немецкий музыковед и акустик XX века, автор книги «Музыка, звук и ощущение» (Music, Sound and Sensation, 1967), в которой исследуются физические и психологические основы музыкального восприятия.</t>
         </is>
       </c>
-      <c r="T63" s="14" t="inlineStr">
+      <c r="U63" s="14" t="inlineStr">
         <is>
           <t>- Music, Sound and Sensation: A Modern Exposition (1967) — цитаты о роли комбинационных тонов и обертонов в музыкальном восприятии</t>
         </is>
       </c>
-      <c r="U63" s="14" t="n"/>
       <c r="V63" s="14" t="n"/>
-      <c r="W63" s="14" t="inlineStr">
+      <c r="W63" s="14" t="n"/>
+      <c r="X63" s="14" t="inlineStr">
         <is>
           <t>Уилсон цитирует Винкеля как авторитетного музыковеда, который в ироничном ключе утверждает, что математически описываемая гармония (синусоидальные волны, чистые интервалы) не вызывает музыкальных переживаний; напротив, для полноценного музыкального опыта требуются такие «несовершенства», как комбинационные тоны и обертоны. Винкель пишет: «Чистые интервалы триады простых тонов не вызывают музыкальных переживаний, а, напротив, на самом деле требуют стимулирующего компонента — по крайней мере, 7-го обертона». Это подкрепляет аргумент Уилсона о том, что музыкальные свойства укоренены в «изменчивой человеческой природе».</t>
         </is>
       </c>
-      <c r="X63" s="14" t="inlineStr">
+      <c r="Y63" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y63" s="14" t="inlineStr">
+      <c r="Z63" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z63" s="14" t="inlineStr">
+      <c r="AA63" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/fritz-winckel</t>
         </is>
       </c>
-      <c r="AA63" s="14" t="inlineStr">
+      <c r="AB63" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB63" s="14" t="n"/>
+      <c r="AC63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -7531,49 +7718,50 @@
       <c r="O64" s="14" t="n"/>
       <c r="P64" s="14" t="n"/>
       <c r="Q64" s="14" t="n"/>
-      <c r="R64" s="14" t="inlineStr">
+      <c r="R64" s="14" t="n"/>
+      <c r="S64" s="14" t="inlineStr">
         <is>
           <t>калипсо</t>
         </is>
       </c>
-      <c r="S64" s="14" t="inlineStr">
+      <c r="T64" s="14" t="inlineStr">
         <is>
           <t>Один из величайших пионеров калипсо золотого века жанра (1930–1950-е). Настоящее имя спорно документировано — сам себя называл Rafael Arias Cairi Llama de Leon, хотя долгое время в источниках фигурировало «Hubert Raphael Charles» (это, по данным современных исследований, ошибка). Сценическое имя «Roaring Lion» получил от уходящего на покой калипсонье по прозвищу Poetical Harris — за мощный, «рычащий» вокал. В 1934 году вместе с Attila the Hun стал первым калипсонье, выехавшим записываться за границу (Нью-Йорк) — тогда же выступил перед президентом США Франклином Рузвельтом в отеле Waldorf Astoria, где на вопрос о происхождении ответил «The Land of Calypso», закрепив это прозвище за Тринидадом. Автор изданной под конец жизни книги по истории жанра «Calypso from France to Trinidad: 800 Years of History» (1986).</t>
         </is>
       </c>
-      <c r="T64" s="14" t="inlineStr">
+      <c r="U64" s="14" t="inlineStr">
         <is>
           <t>- «Ugly Woman» (1933/34) — источник названия книги Куайна «From a Logical Point of View» (1953)</t>
         </is>
       </c>
-      <c r="U64" s="14" t="n"/>
       <c r="V64" s="14" t="n"/>
-      <c r="W64" s="14" t="inlineStr">
+      <c r="W64" s="14" t="n"/>
+      <c r="X64" s="14" t="inlineStr">
         <is>
           <t>Персонаж, связанный с примечанием об ошибках в атрибуции. Уилсон поясняет: У. В. Куайн, называя свой знаменитый сборник статей «From a Logical Point of View» («С логической точки зрения», 1953), заимствовал название из строки калипсо-песни — но приписал её Гарри Белафонте, тогда как настоящий автор и первый исполнитель песни — именно этот калипсонье, который «так и не получил должного признания за свою работу». Проверено по независимым источникам: песня называется «Ugly Woman» (записана в 1933–34 гг.), содержит буквальную строку «That's from a logical point of view / Always love a woman uglier than you» — прямой источник заглавия книги Куайна. В 1957 году актёр и певец Роберт Митчем записал кавер-версию именно под названием «From a Logical Point of View» (альбом «Calypso — Is Like So...») — по всей видимости, именно эта версия и стала непосредственным источником, который слышал Куайн, а сам факт присвоения авторства Белафонте, вероятно, объясняется тем, что Белафонте был несравнимо более известен и ассоциировался с калипсо-бумом середины 1950-х в целом, тогда как ни настоящий автор, ни фактический кавер-исполнитель (Митчем) такой славы не получили.</t>
         </is>
       </c>
-      <c r="X64" s="14" t="inlineStr">
+      <c r="Y64" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y64" s="14" t="inlineStr">
+      <c r="Z64" s="14" t="inlineStr">
         <is>
           <t>chapter_1_i</t>
         </is>
       </c>
-      <c r="Z64" s="14" t="inlineStr">
+      <c r="AA64" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/roaring-lion</t>
         </is>
       </c>
-      <c r="AA64" s="14" t="inlineStr">
+      <c r="AB64" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB64" s="14" t="n"/>
+      <c r="AC64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -7611,99 +7799,100 @@
           <t>2000-12-25</t>
         </is>
       </c>
-      <c r="H65" s="14" t="inlineStr">
+      <c r="H65" s="14" t="n"/>
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>Акрон, Огайо, США</t>
         </is>
       </c>
-      <c r="I65" s="14" t="inlineStr">
+      <c r="J65" s="14" t="inlineStr">
         <is>
           <t>41.0814, -81.5190</t>
         </is>
       </c>
-      <c r="J65" s="14" t="inlineStr">
+      <c r="K65" s="14" t="inlineStr">
         <is>
           <t>Бостон, США</t>
         </is>
       </c>
-      <c r="K65" s="14" t="inlineStr">
+      <c r="L65" s="14" t="inlineStr">
         <is>
           <t>42.3601, -71.0589</t>
         </is>
       </c>
-      <c r="L65" s="14" t="inlineStr">
+      <c r="M65" s="14" t="inlineStr">
         <is>
           <t>Оберлин-колледж; Гарвардский университет</t>
         </is>
       </c>
-      <c r="M65" s="14" t="inlineStr">
+      <c r="N65" s="14" t="inlineStr">
         <is>
           <t>Гарвардский университет</t>
         </is>
       </c>
-      <c r="N65" s="14" t="inlineStr">
+      <c r="O65" s="14" t="inlineStr">
         <is>
           <t>Альфред Норт Уайтхед</t>
         </is>
       </c>
-      <c r="O65" s="14" t="inlineStr">
+      <c r="P65" s="14" t="inlineStr">
         <is>
           <t>Дэвид Льюис</t>
         </is>
       </c>
-      <c r="P65" s="14" t="inlineStr">
+      <c r="Q65" s="14" t="inlineStr">
         <is>
           <t>Хилари Патнэм</t>
         </is>
       </c>
-      <c r="Q65" s="14" t="n"/>
-      <c r="R65" s="14" t="inlineStr">
+      <c r="R65" s="14" t="n"/>
+      <c r="S65" s="14" t="inlineStr">
         <is>
           <t>логика; философия языка; эпистемология</t>
         </is>
       </c>
-      <c r="S65" s="14" t="inlineStr">
+      <c r="T65" s="14" t="inlineStr">
         <is>
           <t>Один из центральных философов-аналитиков XX века. Известен критикой различения аналитических и синтетических суждений (статья «Две догмы эмпиризма»), тезисом о неопределённости перевода и программой натурализованной эпистемологии.</t>
         </is>
       </c>
-      <c r="T65" s="14" t="inlineStr">
+      <c r="U65" s="14" t="inlineStr">
         <is>
           <t>- Холизм подтверждения / тезис Дюэма–Куайна - Критика различения аналитического и синтетического («Две догмы эмпиризма», 1951) - Корабль Нойрата как образ языковой эволюции (Word and Object, 1960) — см. korabl-noyrata - Регламентация языка: максима «Приведите свои дела в простейший регламентированный порядок» (гл. 3, v)</t>
         </is>
       </c>
-      <c r="U65" s="14" t="inlineStr">
+      <c r="V65" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/quine/</t>
         </is>
       </c>
-      <c r="V65" s="14" t="n"/>
-      <c r="W65" s="14" t="inlineStr">
+      <c r="W65" s="14" t="n"/>
+      <c r="X65" s="14" t="inlineStr">
         <is>
           <t>Упомянут как один из первых, кто усомнился в основаниях классических подходов к системам понятий в науке и философии — то есть выступает как предшественник и союзник по духу основного тезиса книги, хотя и с иной, более общей постановкой вопроса. Уилсон, судя по всему, опирается на этот скептицизм как на отправную точку, чтобы затем предложить собственную, более детализированную картину того, как понятия меняются в употреблении.</t>
         </is>
       </c>
-      <c r="X65" s="14" t="inlineStr">
+      <c r="Y65" s="14" t="inlineStr">
         <is>
           <t>предисловие; гл. 3</t>
         </is>
       </c>
-      <c r="Y65" s="14" t="inlineStr">
+      <c r="Z65" s="14" t="inlineStr">
         <is>
           <t>chapter_3_i; chapter_3_ii; chapter_3_v; predislovie</t>
         </is>
       </c>
-      <c r="Z65" s="14" t="inlineStr">
+      <c r="AA65" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/willard-quine</t>
         </is>
       </c>
-      <c r="AA65" s="14" t="inlineStr">
+      <c r="AB65" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB65" s="14" t="n"/>
+      <c r="AC65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
@@ -7743,85 +7932,90 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
+          <t>рак лёгких</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
           <t>Ланкастер, Англия</t>
         </is>
       </c>
-      <c r="I66" s="14" t="inlineStr">
+      <c r="J66" s="14" t="inlineStr">
         <is>
           <t>54.0466, -2.8007</t>
         </is>
       </c>
-      <c r="J66" s="14" t="inlineStr">
+      <c r="K66" s="14" t="inlineStr">
         <is>
           <t>Оксфорд, Англия</t>
         </is>
       </c>
-      <c r="K66" s="14" t="inlineStr">
+      <c r="L66" s="14" t="inlineStr">
         <is>
           <t>51.7520, -1.2577</t>
         </is>
       </c>
-      <c r="L66" s="14" t="inlineStr">
+      <c r="M66" s="14" t="inlineStr">
         <is>
           <t>Баллиол-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M66" s="14" t="inlineStr">
+      <c r="N66" s="14" t="inlineStr">
         <is>
           <t>Оксфордский университет</t>
         </is>
       </c>
-      <c r="N66" s="14" t="n"/>
       <c r="O66" s="14" t="n"/>
       <c r="P66" s="14" t="n"/>
       <c r="Q66" s="14" t="n"/>
-      <c r="R66" s="14" t="inlineStr">
+      <c r="R66" s="14" t="n"/>
+      <c r="S66" s="14" t="inlineStr">
         <is>
           <t>философия обыденного языка; теория речевых актов</t>
         </is>
       </c>
-      <c r="S66" s="14" t="inlineStr">
+      <c r="T66" s="14" t="inlineStr">
         <is>
           <t>Британский философ, один из основателей философии обыденного языка (ordinary language philosophy) и теории речевых актов. Автор работ «Как производить действия при помощи слов» («How to Do Things with Words») и «Чужое сознание» / «Оправдания» («A Plea for Excuses»). Известен методом пристального внимания к тому, как понятия реально используются в языке, — вместо того чтобы конструировать их значения априорно.</t>
         </is>
       </c>
-      <c r="T66" s="14" t="inlineStr">
+      <c r="U66" s="14" t="inlineStr">
         <is>
           <t>- Теория речевых актов (speech acts) — «How to Do Things with Words» - Метод анализа обыденного языка через конкретные случаи употребления - (дозаполнить по мере чтения)</t>
         </is>
       </c>
-      <c r="U66" s="14" t="inlineStr">
+      <c r="V66" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/austin-jl/</t>
         </is>
       </c>
-      <c r="V66" s="14" t="n"/>
-      <c r="W66" s="14" t="inlineStr">
+      <c r="W66" s="14" t="n"/>
+      <c r="X66" s="14" t="inlineStr">
         <is>
           <t>Остиновский метод — внимание к фактическому, ситуативному употреблению слов вместо абстрактных дефиниций — методологически близок общему проекту Уилсона: показать, что значения понятий формируются и «блуждают» именно в практике употребления. Возможный методологический союзник, а не оппонент.</t>
         </is>
       </c>
-      <c r="X66" s="14" t="inlineStr">
+      <c r="Y66" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 3</t>
         </is>
       </c>
-      <c r="Y66" s="14" t="inlineStr">
+      <c r="Z66" s="14" t="inlineStr">
         <is>
           <t>chapter_1_v; chapter_3_i</t>
         </is>
       </c>
-      <c r="Z66" s="14" t="inlineStr">
+      <c r="AA66" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/j-l-austin</t>
         </is>
       </c>
-      <c r="AA66" s="14" t="inlineStr">
+      <c r="AB66" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB66" s="14" t="n"/>
+      <c r="AC66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
@@ -7859,83 +8053,84 @@
           <t>2015-04-21</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr">
+      <c r="H67" s="14" t="n"/>
+      <c r="I67" s="14" t="inlineStr">
         <is>
           <t>Лонг-Бранч, Нью-Джерси, США</t>
         </is>
       </c>
-      <c r="I67" s="14" t="inlineStr">
+      <c r="J67" s="14" t="inlineStr">
         <is>
           <t>40.3040, -73.9920</t>
         </is>
       </c>
-      <c r="J67" s="14" t="inlineStr">
+      <c r="K67" s="14" t="inlineStr">
         <is>
           <t>Итака, Нью-Йорк, США</t>
         </is>
       </c>
-      <c r="K67" s="14" t="inlineStr">
+      <c r="L67" s="14" t="inlineStr">
         <is>
           <t>42.4440, -76.5019</t>
         </is>
       </c>
-      <c r="L67" s="14" t="inlineStr">
+      <c r="M67" s="14" t="inlineStr">
         <is>
           <t>Гарвардский университет</t>
         </is>
       </c>
-      <c r="M67" s="14" t="inlineStr">
+      <c r="N67" s="14" t="inlineStr">
         <is>
           <t>Корнеллский университет</t>
         </is>
       </c>
-      <c r="N67" s="14" t="n"/>
       <c r="O67" s="14" t="n"/>
       <c r="P67" s="14" t="n"/>
       <c r="Q67" s="14" t="n"/>
-      <c r="R67" s="14" t="inlineStr">
+      <c r="R67" s="14" t="n"/>
+      <c r="S67" s="14" t="inlineStr">
         <is>
           <t>литературоведение; романтизм</t>
         </is>
       </c>
-      <c r="S67" s="14" t="inlineStr">
+      <c r="T67" s="14" t="inlineStr">
         <is>
           <t>Американский литературовед, один из крупнейших исследователей английского романтизма.</t>
         </is>
       </c>
-      <c r="T67" s="14" t="inlineStr">
+      <c r="U67" s="14" t="inlineStr">
         <is>
           <t>- M. H. Abrams, Natural Supernaturalism (1973), p. 375 - M. H. Abrams, The Correspondent Breeze (1984) - Романтическое восприятие - Взаимодействие ума и мира</t>
         </is>
       </c>
-      <c r="U67" s="14" t="n"/>
       <c r="V67" s="14" t="n"/>
-      <c r="W67" s="14" t="inlineStr">
+      <c r="W67" s="14" t="n"/>
+      <c r="X67" s="14" t="inlineStr">
         <is>
           <t>Абрамс нужен Уилсону как историк романтической доктрины восприятия. Его формулировка показывает, что для романтического поэта жизненное положение человека зависит от того, как его ум взаимодействует с миром в акте восприятия.</t>
         </is>
       </c>
-      <c r="X67" s="14" t="inlineStr">
+      <c r="Y67" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y67" s="14" t="inlineStr">
+      <c r="Z67" s="14" t="inlineStr">
         <is>
           <t>chapter_2_vi</t>
         </is>
       </c>
-      <c r="Z67" s="14" t="inlineStr">
+      <c r="AA67" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/m-h-abrams</t>
         </is>
       </c>
-      <c r="AA67" s="14" t="inlineStr">
+      <c r="AB67" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB67" s="14" t="n"/>
+      <c r="AC67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
@@ -7973,87 +8168,88 @@
           <t>1989-07-02</t>
         </is>
       </c>
-      <c r="H68" s="14" t="inlineStr">
+      <c r="H68" s="14" t="n"/>
+      <c r="I68" s="14" t="inlineStr">
         <is>
           <t>Анн-Арбор, Мичиган, США</t>
         </is>
       </c>
-      <c r="I68" s="14" t="inlineStr">
+      <c r="J68" s="14" t="inlineStr">
         <is>
           <t>42.2808, -83.7430</t>
         </is>
       </c>
-      <c r="J68" s="14" t="inlineStr">
+      <c r="K68" s="14" t="inlineStr">
         <is>
           <t>Питтсбург, США</t>
         </is>
       </c>
-      <c r="K68" s="14" t="inlineStr">
+      <c r="L68" s="14" t="inlineStr">
         <is>
           <t>40.4406, -79.9959</t>
         </is>
       </c>
-      <c r="L68" s="14" t="inlineStr">
+      <c r="M68" s="14" t="inlineStr">
         <is>
           <t>Мичиганский университет; Ориел-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="M68" s="14" t="inlineStr">
+      <c r="N68" s="14" t="inlineStr">
         <is>
           <t>Миннесотский университет; Йельский университет; Питтсбургский университет</t>
         </is>
       </c>
-      <c r="N68" s="14" t="n"/>
       <c r="O68" s="14" t="n"/>
-      <c r="P68" s="14" t="inlineStr">
+      <c r="P68" s="14" t="n"/>
+      <c r="Q68" s="14" t="inlineStr">
         <is>
           <t>Роберт Брэндом</t>
         </is>
       </c>
-      <c r="Q68" s="14" t="n"/>
-      <c r="R68" s="14" t="inlineStr">
+      <c r="R68" s="14" t="n"/>
+      <c r="S68" s="14" t="inlineStr">
         <is>
           <t>эпистемология; философия сознания; философия языка</t>
         </is>
       </c>
-      <c r="S68" s="14" t="inlineStr">
+      <c r="T68" s="14" t="inlineStr">
         <is>
           <t>Американский философ, один из центральных представителей аналитической философии XX века. Известен критикой «мифа о данном» и разработкой идей о концептуальной роли языка и социальных практик.</t>
         </is>
       </c>
-      <c r="T68" s="14" t="inlineStr">
+      <c r="U68" s="14" t="inlineStr">
         <is>
           <t>- Концептуальное мышление - Социальное посредничество - Язык - Прагматизм</t>
         </is>
       </c>
-      <c r="U68" s="14" t="inlineStr">
+      <c r="V68" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/sellars/</t>
         </is>
       </c>
-      <c r="V68" s="14" t="n"/>
-      <c r="W68" s="14" t="inlineStr">
+      <c r="W68" s="14" t="n"/>
+      <c r="X68" s="14" t="inlineStr">
         <is>
           <t>Селларс появляется в обсуждении роли сообщества в формировании концептуального мышления. Он отвергает слишком простую модель, согласно которой внешний мир непосредственно порождает концептуальную систему отдельного индивида без посредничества семьи и общества. Уилсон связывает эту позицию с влиянием прагматизма, особенно Джона Дьюи, но сопротивляется превращению социального посредничества в доказательство того, что индивидуальная концептуализация не может быть связана с реальными объектами.</t>
         </is>
       </c>
-      <c r="X68" s="14" t="inlineStr">
+      <c r="Y68" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y68" s="14" t="n"/>
-      <c r="Z68" s="14" t="inlineStr">
+      <c r="Z68" s="14" t="n"/>
+      <c r="AA68" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/wilfrid-sellars</t>
         </is>
       </c>
-      <c r="AA68" s="14" t="inlineStr">
+      <c r="AB68" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB68" s="14" t="n"/>
+      <c r="AC68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
@@ -8091,75 +8287,76 @@
           <t>1991-08-21</t>
         </is>
       </c>
-      <c r="H69" s="14" t="inlineStr">
+      <c r="H69" s="14" t="n"/>
+      <c r="I69" s="14" t="inlineStr">
         <is>
           <t>Гамбург</t>
         </is>
       </c>
-      <c r="I69" s="14" t="inlineStr">
+      <c r="J69" s="14" t="inlineStr">
         <is>
           <t>53.5511, 9.9937</t>
         </is>
       </c>
-      <c r="J69" s="14" t="inlineStr">
+      <c r="K69" s="14" t="inlineStr">
         <is>
           <t>Поскьяво, Швейцария</t>
         </is>
       </c>
-      <c r="K69" s="14" t="inlineStr">
+      <c r="L69" s="14" t="inlineStr">
         <is>
           <t>46.3245, 10.0573</t>
         </is>
       </c>
-      <c r="L69" s="14" t="n"/>
       <c r="M69" s="14" t="n"/>
       <c r="N69" s="14" t="n"/>
       <c r="O69" s="14" t="n"/>
       <c r="P69" s="14" t="n"/>
       <c r="Q69" s="14" t="n"/>
-      <c r="R69" s="14" t="inlineStr">
+      <c r="R69" s="14" t="n"/>
+      <c r="S69" s="14" t="inlineStr">
         <is>
           <t>проза; драматургия; биография</t>
         </is>
       </c>
-      <c r="S69" s="14" t="inlineStr">
+      <c r="T69" s="14" t="inlineStr">
         <is>
           <t>Немецкий писатель, драматург и художник, автор биографии Моцарта (1982).</t>
         </is>
       </c>
-      <c r="T69" s="14" t="inlineStr">
+      <c r="U69" s="14" t="inlineStr">
         <is>
           <t>- Mozart (1982), биография — цитата о полярности мажора и минора</t>
         </is>
       </c>
-      <c r="U69" s="14" t="n"/>
       <c r="V69" s="14" t="n"/>
-      <c r="W69" s="14" t="inlineStr">
+      <c r="W69" s="14" t="n"/>
+      <c r="X69" s="14" t="inlineStr">
         <is>
           <t>Уилсон цитирует Хильдесхаймера как пример музыковеда, который наивно принимает эмоциональный контраст мажора и минора за «чёткую полярность», подобную включению и выключению, не осознавая, что для значительной части населения земного шара это различие может проходить незамеченным. Эта цитата служит иллюстрацией старой эстетической традиции, которая абсолютизирует культурно-специфические музыкальные свойства.</t>
         </is>
       </c>
-      <c r="X69" s="14" t="inlineStr">
+      <c r="Y69" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y69" s="14" t="inlineStr">
+      <c r="Z69" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z69" s="14" t="inlineStr">
+      <c r="AA69" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/wolfgang-hildesheimer</t>
         </is>
       </c>
-      <c r="AA69" s="14" t="inlineStr">
+      <c r="AB69" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB69" s="14" t="n"/>
+      <c r="AC69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
@@ -8202,58 +8399,59 @@
       <c r="J70" s="14" t="n"/>
       <c r="K70" s="14" t="n"/>
       <c r="L70" s="14" t="n"/>
-      <c r="M70" s="14" t="inlineStr">
+      <c r="M70" s="14" t="n"/>
+      <c r="N70" s="14" t="inlineStr">
         <is>
           <t>Колумбийский университет</t>
         </is>
       </c>
-      <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n"/>
       <c r="P70" s="14" t="n"/>
       <c r="Q70" s="14" t="n"/>
-      <c r="R70" s="14" t="inlineStr">
+      <c r="R70" s="14" t="n"/>
+      <c r="S70" s="14" t="inlineStr">
         <is>
           <t>музыковедение; музыкальная эстетика</t>
         </is>
       </c>
-      <c r="S70" s="14" t="inlineStr">
+      <c r="T70" s="14" t="inlineStr">
         <is>
           <t>Американский музыковед и философ музыки. Автор работ по эстетике и теории музыки, исследовал связь музыкального восприятия с более широкими культурными и психологическими контекстами.</t>
         </is>
       </c>
-      <c r="T70" s="14" t="inlineStr">
+      <c r="U70" s="14" t="inlineStr">
         <is>
           <t>- Musical Thought in Ancient Greece. New York: Columbia University Press. 1964. ISBN "ISBN (identifier)") 978-0231027267. - A Humanistic Philosophy of Music. New York: New York University Press. 1977. ISBN "ISBN (identifier)") 978-0814749739. - Musical Aesthetics: A Historical Reader. New York: Pendragon Press. 1986–90. (3 volumes) - A History of Western Musical Aesthetics. Lincoln: University of Nebraska Press. 1992. ISBN "ISBN (identifier)") 978-0803228634.</t>
         </is>
       </c>
-      <c r="U70" s="14" t="n"/>
       <c r="V70" s="14" t="n"/>
-      <c r="W70" s="14" t="inlineStr">
+      <c r="W70" s="14" t="n"/>
+      <c r="X70" s="14" t="inlineStr">
         <is>
           <t>Уилсон, вероятно, опирается на работы Липпмана (аналогично Хильдесхаймеру) для тезиса о том, что эстетическое восприятие не является чем-то неизменным. Вместе с кейсом Дарвина (charles-darwin) и примером скрипичной музыки восточного Кентукки (skripichnaya-muzyka-vostochnogo-kentukki), Липпман может служить авторитетным источником, показывающим, что наши "струны" музыкальной чувствительности "блуждают" под влиянием физиологических и культурных факторов.</t>
         </is>
       </c>
-      <c r="X70" s="14" t="inlineStr">
+      <c r="Y70" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y70" s="14" t="inlineStr">
+      <c r="Z70" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z70" s="14" t="inlineStr">
+      <c r="AA70" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/edward-lippmann</t>
         </is>
       </c>
-      <c r="AA70" s="14" t="inlineStr">
+      <c r="AB70" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB70" s="14" t="n"/>
+      <c r="AC70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
@@ -8291,87 +8489,88 @@
           <t>2011-12-27</t>
         </is>
       </c>
-      <c r="H71" s="14" t="inlineStr">
+      <c r="H71" s="14" t="n"/>
+      <c r="I71" s="14" t="inlineStr">
         <is>
           <t>Лондон</t>
         </is>
       </c>
-      <c r="I71" s="14" t="inlineStr">
+      <c r="J71" s="14" t="inlineStr">
         <is>
           <t>51.5074, -0.1278</t>
         </is>
       </c>
-      <c r="J71" s="14" t="inlineStr">
+      <c r="K71" s="14" t="inlineStr">
         <is>
           <t>Оксфорд, Англия</t>
         </is>
       </c>
-      <c r="K71" s="14" t="inlineStr">
+      <c r="L71" s="14" t="inlineStr">
         <is>
           <t>51.7520, -1.2577</t>
         </is>
       </c>
-      <c r="L71" s="14" t="inlineStr">
+      <c r="M71" s="14" t="inlineStr">
         <is>
           <t>Крайст-Чёрч, Оксфорд</t>
         </is>
       </c>
-      <c r="M71" s="14" t="inlineStr">
+      <c r="N71" s="14" t="inlineStr">
         <is>
           <t>Колледж Всех Душ, Оксфорд; Нью-колледж, Оксфорд</t>
         </is>
       </c>
-      <c r="N71" s="14" t="n"/>
       <c r="O71" s="14" t="n"/>
-      <c r="P71" s="14" t="inlineStr">
+      <c r="P71" s="14" t="n"/>
+      <c r="Q71" s="14" t="inlineStr">
         <is>
           <t>Криспин Райт</t>
         </is>
       </c>
-      <c r="Q71" s="14" t="n"/>
-      <c r="R71" s="14" t="inlineStr">
+      <c r="R71" s="14" t="n"/>
+      <c r="S71" s="14" t="inlineStr">
         <is>
           <t>философия языка; философия математики; логика</t>
         </is>
       </c>
-      <c r="S71" s="14" t="inlineStr">
+      <c r="T71" s="14" t="inlineStr">
         <is>
           <t>Британский философ, один из ведущих представителей послевоенной аналитической философии, профессор Оксфорда. Крупнейший исследователь и интерпретатор Фреге («Frege: Philosophy of Language», 1973; «Frege: Philosophy of Mathematics», 1991); разработчик семантического антиреализма — программы, согласно которой значение утверждения задаётся условиями его оправданного утверждения (assertibility), что ведёт к пересмотру классической логики в пользу интуиционистской. Известный борец с расизмом (активно участвовал в кампании против расовой дискриминации в Великобритании 1960-х).</t>
         </is>
       </c>
-      <c r="T71" s="14" t="inlineStr">
+      <c r="U71" s="14" t="inlineStr">
         <is>
           <t>- Конкретных работ Даммита в этом фрагменте Уилсон не называет — только общее указание на его критику классической картины. Наиболее вероятные кандидаты — программные статьи по семантическому антиреализму («What is a Theory of Meaning?», 1975, 1976; «The Reality of the Past», 1969) и книга «The Logical Basis of Metaphysics» (1991). - Michael Dummett, “What is a Theory of Meaning?-II” // Truth and Meaning, Gareth Evans and John McDowell, eds. (Oxford: Oxford University Press, 1978), 137.</t>
         </is>
       </c>
-      <c r="U71" s="14" t="n"/>
       <c r="V71" s="14" t="n"/>
-      <c r="W71" s="14" t="inlineStr">
+      <c r="W71" s="14" t="n"/>
+      <c r="X71" s="14" t="inlineStr">
         <is>
           <t>Упомянут в подразделе (viii) как один из трёх современных критиков klassicheskaya-kartina-kontseptsiy (вместе с Куайном и Брэндомом; см. willard-quine, robert-brandom), чья мотивация — «выделить точный способ, которым классическая картина искажает разумный взгляд на человеческие способности».</t>
         </is>
       </c>
-      <c r="X71" s="14" t="inlineStr">
+      <c r="Y71" s="14" t="inlineStr">
         <is>
           <t>гл. 1; гл. 3</t>
         </is>
       </c>
-      <c r="Y71" s="14" t="inlineStr">
+      <c r="Z71" s="14" t="inlineStr">
         <is>
           <t>chapter_1_viii; chapter_3_iii</t>
         </is>
       </c>
-      <c r="Z71" s="14" t="inlineStr">
+      <c r="AA71" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/michael-dummett</t>
         </is>
       </c>
-      <c r="AA71" s="14" t="inlineStr">
+      <c r="AB71" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB71" s="14" t="n"/>
+      <c r="AC71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
@@ -8411,89 +8610,94 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
+          <t>мезотелиома</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
           <t>Чикаго, США</t>
         </is>
       </c>
-      <c r="I72" s="14" t="inlineStr">
+      <c r="J72" s="14" t="inlineStr">
         <is>
           <t>41.8781, -87.6298</t>
         </is>
       </c>
-      <c r="J72" s="14" t="inlineStr">
+      <c r="K72" s="14" t="inlineStr">
         <is>
           <t>Арлингтон, Массачусетс, США</t>
         </is>
       </c>
-      <c r="K72" s="14" t="inlineStr">
+      <c r="L72" s="14" t="inlineStr">
         <is>
           <t>42.4154, -71.1565</t>
         </is>
       </c>
-      <c r="L72" s="14" t="inlineStr">
+      <c r="M72" s="14" t="inlineStr">
         <is>
           <t>Пенсильванский университет; Калифорнийский университет в Лос-Анджелесе</t>
         </is>
       </c>
-      <c r="M72" s="14" t="inlineStr">
+      <c r="N72" s="14" t="inlineStr">
         <is>
           <t>Принстонский университет; Массачусетский технологический институт; Гарвардский университет</t>
         </is>
       </c>
-      <c r="N72" s="14" t="n"/>
-      <c r="O72" s="14" t="inlineStr">
+      <c r="O72" s="14" t="n"/>
+      <c r="P72" s="14" t="inlineStr">
         <is>
           <t>Джерри Фодор</t>
         </is>
       </c>
-      <c r="P72" s="14" t="inlineStr">
+      <c r="Q72" s="14" t="inlineStr">
         <is>
           <t>Уиллард Куайн</t>
         </is>
       </c>
-      <c r="Q72" s="14" t="n"/>
-      <c r="R72" s="14" t="inlineStr">
+      <c r="R72" s="14" t="n"/>
+      <c r="S72" s="14" t="inlineStr">
         <is>
           <t>философия языка; философия сознания; философия науки</t>
         </is>
       </c>
-      <c r="S72" s="14" t="inlineStr">
+      <c r="T72" s="14" t="inlineStr">
         <is>
           <t>Американский философ, один из наиболее влиятельных аналитических философов второй половины XX века. Работал в философии языка, сознания и науки; известен мысленным экспериментом «Земля-двойник» и тезисом «значение не в голове», функционализмом в философии сознания, а также сменой ряда собственных позиций на протяжении карьеры (от научного реализма к внутреннему реализму и далее к прагматическому реализму).</t>
         </is>
       </c>
-      <c r="T72" s="14" t="inlineStr">
+      <c r="U72" s="14" t="inlineStr">
         <is>
           <t>- Совместная работа пришлась примерно на конец 1960-х – 1976 год: Уилсон закончил бакалавриат в Университете Вашингтона в 1969-м, затем поступил в докторантуру Гарварда, где научным руководителем был Патнэм, и защитил диссертацию в 1976 году. - Работы Патнэма, которые напрямую связаны с тематикой "Блуждающих значений": 1. Putnam H. Is Semantic Possible?//Metaphilosophy, 1970, Т. 1, N 3, C. 187-201. 2. Putnam H. The Meaning of «Meaning»//Minnesota Studies in the Philosophy of Science, 1975, Т. 7, C. 131-193.</t>
         </is>
       </c>
-      <c r="U72" s="14" t="n"/>
       <c r="V72" s="14" t="n"/>
-      <c r="W72" s="14" t="inlineStr">
+      <c r="W72" s="14" t="n"/>
+      <c r="X72" s="14" t="inlineStr">
         <is>
           <t>Уилсон прямо пишет в предисловии, что его конкретный фокус на предикатах и понятиях вырос из его собственной дипломной (диссертационной) работы, написанной под руководством Патнэма, а также из работ Патнэма того периода.</t>
         </is>
       </c>
-      <c r="X72" s="14" t="inlineStr">
+      <c r="Y72" s="14" t="inlineStr">
         <is>
           <t>предисловие</t>
         </is>
       </c>
-      <c r="Y72" s="14" t="inlineStr">
+      <c r="Z72" s="14" t="inlineStr">
         <is>
           <t>predislovie</t>
         </is>
       </c>
-      <c r="Z72" s="14" t="inlineStr">
+      <c r="AA72" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/hilary-putnam</t>
         </is>
       </c>
-      <c r="AA72" s="14" t="inlineStr">
+      <c r="AB72" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB72" s="14" t="n"/>
+      <c r="AC72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
@@ -8533,85 +8737,90 @@
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
+          <t>болезнь Паркинсона, последствия инсульта</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
           <t>Нью-Йорк, США</t>
         </is>
       </c>
-      <c r="I73" s="14" t="inlineStr">
+      <c r="J73" s="14" t="inlineStr">
         <is>
           <t>40.7128, -74.0060</t>
         </is>
       </c>
-      <c r="J73" s="14" t="inlineStr">
+      <c r="K73" s="14" t="inlineStr">
         <is>
           <t>Нью-Йорк, США</t>
         </is>
       </c>
-      <c r="K73" s="14" t="inlineStr">
+      <c r="L73" s="14" t="inlineStr">
         <is>
           <t>40.7128, -74.0060</t>
         </is>
       </c>
-      <c r="L73" s="14" t="inlineStr">
+      <c r="M73" s="14" t="inlineStr">
         <is>
           <t>Колумбийский колледж; Принстонский университет</t>
         </is>
       </c>
-      <c r="M73" s="14" t="inlineStr">
+      <c r="N73" s="14" t="inlineStr">
         <is>
           <t>Массачусетский технологический институт; Ратгерский университет</t>
         </is>
       </c>
-      <c r="N73" s="14" t="inlineStr">
+      <c r="O73" s="14" t="inlineStr">
         <is>
           <t>Хилари Патнэм</t>
         </is>
       </c>
-      <c r="O73" s="14" t="n"/>
       <c r="P73" s="14" t="n"/>
       <c r="Q73" s="14" t="n"/>
-      <c r="R73" s="14" t="inlineStr">
+      <c r="R73" s="14" t="n"/>
+      <c r="S73" s="14" t="inlineStr">
         <is>
           <t>философия сознания; когнитивная наука</t>
         </is>
       </c>
-      <c r="S73" s="14" t="inlineStr">
+      <c r="T73" s="14" t="inlineStr">
         <is>
           <t>Американский философ и когнитивист (1935–2017), автор теории языка мысли и концептуального атомизма. Основная работа, на которую ссылается Уилсон: Concepts: Where Cognitive Science Went Wrong (Oxford UP, 1998).</t>
         </is>
       </c>
-      <c r="T73" s="14" t="inlineStr">
+      <c r="U73" s="14" t="inlineStr">
         <is>
           <t>- J. Fodor, Concepts: Where Cognitive Science Went Wrong (Oxford UP, 1998)</t>
         </is>
       </c>
-      <c r="U73" s="14" t="n"/>
       <c r="V73" s="14" t="n"/>
-      <c r="W73" s="14" t="inlineStr">
+      <c r="W73" s="14" t="n"/>
+      <c r="X73" s="14" t="inlineStr">
         <is>
           <t>Книга Фодора приводится как образец обсуждения, «сосредоточенного исключительно» на генерических примерах: «быть собакой» и «быть дверной ручкой». По мнению Уилсона, ни один из таких образцов вряд ли выявит тонкие напряжения «содержания», важные для его исследования, и такая избирательность свидетельствует об «относительной слепоте к фундаментальным вопросам».</t>
         </is>
       </c>
-      <c r="X73" s="14" t="inlineStr">
+      <c r="Y73" s="14" t="inlineStr">
         <is>
           <t>гл. 3</t>
         </is>
       </c>
-      <c r="Y73" s="14" t="inlineStr">
+      <c r="Z73" s="14" t="inlineStr">
         <is>
           <t>chapter_3_iv</t>
         </is>
       </c>
-      <c r="Z73" s="14" t="inlineStr">
+      <c r="AA73" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/dzherri-fodor</t>
         </is>
       </c>
-      <c r="AA73" s="14" t="inlineStr">
+      <c r="AB73" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB73" s="14" t="n"/>
+      <c r="AC73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
@@ -8654,58 +8863,59 @@
       <c r="J74" s="14" t="n"/>
       <c r="K74" s="14" t="n"/>
       <c r="L74" s="14" t="n"/>
-      <c r="M74" s="14" t="inlineStr">
+      <c r="M74" s="14" t="n"/>
+      <c r="N74" s="14" t="inlineStr">
         <is>
           <t>Университет Северной Каролины в Чапел-Хилле</t>
         </is>
       </c>
-      <c r="N74" s="14" t="n"/>
       <c r="O74" s="14" t="n"/>
       <c r="P74" s="14" t="n"/>
       <c r="Q74" s="14" t="n"/>
-      <c r="R74" s="14" t="inlineStr">
+      <c r="R74" s="14" t="n"/>
+      <c r="S74" s="14" t="inlineStr">
         <is>
           <t>американистика; фольклористика; культурная политика</t>
         </is>
       </c>
-      <c r="S74" s="14" t="inlineStr">
+      <c r="T74" s="14" t="inlineStr">
         <is>
           <t>Американский исследователь фольклора и культурной политики, автор книги All That Is Native and Fine (1983).</t>
         </is>
       </c>
-      <c r="T74" s="14" t="inlineStr">
+      <c r="U74" s="14" t="inlineStr">
         <is>
           <t>- David E. Whisnant, All That Is Native and Fine (Chapel Hill: University of North Carolina Press, 1983), pp. xiii–xiv, 260–261 - Культурная «инаковость» (otherness) - Политика культуры - Сохранение и возрождение культуры - Колониальное подчинение - Освоение ресурсов - Классовое неравенство</t>
         </is>
       </c>
-      <c r="U74" s="14" t="n"/>
       <c r="V74" s="14" t="n"/>
-      <c r="W74" s="14" t="inlineStr">
+      <c r="W74" s="14" t="n"/>
+      <c r="X74" s="14" t="inlineStr">
         <is>
           <t>Уизнант рассматривает фольклористские практики через проблему культурной «инаковости» и политики культуры. Его критика показывает, как слова вроде «культура», «сохранение» и «возрождение» могут скрывать более глубокие социальные отношения — колониальное подчинение, освоение ресурсов и классовое неравенство. Уилсон соглашается с рядом конкретных критических замечаний Уизнанта, но отвергает вывод о том, что вся система музыкальных классификаций безнадёжно испорчена социальными и капиталистическими «шорами».</t>
         </is>
       </c>
-      <c r="X74" s="14" t="inlineStr">
+      <c r="Y74" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y74" s="14" t="inlineStr">
+      <c r="Z74" s="14" t="inlineStr">
         <is>
           <t>chapter_2_v</t>
         </is>
       </c>
-      <c r="Z74" s="14" t="inlineStr">
+      <c r="AA74" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/david-whisnant</t>
         </is>
       </c>
-      <c r="AA74" s="14" t="inlineStr">
+      <c r="AB74" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB74" s="14" t="n"/>
+      <c r="AC74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
@@ -8742,44 +8952,45 @@
       <c r="P75" s="14" t="n"/>
       <c r="Q75" s="14" t="n"/>
       <c r="R75" s="14" t="n"/>
-      <c r="S75" s="14" t="inlineStr">
+      <c r="S75" s="14" t="n"/>
+      <c r="T75" s="14" t="inlineStr">
         <is>
           <t>Профессор философии Университета Вашингтона (Сиэтл): пришёл на факультет в 1966 году, был его деканом в 1980–1982-м, вышел на пенсию в 2003-м, умер 18 апреля 2022 года в Сиэтле (согласно некрологу Reed College). Точный год рождения в надёжных источниках не указан . Б. Аспирантуру проходил в Корнеллском университете (поступил в 1962-м, защитился только в 1972-м), до этого учился в Рид-колледже под руководством Марвина Левича и Хьюго Бедо, где занимался этикой. В Корнелле переключился на философию сознания — под влиянием состава факультета (Сидни Шумейкер, Кит Доннеллан, Норман Малкольм, Дэвид Сакс). Преподавал философию сознания и историю философии; любимым дидактическим приёмом было разбирать со студентами эксперименты Сперри и Газзаниги на пациентах с рассечённым мозолистым телом как повод для философских головоломок о сознании.</t>
         </is>
       </c>
-      <c r="T75" s="14" t="inlineStr">
+      <c r="U75" s="14" t="inlineStr">
         <is>
           <t>- Прямых работ Маркса, на которые бы ссылался Уилсон, не выявлено — роль чисто педагогическая/личная, не библиографическая - Собственная область Маркса — философия сознания (в частности, философские следствия экспериментов на пациентах с расщеплённым мозгом)</t>
         </is>
       </c>
-      <c r="U75" s="14" t="n"/>
       <c r="V75" s="14" t="n"/>
-      <c r="W75" s="14" t="inlineStr">
+      <c r="W75" s="14" t="n"/>
+      <c r="X75" s="14" t="inlineStr">
         <is>
           <t>Не философский источник содержания, а личный учитель на раннем этапе: Уилсон пишет в предисловии, что в молодости много читал Витгенштейна «под умелым руководством» (able tutelage) Чарльза Маркса, и находит примечательным, что сам он с Витгенштейном часто «блуждают по схожим темам» в философских странствиях (см. карточку ludwig-wittgenstein). Поскольку Маркс пришёл в Университет Вашингтона в 1966 году, а Уилсон получил там бакалавриат в 1969-м, речь, судя по всему, идёт именно об университетском (не аспирантском) периоде — то есть Маркс был для Уилсона учителем-бакалаврского уровня, предшествовавшим гарвардскому научному руководству Патнэма (см. hilary-putnam). Специализация самого Маркса — философия сознания, а не история аналитической философии языка; собственно витгенштейноведом он, судя по всему, не был. Зато среди его учителей в Корнелле был Норман Малкольм — один из ближайших личных учеников и друзей самого Витгенштейна в Кембридже, автор мемуарной книги о нём. Если Маркс действительно перенял интерес к Витгенштейну через Малкольма (что напрямую источниками не подтверждено, только через совпадение по месту и времени учёбы), то перед нами двухступенчатая личная передача: Витгенштейн → Малкольм (личный ученик) → Маркс (аспирант в Корнелле в те же годы) → Уилсон (студент, читающий Витгенштейна под руководством Маркса). Это интересная гипотеза, требующая специально исследования.</t>
         </is>
       </c>
-      <c r="X75" s="14" t="inlineStr">
+      <c r="Y75" s="14" t="inlineStr">
         <is>
           <t>предисловие</t>
         </is>
       </c>
-      <c r="Y75" s="14" t="inlineStr">
+      <c r="Z75" s="14" t="inlineStr">
         <is>
           <t>predislovie</t>
         </is>
       </c>
-      <c r="Z75" s="14" t="inlineStr">
+      <c r="AA75" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/charles-marks</t>
         </is>
       </c>
-      <c r="AA75" s="14" t="inlineStr">
+      <c r="AB75" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB75" s="14" t="n"/>
+      <c r="AC75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
@@ -8817,63 +9028,64 @@
       <c r="I76" s="14" t="n"/>
       <c r="J76" s="14" t="n"/>
       <c r="K76" s="14" t="n"/>
-      <c r="L76" s="14" t="inlineStr">
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="14" t="inlineStr">
         <is>
           <t>Стэнфордский университет; Калифорнийский технологический институт; Калифорнийский университет в Ирвайне</t>
         </is>
       </c>
-      <c r="M76" s="14" t="inlineStr">
+      <c r="N76" s="14" t="inlineStr">
         <is>
           <t>Университет Нью-Гэмпшира</t>
         </is>
       </c>
-      <c r="N76" s="14" t="n"/>
       <c r="O76" s="14" t="n"/>
       <c r="P76" s="14" t="n"/>
       <c r="Q76" s="14" t="n"/>
-      <c r="R76" s="14" t="inlineStr">
+      <c r="R76" s="14" t="n"/>
+      <c r="S76" s="14" t="inlineStr">
         <is>
           <t>электротехника; история науки; популяризация математики</t>
         </is>
       </c>
-      <c r="S76" s="14" t="inlineStr">
+      <c r="T76" s="14" t="inlineStr">
         <is>
           <t>Родился 26 ноября 1940 года в Калифорнии, закончил школу в 1958-м, а затем получил степень бакалавра в Стэнфорде (1962), магистра — в Калтехе (1963) и докторскую степень — в Университете Калифорнии в Ирвайне (1972), всё — по электротехнике. До перехода в академию несколько лет проработал инженером-разработчиком цифровой логики и радиолокационных систем в аэрокосмической отрасли Южной Калифорнии. Преподавал в Харви Мадд Колледже, Университете Вирджинии и Военно-морской аспирантуре в Монтерее, а с 2004 года — почётный профессор электротехники Университета Нью-Гэмпшира. Помимо биографии Хевисайда, написал научно-популярные биографии Джорджа Буля и Клода Шеннона (совместную — под названием «The Logician and the Engineer»), ряд книг по истории математических констант и понятий (формула Эйлера, дзета-функция Римана, мнимая единица), а также несколько книг о физике и философских парадоксах путешествий во времени. Также опубликовал около двух десятков научно-фантастических рассказов в журналах Analog, Omni и Twilight Zone. В 1979 году получил первую премию Harry Rowe Mimno от IEEE, а в 2017-м — премию Chandler Davis за выдающийся научно-популярный стиль изложения математики.</t>
         </is>
       </c>
-      <c r="T76" s="14" t="inlineStr">
+      <c r="U76" s="14" t="inlineStr">
         <is>
           <t>1. Nahin P.J. Oliver Heaviside: The Life, Work, and Times of an Electrical Genius of the Victorian Age : A Johns Hopkins paperback. – Johns Hopkins University Press, 2002.</t>
         </is>
       </c>
-      <c r="U76" s="14" t="n"/>
       <c r="V76" s="14" t="n"/>
-      <c r="W76" s="14" t="inlineStr">
+      <c r="W76" s="14" t="n"/>
+      <c r="X76" s="14" t="inlineStr">
         <is>
           <t>Уилсон уделяет особое внимание биографии Хевисайда, написанной Полом Нахином как исторического источника при описании конфликта Хевисайда с академическим математическим сообществом</t>
         </is>
       </c>
-      <c r="X76" s="14" t="inlineStr">
+      <c r="Y76" s="14" t="inlineStr">
         <is>
           <t>предисловие</t>
         </is>
       </c>
-      <c r="Y76" s="14" t="inlineStr">
+      <c r="Z76" s="14" t="inlineStr">
         <is>
           <t>predislovie</t>
         </is>
       </c>
-      <c r="Z76" s="14" t="inlineStr">
+      <c r="AA76" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/p-j-nahin</t>
         </is>
       </c>
-      <c r="AA76" s="14" t="inlineStr">
+      <c r="AB76" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB76" s="14" t="n"/>
+      <c r="AC76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
@@ -8913,93 +9125,98 @@
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
+          <t>осложнения сахарного диабета</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
           <t>Оберлин, Огайо, США</t>
         </is>
       </c>
-      <c r="I77" s="14" t="inlineStr">
+      <c r="J77" s="14" t="inlineStr">
         <is>
           <t>41.2939, -82.2174</t>
         </is>
       </c>
-      <c r="J77" s="14" t="inlineStr">
+      <c r="K77" s="14" t="inlineStr">
         <is>
           <t>Принстон, Нью-Джерси, США</t>
         </is>
       </c>
-      <c r="K77" s="14" t="inlineStr">
+      <c r="L77" s="14" t="inlineStr">
         <is>
           <t>40.3573, -74.6672</t>
         </is>
       </c>
-      <c r="L77" s="14" t="inlineStr">
+      <c r="M77" s="14" t="inlineStr">
         <is>
           <t>Суортмор-колледж; Гарвардский университет</t>
         </is>
       </c>
-      <c r="M77" s="14" t="inlineStr">
+      <c r="N77" s="14" t="inlineStr">
         <is>
           <t>Калифорнийский университет в Лос-Анджелесе; Принстонский университет</t>
         </is>
       </c>
-      <c r="N77" s="14" t="inlineStr">
+      <c r="O77" s="14" t="inlineStr">
         <is>
           <t>Уиллард Куайн</t>
         </is>
       </c>
-      <c r="O77" s="14" t="inlineStr">
+      <c r="P77" s="14" t="inlineStr">
         <is>
           <t>Роберт Брэндом</t>
         </is>
       </c>
-      <c r="P77" s="14" t="n"/>
       <c r="Q77" s="14" t="n"/>
-      <c r="R77" s="14" t="inlineStr">
+      <c r="R77" s="14" t="n"/>
+      <c r="S77" s="14" t="inlineStr">
         <is>
           <t>метафизика; философия языка; модальная логика</t>
         </is>
       </c>
-      <c r="S77" s="14" t="inlineStr">
+      <c r="T77" s="14" t="inlineStr">
         <is>
           <t>Американский философ, один из самых влиятельных аналитических метафизиков второй половины XX века. Профессор Принстонского университета, ученик Куайна. Известен доктриной модального реализма — тезисом, что все логически возможные миры существуют реально, наравне с нашим (главное изложение: «On the Plurality of Worlds», 1986); работами в философии сознания (функционализм), философии науки, теории каузальности (каузальность через контрфактуалы), теории игр и конвенций языка («Convention», 1969).</t>
         </is>
       </c>
-      <c r="T77" s="14" t="inlineStr">
+      <c r="U77" s="14" t="inlineStr">
         <is>
           <t>- В (viii) конкретных работ не назвал — только общее указание, что Льюис укладывается в классическую картину. Обещанная точка сверки — приложение к главе 3.</t>
         </is>
       </c>
-      <c r="U77" s="14" t="inlineStr">
+      <c r="V77" s="14" t="inlineStr">
         <is>
           <t>https://plato.stanford.edu/entries/david-lewis/</t>
         </is>
       </c>
-      <c r="V77" s="14" t="n"/>
-      <c r="W77" s="14" t="inlineStr">
+      <c r="W77" s="14" t="n"/>
+      <c r="X77" s="14" t="inlineStr">
         <is>
           <t>Упомянут в подразделе (viii) как редкий пример современного философа, чей взгляд на концепции Уилсон расценивает как «полностью классический по качеству» — то есть как «тонкую настройку Рассела» (bertrand-russell) в рамках klassicheskaya-kartina-kontseptsiy. Уилсон прямо отмечает, что использовал некоторые идеи Льюиса в приложении к главе 3 (там, где систематизирует тезисы классической картины). В отличие от Куайна , Даммита и Брэндома, Льюис представлен как более утончённый продолжатель.</t>
         </is>
       </c>
-      <c r="X77" s="14" t="inlineStr">
+      <c r="Y77" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y77" s="14" t="inlineStr">
+      <c r="Z77" s="14" t="inlineStr">
         <is>
           <t>chapter_1_viii</t>
         </is>
       </c>
-      <c r="Z77" s="14" t="inlineStr">
+      <c r="AA77" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/david-lewis</t>
         </is>
       </c>
-      <c r="AA77" s="14" t="inlineStr">
+      <c r="AB77" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB77" s="14" t="n"/>
+      <c r="AC77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
@@ -9037,63 +9254,64 @@
       <c r="I78" s="14" t="n"/>
       <c r="J78" s="14" t="n"/>
       <c r="K78" s="14" t="n"/>
-      <c r="L78" s="14" t="inlineStr">
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="14" t="inlineStr">
         <is>
           <t>Тринити-колледж, Кембридж; Оксфордский университет</t>
         </is>
       </c>
-      <c r="M78" s="14" t="inlineStr">
+      <c r="N78" s="14" t="inlineStr">
         <is>
           <t>Сент-Эндрюсский университет; Нью-Йоркский университет; Университет Стерлинга</t>
         </is>
       </c>
-      <c r="N78" s="14" t="n"/>
       <c r="O78" s="14" t="n"/>
-      <c r="P78" s="14" t="inlineStr">
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="inlineStr">
         <is>
           <t>Майкл Даммит</t>
         </is>
       </c>
-      <c r="Q78" s="14" t="n"/>
-      <c r="R78" s="14" t="inlineStr">
+      <c r="R78" s="14" t="n"/>
+      <c r="S78" s="14" t="inlineStr">
         <is>
           <t>философия языка; философия математики; эпистемология</t>
         </is>
       </c>
-      <c r="S78" s="14" t="inlineStr">
+      <c r="T78" s="14" t="inlineStr">
         <is>
           <t>Британский аналитический философ, известный работами по проблемам истины, реализму, антиреализму и философии языка.</t>
         </is>
       </c>
-      <c r="T78" s="14" t="inlineStr">
+      <c r="U78" s="14" t="inlineStr">
         <is>
           <t>- Crispin Wright, Truth and Objectivity (1992) - Объективность - Истина - Корреспонденция - Антиреализм</t>
         </is>
       </c>
-      <c r="U78" s="14" t="n"/>
       <c r="V78" s="14" t="n"/>
-      <c r="W78" s="14" t="inlineStr">
+      <c r="W78" s="14" t="n"/>
+      <c r="X78" s="14" t="inlineStr">
         <is>
           <t>Уилсон приводит проект Райта в Truth and Objectivity как пример более мягкой попытки сохранить понятие объективности после отказа от наивной модели прямого соответствия слова и мира. Он подчёркивает, что точные мотивы Райта ему не вполне ясны.</t>
         </is>
       </c>
-      <c r="X78" s="14" t="inlineStr">
+      <c r="Y78" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y78" s="14" t="n"/>
-      <c r="Z78" s="14" t="inlineStr">
+      <c r="Z78" s="14" t="n"/>
+      <c r="AA78" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/crispin-wright</t>
         </is>
       </c>
-      <c r="AA78" s="14" t="inlineStr">
+      <c r="AB78" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB78" s="14" t="n"/>
+      <c r="AC78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
@@ -9127,75 +9345,76 @@
         </is>
       </c>
       <c r="G79" s="14" t="n"/>
-      <c r="H79" s="14" t="inlineStr">
+      <c r="H79" s="14" t="n"/>
+      <c r="I79" s="14" t="inlineStr">
         <is>
           <t>Мельбурн, Австралия</t>
         </is>
       </c>
-      <c r="I79" s="14" t="inlineStr">
+      <c r="J79" s="14" t="inlineStr">
         <is>
           <t>-37.8136, 144.9631</t>
         </is>
       </c>
-      <c r="J79" s="14" t="n"/>
       <c r="K79" s="14" t="n"/>
-      <c r="L79" s="14" t="inlineStr">
+      <c r="L79" s="14" t="n"/>
+      <c r="M79" s="14" t="inlineStr">
         <is>
           <t>Мельбурнский университет; Университет Ла Троба</t>
         </is>
       </c>
-      <c r="M79" s="14" t="inlineStr">
+      <c r="N79" s="14" t="inlineStr">
         <is>
           <t>Австралийский национальный университет</t>
         </is>
       </c>
-      <c r="N79" s="14" t="n"/>
       <c r="O79" s="14" t="n"/>
       <c r="P79" s="14" t="n"/>
       <c r="Q79" s="14" t="n"/>
-      <c r="R79" s="14" t="inlineStr">
+      <c r="R79" s="14" t="n"/>
+      <c r="S79" s="14" t="inlineStr">
         <is>
           <t>философия сознания; метафизика</t>
         </is>
       </c>
-      <c r="S79" s="14" t="inlineStr">
+      <c r="T79" s="14" t="inlineStr">
         <is>
           <t>Австралийский философ, профессор Принстонского и Австралийского национального университетов. Известен аргументом «комнаты Мэри» (knowledge argument) против физикализма, работами по философии сознания, квалиа и метафизике. Автор книги «От метафизики к этике» (From Metaphysics to Ethics, 1998).</t>
         </is>
       </c>
-      <c r="T79" s="14" t="inlineStr">
+      <c r="U79" s="14" t="inlineStr">
         <is>
           <t>- «Проблемы локальности» (locality problems) — вопросы о том, где (в какой сфере) атрибут получает своё основное распространение</t>
         </is>
       </c>
-      <c r="U79" s="14" t="n"/>
       <c r="V79" s="14" t="n"/>
-      <c r="W79" s="14" t="inlineStr">
+      <c r="W79" s="14" t="n"/>
+      <c r="X79" s="14" t="inlineStr">
         <is>
           <t>Уилсон упоминает Джексона в контексте обсуждения субъективистских моделей музыкальных атрибутов. Он ссылается на джексоновский термин «проблемы локальности» (locality problems), которым тот обозначает вопросы о том, в какой сфере (физической или ментальной) атрибут получает своё основное распространение. Уилсон использует это понятие, чтобы охарактеризовать субъективистскую позицию, согласно которой музыкальные свойства типа «выражение печали» должны быть локализованы в ментальной сфере.</t>
         </is>
       </c>
-      <c r="X79" s="14" t="inlineStr">
+      <c r="Y79" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y79" s="14" t="inlineStr">
+      <c r="Z79" s="14" t="inlineStr">
         <is>
           <t>chapter_2_iv</t>
         </is>
       </c>
-      <c r="Z79" s="14" t="inlineStr">
+      <c r="AA79" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/frank-jackson</t>
         </is>
       </c>
-      <c r="AA79" s="14" t="inlineStr">
+      <c r="AB79" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB79" s="14" t="n"/>
+      <c r="AC79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
@@ -9234,58 +9453,59 @@
       <c r="J80" s="14" t="n"/>
       <c r="K80" s="14" t="n"/>
       <c r="L80" s="14" t="n"/>
-      <c r="M80" s="14" t="inlineStr">
+      <c r="M80" s="14" t="n"/>
+      <c r="N80" s="14" t="inlineStr">
         <is>
           <t>Брауновский университет</t>
         </is>
       </c>
-      <c r="N80" s="14" t="n"/>
       <c r="O80" s="14" t="n"/>
       <c r="P80" s="14" t="n"/>
       <c r="Q80" s="14" t="n"/>
-      <c r="R80" s="14" t="inlineStr">
+      <c r="R80" s="14" t="n"/>
+      <c r="S80" s="14" t="inlineStr">
         <is>
           <t>этномузыкология; фольклористика</t>
         </is>
       </c>
-      <c r="S80" s="14" t="inlineStr">
+      <c r="T80" s="14" t="inlineStr">
         <is>
           <t>Американский этномузыковед и фольклорист. В рассматриваемом Уилсоном контексте Титон защищает такой вариант этномузыкологии, в котором главное место занимает понимание жизненного опыта людей, создающих музыку, а не его естественно-научное объяснение.</t>
         </is>
       </c>
-      <c r="T80" s="14" t="inlineStr">
+      <c r="U80" s="14" t="inlineStr">
         <is>
           <t>- Jeff Todd Titon, “Reconstructing the Blues” // Neil V. Rosenberg, ed., Transforming Tradition (1993), p. 238 - Jeff Todd Titon, “Knowing Fieldwork” // G. F. Barz and T. J. Cooley, eds., Shadows in the Field, pp. 87–100 - Понимание вместо объяснения - Музыка как социально сконструированный культурный феномен - Совместное музицирование и полевое участие - Субъективный музыкальный опыт</t>
         </is>
       </c>
-      <c r="U80" s="14" t="n"/>
       <c r="V80" s="14" t="n"/>
-      <c r="W80" s="14" t="inlineStr">
+      <c r="W80" s="14" t="n"/>
+      <c r="X80" s="14" t="inlineStr">
         <is>
           <t>Титон предлагает философское обоснование собственных этномузыкологических практик. Он рассматривает музыку как социально сконструированный культурный феномен и подчёркивает значение непосредственного музыкального опыта, совместного музицирования и полевой работы. Уилсон интерпретирует эту позицию как движение к субъективизму и отмечает в ней «сильный привкус» партиципативного идеализма. В дальнейшем критика Титона связывается с вопросом о том, может ли внутренний музыкальный опыт служить основанием публичного гуманитарного знания.</t>
         </is>
       </c>
-      <c r="X80" s="14" t="inlineStr">
+      <c r="Y80" s="14" t="inlineStr">
         <is>
           <t>гл. 2; гл. 3</t>
         </is>
       </c>
-      <c r="Y80" s="14" t="inlineStr">
+      <c r="Z80" s="14" t="inlineStr">
         <is>
           <t>chapter_2_v; chapter_3_iv</t>
         </is>
       </c>
-      <c r="Z80" s="14" t="inlineStr">
+      <c r="AA80" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/jeff-todd-titon</t>
         </is>
       </c>
-      <c r="AA80" s="14" t="inlineStr">
+      <c r="AB80" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB80" s="14" t="n"/>
+      <c r="AC80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
@@ -9323,63 +9543,64 @@
       <c r="I81" s="14" t="n"/>
       <c r="J81" s="14" t="n"/>
       <c r="K81" s="14" t="n"/>
-      <c r="L81" s="14" t="inlineStr">
+      <c r="L81" s="14" t="n"/>
+      <c r="M81" s="14" t="inlineStr">
         <is>
           <t>Суортмор-колледж; Массачусетский технологический институт</t>
         </is>
       </c>
-      <c r="M81" s="14" t="inlineStr">
+      <c r="N81" s="14" t="inlineStr">
         <is>
           <t>Брандейский университет; Университет Тафтса</t>
         </is>
       </c>
-      <c r="N81" s="14" t="n"/>
       <c r="O81" s="14" t="n"/>
       <c r="P81" s="14" t="n"/>
       <c r="Q81" s="14" t="n"/>
-      <c r="R81" s="14" t="inlineStr">
+      <c r="R81" s="14" t="n"/>
+      <c r="S81" s="14" t="inlineStr">
         <is>
           <t>лингвистика; семантика; когнитивная наука; музыкальное познание</t>
         </is>
       </c>
-      <c r="S81" s="14" t="inlineStr">
+      <c r="T81" s="14" t="inlineStr">
         <is>
           <t>Американский лингвист, один из ведущих специалистов по семантике и когнитивной лингвистике, работал над теорией концептуальной семантики (Conceptual Semantics) — альтернативой чисто формальным подходам к значению, связывающей языковую семантику со структурами мышления в целом. Долгое время работал в Университете Брандейса и Университете Тафтса.</t>
         </is>
       </c>
-      <c r="T81" s="14" t="inlineStr">
+      <c r="U81" s="14" t="inlineStr">
         <is>
           <t>- Ray Jackendoff, "What is a Concept that a Person May Grasp It?" // Eric Margolis and Stephen Laurence, eds., Concepts (Cambridge, Mass.: MIT Press, 1999), 307</t>
         </is>
       </c>
-      <c r="U81" s="14" t="n"/>
       <c r="V81" s="14" t="n"/>
-      <c r="W81" s="14" t="inlineStr">
+      <c r="W81" s="14" t="n"/>
+      <c r="X81" s="14" t="inlineStr">
         <is>
           <t>Процитирован (по статье «What is a Concept that a Person May Grasp It?», 1999) как представитель влиятельного лингвистического аргумента в пользу семантической завершённости: раз говорящие способны понимать бесконечное количество ранее не встречавшихся предложений («креативность языка»), то в основе этого должен лежать конечный набор полностью усвоенных «ментальных примитивов» и принципов их композиции — а базовыми единицами этого набора являются лексические концепции, выражаемые словами. Уилсон приводит эту цитату не для того, чтобы опровергнуть лингвистику как таковую, а чтобы показать, откуда происходит философская привлекательность тезиса о семантической завершённости, который сам он оспаривает.</t>
         </is>
       </c>
-      <c r="X81" s="14" t="inlineStr">
+      <c r="Y81" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y81" s="14" t="inlineStr">
+      <c r="Z81" s="14" t="inlineStr">
         <is>
           <t>chapter_1_vi</t>
         </is>
       </c>
-      <c r="Z81" s="14" t="inlineStr">
+      <c r="AA81" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/ray-jackendoff</t>
         </is>
       </c>
-      <c r="AA81" s="14" t="inlineStr">
+      <c r="AB81" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB81" s="14" t="n"/>
+      <c r="AC81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
@@ -9417,71 +9638,72 @@
       <c r="I82" s="14" t="n"/>
       <c r="J82" s="14" t="n"/>
       <c r="K82" s="14" t="n"/>
-      <c r="L82" s="14" t="inlineStr">
+      <c r="L82" s="14" t="n"/>
+      <c r="M82" s="14" t="inlineStr">
         <is>
           <t>Йельский университет; Принстонский университет</t>
         </is>
       </c>
-      <c r="M82" s="14" t="inlineStr">
+      <c r="N82" s="14" t="inlineStr">
         <is>
           <t>Питтсбургский университет</t>
         </is>
       </c>
-      <c r="N82" s="14" t="inlineStr">
+      <c r="O82" s="14" t="inlineStr">
         <is>
           <t>Дэвид Льюис</t>
         </is>
       </c>
-      <c r="O82" s="14" t="n"/>
-      <c r="P82" s="14" t="inlineStr">
+      <c r="P82" s="14" t="n"/>
+      <c r="Q82" s="14" t="inlineStr">
         <is>
           <t>Уилфрид Селларс</t>
         </is>
       </c>
-      <c r="Q82" s="14" t="n"/>
-      <c r="R82" s="14" t="inlineStr">
+      <c r="R82" s="14" t="n"/>
+      <c r="S82" s="14" t="inlineStr">
         <is>
           <t>философия языка; инференциализм; прагматизм</t>
         </is>
       </c>
-      <c r="S82" s="14" t="inlineStr">
+      <c r="T82" s="14" t="inlineStr">
         <is>
           <t>Американский философ, коллега Уилсона по кафедре философии Питтсбургского университета (Distinguished Professor). Ученик Ричарда Рорти. Наиболее известен программой инференциализма — теорией значения, согласно которой содержание понятий задаётся не отношением к миру (как в референциальных теориях), а сетью инференциальных обязательств: понимать значение утверждения — это уметь пользоваться им в игре «давания и требования оснований» (giving and asking for reasons). Главное изложение — фундаментальная монография «Making It Explicit» (1994); более доступная версия — «Articulating Reasons» (2000). Работает также над Гегелем («A Spirit of Trust», 2019).</t>
         </is>
       </c>
-      <c r="T82" s="14" t="inlineStr">
+      <c r="U82" s="14" t="inlineStr">
         <is>
           <t>- Конкретных работ Брэндома в этом фрагменте Уилсон не называет — только общее указание на его критику классической картины. Наиболее вероятные кандидаты — «Making It Explicit» (Cambridge, Mass.: Harvard University Press, 1994) и «Articulating Reasons» (2000).</t>
         </is>
       </c>
-      <c r="U82" s="14" t="n"/>
       <c r="V82" s="14" t="n"/>
-      <c r="W82" s="14" t="inlineStr">
+      <c r="W82" s="14" t="n"/>
+      <c r="X82" s="14" t="inlineStr">
         <is>
           <t>Упомянут в подразделе (viii) как один из трёх современных критиков klassicheskaya-kartina-kontseptsiy (вместе с Куайном и Даммитом; см. willard-quine, michael-dummett), чьи «варьирующиеся диагностики» Уилсон не разделяет, но чью общую цель — изолировать точный способ, которым классическая картина искажает разумный взгляд на человеческие способности — он полностью разделяет. Книга Уилсона названа его собственной попыткой довести до конца похожий проект.</t>
         </is>
       </c>
-      <c r="X82" s="14" t="inlineStr">
+      <c r="Y82" s="14" t="inlineStr">
         <is>
           <t>гл. 1</t>
         </is>
       </c>
-      <c r="Y82" s="14" t="inlineStr">
+      <c r="Z82" s="14" t="inlineStr">
         <is>
           <t>chapter_1_viii</t>
         </is>
       </c>
-      <c r="Z82" s="14" t="inlineStr">
+      <c r="AA82" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-brandom</t>
         </is>
       </c>
-      <c r="AA82" s="14" t="inlineStr">
+      <c r="AB82" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB82" s="14" t="n"/>
+      <c r="AC82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
@@ -9521,49 +9743,50 @@
       <c r="O83" s="14" t="n"/>
       <c r="P83" s="14" t="n"/>
       <c r="Q83" s="14" t="n"/>
-      <c r="R83" s="14" t="inlineStr">
+      <c r="R83" s="14" t="n"/>
+      <c r="S83" s="14" t="inlineStr">
         <is>
           <t>народная музыка; скрипка</t>
         </is>
       </c>
-      <c r="S83" s="14" t="inlineStr">
+      <c r="T83" s="14" t="inlineStr">
         <is>
           <t>Музыкант и исследователь, автор заметок к записи Her Bright Smile Haunts Me Still (Appleseed APR CD 1035, 2000), посвящённой песням Чарли Уорнерса (Warners).</t>
         </is>
       </c>
-      <c r="T83" s="14" t="inlineStr">
+      <c r="U83" s="14" t="inlineStr">
         <is>
           <t>- Tim Erikson, заметки к Her Bright Smile Haunts Me Still, Appleseed APR CD 1035 (2000) - Сохранение через исполнение - Музыкальный опыт - Партиципативность - Напряжение между сохранением и реконструкцией</t>
         </is>
       </c>
-      <c r="U83" s="14" t="n"/>
       <c r="V83" s="14" t="n"/>
-      <c r="W83" s="14" t="inlineStr">
+      <c r="W83" s="14" t="n"/>
+      <c r="X83" s="14" t="inlineStr">
         <is>
           <t>Эриксон служит практическим примером партиципативного подхода к сохранению музыки. В его рассуждении ценность музыкальной записи не существует независимо от восприятия и опыта: надёжное сохранение требует «жить» музыкой и исполнять её. Сам Эриксон участвует в исполнении песен Уорнерса. Уилсон, однако, считает, что подобное участие способно не только сохранить, но и исказить исходный музыкальный материал, уничтожая тонкие детали, которые могли бы быть важны будущим слушателям.</t>
         </is>
       </c>
-      <c r="X83" s="14" t="inlineStr">
+      <c r="Y83" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y83" s="14" t="inlineStr">
+      <c r="Z83" s="14" t="inlineStr">
         <is>
           <t>chapter_2_v</t>
         </is>
       </c>
-      <c r="Z83" s="14" t="inlineStr">
+      <c r="AA83" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/tim-erikson</t>
         </is>
       </c>
-      <c r="AA83" s="14" t="inlineStr">
+      <c r="AB83" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB83" s="14" t="n"/>
+      <c r="AC83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
@@ -9598,58 +9821,59 @@
       <c r="J84" s="14" t="n"/>
       <c r="K84" s="14" t="n"/>
       <c r="L84" s="14" t="n"/>
-      <c r="M84" s="14" t="inlineStr">
+      <c r="M84" s="14" t="n"/>
+      <c r="N84" s="14" t="inlineStr">
         <is>
           <t>Калифорнийский университет в Санта-Барбаре</t>
         </is>
       </c>
-      <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n"/>
       <c r="P84" s="14" t="n"/>
       <c r="Q84" s="14" t="n"/>
-      <c r="R84" s="14" t="inlineStr">
+      <c r="R84" s="14" t="n"/>
+      <c r="S84" s="14" t="inlineStr">
         <is>
           <t>этномузыкология</t>
         </is>
       </c>
-      <c r="S84" s="14" t="inlineStr">
+      <c r="T84" s="14" t="inlineStr">
         <is>
           <t>Американский этномузыковед, редактор и автор работ по полевой этномузыкологии. В данном фрагменте Уилсон обращается прежде всего к его введению в сборник Shadows in the Field.</t>
         </is>
       </c>
-      <c r="T84" s="14" t="inlineStr">
+      <c r="U84" s="14" t="inlineStr">
         <is>
           <t>- Timothy J. Cooley, “Casting Shadows in the Field: An Introduction” // G. F. Barz and T. J. Cooley, eds., Shadows in the Field (1997), p. 11 - Проблема объективности - Кризис научной/интеллектуальной гегемонии - Интерпретирующие сообщества - Семантический холизм - Политическая нагруженность классификаций</t>
         </is>
       </c>
-      <c r="U84" s="14" t="n"/>
       <c r="V84" s="14" t="n"/>
-      <c r="W84" s="14" t="inlineStr">
+      <c r="W84" s="14" t="n"/>
+      <c r="X84" s="14" t="inlineStr">
         <is>
           <t>Кули вводит проблему объективности этномузыкологического знания на фоне кризиса западной интеллектуальной и научной гегемонии. Уилсон связывает эти сомнения с более широкой логикой холизма: если значение и классификация зависят от сети социальных и культурных отношений, возникает вопрос о возможности объективного описания музыки. В предельной форме такая логика превращает даже обозначение произведения как «народной песни» в потенциально политический акт.</t>
         </is>
       </c>
-      <c r="X84" s="14" t="inlineStr">
+      <c r="Y84" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y84" s="14" t="inlineStr">
+      <c r="Z84" s="14" t="inlineStr">
         <is>
           <t>chapter_2_v</t>
         </is>
       </c>
-      <c r="Z84" s="14" t="inlineStr">
+      <c r="AA84" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/timothy-cooley</t>
         </is>
       </c>
-      <c r="AA84" s="14" t="inlineStr">
+      <c r="AB84" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB84" s="14" t="n"/>
+      <c r="AC84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
@@ -9685,48 +9909,49 @@
       <c r="O85" s="14" t="n"/>
       <c r="P85" s="14" t="n"/>
       <c r="Q85" s="14" t="n"/>
-      <c r="R85" s="14" t="inlineStr">
+      <c r="R85" s="14" t="n"/>
+      <c r="S85" s="14" t="inlineStr">
         <is>
           <t>музыковедение</t>
         </is>
       </c>
-      <c r="S85" s="14" t="inlineStr">
+      <c r="T85" s="14" t="inlineStr">
         <is>
           <t>Немецкий музыковед, автор комментария к записи симфоний №40 и №41 Моцарта в исполнении Венского филармонического оркестра под управлением Леонарда Бернстайна (Deutsche Grammophon, 1984).</t>
         </is>
       </c>
-      <c r="T85" s="14" t="n"/>
       <c r="U85" s="14" t="n"/>
       <c r="V85" s="14" t="n"/>
-      <c r="W85" s="14" t="inlineStr">
+      <c r="W85" s="14" t="n"/>
+      <c r="X85" s="14" t="inlineStr">
         <is>
           <t>Цитируется по поводу исторической изменчивости восприятия Симфонии №40: Шуман слышал в ней «Греческую грацию», другой автор интерпретировал её в духе итальянской оперы-буфф, тогда как современные слушатели (и сам Уилсон) склонны воспринимать её мрачный, драматический пафос — трагедию, скорбь, отчаяние.</t>
         </is>
       </c>
-      <c r="X85" s="14" t="inlineStr">
+      <c r="Y85" s="14" t="inlineStr">
         <is>
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Y85" s="14" t="inlineStr">
+      <c r="Z85" s="14" t="inlineStr">
         <is>
           <t>chapter_2_i</t>
         </is>
       </c>
-      <c r="Z85" s="14" t="inlineStr">
+      <c r="AA85" s="14" t="inlineStr">
         <is>
           <t>https://kagort.github.io/wand_sign_navigator/03-people/volker-scherliess</t>
         </is>
       </c>
-      <c r="AA85" s="14" t="inlineStr">
+      <c r="AB85" s="14" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="AB85" s="14" t="n"/>
+      <c r="AC85" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AB85"/>
+  <autoFilter ref="A3:AC85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9737,7 +9962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9782,63 +10007,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Место рождения / смерти</t>
+          <t>Причина смерти</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>birth_place / death_place</t>
+          <t>cause_of_death</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>текст; спорное — с пометкой «предположительно»</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Координаты</t>
+          <t>Место рождения / смерти</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>birth_coords / death_coords</t>
+          <t>birth_place / death_place</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[широта, долгота]</t>
+          <t>текст</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Национальность</t>
+          <t>Координаты</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nationality</t>
+          <t>birth_coords / death_coords</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>[широта, долгота]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alma mater</t>
+          <t>Национальность</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>alma_mater</t>
+          <t>nationality</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9850,100 +10075,117 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Аффилиация, области интересов, награды</t>
+          <t>Alma mater</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>affiliations, fields, awards</t>
+          <t>alma_mater</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>текст</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Учителя / ученики / коллеги</t>
+          <t>Аффилиация, области интересов, награды</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>teachers / students / colleagues</t>
+          <t>affiliations, fields, awards</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>список ссылок [[id]] на карточки</t>
+          <t>список</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ссылки SEP / Wikipedia</t>
+          <t>Учителя / ученики / коллеги</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sep / wiki_ru</t>
+          <t>teachers / students / colleagues</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>список ссылок [[id]] на карточки</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Данные проверены</t>
+          <t>Ссылки SEP / Wikipedia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bio_checked</t>
+          <t>sep / wiki_ru</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>true / false</t>
+          <t>URL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Кто это, роль в книге, труды</t>
+          <t>Данные проверены</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>разделы карточки «Кто это», «Роль в аргументации Уилсона», «Ключевые понятия/работы»</t>
+          <t>bio_checked</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>текст карточки</t>
+          <t>true / false</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Кто это, роль в книге, труды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>разделы карточки «Кто это», «Роль в аргументации Уилсона», «Ключевые понятия/работы»</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>текст карточки</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Разделы книги</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>ссылки [[chapter_N_x]] в карточке</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>вычисляется</t>
         </is>

--- a/data/people.xlsx
+++ b/data/people.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник полей" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'База данных'!$A$3:$AC$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'База данных'!$A$3:$AC$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="U9" s="14" t="inlineStr">
         <is>
-          <t>- Robert Boyle, “About the Excellency and Grounds of the Mechanical Hypothesis” // Selected Philosophical Papers of Robert Boyle (Indianapolis: Hackett, 1991), 153 — сноска 17.</t>
+          <t>- Robert Boyle, “About the Excellency and Grounds of the Mechanical Hypothesis” // Selected Philosophical Papers of Robert Boyle (Indianapolis: Hackett, 1991), 153 — сноска 17. - Robert Boyle, «О превосходстве и обоснованности механической гипотезы» (1674) — упомянуто в гл. 3, §(vii), с. 177</t>
         </is>
       </c>
       <c r="V9" s="14" t="inlineStr">
@@ -1385,7 +1385,7 @@
       <c r="W9" s="14" t="n"/>
       <c r="X9" s="14" t="inlineStr">
         <is>
-          <t>Бойль представляет эпоху механистической философии, когда любая физическая классификация, не понятая «в квази-геометрической манере быть зубчатым колесом», отвергалась как оккультная. Цитата (с. 162–163): принципы «материя, движение…, величина, форма, положение тела, порядок, текстура» настолько «просты, ясны и всеобъемлющи», что нематериальный агент лишь затруднил бы объяснение. Для Бойля ядро «быть зубчатым колесом» составляет сильный набор инференциальных направленностей — наше «глубокое понимание того, как работает механизм». На бойлевских основаниях сначала было отвергнуто как «оккультное» ньютоновское тяготение, действующее на расстоянии (с. 165); поздние «тёплые и нечёткие» требования к объяснению, против которых выступали Мах и Дюгем, «сходны с требованиями Бойля» (с. 166).</t>
+          <t>Бойль представляет эпоху механистической философии, когда любая физическая классификация, не понятая «в квази-геометрической манере быть зубчатым колесом», отвергалась как оккультная. Цитата (с. 162–163): принципы «материя, движение…, величина, форма, положение тела, порядок, текстура» настолько «просты, ясны и всеобъемлющи», что нематериальный агент лишь затруднил бы объяснение. Для Бойля ядро «быть зубчатым колесом» составляет сильный набор инференциальных направленностей — наше «глубокое понимание того, как работает механизм». На бойлевских основаниях сначала было отвергнуто как «оккультное» ньютоновское тяготение, действующее на расстоянии (с. 165); поздние «тёплые и нечёткие» требования к объяснению, против которых выступали Мах и Дюгем, «сходны с требованиями Бойля» (с. 166). Гл. 3, §(vii) (с. 174–180). Жалоба Бойля на «оккультность» ньютоновского тяготения открывает разбор примера с пушечным ядром: можем ли мы показать, что действительно понимаем этот признак? Сегодня принято считать, что Бойль и Рид «придерживались старомодных представлений» о том, что нужно для понимания понятия. Но, по Уилсону, понятие «теоретического содержания» исторически возникло из признания, что Бойль, «по сути, прав», а науке для её узких целей не нужно об этом беспокоиться. Его ввели в конце XIX века, чтобы критика в духе Бойля не тормозила научный прогресс. Требование «канонически прямого» знакомства с физическими направленностями угрожает вернуть нас «в тиски требований в духе Бойля к пониманию» (с. 180).</t>
         </is>
       </c>
       <c r="Y9" s="14" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="Z9" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_vi</t>
+          <t>chapter_3_vi; chapter_3_vii</t>
         </is>
       </c>
       <c r="AA9" s="14" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="Y10" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 1; гл. 3</t>
         </is>
       </c>
       <c r="Z10" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_iii; chapter_3_vi</t>
+          <t>chapter_1_iii; chapter_3_vi; chapter_3_vii</t>
         </is>
       </c>
       <c r="AA10" s="14" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="Y17" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 1; гл. 3</t>
         </is>
       </c>
       <c r="Z17" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_vi</t>
+          <t>chapter_1_vi; chapter_3_vii</t>
         </is>
       </c>
       <c r="AA17" s="14" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="U18" s="14" t="inlineStr">
         <is>
-          <t>- Прямой реализм восприятия (direct realism) — против «теории идей» - Принципы здравого смысла (common sense) как источник эпистемического оправдания - Thomas Reid, Essays on the Intellectual Powers of Man, 57–58 — цитата о твёрдости (сноска 21) - Понятие совершенной твёрдости как основа понятия твёрдого тела - (дозаполнить по мере чтения)</t>
+          <t>- Прямой реализм восприятия (direct realism) — против «теории идей» - Принципы здравого смысла (common sense) как источник эпистемического оправдания - Thomas Reid, Essays on the Intellectual Powers of Man, 57–58 — цитата о твёрдости (сноска 21) - Понятие совершенной твёрдости как основа понятия твёрдого тела - Thomas Reid, Essays on the Intellectual Powers of Man, 272–273 — о неизвестной «сердцевине» тяготения (сноска 26 гл. 3) - (дозаполнить по мере чтения)</t>
         </is>
       </c>
       <c r="V18" s="14" t="inlineStr">
@@ -2416,7 +2416,7 @@
       <c r="W18" s="14" t="n"/>
       <c r="X18" s="14" t="inlineStr">
         <is>
-          <t>(гипотеза, требует проверки по тексту) Рид — вероятный союзник в вопросе доверия обыденным, «здравосмысленным» классификациям и практикам употребления понятий, в противовес скептическим и редукционистским программам (в духе Юма). Подтверждено в гл. 3, §(vi) (с. 167–168). Рид — главный оппонент Декарта в споре о том, что составляет ядро «есть твёрдый». Для Декарта твёрдость, как и краснота, классифицирует лишь наши ощущения сопротивления. Рид, «не желая отрывать наше постижение классификационных понятий от физического мира в манере завесы восприятия», «справедливо возражал»: истинное понятие твёрдости — прочное сцепление частей тела, и оно «внутренне вообще не связано» с ощущением прикосновения: «Прочное сцепление частей тела не более похоже на то ощущение… чем вибрация звучного тела похожа на звук, который я слышу». Словарь Webster тоже определяет твёрдость без упоминания ощущений. Но, замечает Уилсон, ридовская направленность указывает на молекулярный уровень, недоступный повседневной классификации (и к тому же «довольно ошибочна»). По сути Рид утверждает, что ребёнок начинает с картезианских, основанных на ощущениях направленностей (твёрдая резиновая уточка), а «где-то между шестью месяцами и шестнадцатью годами» говорящие сдвигают привязки «есть твёрдый» к экстернализированному классификатору. Уилсон сопоставляет это с картиной красноты у Хелен Келлер. Сам Рид отмечает, что понятие совершенной твёрдости важно для понятия твёрдого тела, а оно — основа инференциальных способностей «зубчатого колеса» (см. inferentsialnaya-napravlennost).</t>
+          <t>(гипотеза, требует проверки по тексту) Рид — вероятный союзник в вопросе доверия обыденным, «здравосмысленным» классификациям и практикам употребления понятий, в противовес скептическим и редукционистским программам (в духе Юма). Подтверждено в гл. 3, §(vi) (с. 167–168). Рид — главный оппонент Декарта в споре о том, что составляет ядро «есть твёрдый». Для Декарта твёрдость, как и краснота, классифицирует лишь наши ощущения сопротивления. Рид, «не желая отрывать наше постижение классификационных понятий от физического мира в манере завесы восприятия», «справедливо возражал»: истинное понятие твёрдости — прочное сцепление частей тела, и оно «внутренне вообще не связано» с ощущением прикосновения: «Прочное сцепление частей тела не более похоже на то ощущение… чем вибрация звучного тела похожа на звук, который я слышу». Словарь Webster тоже определяет твёрдость без упоминания ощущений. Но, замечает Уилсон, ридовская направленность указывает на молекулярный уровень, недоступный повседневной классификации (и к тому же «довольно ошибочна»). По сути Рид утверждает, что ребёнок начинает с картезианских, основанных на ощущениях направленностей (твёрдая резиновая уточка), а «где-то между шестью месяцами и шестнадцатью годами» говорящие сдвигают привязки «есть твёрдый» к экстернализированному классификатору. Уилсон сопоставляет это с картиной красноты у Хелен Келлер. Сам Рид отмечает, что понятие совершенной твёрдости важно для понятия твёрдого тела, а оно — основа инференциальных способностей «зубчатого колеса» (см. inferentsialnaya-napravlennost). Гл. 3, §(vii) (с. 170–171, 177). Ридовская картина твёрдости служит образцом того, как классики помещали «коренное» содержание физического предиката на непрозрачный конец спектра направленностей. Она «не оказывает никакой непосредственной помощи» в решении, твёрд ли кусок пластика: для этого надо царапать, стучать или давить, а эти операции могут расходиться (обещано в гл. 6, §(ix)). Рид, по-видимому, полагал, что его картина в нужных обстоятельствах подскажет, какая операция «окажется наиболее лояльной» главному взгляду. Значит, направленности «твёрдости» должны делиться на центральное ядро и «соображения-саттелиты», на которые мы ссылаемся, отвечая на вопрос «Почему вы назвали этот кусок эбенового дерева твёрдым?». Ещё удивительнее, что тот же Рид, так решительно отделяющий содержание твёрдости от показателей среды, допускает: у тяготения необходимая сердцевина «остаётся пока неизвестной».</t>
         </is>
       </c>
       <c r="Y18" s="14" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="Z18" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_v; chapter_3_vi; predislovie</t>
+          <t>chapter_2_v; chapter_3_vi; chapter_3_vii; predislovie</t>
         </is>
       </c>
       <c r="AA18" s="14" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="Z27" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_iv</t>
+          <t>chapter_3_iv; chapter_3_vii</t>
         </is>
       </c>
       <c r="AA27" s="14" t="inlineStr">
@@ -4181,12 +4181,12 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Герман фон Гельмгольц</t>
+          <t>Карл Вейерштрасс</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Hermann von Helmholtz</t>
+          <t>Karl Weierstrass</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -4196,102 +4196,106 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/h_helmholtz.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/karl_weierstrass.jpg</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>1821–1894</t>
+          <t>1815–1897</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>1821-08-31</t>
+          <t>1815-10-31</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>1894-09-08</t>
+          <t>1897-02-19</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>кровоизлияние в мозг</t>
+          <t>пневмония</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>Потсдам, Пруссия</t>
+          <t>Остенфельде, Вестфалия</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>52.3906, 13.0645</t>
+          <t>51.8700, 8.0800</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>Шарлоттенбург (Берлин)</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>52.5167, 13.3000</t>
+          <t>52.5200, 13.4050</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>Медико-хирургический институт Фридриха Вильгельма, Берлин</t>
+          <t>Боннский университет (без степени); Академия в Мюнстере</t>
         </is>
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>Кёнигсбергский университет; Боннский университет; Гейдельбергский университет; Берлинский университет</t>
+          <t>Берлинский университет; Королевский промышленный институт (Берлин); Прусская академия наук</t>
         </is>
       </c>
       <c r="O34" s="14" t="n"/>
-      <c r="P34" s="14" t="inlineStr">
-        <is>
-          <t>Генрих Герц</t>
-        </is>
-      </c>
+      <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
-      <c r="R34" s="14" t="n"/>
+      <c r="R34" s="14" t="inlineStr">
+        <is>
+          <t>Медаль Копли (1895)</t>
+        </is>
+      </c>
       <c r="S34" s="14" t="inlineStr">
         <is>
-          <t>физиология; физика; физиологическая акустика и оптика</t>
+          <t>математический анализ; теория функций</t>
         </is>
       </c>
       <c r="T34" s="14" t="inlineStr">
         <is>
-          <t>Немецкий физик, физиолог и философ науки. Один из первооткрывателей закона сохранения энергии, автор фундаментальных работ по физиологической оптике и акустике («Handbuch der physiologischen Optik»), а также эпистемологических работ о природе геометрических аксиом и о роли знаков/символов в восприятии («Die Tatsachen in der Wahrnehmung», 1878) — идея, что наши перцептивные и понятийные «образы» суть условные, практически выработанные знаки, а не прямые слепки с реальности.</t>
+          <t>Немецкий математик, «отец современного анализа». Долго был провинциальным школьным учителем; в 1856 году его пригласили в Берлин, где он стал профессором университета. Дал строгое «эпсилон-дельта» обоснование понятий предела и непрерывности, построил непрерывную нигде не дифференцируемую функцию, развил теорию аналитических функций и равномерной сходимости рядов. Среди учеников — Софья Ковалевская, Г. А. Шварц, Г. Миттаг-Леффлер.</t>
         </is>
       </c>
       <c r="U34" s="14" t="inlineStr">
         <is>
-          <t>- Ранний, «умеренный» холизм немецкой физики середины XIX века (без указания конкретного труда — требует уточнения по внутренней ссылке 4,iii) - (гипотеза, не подтверждена цитатой): возможна связь с концепцией Гельмгольца о знаках/символах восприятия как параллелью к идее Уилсона о «блуждании» значений понятий</t>
+          <t>- Строгое обоснование анализа («арифметизация анализа») — у Уилсона без ссылки на конкретные работы.</t>
         </is>
       </c>
       <c r="V34" s="14" t="n"/>
-      <c r="W34" s="14" t="n"/>
+      <c r="W34" s="14" t="inlineStr">
+        <is>
+          <t>https://ru.wikipedia.org/wiki/Вейерштрасс,_Карл</t>
+        </is>
+      </c>
       <c r="X34" s="14" t="inlineStr">
         <is>
-          <t>Назван (наряду с Генрихом Герцем) как пример «холизма» в его первоначальном, сдержанном виде — как он возникал в середине XIX века у немецких физиков в качестве умеренного отхода от «классической закостенелости», а не как радикальное учение. Уилсон противопоставляет эту раннюю, умеренную форму холизма её позднейшим «диким и разрушительным» крайностям XX века (кунианизм, пост-структурализм), от которых сам явно дистанцируется. Даёт внутреннюю отсылку «(4, iii)» — судя по всему, к месту в главе 4, где эта тема развёрнута подробнее; при чтении главы 4 стоит свериться.</t>
+          <t>Упомянут вместе с Коши как вершина движения за обоснование прикладной математики. Уилсон пишет, что прикладная математика не может просто давать рецепты вычислений: она должна «гарантировать значимость (underwrite the validity)» своих процедур. Это осознание пришло в эпоху Эйлера (1750-е годы) и достигло «полного расцвета» в середине XIX века в работах Коши и Вейерштрасса. Благодаря им можно отличить случаи, где за облаком саттелитных направленностей стоит настоящий центр (вычисления для модуса (0,3) барабана, см. komponentnye-modusy-vibratsii), от формальных выкладок, где его нет. Уилсон обещает, что эта тема станет центральной в обзорах «картин» и «доказательств обоснованности».</t>
         </is>
       </c>
       <c r="Y34" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z34" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_ix</t>
+          <t>chapter_3_vii</t>
         </is>
       </c>
       <c r="AA34" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/hermann-helmholtz</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/karl-weierstrass</t>
         </is>
       </c>
       <c r="AB34" s="14" t="inlineStr">
@@ -4304,121 +4308,117 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Томас Генри Хаксли</t>
+          <t>Герман фон Гельмгольц</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Thomas Henry Huxley</t>
+          <t>Hermann von Helmholtz</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
+          <t>немец</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/t_h_huxley.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/h_helmholtz.jpg</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>1825–1895</t>
+          <t>1821–1894</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>1825-05-04</t>
+          <t>1821-08-31</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>1895-06-29</t>
+          <t>1894-09-08</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>сердечный приступ</t>
+          <t>кровоизлияние в мозг</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>Илинг, Лондон</t>
+          <t>Потсдам, Пруссия</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>51.5130, -0.3089</t>
+          <t>52.3906, 13.0645</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>Истборн, Англия</t>
+          <t>Шарлоттенбург (Берлин)</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>50.7680, 0.2905</t>
+          <t>52.5167, 13.3000</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>Медицинская школа больницы Чаринг-Кросс</t>
+          <t>Медико-хирургический институт Фридриха Вильгельма, Берлин</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
-          <t>Королевская горная школа, Лондон</t>
+          <t>Кёнигсбергский университет; Боннский университет; Гейдельбергский университет; Берлинский университет</t>
         </is>
       </c>
       <c r="O35" s="14" t="n"/>
-      <c r="P35" s="14" t="n"/>
-      <c r="Q35" s="14" t="inlineStr">
-        <is>
-          <t>Чарльз Дарвин</t>
-        </is>
-      </c>
-      <c r="R35" s="14" t="inlineStr">
-        <is>
-          <t>Медаль Копли (1888)</t>
-        </is>
-      </c>
+      <c r="P35" s="14" t="inlineStr">
+        <is>
+          <t>Генрих Герц</t>
+        </is>
+      </c>
+      <c r="Q35" s="14" t="n"/>
+      <c r="R35" s="14" t="n"/>
       <c r="S35" s="14" t="inlineStr">
         <is>
-          <t>сравнительная анатомия; эволюционная биология</t>
+          <t>физиология; физика; физиологическая акустика и оптика</t>
         </is>
       </c>
       <c r="T35" s="14" t="inlineStr">
         <is>
-          <t>Английский биолог, известен как «бульдог Дарвина» за энергичную публичную защиту теории эволюции (в том числе в знаменитых дебатах с епископом Сэмюэлем Уилберфорсом, 1860). Ввёл в обиход термин «агностик». Дед писателя Олдоса Хаксли и биолога Джулиана Хаксли. Автор эссе «On the Method of Zadig» (в сборнике «Science and Culture», 1882), откуда взята цитата у Уилсона.</t>
+          <t>Немецкий физик, физиолог и философ науки. Один из первооткрывателей закона сохранения энергии, автор фундаментальных работ по физиологической оптике и акустике («Handbuch der physiologischen Optik»), а также эпистемологических работ о природе геометрических аксиом и о роли знаков/символов в восприятии («Die Tatsachen in der Wahrnehmung», 1878) — идея, что наши перцептивные и понятийные «образы» суть условные, практически выработанные знаки, а не прямые слепки с реальности.</t>
         </is>
       </c>
       <c r="U35" s="14" t="inlineStr">
         <is>
-          <t>- T. H. Huxley, "On the Method of Zadig" // Science and Culture (New York: D. Appleton, 1882) - T. H. Huxley, Hume, with Helps to the Study of Berkeley (1898) - Наука как «тренированный и организованный здравый смысл» - Метод Задиг / ретроспективное пророчество - Научное описание и обычные качества опыта Про само название эссе. Задиг — главный герой философской повести Вольтера «Задиг, или Судьба» (1747): по одним лишь следам на земле он точно описывает сбежавшую собаку королевы и лошадь короля, которых никогда не видел (сюжет, предвосхищающий метод Шерлока Холмса на век раньше). Эссе Хаксли (впервые 1880, Popular Science Monthly; переиздано в «Science and Culture», 1882) использует этот сюжет для тезиса о «ретроспективном пророчестве» — способности восстанавливать факты прошлого по наблюдаемым в настоящем следам, не мистическом даре, а методе, на котором строятся геология, палеонтология, археология. Эссе открывается эпиграфом из Кювье, который по зубам и челюсти ископаемого верно предсказал строение его таза — той же логикой, что и Задиг по следам копыт заключил о хвосте лошади. То есть отсылка у Хаксли не случайна: цитируемый Уилсоном тезис («наука — тренированный здравый смысл») в самом эссе Хаксли развёрнут именно на этом примере.</t>
+          <t>- Ранний, «умеренный» холизм немецкой физики середины XIX века (без указания конкретного труда — требует уточнения по внутренней ссылке 4,iii) - (гипотеза, не подтверждена цитатой): возможна связь с концепцией Гельмгольца о знаках/символах восприятия как параллелью к идее Уилсона о «блуждании» значений понятий</t>
         </is>
       </c>
       <c r="V35" s="14" t="n"/>
       <c r="W35" s="14" t="n"/>
       <c r="X35" s="14" t="inlineStr">
         <is>
-          <t>Процитирован в связи с тезисом о том, что мир природы «редко благосклонен к дисциплинарному разделению» — даже изучение морских водорослей ведёт в химию, физику, математику и философию. Уилсон приводит афоризм Хаксли о том, что наука — это «не что иное, как тренированный и организованный здравый смысл», отличающийся от обычного здравого смысла лишь так, как ветеран отличается от новобранца, а его методы — лишь так, как фехтовальная техника гвардейца («cut and thrust» — рубящие и колющие удары) отличается от того, как дикарь орудует дубиной. ⚠️ Важное расхождение с переводом. В оригинале у Хаксли дубина — только у «дикаря»; у гвардейца — именно фехтовальная техника («cut and thrust», рубяще-колющие удары холодным оружием/штыком), а не дубина. Русский перевод («удары гвардейца отличаются от манеры дикаря владеть своей дубинкой») видоизменил конструкцию так, что дубинка читается как общий инструмент для обеих сравниваемых сторон. Возможно, в этом пассаже речь идёт об оружии австралийских аборигенов. В 1847 г. в ходе первой картографической экспедиции к Большому Барьерному рифу фрегат "Rattlesnake", на котором Хаксли служил хирургом и естествоиспытателем, бросил якорь у мыса Апстарт, и учёный получил возможность ознакомиться с бытом местных племён. Предположительно автор видел своими глазами боевое применение дубинки Лил-лил</t>
+          <t>Назван (наряду с Генрихом Герцем) как пример «холизма» в его первоначальном, сдержанном виде — как он возникал в середине XIX века у немецких физиков в качестве умеренного отхода от «классической закостенелости», а не как радикальное учение. Уилсон противопоставляет эту раннюю, умеренную форму холизма её позднейшим «диким и разрушительным» крайностям XX века (кунианизм, пост-структурализм), от которых сам явно дистанцируется. Даёт внутреннюю отсылку «(4, iii)» — судя по всему, к месту в главе 4, где эта тема развёрнута подробнее; при чтении главы 4 стоит свериться.</t>
         </is>
       </c>
       <c r="Y35" s="14" t="inlineStr">
         <is>
-          <t>гл. 1; гл. 2</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z35" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_iv; chapter_2_vi</t>
+          <t>chapter_1_ix</t>
         </is>
       </c>
       <c r="AA35" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/t-h-huxley</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/hermann-helmholtz</t>
         </is>
       </c>
       <c r="AB35" s="14" t="inlineStr">
@@ -4431,109 +4431,121 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Франц Рёло</t>
+          <t>Томас Генри Хаксли</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Franz Reuleaux</t>
+          <t>Thomas Henry Huxley</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>немец</t>
+          <t>британец</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/freuleaux.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/t_h_huxley.jpg</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>1829–1905</t>
+          <t>1825–1895</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>1829-09-30</t>
+          <t>1825-05-04</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>1905-08-20</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="n"/>
+          <t>1895-06-29</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>сердечный приступ</t>
+        </is>
+      </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Эшвайлер, Пруссия</t>
+          <t>Илинг, Лондон</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>50.8172, 6.2650</t>
+          <t>51.5130, -0.3089</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>Берлин</t>
+          <t>Истборн, Англия</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>52.5200, 13.4050</t>
+          <t>50.7680, 0.2905</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>Политехникум Карлсруэ</t>
+          <t>Медицинская школа больницы Чаринг-Кросс</t>
         </is>
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>Цюрихский политехникум; Королевская ремесленная академия (Технический университет Берлина)</t>
+          <t>Королевская горная школа, Лондон</t>
         </is>
       </c>
       <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
-      <c r="Q36" s="14" t="n"/>
-      <c r="R36" s="14" t="n"/>
+      <c r="Q36" s="14" t="inlineStr">
+        <is>
+          <t>Чарльз Дарвин</t>
+        </is>
+      </c>
+      <c r="R36" s="14" t="inlineStr">
+        <is>
+          <t>Медаль Копли (1888)</t>
+        </is>
+      </c>
       <c r="S36" s="14" t="inlineStr">
         <is>
-          <t>кинематика машин; машиноведение</t>
+          <t>сравнительная анатомия; эволюционная биология</t>
         </is>
       </c>
       <c r="T36" s="14" t="inlineStr">
         <is>
-          <t>Немецкий инженер-машиностроитель, профессор Королевской технической академии в Берлине, основатель кинематики машин как систематической дисциплины. В работе «Теоретическая кинематика: основы теории машиноведения» (1875) разработал строгую понятийную схему для описания механизмов в отрыве от их конкретного материального воплощения — систему классификации «кинематических пар» (типов соединений между звеньями машины), позволяющую абстрактно анализировать движение независимо от того, из чего механизм сделан.</t>
+          <t>Английский биолог, известен как «бульдог Дарвина» за энергичную публичную защиту теории эволюции (в том числе в знаменитых дебатах с епископом Сэмюэлем Уилберфорсом, 1860). Ввёл в обиход термин «агностик». Дед писателя Олдоса Хаксли и биолога Джулиана Хаксли. Автор эссе «On the Method of Zadig» (в сборнике «Science and Culture», 1882), откуда взята цитата у Уилсона.</t>
         </is>
       </c>
       <c r="U36" s="14" t="inlineStr">
         <is>
-          <t>- «Theoretische Kinematik» (1875) — систематическая теория машиноведения - Классификация «кинематических пар» — абстрактная понятийная схема для описания механизмов независимо от материального воплощения</t>
+          <t>- T. H. Huxley, "On the Method of Zadig" // Science and Culture (New York: D. Appleton, 1882) - T. H. Huxley, Hume, with Helps to the Study of Berkeley (1898) - Наука как «тренированный и организованный здравый смысл» - Метод Задиг / ретроспективное пророчество - Научное описание и обычные качества опыта Про само название эссе. Задиг — главный герой философской повести Вольтера «Задиг, или Судьба» (1747): по одним лишь следам на земле он точно описывает сбежавшую собаку королевы и лошадь короля, которых никогда не видел (сюжет, предвосхищающий метод Шерлока Холмса на век раньше). Эссе Хаксли (впервые 1880, Popular Science Monthly; переиздано в «Science and Culture», 1882) использует этот сюжет для тезиса о «ретроспективном пророчестве» — способности восстанавливать факты прошлого по наблюдаемым в настоящем следам, не мистическом даре, а методе, на котором строятся геология, палеонтология, археология. Эссе открывается эпиграфом из Кювье, который по зубам и челюсти ископаемого верно предсказал строение его таза — той же логикой, что и Задиг по следам копыт заключил о хвосте лошади. То есть отсылка у Хаксли не случайна: цитируемый Уилсоном тезис («наука — тренированный здравый смысл») в самом эссе Хаксли развёрнут именно на этом примере.</t>
         </is>
       </c>
       <c r="V36" s="14" t="n"/>
       <c r="W36" s="14" t="n"/>
       <c r="X36" s="14" t="inlineStr">
         <is>
-          <t>Указан Уилсоном в предисловии наравне с Хевисайдом и Адамаром как один из авторов, чьим трудам он «особенно обязан» — трое инженеров и прикладных математиков второй половины XIX века, чьи замечания о концептуальной неоднозначности вдохновили общий замысел книги. Наиболее вероятная содержательная связь: классификационная схема Рёло — образцовый пример того, как из инженерной практики (работы с конкретными механизмами) вырастает абстрактная понятийная система (кинематические пары), которая затем сама начинает жить самостоятельной жизнью и требует уточнения при переносе на новые типы механизмов. Это специфичный пример «блуждания» понятия в духе центрального тезиса книги.</t>
+          <t>Процитирован в связи с тезисом о том, что мир природы «редко благосклонен к дисциплинарному разделению» — даже изучение морских водорослей ведёт в химию, физику, математику и философию. Уилсон приводит афоризм Хаксли о том, что наука — это «не что иное, как тренированный и организованный здравый смысл», отличающийся от обычного здравого смысла лишь так, как ветеран отличается от новобранца, а его методы — лишь так, как фехтовальная техника гвардейца («cut and thrust» — рубящие и колющие удары) отличается от того, как дикарь орудует дубиной. ⚠️ Важное расхождение с переводом. В оригинале у Хаксли дубина — только у «дикаря»; у гвардейца — именно фехтовальная техника («cut and thrust», рубяще-колющие удары холодным оружием/штыком), а не дубина. Русский перевод («удары гвардейца отличаются от манеры дикаря владеть своей дубинкой») видоизменил конструкцию так, что дубинка читается как общий инструмент для обеих сравниваемых сторон. Возможно, в этом пассаже речь идёт об оружии австралийских аборигенов. В 1847 г. в ходе первой картографической экспедиции к Большому Барьерному рифу фрегат "Rattlesnake", на котором Хаксли служил хирургом и естествоиспытателем, бросил якорь у мыса Апстарт, и учёный получил возможность ознакомиться с бытом местных племён. Предположительно автор видел своими глазами боевое применение дубинки Лил-лил</t>
         </is>
       </c>
       <c r="Y36" s="14" t="inlineStr">
         <is>
-          <t>предисловие</t>
+          <t>гл. 1; гл. 2</t>
         </is>
       </c>
       <c r="Z36" s="14" t="inlineStr">
         <is>
-          <t>predislovie</t>
+          <t>chapter_1_iv; chapter_2_vi</t>
         </is>
       </c>
       <c r="AA36" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/franz-reuleaux</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/t-h-huxley</t>
         </is>
       </c>
       <c r="AB36" s="14" t="inlineStr">
@@ -4546,105 +4558,109 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Роберт Ингерсолл</t>
+          <t>Франц Рёло</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Robert Ingersoll</t>
+          <t>Franz Reuleaux</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>немец</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/r_ingersoll.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/freuleaux.jpg</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>1833–1899</t>
+          <t>1829–1905</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>1833-08-11</t>
+          <t>1829-09-30</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>1899-07-21</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>сердечная недостаточность</t>
-        </is>
-      </c>
+          <t>1905-08-20</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="n"/>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>Дрезден, Нью-Йорк, США</t>
+          <t>Эшвайлер, Пруссия</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>42.6840, -76.9570</t>
+          <t>50.8172, 6.2650</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>Доббс-Ферри, Нью-Йорк, США</t>
+          <t>Берлин</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>41.0145, -73.8726</t>
-        </is>
-      </c>
-      <c r="M37" s="14" t="n"/>
-      <c r="N37" s="14" t="n"/>
+          <t>52.5200, 13.4050</t>
+        </is>
+      </c>
+      <c r="M37" s="14" t="inlineStr">
+        <is>
+          <t>Политехникум Карлсруэ</t>
+        </is>
+      </c>
+      <c r="N37" s="14" t="inlineStr">
+        <is>
+          <t>Цюрихский политехникум; Королевская ремесленная академия (Технический университет Берлина)</t>
+        </is>
+      </c>
       <c r="O37" s="14" t="n"/>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14" t="n"/>
       <c r="S37" s="14" t="inlineStr">
         <is>
-          <t>ораторское искусство; агностицизм; право</t>
+          <t>кинематика машин; машиноведение</t>
         </is>
       </c>
       <c r="T37" s="14" t="inlineStr">
         <is>
-          <t>Американский юрист, ветеран Гражданской войны и знаменитый оратор второй половины XIX века, прозванный «Великим Агностиком» (The Great Agnostic) — самый известный публичный критик религиозной догмы своего времени в США, прославился зажигательными скептическими речами против религиозной ортодоксии.</t>
+          <t>Немецкий инженер-машиностроитель, профессор Королевской технической академии в Берлине, основатель кинематики машин как систематической дисциплины. В работе «Теоретическая кинематика: основы теории машиноведения» (1875) разработал строгую понятийную схему для описания механизмов в отрыве от их конкретного материального воплощения — систему классификации «кинематических пар» (типов соединений между звеньями машины), позволяющую абстрактно анализировать движение независимо от того, из чего механизм сделан.</t>
         </is>
       </c>
       <c r="U37" s="14" t="inlineStr">
         <is>
-          <t>- Не применимо — используется как культурная аллюзия/типаж, а не как источник идей</t>
+          <t>- «Theoretische Kinematik» (1875) — систематическая теория машиноведения - Классификация «кинематических пар» — абстрактная понятийная схема для описания механизмов независимо от материального воплощения</t>
         </is>
       </c>
       <c r="V37" s="14" t="n"/>
       <c r="W37" s="14" t="n"/>
       <c r="X37" s="14" t="inlineStr">
         <is>
-          <t>Использован как риторический типаж-сравнение: Уилсон пишет, что некоторые читатели-номиналисты, воодушевлённые собственным скептицизмом, могут почувствовать порыв стать «Робертом Ингерсоллом метафизических излишеств» — то есть крестоносцем, очищающим философский ландшафт от «гнили мистических универсалий», подобно тому как сам Ингерсолл боролся с религиозной догмой. Это литературная аллюзия для описания определённого психологического типа читателя, а не цитирование идей самого Ингерсолла.</t>
+          <t>Указан Уилсоном в предисловии наравне с Хевисайдом и Адамаром как один из авторов, чьим трудам он «особенно обязан» — трое инженеров и прикладных математиков второй половины XIX века, чьи замечания о концептуальной неоднозначности вдохновили общий замысел книги. Наиболее вероятная содержательная связь: классификационная схема Рёло — образцовый пример того, как из инженерной практики (работы с конкретными механизмами) вырастает абстрактная понятийная система (кинематические пары), которая затем сама начинает жить самостоятельной жизнью и требует уточнения при переносе на новые типы механизмов. Это специфичный пример «блуждания» понятия в духе центрального тезиса книги.</t>
         </is>
       </c>
       <c r="Y37" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>предисловие</t>
         </is>
       </c>
       <c r="Z37" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_ii</t>
+          <t>predislovie</t>
         </is>
       </c>
       <c r="AA37" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-ingersoll</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/franz-reuleaux</t>
         </is>
       </c>
       <c r="AB37" s="14" t="inlineStr">
@@ -4657,113 +4673,105 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Эрнст Мах</t>
+          <t>Роберт Ингерсолл</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Ernst Mach</t>
+          <t>Robert Ingersoll</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>австриец</t>
+          <t>американец</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/ernst_mach.webp</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/r_ingersoll.jpg</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>1838–1916</t>
+          <t>1833–1899</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>1838-02-18</t>
+          <t>1833-08-11</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>1916-02-19</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="n"/>
+          <t>1899-07-21</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>сердечная недостаточность</t>
+        </is>
+      </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>Хирлиц (Хрлице) близ Брюнна, Моравия</t>
+          <t>Дрезден, Нью-Йорк, США</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>49.1300, 16.6500</t>
+          <t>42.6840, -76.9570</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>Фатерштеттен близ Мюнхена, Германия</t>
+          <t>Доббс-Ферри, Нью-Йорк, США</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>48.1050, 11.7690</t>
-        </is>
-      </c>
-      <c r="M38" s="14" t="inlineStr">
-        <is>
-          <t>Венский университет</t>
-        </is>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>Грацский университет; Пражский (Карлов) университет; Венский университет</t>
-        </is>
-      </c>
+          <t>41.0145, -73.8726</t>
+        </is>
+      </c>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
       <c r="R38" s="14" t="n"/>
       <c r="S38" s="14" t="inlineStr">
         <is>
-          <t>физика; психофизика; философия науки</t>
+          <t>ораторское искусство; агностицизм; право</t>
         </is>
       </c>
       <c r="T38" s="14" t="inlineStr">
         <is>
-          <t>Австрийский физик и философ. Исследовал ударные волны (отсюда «число Маха»), психофизиологию ощущений; критиковал ньютоновские абсолютные пространство и время, что повлияло на Эйнштейна. Один из главных представителей позитивизма конца XIX века.</t>
+          <t>Американский юрист, ветеран Гражданской войны и знаменитый оратор второй половины XIX века, прозванный «Великим Агностиком» (The Great Agnostic) — самый известный публичный критик религиозной догмы своего времени в США, прославился зажигательными скептическими речами против религиозной ортодоксии.</t>
         </is>
       </c>
       <c r="U38" s="14" t="inlineStr">
         <is>
-          <t>- Ernst Mach, Principles of Physical Optics (New York: Dover, n.d.), 1 — сноска 14.</t>
-        </is>
-      </c>
-      <c r="V38" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/ernst-mach/</t>
-        </is>
-      </c>
+          <t>- Не применимо — используется как культурная аллюзия/типаж, а не как источник идей</t>
+        </is>
+      </c>
+      <c r="V38" s="14" t="n"/>
       <c r="W38" s="14" t="n"/>
       <c r="X38" s="14" t="inlineStr">
         <is>
-          <t>Краснота как неописуемое. Мах — голос «известного взгляда», что постижение «быть красным» непосредственно и неразложимо: «Яркость, темнота, свет и цвет не поддаются описанию… могут быть только поименованы» (с. 159). Отсюда и вывод, что говорить об «ингредиентах» красноты ошибочно: понятие либо постигнуто полностью, либо его нет (с. 161). Против «тёплых и нечётких» требований. Вместе с Дюгемом и другими учёными 1880–1910 гг. Мах утверждал, что прогрессу физики мешает приверженность «тёплым и нечётким» требованиям к объяснению в духе Бойля. Уилсон признаёт, что «в своём критическом чутье Мах и Дюгем часто оказывались правы», но «как специалисты по семантической диагностике они перестарались»: многозначное выражение «теоретическое содержание» — наследие этих чрезмерных мнений (с. 166).</t>
+          <t>Использован как риторический типаж-сравнение: Уилсон пишет, что некоторые читатели-номиналисты, воодушевлённые собственным скептицизмом, могут почувствовать порыв стать «Робертом Ингерсоллом метафизических излишеств» — то есть крестоносцем, очищающим философский ландшафт от «гнили мистических универсалий», подобно тому как сам Ингерсолл боролся с религиозной догмой. Это литературная аллюзия для описания определённого психологического типа читателя, а не цитирование идей самого Ингерсолла.</t>
         </is>
       </c>
       <c r="Y38" s="14" t="inlineStr">
         <is>
-          <t>гл. 3</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z38" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_vi</t>
+          <t>chapter_1_ii</t>
         </is>
       </c>
       <c r="AA38" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/ernst-mach</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-ingersoll</t>
         </is>
       </c>
       <c r="AB38" s="14" t="inlineStr">
@@ -4776,72 +4784,68 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Уильям Джеймс</t>
+          <t>Эрнст Мах</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>William James</t>
+          <t>Ernst Mach</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>австриец</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/w_james.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/ernst_mach.webp</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>1842–1910</t>
+          <t>1838–1916</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>1842-01-11</t>
+          <t>1838-02-18</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>1910-08-26</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>сердечная недостаточность</t>
-        </is>
-      </c>
+          <t>1916-02-19</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="n"/>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>Нью-Йорк, США</t>
+          <t>Хирлиц (Хрлице) близ Брюнна, Моравия</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>40.7128, -74.0060</t>
+          <t>49.1300, 16.6500</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>Чокоруа, Нью-Гэмпшир, США</t>
+          <t>Фатерштеттен близ Мюнхена, Германия</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>43.8800, -71.2300</t>
+          <t>48.1050, 11.7690</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>Гарвардская медицинская школа</t>
+          <t>Венский университет</t>
         </is>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
-          <t>Гарвардский университет</t>
+          <t>Грацский университет; Пражский (Карлов) университет; Венский университет</t>
         </is>
       </c>
       <c r="O39" s="14" t="n"/>
@@ -4850,43 +4854,43 @@
       <c r="R39" s="14" t="n"/>
       <c r="S39" s="14" t="inlineStr">
         <is>
-          <t>психология; прагматизм</t>
+          <t>физика; психофизика; философия науки</t>
         </is>
       </c>
       <c r="T39" s="14" t="inlineStr">
         <is>
-          <t>Американский философ и психолог, один из основателей прагматизма, автор The Principles of Psychology. В данном фрагменте цитируется как свидетель радикальной изменчивости человеческого восприятия и вкуса на протяжении жизни.</t>
+          <t>Австрийский физик и философ. Исследовал ударные волны (отсюда «число Маха»), психофизиологию ощущений; критиковал ньютоновские абсолютные пространство и время, что повлияло на Эйнштейна. Один из главных представителей позитивизма конца XIX века.</t>
         </is>
       </c>
       <c r="U39" s="14" t="inlineStr">
         <is>
-          <t>- The Principles of Psychology (изд. 1983), с. 227–228 - Talks to Teachers on Psychology: and to Students of Some of Life's Ideals (1913), с. 71–73</t>
+          <t>- Ernst Mach, Principles of Physical Optics (New York: Dover, n.d.), 1 — сноска 14.</t>
         </is>
       </c>
       <c r="V39" s="14" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/james/</t>
+          <t>https://plato.stanford.edu/entries/ernst-mach/</t>
         </is>
       </c>
       <c r="W39" s="14" t="n"/>
       <c r="X39" s="14" t="inlineStr">
         <is>
-          <t>Уилсон приводит развёрнутую цитату Джеймса о том, как со временем меняется отношение к одним и тем же вещам — книги, люди, произведения искусства «тускнеют» независимо от воли человека. Цитата подкрепляет тезис Уилсона о том, что колебания эстетической восприимчивости — естественный, отчасти непредсказуемый аспект человеческого существования, а не повод для морального упрёка (как в случае с Дарвином). В сноске Уилсон отмечает иронию: в другой своей работе («Talks to Teachers on Psychology») сам Джеймс упрекал Дарвина за «неподходящие привычки», проявив то же морализаторство, которое сам же здесь и разоблачает.</t>
+          <t>Краснота как неописуемое. Мах — голос «известного взгляда», что постижение «быть красным» непосредственно и неразложимо: «Яркость, темнота, свет и цвет не поддаются описанию… могут быть только поименованы» (с. 159). Отсюда и вывод, что говорить об «ингредиентах» красноты ошибочно: понятие либо постигнуто полностью, либо его нет (с. 161). Против «тёплых и нечётких» требований. Вместе с Дюгемом и другими учёными 1880–1910 гг. Мах утверждал, что прогрессу физики мешает приверженность «тёплым и нечётким» требованиям к объяснению в духе Бойля. Уилсон признаёт, что «в своём критическом чутье Мах и Дюгем часто оказывались правы», но «как специалисты по семантической диагностике они перестарались»: многозначное выражение «теоретическое содержание» — наследие этих чрезмерных мнений (с. 166).</t>
         </is>
       </c>
       <c r="Y39" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z39" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_ii</t>
+          <t>chapter_3_vi</t>
         </is>
       </c>
       <c r="AA39" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/william-james</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/ernst-mach</t>
         </is>
       </c>
       <c r="AB39" s="14" t="inlineStr">
@@ -4899,64 +4903,72 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Бернард Бозанкет</t>
+          <t>Уильям Джеймс</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Bernard Bosanquet</t>
+          <t>William James</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="n"/>
+          <t>американец</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/w_james.jpg</t>
+        </is>
+      </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>1848–1923</t>
+          <t>1842–1910</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>1848-06-14</t>
+          <t>1842-01-11</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>1923-02-08</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="n"/>
+          <t>1910-08-26</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>сердечная недостаточность</t>
+        </is>
+      </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>Рок-Холл близ Алника, Нортумберленд, Англия</t>
+          <t>Нью-Йорк, США</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>55.4500, -1.7000</t>
+          <t>40.7128, -74.0060</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Чокоруа, Нью-Гэмпшир, США</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>51.5074, -0.1278</t>
+          <t>43.8800, -71.2300</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>Баллиол-колледж, Оксфорд</t>
+          <t>Гарвардская медицинская школа</t>
         </is>
       </c>
       <c r="N40" s="14" t="inlineStr">
         <is>
-          <t>Университетский колледж, Оксфорд; Сент-Эндрюсский университет</t>
+          <t>Гарвардский университет</t>
         </is>
       </c>
       <c r="O40" s="14" t="n"/>
@@ -4965,39 +4977,43 @@
       <c r="R40" s="14" t="n"/>
       <c r="S40" s="14" t="inlineStr">
         <is>
-          <t>абсолютный идеализм; эстетика; логика</t>
+          <t>психология; прагматизм</t>
         </is>
       </c>
       <c r="T40" s="14" t="inlineStr">
         <is>
-          <t>Английский философ, представитель британского абсолютного идеализма. Автор The Essentials of Logic, откуда Уилсон цитирует формулу о «мире как идее».</t>
+          <t>Американский философ и психолог, один из основателей прагматизма, автор The Principles of Psychology. В данном фрагменте цитируется как свидетель радикальной изменчивости человеческого восприятия и вкуса на протяжении жизни.</t>
         </is>
       </c>
       <c r="U40" s="14" t="inlineStr">
         <is>
-          <t>- Bernard Bosanquet, The Essentials of Logic, p. 6 - «Мир как идея» - Партиципативный идеализм - Амфиболизм</t>
-        </is>
-      </c>
-      <c r="V40" s="14" t="n"/>
+          <t>- The Principles of Psychology (изд. 1983), с. 227–228 - Talks to Teachers on Psychology: and to Students of Some of Life's Ideals (1913), с. 71–73 - “Pragmatism’s Conception of Truth” // Essays in Pragmatism (New York: Hafner, 1948), 167 — гл. 3, сноска 27</t>
+        </is>
+      </c>
+      <c r="V40" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/james/</t>
+        </is>
+      </c>
       <c r="W40" s="14" t="n"/>
       <c r="X40" s="14" t="inlineStr">
         <is>
-          <t>Бозанкет представляет самую сильную форму амфиболизма — партиципативный идеализм. Мир, общий для всех людей, в этой формулировке существует для каждого как нечто созданное в его собственном уме, связанном с собственным телом.</t>
+          <t>Уилсон приводит развёрнутую цитату Джеймса о том, как со временем меняется отношение к одним и тем же вещам — книги, люди, произведения искусства «тускнеют» независимо от воли человека. Цитата подкрепляет тезис Уилсона о том, что колебания эстетической восприимчивости — естественный, отчасти непредсказуемый аспект человеческого существования, а не повод для морального упрёка (как в случае с Дарвином). В сноске Уилсон отмечает иронию: в другой своей работе («Talks to Teachers on Psychology») сам Джеймс упрекал Дарвина за «неподходящие привычки», проявив то же морализаторство, которое сам же здесь и разоблачает. Гл. 3, §(vii) (с. 178–179). Джеймс выступает свидетелем того, как менялась оценка понятия энергии. Первые пятьдесят лет его считали известным только структурно, по способности организовывать научные выводы в инструментально эффективный паттерн. Джеймс пишет: «Термин ‘энергия’ даже не претендует на то, чтобы обозначать что-то ‘объективное’. Это всего лишь способ поверхностного измерения явлений, позволяющий свести их изменения к простой формуле». Уилсона «поражает», что Джеймс считает это общеизвестным, будто споры здесь невозможны. Сегодня понятие энергии считают вполне понятым, хотя знаний о ней заметно не прибавилось: к нему просто привыкли, как Хиггинс к Элизе. Отсюда вывод: формулам вроде «теоретическое содержание» нельзя давать «разгуливать свободно» при анализе языка.</t>
         </is>
       </c>
       <c r="Y40" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 2; гл. 3</t>
         </is>
       </c>
       <c r="Z40" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_vi</t>
+          <t>chapter_2_ii; chapter_3_vii</t>
         </is>
       </c>
       <c r="AA40" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/bernard-bosanquet</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/william-james</t>
         </is>
       </c>
       <c r="AB40" s="14" t="inlineStr">
@@ -5010,117 +5026,105 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Готлоб Фреге</t>
+          <t>Бернард Бозанкет</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Gottlob Frege</t>
+          <t>Bernard Bosanquet</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>немец</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/frege.jpg</t>
-        </is>
-      </c>
+          <t>британец</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="n"/>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>1848–1925</t>
+          <t>1848–1923</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>1848-11-08</t>
+          <t>1848-06-14</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>1925-07-26</t>
+          <t>1923-02-08</t>
         </is>
       </c>
       <c r="H41" s="14" t="n"/>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>Висмар, Мекленбург</t>
+          <t>Рок-Холл близ Алника, Нортумберленд, Англия</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>53.8913, 11.4650</t>
+          <t>55.4500, -1.7000</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>Бад-Кляйнен, Мекленбург</t>
+          <t>Лондон</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>53.7700, 11.4700</t>
+          <t>51.5074, -0.1278</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>Йенский университет; Гёттингенский университет</t>
+          <t>Баллиол-колледж, Оксфорд</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
-          <t>Йенский университет</t>
+          <t>Университетский колледж, Оксфорд; Сент-Эндрюсский университет</t>
         </is>
       </c>
       <c r="O41" s="14" t="n"/>
       <c r="P41" s="14" t="n"/>
-      <c r="Q41" s="14" t="inlineStr">
-        <is>
-          <t>Бертран Рассел; Людвиг Витгенштейн</t>
-        </is>
-      </c>
+      <c r="Q41" s="14" t="n"/>
       <c r="R41" s="14" t="n"/>
       <c r="S41" s="14" t="inlineStr">
         <is>
-          <t>логика; философия математики; философия языка</t>
+          <t>абсолютный идеализм; эстетика; логика</t>
         </is>
       </c>
       <c r="T41" s="14" t="inlineStr">
         <is>
-          <t>Немецкий философ и логик XIX века, один из главных основоположников современной логики и аналитической традиции в философии. Автор «понятийного письма» (Begriffsschrift) — формальной логической системы, предвосхитившей современную символическую логику, различения смысла и значения (Sinn/Bedeutung), значительных работ в философии математики и логицизме.</t>
+          <t>Английский философ, представитель британского абсолютного идеализма. Автор The Essentials of Logic, откуда Уилсон цитирует формулу о «мире как идее».</t>
         </is>
       </c>
       <c r="U41" s="14" t="inlineStr">
         <is>
-          <t>- Учение о «третьей сфере» существования концепций/мыслей — из эссе «Мысль» («Der Gedanke», 1918), канонического источника этой доктрины у Фреге. -</t>
-        </is>
-      </c>
-      <c r="V41" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/frege/</t>
-        </is>
-      </c>
+          <t>- Bernard Bosanquet, The Essentials of Logic, p. 6 - «Мир как идея» - Партиципативный идеализм - Амфиболизм</t>
+        </is>
+      </c>
+      <c r="V41" s="14" t="n"/>
       <c r="W41" s="14" t="n"/>
       <c r="X41" s="14" t="inlineStr">
         <is>
-          <t>Введён как фигура, с которой ассоциируется представление о гипотетической «третьей сфере» существования — не ментальной и не физической, — где, как считается, находится весь возможный запас концепций и мыслей. Уилсон явно отказывается от онтологического спора вокруг этого образа и предлагает прочитать содержательное ядро идеи Фреге на обычном языке — так рождается его термин klassicheskaya-kartina-kontseptsiy. Примечательно: хотя автор признаётся, что часто цитирует Фреге на протяжении книги, он прямо говорит, что более чистым представителем классической картины считает не его, а bertrand-russell — потому что у Фреге слишком много «эксцентричных» взглядов, не относящихся напрямую к обсуждаемой теме.</t>
+          <t>Бозанкет представляет самую сильную форму амфиболизма — партиципативный идеализм. Мир, общий для всех людей, в этой формулировке существует для каждого как нечто созданное в его собственном уме, связанном с собственным телом.</t>
         </is>
       </c>
       <c r="Y41" s="14" t="inlineStr">
         <is>
-          <t>гл. 1; гл. 3</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z41" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_ii; chapter_3_ii</t>
+          <t>chapter_2_vi</t>
         </is>
       </c>
       <c r="AA41" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/gottlob-frege</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/bernard-bosanquet</t>
         </is>
       </c>
       <c r="AB41" s="14" t="inlineStr">
@@ -5133,109 +5137,117 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Оливер Хевисайд</t>
+          <t>Готлоб Фреге</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Oliver Heaviside</t>
+          <t>Gottlob Frege</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
+          <t>немец</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/oheaviside.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/frege.jpg</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>1850–1925</t>
+          <t>1848–1925</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>1850-05-18</t>
+          <t>1848-11-08</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>1925-02-03</t>
+          <t>1925-07-26</t>
         </is>
       </c>
       <c r="H42" s="14" t="n"/>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>Кэмден-Таун, Лондон</t>
+          <t>Висмар, Мекленбург</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>51.5390, -0.1426</t>
+          <t>53.8913, 11.4650</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>Торки, Девон, Англия</t>
+          <t>Бад-Кляйнен, Мекленбург</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>50.4619, -3.5253</t>
+          <t>53.7700, 11.4700</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>самоучка</t>
-        </is>
-      </c>
-      <c r="N42" s="14" t="n"/>
+          <t>Йенский университет; Гёттингенский университет</t>
+        </is>
+      </c>
+      <c r="N42" s="14" t="inlineStr">
+        <is>
+          <t>Йенский университет</t>
+        </is>
+      </c>
       <c r="O42" s="14" t="n"/>
       <c r="P42" s="14" t="n"/>
-      <c r="Q42" s="14" t="n"/>
-      <c r="R42" s="14" t="inlineStr">
-        <is>
-          <t>Медаль Фарадея (1922, первый лауреат)</t>
-        </is>
-      </c>
+      <c r="Q42" s="14" t="inlineStr">
+        <is>
+          <t>Бертран Рассел; Людвиг Витгенштейн</t>
+        </is>
+      </c>
+      <c r="R42" s="14" t="n"/>
       <c r="S42" s="14" t="inlineStr">
         <is>
-          <t>электротехника; операционное исчисление; электродинамика</t>
+          <t>логика; философия математики; философия языка</t>
         </is>
       </c>
       <c r="T42" s="14" t="inlineStr">
         <is>
-          <t>Английский физик-самоучка, математик и инженер-электрик. Не имел формального университетского образования, но переформулировал уравнения Максвелла в привычном сегодня векторном виде, разработал операционное исчисление, ввёл в обиход термины «импеданс», «индуктивность», «проводимость», предсказал существование ионосферы (позже названной слоем Хевисайда).</t>
+          <t>Немецкий философ и логик XIX века, один из главных основоположников современной логики и аналитической традиции в философии. Автор «понятийного письма» (Begriffsschrift) — формальной логической системы, предвосхитившей современную символическую логику, различения смысла и значения (Sinn/Bedeutung), значительных работ в философии математики и логицизме.</t>
         </is>
       </c>
       <c r="U42" s="14" t="inlineStr">
         <is>
-          <t>- Операционное исчисление (operational calculus) — метод, которым Хевисайд пользовался без строгого математического обоснования, что вызвало споры с академическими математиками его времени - Векторная переформулировка уравнений Максвелла - Телеграфные уравнения (theory of transmission lines)</t>
-        </is>
-      </c>
-      <c r="V42" s="14" t="n"/>
+          <t>- Учение о «третьей сфере» существования концепций/мыслей — из эссе «Мысль» («Der Gedanke», 1918), канонического источника этой доктрины у Фреге. -</t>
+        </is>
+      </c>
+      <c r="V42" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/frege/</t>
+        </is>
+      </c>
       <c r="W42" s="14" t="n"/>
       <c r="X42" s="14" t="inlineStr">
         <is>
-          <t>Вторая ключевая фигура после Куайна, упомянутая уже в предисловии. Уилсон ссылается на него в контексте собственного проекта «Классическая механика сто лет спустя», нацеленного на то, чтобы проследить эволюцию значений базовых понятий классической физики. Для Уилсона Хевисайд — пример практика, который самозабвенно боролся с теоретическими догмами через саму практику, а не через формальное философское обоснование — то есть иллюстрация того, что понятия могут развиваться и уточняться «снизу», в ходе инженерной и вычислительной работы, опережая их строгое теоретическое осмысление.</t>
+          <t>Введён как фигура, с которой ассоциируется представление о гипотетической «третьей сфере» существования — не ментальной и не физической, — где, как считается, находится весь возможный запас концепций и мыслей. Уилсон явно отказывается от онтологического спора вокруг этого образа и предлагает прочитать содержательное ядро идеи Фреге на обычном языке — так рождается его термин klassicheskaya-kartina-kontseptsiy. Примечательно: хотя автор признаётся, что часто цитирует Фреге на протяжении книги, он прямо говорит, что более чистым представителем классической картины считает не его, а bertrand-russell — потому что у Фреге слишком много «эксцентричных» взглядов, не относящихся напрямую к обсуждаемой теме.</t>
         </is>
       </c>
       <c r="Y42" s="14" t="inlineStr">
         <is>
-          <t>предисловие; гл. 3</t>
+          <t>гл. 1; гл. 3</t>
         </is>
       </c>
       <c r="Z42" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_v; predislovie</t>
+          <t>chapter_1_ii; chapter_3_ii</t>
         </is>
       </c>
       <c r="AA42" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/oliver-heaviside</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/gottlob-frege</t>
         </is>
       </c>
       <c r="AB42" s="14" t="inlineStr">
@@ -5248,117 +5260,109 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Генрих Герц</t>
+          <t>Оливер Хевисайд</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Heinrich Hertz</t>
+          <t>Oliver Heaviside</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>немец</t>
+          <t>британец</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/h_hertz.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/oheaviside.jpg</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>1857–1894</t>
+          <t>1850–1925</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>1857-02-22</t>
+          <t>1850-05-18</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>1894-01-01</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>гранулематоз с полиангиитом (предположительно)</t>
-        </is>
-      </c>
+          <t>1925-02-03</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="n"/>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>Гамбург</t>
+          <t>Кэмден-Таун, Лондон</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>53.5511, 9.9937</t>
+          <t>51.5390, -0.1426</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>Бонн</t>
+          <t>Торки, Девон, Англия</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>50.7374, 7.0982</t>
+          <t>50.4619, -3.5253</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>Берлинский университет</t>
-        </is>
-      </c>
-      <c r="N43" s="14" t="inlineStr">
-        <is>
-          <t>Кильский университет; Политехникум Карлсруэ; Боннский университет</t>
-        </is>
-      </c>
-      <c r="O43" s="14" t="inlineStr">
-        <is>
-          <t>Герман фон Гельмгольц</t>
-        </is>
-      </c>
+          <t>самоучка</t>
+        </is>
+      </c>
+      <c r="N43" s="14" t="n"/>
+      <c r="O43" s="14" t="n"/>
       <c r="P43" s="14" t="n"/>
       <c r="Q43" s="14" t="n"/>
-      <c r="R43" s="14" t="n"/>
+      <c r="R43" s="14" t="inlineStr">
+        <is>
+          <t>Медаль Фарадея (1922, первый лауреат)</t>
+        </is>
+      </c>
       <c r="S43" s="14" t="inlineStr">
         <is>
-          <t>физика; электродинамика; механика</t>
+          <t>электротехника; операционное исчисление; электродинамика</t>
         </is>
       </c>
       <c r="T43" s="14" t="inlineStr">
         <is>
-          <t>Немецкий физик, экспериментально подтвердивший существование электромагнитных волн, предсказанных теорией Максвелла (1886–1889) — единица частоты названа в его честь. В конце жизни написал философски значимый труд «Die Prinzipien der Mechanik» («Принципы механики», опубликован посмертно в 1894 году), где предложил переформулировать классическую механику без понятия силы как примитивного, взяв вместо этого за основу массу, пространство и время — и явно оговорил, что физические теории следует оценивать не как «истинные копии» реальности, а как более или менее «допустимые», «правильные» и «целесообразные» изображения (zulässige, richtige, zweckmäßige Bilder).</t>
+          <t>Английский физик-самоучка, математик и инженер-электрик. Не имел формального университетского образования, но переформулировал уравнения Максвелла в привычном сегодня векторном виде, разработал операционное исчисление, ввёл в обиход термины «импеданс», «индуктивность», «проводимость», предсказал существование ионосферы (позже названной слоем Хевисайда).</t>
         </is>
       </c>
       <c r="U43" s="14" t="inlineStr">
         <is>
-          <t>- «Die Prinzipien der Mechanik» (1894) — переформулировка механики без силы как примитивного понятия, концепция теорий как «допустимых изображений» (zulässige Bilder)</t>
+          <t>- Операционное исчисление (operational calculus) — метод, которым Хевисайд пользовался без строгого математического обоснования, что вызвало споры с академическими математиками его времени - Векторная переформулировка уравнений Максвелла - Телеграфные уравнения (theory of transmission lines)</t>
         </is>
       </c>
       <c r="V43" s="14" t="n"/>
       <c r="W43" s="14" t="n"/>
       <c r="X43" s="14" t="inlineStr">
         <is>
-          <t>Назван вместе с Гельмгольцем как пример раннего, «сдержанного» холизма XIX века — умеренного отступления от классической ортодоксии, в противовес позднейшим крайним формам (кунианизм, пост-структурализм). (Гипотеза, требует проверки): учитывая, что вся книга Уилсона посвящена именно понятиям классической механики и их «блужданию», герцевская идея теорий-как-допустимых-изображений (Bilder) — вероятно, не случайное совпадение, а содержательно значимая точка соприкосновения, которая может всплыть в других главах книги, посвящённых механике напрямую.</t>
+          <t>Вторая ключевая фигура после Куайна, упомянутая уже в предисловии. Уилсон ссылается на него в контексте собственного проекта «Классическая механика сто лет спустя», нацеленного на то, чтобы проследить эволюцию значений базовых понятий классической физики. Для Уилсона Хевисайд — пример практика, который самозабвенно боролся с теоретическими догмами через саму практику, а не через формальное философское обоснование — то есть иллюстрация того, что понятия могут развиваться и уточняться «снизу», в ходе инженерной и вычислительной работы, опережая их строгое теоретическое осмысление.</t>
         </is>
       </c>
       <c r="Y43" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>предисловие; гл. 3</t>
         </is>
       </c>
       <c r="Z43" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_ix</t>
+          <t>chapter_3_v; predislovie</t>
         </is>
       </c>
       <c r="AA43" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/heinrich-hertz</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/oliver-heaviside</t>
         </is>
       </c>
       <c r="AB43" s="14" t="inlineStr">
@@ -5371,117 +5375,117 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Джон Дьюи</t>
+          <t>Генрих Герц</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>John Dewey</t>
+          <t>Heinrich Hertz</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>немец</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j_dewey.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/h_hertz.jpg</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>1859–1952</t>
+          <t>1857–1894</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>1859-10-20</t>
+          <t>1857-02-22</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>1952-06-01</t>
+          <t>1894-01-01</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>пневмония</t>
+          <t>гранулематоз с полиангиитом (предположительно)</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>Берлингтон, Вермонт, США</t>
+          <t>Гамбург</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>44.4759, -73.2121</t>
+          <t>53.5511, 9.9937</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>Нью-Йорк, США</t>
+          <t>Бонн</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>40.7128, -74.0060</t>
+          <t>50.7374, 7.0982</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>Вермонтский университет; Университет Джонса Хопкинса</t>
+          <t>Берлинский университет</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
         <is>
-          <t>Чикагский университет; Колумбийский университет</t>
-        </is>
-      </c>
-      <c r="O44" s="14" t="n"/>
+          <t>Кильский университет; Политехникум Карлсруэ; Боннский университет</t>
+        </is>
+      </c>
+      <c r="O44" s="14" t="inlineStr">
+        <is>
+          <t>Герман фон Гельмгольц</t>
+        </is>
+      </c>
       <c r="P44" s="14" t="n"/>
       <c r="Q44" s="14" t="n"/>
       <c r="R44" s="14" t="n"/>
       <c r="S44" s="14" t="inlineStr">
         <is>
-          <t>прагматизм; философия образования; эпистемология</t>
+          <t>физика; электродинамика; механика</t>
         </is>
       </c>
       <c r="T44" s="14" t="inlineStr">
         <is>
-          <t>Американский философ, психолог и реформатор образования, один из центральных представителей американского прагматизма (наряду с Пирсом и Джеймсом). Автор работ по логике как теории исследования, философии опыта и природы, а также обширных трудов по реформе образования.</t>
+          <t>Немецкий физик, экспериментально подтвердивший существование электромагнитных волн, предсказанных теорией Максвелла (1886–1889) — единица частоты названа в его честь. В конце жизни написал философски значимый труд «Die Prinzipien der Mechanik» («Принципы механики», опубликован посмертно в 1894 году), где предложил переформулировать классическую механику без понятия силы как примитивного, взяв вместо этого за основу массу, пространство и время — и явно оговорил, что физические теории следует оценивать не как «истинные копии» реальности, а как более или менее «допустимые», «правильные» и «целесообразные» изображения (zulässige, richtige, zweckmäßige Bilder).</t>
         </is>
       </c>
       <c r="U44" s="14" t="inlineStr">
         <is>
-          <t>John Dewey, Logic: The Theory of Inquiry (New York: Holt, Rinehart and Win- ston, 1938).</t>
-        </is>
-      </c>
-      <c r="V44" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/dewey/</t>
-        </is>
-      </c>
+          <t>- «Die Prinzipien der Mechanik» (1894) — переформулировка механики без силы как примитивного понятия, концепция теорий как «допустимых изображений» (zulässige Bilder)</t>
+        </is>
+      </c>
+      <c r="V44" s="14" t="n"/>
       <c r="W44" s="14" t="n"/>
       <c r="X44" s="14" t="inlineStr">
         <is>
-          <t>(пока минимальный текстовой материал) Упомянут вскользь, одним именем, в пункте (11) подраздела (iii) — как более ранний мыслитель, независимо от Витгенштейна обеспокоенный «полным классическим попурри» в отношении концепций. То есть назван как ещё один, отдельный от витгенштейновской линии, источник скепсиса по отношению к klassicheskaya-kartina-kontseptsiy. Никаких конкретных работ или тезисов Дьюи не названо.</t>
+          <t>Назван вместе с Гельмгольцем как пример раннего, «сдержанного» холизма XIX века — умеренного отступления от классической ортодоксии, в противовес позднейшим крайним формам (кунианизм, пост-структурализм). (Гипотеза, требует проверки): учитывая, что вся книга Уилсона посвящена именно понятиям классической механики и их «блужданию», герцевская идея теорий-как-допустимых-изображений (Bilder) — вероятно, не случайное совпадение, а содержательно значимая точка соприкосновения, которая может всплыть в других главах книги, посвящённых механике напрямую.</t>
         </is>
       </c>
       <c r="Y44" s="14" t="inlineStr">
         <is>
-          <t>гл. 1; гл. 2; гл. 3</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z44" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_iv; chapter_2_iv; chapter_3_ii</t>
+          <t>chapter_1_ix</t>
         </is>
       </c>
       <c r="AA44" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/john-dewey</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/heinrich-hertz</t>
         </is>
       </c>
       <c r="AB44" s="14" t="inlineStr">
@@ -5494,113 +5498,117 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Альфред Норт Уайтхед</t>
+          <t>Джон Дьюи</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Alfred North Whitehead</t>
+          <t>John Dewey</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="n"/>
+          <t>американец</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j_dewey.jpg</t>
+        </is>
+      </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>1861–1947</t>
+          <t>1859–1952</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>1861-02-15</t>
+          <t>1859-10-20</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>1947-12-30</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="n"/>
+          <t>1952-06-01</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>пневмония</t>
+        </is>
+      </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>Рамсгит, Англия</t>
+          <t>Берлингтон, Вермонт, США</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>51.3350, 1.4190</t>
+          <t>44.4759, -73.2121</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>Кембридж, Массачусетс, США</t>
+          <t>Нью-Йорк, США</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>42.3736, -71.1097</t>
+          <t>40.7128, -74.0060</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
         <is>
-          <t>Тринити-колледж, Кембридж</t>
+          <t>Вермонтский университет; Университет Джонса Хопкинса</t>
         </is>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
-          <t>Тринити-колледж, Кембридж; Имперский колледж, Лондон; Гарвардский университет</t>
+          <t>Чикагский университет; Колумбийский университет</t>
         </is>
       </c>
       <c r="O45" s="14" t="n"/>
-      <c r="P45" s="14" t="inlineStr">
-        <is>
-          <t>Бертран Рассел; Уиллард Куайн</t>
-        </is>
-      </c>
+      <c r="P45" s="14" t="n"/>
       <c r="Q45" s="14" t="n"/>
       <c r="R45" s="14" t="n"/>
       <c r="S45" s="14" t="inlineStr">
         <is>
-          <t>математика; логика; философия процесса</t>
+          <t>прагматизм; философия образования; эпистемология</t>
         </is>
       </c>
       <c r="T45" s="14" t="inlineStr">
         <is>
-          <t>Английский математик и философ, один из создателей процессуальной философии.</t>
+          <t>Американский философ, психолог и реформатор образования, один из центральных представителей американского прагматизма (наряду с Пирсом и Джеймсом). Автор работ по логике как теории исследования, философии опыта и природы, а также обширных трудов по реформе образования.</t>
         </is>
       </c>
       <c r="U45" s="14" t="inlineStr">
         <is>
-          <t>- Alfred North Whitehead, The Concept of Nature, p. 29 - Научная абстракция - Природа - Геометризация физических объектов</t>
+          <t>John Dewey, Logic: The Theory of Inquiry (New York: Holt, Rinehart and Win- ston, 1938).</t>
         </is>
       </c>
       <c r="V45" s="14" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/whitehead/</t>
+          <t>https://plato.stanford.edu/entries/dewey/</t>
         </is>
       </c>
       <c r="W45" s="14" t="n"/>
       <c r="X45" s="14" t="inlineStr">
         <is>
-          <t>Уайтхед используется как источник мысли о том, что научное описание неизбежно выбирает определённые аспекты природы. Физико-геометрическая схема может быть исключительно полезной, но это не делает её полным описанием всех свойств реально существующего мира.</t>
+          <t>(пока минимальный текстовой материал) Упомянут вскользь, одним именем, в пункте (11) подраздела (iii) — как более ранний мыслитель, независимо от Витгенштейна обеспокоенный «полным классическим попурри» в отношении концепций. То есть назван как ещё один, отдельный от витгенштейновской линии, источник скепсиса по отношению к klassicheskaya-kartina-kontseptsiy. Никаких конкретных работ или тезисов Дьюи не названо.</t>
         </is>
       </c>
       <c r="Y45" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 1; гл. 2; гл. 3</t>
         </is>
       </c>
       <c r="Z45" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_vi</t>
+          <t>chapter_1_iv; chapter_2_iv; chapter_3_ii</t>
         </is>
       </c>
       <c r="AA45" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/alfred-north-whitehead</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/john-dewey</t>
         </is>
       </c>
       <c r="AB45" s="14" t="inlineStr">
@@ -5613,117 +5621,113 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Пьер Дюгем</t>
+          <t>Альфред Норт Уайтхед</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Pierre Duhem</t>
+          <t>Alfred North Whitehead</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>француз</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/pierre_duhem.jpg</t>
-        </is>
-      </c>
+          <t>британец</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="n"/>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>1861–1916</t>
+          <t>1861–1947</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>1861-06-09</t>
+          <t>1861-02-15</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>1916-09-14</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>сердечный приступ</t>
-        </is>
-      </c>
+          <t>1947-12-30</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="n"/>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Рамсгит, Англия</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>48.8566, 2.3522</t>
+          <t>51.3350, 1.4190</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>Кабреспин, Франция</t>
+          <t>Кембридж, Массачусетс, США</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>43.3700, 2.4500</t>
+          <t>42.3736, -71.1097</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>Высшая нормальная школа</t>
+          <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
       <c r="N46" s="14" t="inlineStr">
         <is>
-          <t>Лилльский университет; Реннский университет; Университет Бордо</t>
+          <t>Тринити-колледж, Кембридж; Имперский колледж, Лондон; Гарвардский университет</t>
         </is>
       </c>
       <c r="O46" s="14" t="n"/>
-      <c r="P46" s="14" t="n"/>
+      <c r="P46" s="14" t="inlineStr">
+        <is>
+          <t>Бертран Рассел; Уиллард Куайн</t>
+        </is>
+      </c>
       <c r="Q46" s="14" t="n"/>
       <c r="R46" s="14" t="n"/>
       <c r="S46" s="14" t="inlineStr">
         <is>
-          <t>термодинамика; философия науки; история науки</t>
+          <t>математика; логика; философия процесса</t>
         </is>
       </c>
       <c r="T46" s="14" t="inlineStr">
         <is>
-          <t>Французский физик (термодинамика), историк и философ науки. В книге «Физическая теория, её цель и строение» (1906) показал, что гипотезу нельзя проверить изолированно — только вместе с вспомогательными допущениями (позже — тезис Дюэма–Куайна). Открыл для истории науки средневековую физику.</t>
+          <t>Английский математик и философ, один из создателей процессуальной философии.</t>
         </is>
       </c>
       <c r="U46" s="14" t="inlineStr">
         <is>
-          <t>- Тезис о холизме проверки (Дюэма–Куайна) — у Уилсона в этом месте не назван, но ср. willard-quine.</t>
+          <t>- Alfred North Whitehead, The Concept of Nature, p. 29 - Научная абстракция - Природа - Геометризация физических объектов</t>
         </is>
       </c>
       <c r="V46" s="14" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/duhem/</t>
+          <t>https://plato.stanford.edu/entries/whitehead/</t>
         </is>
       </c>
       <c r="W46" s="14" t="n"/>
       <c r="X46" s="14" t="inlineStr">
         <is>
-          <t>Вместе с Махом и другими учёными 1880–1910 гг. Дюгем утверждал, что прогрессу физики мешает приверженность «тёплым и нечётким» требованиям к объяснению, сходным с бойлевскими (ср. robert-boyle). Именно на этом выражение «теоретическое содержание» впервые приобрело философское значение: как способ сказать, что науке не нужны «тёплые и нечёткие» качества в объяснениях. Уилсон признаёт, что «в своём критическом чутье Мах и Дюгем часто оказывались правы», но «как специалисты по семантической диагностике они перестарались» (с. 166).</t>
+          <t>Уайтхед используется как источник мысли о том, что научное описание неизбежно выбирает определённые аспекты природы. Физико-геометрическая схема может быть исключительно полезной, но это не делает её полным описанием всех свойств реально существующего мира.</t>
         </is>
       </c>
       <c r="Y46" s="14" t="inlineStr">
         <is>
-          <t>гл. 3</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z46" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_vi</t>
+          <t>chapter_2_vi</t>
         </is>
       </c>
       <c r="AA46" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/pierre-duhem</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/alfred-north-whitehead</t>
         </is>
       </c>
       <c r="AB46" s="14" t="inlineStr">
@@ -5736,12 +5740,12 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Жак Адамар</t>
+          <t>Пьер Дюгем</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Jacques Hadamard</t>
+          <t>Pierre Duhem</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -5751,43 +5755,47 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/hadamard.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/pierre_duhem.jpg</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>1865–1963</t>
+          <t>1861–1916</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>1865-12-08</t>
+          <t>1861-06-09</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>1963-10-17</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="n"/>
+          <t>1916-09-14</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>сердечный приступ</t>
+        </is>
+      </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>Версаль, Франция</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>48.8049, 2.1204</t>
+          <t>48.8566, 2.3522</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>Париж</t>
+          <t>Кабреспин, Франция</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>48.8566, 2.3522</t>
+          <t>43.3700, 2.4500</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -5797,7 +5805,7 @@
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>Коллеж де Франс; Политехническая школа; Парижский университет</t>
+          <t>Лилльский университет; Реннский университет; Университет Бордо</t>
         </is>
       </c>
       <c r="O47" s="14" t="n"/>
@@ -5806,39 +5814,43 @@
       <c r="R47" s="14" t="n"/>
       <c r="S47" s="14" t="inlineStr">
         <is>
-          <t>математический анализ; теория чисел; дифференциальные уравнения</t>
+          <t>термодинамика; философия науки; история науки</t>
         </is>
       </c>
       <c r="T47" s="14" t="inlineStr">
         <is>
-          <t>Французский математик, один из крупнейших математиков рубежа XIX–XX веков. Доказал теорему о распределении простых чисел (1896, независимо от де ла Валле-Пуссена), внёс фундаментальный вклад в комплексный анализ, теорию дифференциальных уравнений в частных производных и вариационное исчисление. Ввёл понятие «корректно поставленной задачи» (well-posed problem) — задачи, для которой решение существует, единственно и непрерывно зависит от исходных данных; это понятие стало основополагающим для математической физики. Также автор известной работы о психологии математического творчества («Психология изобретения в области математики»).</t>
+          <t>Французский физик (термодинамика), историк и философ науки. В книге «Физическая теория, её цель и строение» (1906) показал, что гипотезу нельзя проверить изолированно — только вместе с вспомогательными допущениями (позже — тезис Дюэма–Куайна). Открыл для истории науки средневековую физику.</t>
         </is>
       </c>
       <c r="U47" s="14" t="inlineStr">
         <is>
-          <t>- Понятие «корректно поставленной задачи» (well-posed problem) — существование, единственность и устойчивость решения относительно исходных данных - Практика исследования моделей как семейств условий (начальные/граничные значения), а не изолированных случаев</t>
-        </is>
-      </c>
-      <c r="V47" s="14" t="n"/>
+          <t>- Тезис о холизме проверки (Дюэма–Куайна) — у Уилсона в этом месте не назван, но ср. willard-quine.</t>
+        </is>
+      </c>
+      <c r="V47" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/duhem/</t>
+        </is>
+      </c>
       <c r="W47" s="14" t="n"/>
       <c r="X47" s="14" t="inlineStr">
         <is>
-          <t>Указан Уилсоном в предисловии наравне с Хевисайдом и Рёло как один из авторов, чьим трудам он «особенно обязан» — трое инженеров и прикладных математиков второй половины XIX века, чьи замечания о концептуальной неоднозначности вдохновили общий замысел книги: демонстрация того, что понятия (в частности, используемые в механике) меняют своё значение при переносе в разные среды применения. Ключевая содержательная связь, судя по вторичной литературе о книге: концепция Адамара о «корректно поставленной задаче» — идея, что прикладные математики работают не с единичным случаем, а с целым семейством условий, варьируемых по начальным и граничным значениям — используется Уилсоном как модель того, как понятия должны пониматься через диапазон применения, а не через одно фиксированное значение. Это прямо перекликается с центральной темой книги — blujdayushee-kachestvo.</t>
+          <t>Вместе с Махом и другими учёными 1880–1910 гг. Дюгем утверждал, что прогрессу физики мешает приверженность «тёплым и нечётким» требованиям к объяснению, сходным с бойлевскими (ср. robert-boyle). Именно на этом выражение «теоретическое содержание» впервые приобрело философское значение: как способ сказать, что науке не нужны «тёплые и нечёткие» качества в объяснениях. Уилсон признаёт, что «в своём критическом чутье Мах и Дюгем часто оказывались правы», но «как специалисты по семантической диагностике они перестарались» (с. 166).</t>
         </is>
       </c>
       <c r="Y47" s="14" t="inlineStr">
         <is>
-          <t>предисловие</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z47" s="14" t="inlineStr">
         <is>
-          <t>predislovie</t>
+          <t>chapter_3_vi</t>
         </is>
       </c>
       <c r="AA47" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/jacques-hadamard</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/pierre-duhem</t>
         </is>
       </c>
       <c r="AB47" s="14" t="inlineStr">
@@ -5851,109 +5863,109 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Хилэр Беллок</t>
+          <t>Жак Адамар</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Hilaire Belloc</t>
+          <t>Jacques Hadamard</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>британец французского происхождения</t>
+          <t>француз</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/h_belloc.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/hadamard.jpg</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>1870–1953</t>
+          <t>1865–1963</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>1870-07-27</t>
+          <t>1865-12-08</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>1953-07-16</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>ожоги и шок после падения в камин</t>
-        </is>
-      </c>
+          <t>1963-10-17</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="n"/>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>Ла-Сель-Сен-Клу, Франция</t>
+          <t>Версаль, Франция</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>48.8500, 2.1300</t>
+          <t>48.8049, 2.1204</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>Гилфорд, Англия</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>51.2362, -0.5704</t>
+          <t>48.8566, 2.3522</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>Баллиол-колледж, Оксфорд</t>
-        </is>
-      </c>
-      <c r="N48" s="14" t="n"/>
+          <t>Высшая нормальная школа</t>
+        </is>
+      </c>
+      <c r="N48" s="14" t="inlineStr">
+        <is>
+          <t>Коллеж де Франс; Политехническая школа; Парижский университет</t>
+        </is>
+      </c>
       <c r="O48" s="14" t="n"/>
       <c r="P48" s="14" t="n"/>
       <c r="Q48" s="14" t="n"/>
       <c r="R48" s="14" t="n"/>
       <c r="S48" s="14" t="inlineStr">
         <is>
-          <t>поэзия; эссеистика; история</t>
+          <t>математический анализ; теория чисел; дифференциальные уравнения</t>
         </is>
       </c>
       <c r="T48" s="14" t="inlineStr">
         <is>
-          <t>Англо-французский писатель, поэт, эссеист, историк и политик (член парламента от Солфорда, 1906–1910), близкий друг и соавтор Г. К. Честертона. Наиболее известен циклом иронично-нравоучительных детских стихов «Cautionary Tales for Children» и родственными сборниками вроде «Cautionary Verses» — сатирическими баснями о детях, которых постигает нелепая, преувеличенно жестокая кара за шалости.</t>
+          <t>Французский математик, один из крупнейших математиков рубежа XIX–XX веков. Доказал теорему о распределении простых чисел (1896, независимо от де ла Валле-Пуссена), внёс фундаментальный вклад в комплексный анализ, теорию дифференциальных уравнений в частных производных и вариационное исчисление. Ввёл понятие «корректно поставленной задачи» (well-posed problem) — задачи, для которой решение существует, единственно и непрерывно зависит от исходных данных; это понятие стало основополагающим для математической физики. Также автор известной работы о психологии математического творчества («Психология изобретения в области математики»).</t>
         </is>
       </c>
       <c r="U48" s="14" t="inlineStr">
         <is>
-          <t>- Hilaire Belloc, «Jim, Who Ran Away from his Nurse, and was Eaten by a Lion», в сб. «Cautionary Verses» (New York: Alfred A. Knopf, 1976), 12.</t>
+          <t>- Понятие «корректно поставленной задачи» (well-posed problem) — существование, единственность и устойчивость решения относительно исходных данных - Практика исследования моделей как семейств условий (начальные/граничные значения), а не изолированных случаев</t>
         </is>
       </c>
       <c r="V48" s="14" t="n"/>
       <c r="W48" s="14" t="n"/>
       <c r="X48" s="14" t="inlineStr">
         <is>
-          <t>Процитировано двустишие из стихотворения «Jim, Who Ran Away from His Nurse, and Was Eaten by a Lion» («Джим, который сбежал от няни и был съеден львом», сб. «Cautionary Verses», 1976): совет «всегда держись близ медсестры / из страха встрять во что похуже». Уилсон приводит эти строки иронически — как образ психологии чрезмерной осторожности, к которой сводится один из возможных ответов на дилемму «классицизм vs. дикие анти-классические крайности»: если единственная альтернатива классическому мышлению — кунианизм и пост-структурализм, разумнее держаться классицизма из страха перед худшим. Уилсон сразу же дистанцируется от такой позиции, называя собственную оценку анти-классицизма «значительно более сдержанной».</t>
+          <t>Указан Уилсоном в предисловии наравне с Хевисайдом и Рёло как один из авторов, чьим трудам он «особенно обязан» — трое инженеров и прикладных математиков второй половины XIX века, чьи замечания о концептуальной неоднозначности вдохновили общий замысел книги: демонстрация того, что понятия (в частности, используемые в механике) меняют своё значение при переносе в разные среды применения. Ключевая содержательная связь, судя по вторичной литературе о книге: концепция Адамара о «корректно поставленной задаче» — идея, что прикладные математики работают не с единичным случаем, а с целым семейством условий, варьируемых по начальным и граничным значениям — используется Уилсоном как модель того, как понятия должны пониматься через диапазон применения, а не через одно фиксированное значение. Это прямо перекликается с центральной темой книги — blujdayushee-kachestvo.</t>
         </is>
       </c>
       <c r="Y48" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>предисловие</t>
         </is>
       </c>
       <c r="Z48" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_ix</t>
+          <t>predislovie</t>
         </is>
       </c>
       <c r="AA48" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/hilaire-belloc</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/jacques-hadamard</t>
         </is>
       </c>
       <c r="AB48" s="14" t="inlineStr">
@@ -5966,133 +5978,105 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Бертран Рассел</t>
+          <t>Альфред Лоусон</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Bertrand Russell</t>
+          <t>Alfred William Lawson</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
+          <t>американец (уроженец Англии)</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/russel_1936.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/alfred_lawson.jpg</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>1872–1970</t>
+          <t>1869–1954</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>1872-05-18</t>
+          <t>1869-03-24</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>1970-02-02</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>грипп</t>
-        </is>
-      </c>
+          <t>1954-11-29</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="n"/>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>Треллек, Уэльс</t>
+          <t>Лондон</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>51.7500, -2.7800</t>
+          <t>51.5074, -0.1278</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>Пенриндейдрайт, Уэльс</t>
+          <t>Сан-Антонио, Техас, США</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>52.9300, -4.0700</t>
-        </is>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Тринити-колледж, Кембридж</t>
-        </is>
-      </c>
+          <t>29.4241, -98.4936</t>
+        </is>
+      </c>
+      <c r="M49" s="14" t="n"/>
       <c r="N49" s="14" t="inlineStr">
         <is>
-          <t>Тринити-колледж, Кембридж; Чикагский университет; Калифорнийский университет в Лос-Анджелесе</t>
-        </is>
-      </c>
-      <c r="O49" s="14" t="inlineStr">
-        <is>
-          <t>Альфред Норт Уайтхед</t>
-        </is>
-      </c>
-      <c r="P49" s="14" t="inlineStr">
-        <is>
-          <t>Людвиг Витгенштейн</t>
-        </is>
-      </c>
-      <c r="Q49" s="14" t="inlineStr">
-        <is>
-          <t>Готлоб Фреге; Годфри Харольд Харди</t>
-        </is>
-      </c>
-      <c r="R49" s="14" t="inlineStr">
-        <is>
-          <t>Нобелевская премия по литературе (1950)</t>
-        </is>
-      </c>
+          <t>Humanity Benefactor Foundation; University of Lawsonomy (Де-Мойн)</t>
+        </is>
+      </c>
+      <c r="O49" s="14" t="n"/>
+      <c r="P49" s="14" t="n"/>
+      <c r="Q49" s="14" t="n"/>
+      <c r="R49" s="14" t="n"/>
       <c r="S49" s="14" t="inlineStr">
         <is>
-          <t>математическая логика; аналитическая философия; эпистемология</t>
+          <t>бейсбол; авиация; «лоусономия»</t>
         </is>
       </c>
       <c r="T49" s="14" t="inlineStr">
         <is>
-          <t>Британский философ, логик и математик, один из основателей аналитической философии. Соавтор (вместе с Уайтхедом) «Principia Mathematica» — попытки свести математику к логике. Автор теории дескрипций, логического атомизма; лауреат Нобелевской премии по литературе (1950).</t>
+          <t>Американский бейсболист, пионер авиации и утопический «философ». В молодости профессиональный питчер и организатор бейсбольных лиг. Издавал одни из первых авиационных журналов (Fly, Aircraft), в 1919 году построил один из первых пассажирских самолётов (Lawson Airliner). С 1920-х годов проповедовал собственную всеобъемлющую доктрину — лоусономию: физику, построенную на «давлении и всасывании» (Suction and Pressure), «проницаемости» (Penetrability) и движении «зиг, заг и вихрь» (Zig-Zag-and-Swirl). В годы Депрессии вёл экономическое движение Direct Credits Society, в 1943 году основал в Де-Мойне «Университет лоусономии».</t>
         </is>
       </c>
       <c r="U49" s="14" t="inlineStr">
         <is>
-          <t>- Логический атомизм / программа сведения математики к логике («Principia Mathematica») - «Проблемы философии» (The Problems of Philosophy, 1912) — основной каркас для систематизации klassicheskaya-kartina-kontseptsiy, см. отдельную карточку problemy-filosofii-1912</t>
-        </is>
-      </c>
-      <c r="V49" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/russell/</t>
-        </is>
-      </c>
+          <t>- Сноска 24: Lyell D. Henry Jr., Zig-Zag-and-Swirl: Alfred W. Lawson's Quest for Greatness (Iowa City: University of Iowa Press, 1991). В переводе автор указан как «Henry Lyell». - Сноска 24: Martin Gardner, Fads and Fallacies in the Name of Science (New York: Dover, 1957); у Гарднера о Лоусоне есть отдельный очерк.</t>
+        </is>
+      </c>
+      <c r="V49" s="14" t="n"/>
       <c r="W49" s="14" t="n"/>
       <c r="X49" s="14" t="inlineStr">
         <is>
-          <t>Уилсон прямо пишет в предисловии, что на философской стороне Рассел и Куайн долгое время служили для него «опорами», между которыми он старался прокладывать курс в вопросах, касающихся концепций, предикатов и работы с понятиями (см. также willard-quine — второй полюс той же пары). Гораздо более весомая роль обнаружилась в главе 1. Хотя Уилсон чаще цитирует Фреге (см. gottlob-frege), он прямо заявляет, что именно Рассел — более чистый, показательный представитель того, что он называет klassicheskaya-kartina-kontseptsiy («классическая картина концепций»): у Фреге слишком много «эксцентричных» побочных взглядов, а Рассел даёт более чистый случай. Работа «Проблемы философии» (1912) названа «основным каркасом», из которого Уилсон выводит систематизированный список тезисов классической картины (полностью — в приложении к главе 3, см. problemy-filosofii-1912).</t>
+          <t>Образец «мошенника» (или самообманщика), который продаёт сомнительный товар, пользуясь непрозрачностью коренных направленностей. Конкретные указания, как употреблять его основные понятия («зиг», «заг», «вихрь»), не связаны никакой очевидной нитью, кроме того, что «Лоусон сказал, что дело обстоит именно так». Вопрос Уилсона: как определить, что Лоусон не обманывал себя относительно концептуального центра в рое инструкций, которые сам издавал (с. 173)? Дальше Лоусон служит мерилом. Математики, рассуждающие слепо и формалистически, иногда строили доктрины, «сравнимые с корпусом Лоусона»: облако саттелитных направленностей без «центрального солнца» (с. 173). Традиционалисты отказывают Хелен Келлер в постижении красноты так же, как за «зигом», «загом» и «вихрем» не стоит связной концепции (с. 174). Наконец, если мы только записываем дифференциальные уравнения тяготения и больше ничего с ними не делаем, мы не лучше Лоусона, который мог бы записать «Вселенная вечно находится в состоянии зига, зага и вихрей», но ни для чего этого не использовать (с. 175).</t>
         </is>
       </c>
       <c r="Y49" s="14" t="inlineStr">
         <is>
-          <t>гл. 1; гл. 2; гл. 3</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z49" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_ii; chapter_2_vi; chapter_3_iii</t>
+          <t>chapter_3_vii</t>
         </is>
       </c>
       <c r="AA49" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/bertrand-russell</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/alfred-lawson</t>
         </is>
       </c>
       <c r="AB49" s="14" t="inlineStr">
@@ -6100,118 +6084,118 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="AC49" s="14" t="n"/>
+      <c r="AC49" s="14" t="inlineStr">
+        <is>
+          <t>Родился в Лондоне, вырос в Детройте.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Годфри Харольд Харди</t>
+          <t>Хилэр Беллок</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>G. H. Hardy</t>
+          <t>Hilaire Belloc</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
+          <t>британец французского происхождения</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/gotfrey-harold-hardy.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/h_belloc.jpg</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>1877–1947</t>
+          <t>1870–1953</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>1877-02-07</t>
+          <t>1870-07-27</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>1947-12-01</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="n"/>
+          <t>1953-07-16</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>ожоги и шок после падения в камин</t>
+        </is>
+      </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>Кранли, Суррей, Англия</t>
+          <t>Ла-Сель-Сен-Клу, Франция</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>51.1410, -0.4880</t>
+          <t>48.8500, 2.1300</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>Кембридж, Англия</t>
+          <t>Гилфорд, Англия</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>52.2053, 0.1218</t>
+          <t>51.2362, -0.5704</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>Тринити-колледж, Кембридж</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Тринити-колледж, Кембридж; Нью-колледж, Оксфорд</t>
-        </is>
-      </c>
+          <t>Баллиол-колледж, Оксфорд</t>
+        </is>
+      </c>
+      <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
       <c r="P50" s="14" t="n"/>
-      <c r="Q50" s="14" t="inlineStr">
-        <is>
-          <t>Бертран Рассел</t>
-        </is>
-      </c>
+      <c r="Q50" s="14" t="n"/>
       <c r="R50" s="14" t="n"/>
       <c r="S50" s="14" t="inlineStr">
         <is>
-          <t>теория чисел; математический анализ</t>
+          <t>поэзия; эссеистика; история</t>
         </is>
       </c>
       <c r="T50" s="14" t="inlineStr">
         <is>
-          <t>Английский математик (1877–1947), работал в Кембридже в области теории чисел и анализа. Автор книги «Divergent Series» (Oxford, 1949, вышла посмертно), посвящённой методам суммирования расходящихся рядов. Уилсон представляет его как друга Рассела.</t>
+          <t>Англо-французский писатель, поэт, эссеист, историк и политик (член парламента от Солфорда, 1906–1910), близкий друг и соавтор Г. К. Честертона. Наиболее известен циклом иронично-нравоучительных детских стихов «Cautionary Tales for Children» и родственными сборниками вроде «Cautionary Verses» — сатирическими баснями о детях, которых постигает нелепая, преувеличенно жестокая кара за шалости.</t>
         </is>
       </c>
       <c r="U50" s="14" t="inlineStr">
         <is>
-          <t>- G. H. Hardy, Divergent Series (Oxford UP, 1949), с. 5–6 - Определение суммы ряда как задача выбора, а не открытия</t>
+          <t>- Hilaire Belloc, «Jim, Who Ran Away from his Nurse, and was Eaten by a Lion», в сб. «Cautionary Verses» (New York: Alfred A. Knopf, 1976), 12.</t>
         </is>
       </c>
       <c r="V50" s="14" t="n"/>
       <c r="W50" s="14" t="n"/>
       <c r="X50" s="14" t="inlineStr">
         <is>
-          <t>Харди служит примером «улучшения состояния ума» в математике, то есть того, как методологический совет «сначала определим термины» действительно помогает. Он даёт более широкое определение «суммы» бесконечного ряда, чем классическое определение Коши. Харди утверждает, что математики XVIII века спрашивали «что такое 1 – 1 + 1 …?», а не «как нам определить 1 – 1 + 1 …?», и потому попадали в чисто вербальные споры. Уилсон признаёт вклад Харди, но слышит в формуле «у них не было привычки давать определения» нотку незаслуженного превосходства. Его возражение: вершины, на которых стоит сам Харди, не радикально выше прежних, и его открытия так же подвержены случайностям, поскольку недоумение и противоречия остаются постоянными атрибутами человеческого положения. Уилсон сравнивает эту снисходительность с самодовольством критика из главы 2, упрекавшего Дарвина в неспособности оценить Теннисона. Кроме того, Харди, сам того не желая, расплывчат в том, что такое «установление определения». К этому Уилсон обещает вернуться в следующей главе.</t>
+          <t>Процитировано двустишие из стихотворения «Jim, Who Ran Away from His Nurse, and Was Eaten by a Lion» («Джим, который сбежал от няни и был съеден львом», сб. «Cautionary Verses», 1976): совет «всегда держись близ медсестры / из страха встрять во что похуже». Уилсон приводит эти строки иронически — как образ психологии чрезмерной осторожности, к которой сводится один из возможных ответов на дилемму «классицизм vs. дикие анти-классические крайности»: если единственная альтернатива классическому мышлению — кунианизм и пост-структурализм, разумнее держаться классицизма из страха перед худшим. Уилсон сразу же дистанцируется от такой позиции, называя собственную оценку анти-классицизма «значительно более сдержанной».</t>
         </is>
       </c>
       <c r="Y50" s="14" t="inlineStr">
         <is>
-          <t>гл. 3</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z50" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_iv</t>
+          <t>chapter_1_ix</t>
         </is>
       </c>
       <c r="AA50" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/godfri-kharold-khardi</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/hilaire-belloc</t>
         </is>
       </c>
       <c r="AB50" s="14" t="inlineStr">
@@ -6224,113 +6208,133 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Хелен Келлер</t>
+          <t>Бертран Рассел</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Helen Keller</t>
+          <t>Bertrand Russell</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>американка</t>
+          <t>британец</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/helen_keller.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/russel_1936.jpg</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>1880–1968</t>
+          <t>1872–1970</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>1880-06-27</t>
+          <t>1872-05-18</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>1968-06-01</t>
+          <t>1970-02-02</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>последствия инсультов</t>
+          <t>грипп</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>Таскамбия, Алабама, США</t>
+          <t>Треллек, Уэльс</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>34.7309, -87.7025</t>
+          <t>51.7500, -2.7800</t>
         </is>
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>Истон, Коннектикут, США</t>
+          <t>Пенриндейдрайт, Уэльс</t>
         </is>
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
-          <t>41.2500, -73.3000</t>
+          <t>52.9300, -4.0700</t>
         </is>
       </c>
       <c r="M51" s="14" t="inlineStr">
         <is>
-          <t>Рэдклифф-колледж</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="n"/>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="14" t="n"/>
-      <c r="Q51" s="14" t="n"/>
+          <t>Тринити-колледж, Кембридж</t>
+        </is>
+      </c>
+      <c r="N51" s="14" t="inlineStr">
+        <is>
+          <t>Тринити-колледж, Кембридж; Чикагский университет; Калифорнийский университет в Лос-Анджелесе</t>
+        </is>
+      </c>
+      <c r="O51" s="14" t="inlineStr">
+        <is>
+          <t>Альфред Норт Уайтхед</t>
+        </is>
+      </c>
+      <c r="P51" s="14" t="inlineStr">
+        <is>
+          <t>Людвиг Витгенштейн</t>
+        </is>
+      </c>
+      <c r="Q51" s="14" t="inlineStr">
+        <is>
+          <t>Готлоб Фреге; Годфри Харольд Харди</t>
+        </is>
+      </c>
       <c r="R51" s="14" t="inlineStr">
         <is>
-          <t>Президентская медаль Свободы (1964)</t>
+          <t>Нобелевская премия по литературе (1950)</t>
         </is>
       </c>
       <c r="S51" s="14" t="inlineStr">
         <is>
-          <t>литература; общественная деятельность</t>
+          <t>математическая логика; аналитическая философия; эпистемология</t>
         </is>
       </c>
       <c r="T51" s="14" t="inlineStr">
         <is>
-          <t>Американская писательница и общественный деятель, с полутора лет слепая и глухая. Научилась общаться и читать с помощью учительницы Энн Салливан, окончила Рэдклифф-колледж; автор нескольких автобиографических книг.</t>
+          <t>Британский философ, логик и математик, один из основателей аналитической философии. Соавтор (вместе с Уайтхедом) «Principia Mathematica» — попытки свести математику к логике. Автор теории дескрипций, логического атомизма; лауреат Нобелевской премии по литературе (1950).</t>
         </is>
       </c>
       <c r="U51" s="14" t="inlineStr">
         <is>
-          <t>- Helen Keller, The World I Live In (New York: The Century Company, 1908), 105 — сноска 16.</t>
-        </is>
-      </c>
-      <c r="V51" s="14" t="n"/>
+          <t>- Логический атомизм / программа сведения математики к логике («Principia Mathematica») - «Проблемы философии» (The Problems of Philosophy, 1912) — основной каркас для систематизации klassicheskaya-kartina-kontseptsiy, см. отдельную карточку problemy-filosofii-1912</t>
+        </is>
+      </c>
+      <c r="V51" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/russell/</t>
+        </is>
+      </c>
       <c r="W51" s="14" t="n"/>
       <c r="X51" s="14" t="inlineStr">
         <is>
-          <t>Главное «возражение» против взгляда Маха и Локка, что краснота постигается только через ощущение. Келлер утверждает, что постигает понятие красноты вопреки сенсорным ограничениям: «Я понимаю, чем отличается алый цвет от малинового, потому что знаю, что запах апельсина отличается от запаха грейпфрута… красный говорит о любви, стыде или силе» (с. 160). Уилсон видит здесь упор на инференциальную направленность «есть красный». Ортодоксия отвечает, что это лишь «структурные сопутствующие обстоятельства»: даже если бы Келлер знала физику красителей лучше нас, ей всё равно недоставало бы «основных ингредиентов» красноты (с. 161). При этом сторонники «публичной» точки зрения (ядро — согласие с классификациями сообщества) не готовы последовать её примеру: «она не может классифицировать розы и пожарные машины так же быстро и непосредственно, как остальные из нас» (с. 162). На с. 168 Уилсон сопоставляет её картину красноты с картиной твёрдости у Рида: может ли говорящий «где-то между 6 месяцами и 16 годами» незаметно сдвинуть содержание «есть красный» к такому признаку?</t>
+          <t>Уилсон прямо пишет в предисловии, что на философской стороне Рассел и Куайн долгое время служили для него «опорами», между которыми он старался прокладывать курс в вопросах, касающихся концепций, предикатов и работы с понятиями (см. также willard-quine — второй полюс той же пары). Гораздо более весомая роль обнаружилась в главе 1. Хотя Уилсон чаще цитирует Фреге (см. gottlob-frege), он прямо заявляет, что именно Рассел — более чистый, показательный представитель того, что он называет klassicheskaya-kartina-kontseptsiy («классическая картина концепций»): у Фреге слишком много «эксцентричных» побочных взглядов, а Рассел даёт более чистый случай. Работа «Проблемы философии» (1912) названа «основным каркасом», из которого Уилсон выводит систематизированный список тезисов классической картины (полностью — в приложении к главе 3, см. problemy-filosofii-1912).</t>
         </is>
       </c>
       <c r="Y51" s="14" t="inlineStr">
         <is>
-          <t>гл. 3</t>
+          <t>гл. 1; гл. 2; гл. 3</t>
         </is>
       </c>
       <c r="Z51" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_vi</t>
+          <t>chapter_1_ii; chapter_2_vi; chapter_3_iii</t>
         </is>
       </c>
       <c r="AA51" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/helen-keller</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/bertrand-russell</t>
         </is>
       </c>
       <c r="AB51" s="14" t="inlineStr">
@@ -6343,117 +6347,113 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Отто Нейрат</t>
+          <t>Годфри Харольд Харди</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Otto Neurath</t>
+          <t>G. H. Hardy</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>австриец</t>
+          <t>британец</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/otto_neurath.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/gotfrey-harold-hardy.jpg</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>1882–1945</t>
+          <t>1877–1947</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>1882-12-10</t>
+          <t>1877-02-07</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>1945-12-22</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>сердечный приступ</t>
-        </is>
-      </c>
+          <t>1947-12-01</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="n"/>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>Вена, Австро-Венгрия</t>
+          <t>Кранли, Суррей, Англия</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>48.2082, 16.3738</t>
+          <t>51.1410, -0.4880</t>
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>Оксфорд, Англия</t>
+          <t>Кембридж, Англия</t>
         </is>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>51.7520, -1.2577</t>
+          <t>52.2053, 0.1218</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>Берлинский университет</t>
+          <t>Тринити-колледж, Кембридж</t>
         </is>
       </c>
       <c r="N52" s="14" t="inlineStr">
         <is>
-          <t>Венский кружок; Музей общества и экономики, Вена; Институт ISOTYPE</t>
+          <t>Тринити-колледж, Кембридж; Нью-колледж, Оксфорд</t>
         </is>
       </c>
       <c r="O52" s="14" t="n"/>
       <c r="P52" s="14" t="n"/>
-      <c r="Q52" s="14" t="n"/>
+      <c r="Q52" s="14" t="inlineStr">
+        <is>
+          <t>Бертран Рассел</t>
+        </is>
+      </c>
       <c r="R52" s="14" t="n"/>
       <c r="S52" s="14" t="inlineStr">
         <is>
-          <t>философия науки; социология; политэкономия; визуальная статистика</t>
+          <t>теория чисел; математический анализ</t>
         </is>
       </c>
       <c r="T52" s="14" t="inlineStr">
         <is>
-          <t>Австрийский философ и социолог, один из ведущих участников Венского кружка (Wiener Kreis) — интеллектуального сообщества логических позитивистов, сформировавшегося в Вене в 1920–30-х годах вокруг Морица Шлика. Нейрат был одним из авторов манифеста Венского кружка «Научное миропонимание» (1929). Помимо философии науки, известен работами по политэкономии, социологии и созданию системы визуальных знаков ISOTYPE — универсального изобразительного языка для представления статистики и социальных данных, оказавшего заметное влияние на современный информационный дизайн. После аншлюса эмигрировал из Австрии, работал в Нидерландах, затем в Великобритании, где и умер в 1945 году.</t>
+          <t>Английский математик (1877–1947), работал в Кембридже в области теории чисел и анализа. Автор книги «Divergent Series» (Oxford, 1949, вышла посмертно), посвящённой методам суммирования расходящихся рядов. Уилсон представляет его как друга Рассела.</t>
         </is>
       </c>
       <c r="U52" s="14" t="inlineStr">
         <is>
-          <t>- Метафора корабля Нейрата (в русской традиции чаще «корабль Нейрата» или «корабль Нойрата») — образ, впервые чётко сформулированный Нейратом ок. 1913 года, затем неоднократно повторённый им в статьях о протокольных предложениях и научном методе. У Уилсона фигурирует опосредованно, через цитату Куайна из Word and Object (Cambridge, Mass.: MIT Press, 1960), с. 124.</t>
-        </is>
-      </c>
-      <c r="V52" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/neurath/</t>
-        </is>
-      </c>
+          <t>- G. H. Hardy, Divergent Series (Oxford UP, 1949), с. 5–6 - Определение суммы ряда как задача выбора, а не открытия</t>
+        </is>
+      </c>
+      <c r="V52" s="14" t="n"/>
       <c r="W52" s="14" t="n"/>
       <c r="X52" s="14" t="inlineStr">
         <is>
-          <t>Появляется в подразделе (vii) как автор одной из центральных методологических метафор всей книги — корабля, который приходится ремонтировать в открытом море, не сходя на берег (см. metafora-morskogo-puteshestviya). Сам Нейрат заимствовал этот образ из античной темы «корабля Тесея», а Куайн (см. willard-quine) перенял его у Нейрата и сделал одной из своих любимых философских метафор (Уилсон приводит цитату из «Word and Object», 1960, с. 124). Уилсон принимает эту метафору, но добавляет собственную мягкую оговорку: он допускает, что в конечном итоге может наступить день, когда «наш корабль будет достроен» и мы поймём, как его части подходят друг к другу, — то есть смягчает жёсткую куайновскую версию о том, что человечество навсегда обречено жить внутри незавершённого концептуального языка.</t>
+          <t>Харди служит примером «улучшения состояния ума» в математике, то есть того, как методологический совет «сначала определим термины» действительно помогает. Он даёт более широкое определение «суммы» бесконечного ряда, чем классическое определение Коши. Харди утверждает, что математики XVIII века спрашивали «что такое 1 – 1 + 1 …?», а не «как нам определить 1 – 1 + 1 …?», и потому попадали в чисто вербальные споры. Уилсон признаёт вклад Харди, но слышит в формуле «у них не было привычки давать определения» нотку незаслуженного превосходства. Его возражение: вершины, на которых стоит сам Харди, не радикально выше прежних, и его открытия так же подвержены случайностям, поскольку недоумение и противоречия остаются постоянными атрибутами человеческого положения. Уилсон сравнивает эту снисходительность с самодовольством критика из главы 2, упрекавшего Дарвина в неспособности оценить Теннисона. Кроме того, Харди, сам того не желая, расплывчат в том, что такое «установление определения». К этому Уилсон обещает вернуться в следующей главе.</t>
         </is>
       </c>
       <c r="Y52" s="14" t="inlineStr">
         <is>
-          <t>гл. 1; гл. 3</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z52" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_vii; chapter_3_v</t>
+          <t>chapter_3_iv</t>
         </is>
       </c>
       <c r="AA52" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/otto-neurath</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/godfri-kharold-khardi</t>
         </is>
       </c>
       <c r="AB52" s="14" t="inlineStr">
@@ -6466,113 +6466,113 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Л. Сьюзен Стеббинг</t>
+          <t>Хелен Келлер</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>L. Susan Stebbing</t>
+          <t>Helen Keller</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>британка</t>
+          <t>американка</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/s_stebbing.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/helen_keller.jpg</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>1885–1943</t>
+          <t>1880–1968</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>1885-12-02</t>
+          <t>1880-06-27</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>1943-09-11</t>
+          <t>1968-06-01</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>рак</t>
+          <t>последствия инсультов</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>Уимблдон, Лондон</t>
+          <t>Таскамбия, Алабама, США</t>
         </is>
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>51.4214, -0.2064</t>
+          <t>34.7309, -87.7025</t>
         </is>
       </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Истон, Коннектикут, США</t>
         </is>
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
-          <t>51.5074, -0.1278</t>
+          <t>41.2500, -73.3000</t>
         </is>
       </c>
       <c r="M53" s="14" t="inlineStr">
         <is>
-          <t>Гиртон-колледж, Кембридж</t>
-        </is>
-      </c>
-      <c r="N53" s="14" t="inlineStr">
-        <is>
-          <t>Бедфорд-колледж, Лондонский университет</t>
-        </is>
-      </c>
+          <t>Рэдклифф-колледж</t>
+        </is>
+      </c>
+      <c r="N53" s="14" t="n"/>
       <c r="O53" s="14" t="n"/>
       <c r="P53" s="14" t="n"/>
       <c r="Q53" s="14" t="n"/>
-      <c r="R53" s="14" t="n"/>
+      <c r="R53" s="14" t="inlineStr">
+        <is>
+          <t>Президентская медаль Свободы (1964)</t>
+        </is>
+      </c>
       <c r="S53" s="14" t="inlineStr">
         <is>
-          <t>логика; аналитическая философия; критическое мышление</t>
+          <t>литература; общественная деятельность</t>
         </is>
       </c>
       <c r="T53" s="14" t="inlineStr">
         <is>
-          <t>Британский философ и логик, одна из первых женщин-профессоров философии в Великобритании. Автор Philosophy and the Physicists (1937).</t>
+          <t>Американская писательница и общественный деятель, с полутора лет слепая и глухая. Научилась общаться и читать с помощью учительницы Энн Салливан, окончила Рэдклифф-колледж; автор нескольких автобиографических книг.</t>
         </is>
       </c>
       <c r="U53" s="14" t="inlineStr">
         <is>
-          <t>- L. Susan Stebbing, Philosophy and the Physicists (1937), p. 64 - Метод и метафизика - Цвет - Физическое описание</t>
+          <t>- Helen Keller, The World I Live In (New York: The Century Company, 1908), 105 — сноска 16.</t>
         </is>
       </c>
       <c r="V53" s="14" t="n"/>
       <c r="W53" s="14" t="n"/>
       <c r="X53" s="14" t="inlineStr">
         <is>
-          <t>Стеббинг помогает Уилсону показать, как физическое описание цвета может быть ошибочно превращено в метафизический тезис. По её замечанию, отрицатели объективности цвета сделали из метода физики метафизику, забыв, что этот метод разрабатывался для определённых исследовательских целей.</t>
+          <t>Главное «возражение» против взгляда Маха и Локка, что краснота постигается только через ощущение. Келлер утверждает, что постигает понятие красноты вопреки сенсорным ограничениям: «Я понимаю, чем отличается алый цвет от малинового, потому что знаю, что запах апельсина отличается от запаха грейпфрута… красный говорит о любви, стыде или силе» (с. 160). Уилсон видит здесь упор на инференциальную направленность «есть красный». Ортодоксия отвечает, что это лишь «структурные сопутствующие обстоятельства»: даже если бы Келлер знала физику красителей лучше нас, ей всё равно недоставало бы «основных ингредиентов» красноты (с. 161). При этом сторонники «публичной» точки зрения (ядро — согласие с классификациями сообщества) не готовы последовать её примеру: «она не может классифицировать розы и пожарные машины так же быстро и непосредственно, как остальные из нас» (с. 162). На с. 168 Уилсон сопоставляет её картину красноты с картиной твёрдости у Рида: может ли говорящий «где-то между 6 месяцами и 16 годами» незаметно сдвинуть содержание «есть красный» к такому признаку?</t>
         </is>
       </c>
       <c r="Y53" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z53" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_vi</t>
+          <t>chapter_3_vi; chapter_3_vii</t>
         </is>
       </c>
       <c r="AA53" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/l-susan-stebbing</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/helen-keller</t>
         </is>
       </c>
       <c r="AB53" s="14" t="inlineStr">
@@ -6585,42 +6585,42 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Людвиг Витгенштейн</t>
+          <t>Отто Нейрат</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Ludwig Wittgenstein</t>
+          <t>Otto Neurath</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>австриец, британский подданный с 1939</t>
+          <t>австриец</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/l_vitgenshtejn.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/otto_neurath.jpg</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>1889–1951</t>
+          <t>1882–1945</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>1889-04-26</t>
+          <t>1882-12-10</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>1951-04-29</t>
+          <t>1945-12-22</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>рак простаты</t>
+          <t>сердечный приступ</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
@@ -6635,60 +6635,52 @@
       </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>Кембридж, Англия</t>
+          <t>Оксфорд, Англия</t>
         </is>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>52.2053, 0.1218</t>
+          <t>51.7520, -1.2577</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>Высшая техническая школа Шарлоттенбурга; Манчестерский университет; Тринити-колледж, Кембридж</t>
+          <t>Берлинский университет</t>
         </is>
       </c>
       <c r="N54" s="14" t="inlineStr">
         <is>
-          <t>Тринити-колледж, Кембридж</t>
-        </is>
-      </c>
-      <c r="O54" s="14" t="inlineStr">
-        <is>
-          <t>Бертран Рассел</t>
-        </is>
-      </c>
+          <t>Венский кружок; Музей общества и экономики, Вена; Институт ISOTYPE</t>
+        </is>
+      </c>
+      <c r="O54" s="14" t="n"/>
       <c r="P54" s="14" t="n"/>
-      <c r="Q54" s="14" t="inlineStr">
-        <is>
-          <t>Готлоб Фреге</t>
-        </is>
-      </c>
+      <c r="Q54" s="14" t="n"/>
       <c r="R54" s="14" t="n"/>
       <c r="S54" s="14" t="inlineStr">
         <is>
-          <t>философия языка; философия логики; философия математики</t>
+          <t>философия науки; социология; политэкономия; визуальная статистика</t>
         </is>
       </c>
       <c r="T54" s="14" t="inlineStr">
         <is>
-          <t>Австрийско-британский философ, один из самых влиятельных мыслителей XX века в философии языка. Условно разделяется на «раннего» (логический атомизм, «Логико-философский трактат», идея языка как картины мира) и «позднего» (философия обыденного языка, «Философские исследования», идея значения как употребления, языковые игры). Рецензенты считают, что «Блуждающие значения» сохраняют дух позднего Витгенштейна. Показательно, что в самой книге Уилсона фигурируют оба периода в диаметрально противоположных ролях (см. раздел «Ранний и поздний Витгенштейн в аргументации Уилсона» ниже).</t>
+          <t>Австрийский философ и социолог, один из ведущих участников Венского кружка (Wiener Kreis) — интеллектуального сообщества логических позитивистов, сформировавшегося в Вене в 1920–30-х годах вокруг Морица Шлика. Нейрат был одним из авторов манифеста Венского кружка «Научное миропонимание» (1929). Помимо философии науки, известен работами по политэкономии, социологии и созданию системы визуальных знаков ISOTYPE — универсального изобразительного языка для представления статистики и социальных данных, оказавшего заметное влияние на современный информационный дизайн. После аншлюса эмигрировал из Австрии, работал в Нидерландах, затем в Великобритании, где и умер в 1945 году.</t>
         </is>
       </c>
       <c r="U54" s="14" t="inlineStr">
         <is>
-          <t>- Поздний Витгенштейн: значение как употребление, языковые игры («Философские исследования», см. отдельную карточку filosofskie-issledovaniya-vitgenshteyna) - «Философские исследования», §18 — метафора языка как старого города (лабиринт узких улиц и площадей разных эпох плюс новые районы с регулярной планировкой) - Ранний Витгенштейн: «Логико-философский трактат» (1921) — идея Души, проецирующей значение на символы через интенцию (см. logiko-filosofsky-traktat) - (дозаполнить по мере чтения — само название книги, «Блуждающие значения», возможно, перекликается с образом «блуждания» по темам, о котором пишет Уилсон в этом же фрагменте предисловия)</t>
+          <t>- Метафора корабля Нейрата (в русской традиции чаще «корабль Нейрата» или «корабль Нойрата») — образ, впервые чётко сформулированный Нейратом ок. 1913 года, затем неоднократно повторённый им в статьях о протокольных предложениях и научном методе. У Уилсона фигурирует опосредованно, через цитату Куайна из Word and Object (Cambridge, Mass.: MIT Press, 1960), с. 124.</t>
         </is>
       </c>
       <c r="V54" s="14" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/wittgenstein/</t>
+          <t>https://plato.stanford.edu/entries/neurath/</t>
         </is>
       </c>
       <c r="W54" s="14" t="n"/>
       <c r="X54" s="14" t="inlineStr">
         <is>
-          <t>Уилсон в предисловии пишет, что несколько рецензентов охарактеризовали высказанные в книге взгляды как «витгенштейнианские» — и он, возможно, с этим согласен. В юности он много читал Витгенштейна под руководством своего учителя Чарльза Маркса и находит примечательным, что они с Витгенштейном часто «блуждают» по схожим темам в своих философских странствиях. В главе 1 (раздел «Смягчённый скептицизм») Витгенштейн появляется ещё раз как источник альтернативной метафоры. Разбирая, как в языке возникают локальные «карманы» нового словоупотребления рядом со старым, Уилсон сперва предлагает собственный образ («поликристаллическая» структура значения слова, зарождение новых «зёрен»-употреблений по краям старых — метафора из материаловедения, эпитаксиальный рост кристаллов), а затем прямо предлагает витгенштейновскую метафору города как альтернативу или дополнение к своей: язык — это старинный город, лабиринт узких улиц и площадей вперемешку с домами разных эпох, окружённый новыми районами с прямой, регулярной планировкой. Источник — «Философские исследования», §18 (в тексте сноска дана как «Investigations, x18», по всей видимости — опечатка). ### Ранний и поздний Витгенштейн в аргументации Уилсона В главе 3, §(ii) («Классический клей») Витгенштейн появляется в третий раз — но уже как ранний Витгенштейн периода Трактата, и в роли, прямо противоположной главе 1. Уилсон приводит его идею Души как невидимого присутствия, «оживляющего» обычные символы через акт интенционального проецирования — иллюстрируя это бытовым образом кухонной утвари на столе, которая символизирует Битву при Энтитеме (Antietam) потому, что дед рассказчика пожелал реализовать эту связь. Этот ранний Витгенштейн вводится Уилсоном как исторический представитель интенционально-обоснованной картины предикатной значимости — картины, которую Уилсон явно отграничивает от защищаемого им классического склеивания Рассела, и которая, доведённая до крайности, граничит с «оккультной». Таким образом, один и тот же философ у Уилсона фигурирует дважды в противоположных функциях: ранний Витгенштейн (гл. 3) иллюстрирует почти магическую, интенционально-волевую картину языка, которую Уилсон скорее дистанцирует от собственной позиции; поздний Витгенштейн (гл. 1, предисловие) назван важнейшим анти-классическим событием и источником дружественной, созвучной Уилсону метафоры города.</t>
+          <t>Появляется в подразделе (vii) как автор одной из центральных методологических метафор всей книги — корабля, который приходится ремонтировать в открытом море, не сходя на берег (см. metafora-morskogo-puteshestviya). Сам Нейрат заимствовал этот образ из античной темы «корабля Тесея», а Куайн (см. willard-quine) перенял его у Нейрата и сделал одной из своих любимых философских метафор (Уилсон приводит цитату из «Word and Object», 1960, с. 124). Уилсон принимает эту метафору, но добавляет собственную мягкую оговорку: он допускает, что в конечном итоге может наступить день, когда «наш корабль будет достроен» и мы поймём, как его части подходят друг к другу, — то есть смягчает жёсткую куайновскую версию о том, что человечество навсегда обречено жить внутри незавершённого концептуального языка.</t>
         </is>
       </c>
       <c r="Y54" s="14" t="inlineStr">
@@ -6698,12 +6690,12 @@
       </c>
       <c r="Z54" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_iii; chapter_1_ix; chapter_3_ii</t>
+          <t>chapter_1_vii; chapter_3_v</t>
         </is>
       </c>
       <c r="AA54" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/ludwig-wittgenstein</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/otto-neurath</t>
         </is>
       </c>
       <c r="AB54" s="14" t="inlineStr">
@@ -6716,105 +6708,113 @@
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>Бастер Китон</t>
+          <t>Л. Сьюзен Стеббинг</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Buster Keaton</t>
+          <t>L. Susan Stebbing</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>британка</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/buster-keaton.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/s_stebbing.jpg</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>1895–1966</t>
+          <t>1885–1943</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>1895-10-04</t>
+          <t>1885-12-02</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>1966-02-01</t>
+          <t>1943-09-11</t>
         </is>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>рак лёгких</t>
+          <t>рак</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>Пикуа, Канзас, США</t>
+          <t>Уимблдон, Лондон</t>
         </is>
       </c>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>37.9200, -95.5300</t>
+          <t>51.4214, -0.2064</t>
         </is>
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>Вудленд-Хиллз, Лос-Анджелес, США</t>
+          <t>Лондон</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
-          <t>34.1680, -118.6050</t>
-        </is>
-      </c>
-      <c r="M55" s="14" t="n"/>
-      <c r="N55" s="14" t="n"/>
+          <t>51.5074, -0.1278</t>
+        </is>
+      </c>
+      <c r="M55" s="14" t="inlineStr">
+        <is>
+          <t>Гиртон-колледж, Кембридж</t>
+        </is>
+      </c>
+      <c r="N55" s="14" t="inlineStr">
+        <is>
+          <t>Бедфорд-колледж, Лондонский университет</t>
+        </is>
+      </c>
       <c r="O55" s="14" t="n"/>
       <c r="P55" s="14" t="n"/>
       <c r="Q55" s="14" t="n"/>
-      <c r="R55" s="14" t="inlineStr">
-        <is>
-          <t>Почётный «Оскар» (1960)</t>
-        </is>
-      </c>
+      <c r="R55" s="14" t="n"/>
       <c r="S55" s="14" t="inlineStr">
         <is>
-          <t>кино; комедия</t>
+          <t>логика; аналитическая философия; критическое мышление</t>
         </is>
       </c>
       <c r="T55" s="14" t="inlineStr">
         <is>
-          <t>Американский комик и режиссёр немого кино, «Великий Каменное Лицо»: «Генерал», «Шерлок-младший», «Пароходный Билл-младший».</t>
-        </is>
-      </c>
-      <c r="U55" s="14" t="n"/>
+          <t>Британский философ и логик, одна из первых женщин-профессоров философии в Великобритании. Автор Philosophy and the Physicists (1937).</t>
+        </is>
+      </c>
+      <c r="U55" s="14" t="inlineStr">
+        <is>
+          <t>- L. Susan Stebbing, Philosophy and the Physicists (1937), p. 64 - Метод и метафизика - Цвет - Физическое описание</t>
+        </is>
+      </c>
       <c r="V55" s="14" t="n"/>
       <c r="W55" s="14" t="n"/>
       <c r="X55" s="14" t="inlineStr">
         <is>
-          <t>В честь фильма Китона «Шерлок-младший» (Sherlock Jr., 1924) Уилсон называет юмовские рассуждения «аргументами Шерлока-младшего» (с. 165). В фильме киномеханик во сне входит в экран, и монтаж мгновенно меняет вокруг него обстановку. Так и юмовский аргумент утверждает, что «кинематографический монтаж реального жизненного опыта» можно отредактировать любым нестандартным способом: зубчатое колесо в железном корпусе последовательно заменяется зубчатым колесом с крылышками. Мы всё равно классифицировали бы предмет в каждом кадре как «зубчатое колесо» — значит, понятие не может содержать богатый набор инференциальных ассоциаций как часть инвариантного содержания.</t>
+          <t>Стеббинг помогает Уилсону показать, как физическое описание цвета может быть ошибочно превращено в метафизический тезис. По её замечанию, отрицатели объективности цвета сделали из метода физики метафизику, забыв, что этот метод разрабатывался для определённых исследовательских целей.</t>
         </is>
       </c>
       <c r="Y55" s="14" t="inlineStr">
         <is>
-          <t>гл. 3</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z55" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_vi</t>
+          <t>chapter_2_vi</t>
         </is>
       </c>
       <c r="AA55" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/buster-keaton</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/l-susan-stebbing</t>
         </is>
       </c>
       <c r="AB55" s="14" t="inlineStr">
@@ -6827,113 +6827,125 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Пауль Хиндемит</t>
+          <t>Людвиг Витгенштейн</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Paul Hindemith</t>
+          <t>Ludwig Wittgenstein</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>немец</t>
+          <t>австриец, британский подданный с 1939</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/hindemith.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/l_vitgenshtejn.jpg</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>1895–1963</t>
+          <t>1889–1951</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>1895-11-16</t>
+          <t>1889-04-26</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>1963-12-28</t>
+          <t>1951-04-29</t>
         </is>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>острый панкреатит</t>
+          <t>рак простаты</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>Ханау, Германия</t>
+          <t>Вена, Австро-Венгрия</t>
         </is>
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>50.1264, 8.9283</t>
+          <t>48.2082, 16.3738</t>
         </is>
       </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>Франкфурт-на-Майне, Германия</t>
+          <t>Кембридж, Англия</t>
         </is>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>50.1109, 8.6821</t>
+          <t>52.2053, 0.1218</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>Консерватория Хоха, Франкфурт</t>
+          <t>Высшая техническая школа Шарлоттенбурга; Манчестерский университет; Тринити-колледж, Кембридж</t>
         </is>
       </c>
       <c r="N56" s="14" t="inlineStr">
         <is>
-          <t>Берлинская высшая школа музыки; Йельский университет</t>
-        </is>
-      </c>
-      <c r="O56" s="14" t="n"/>
+          <t>Тринити-колледж, Кембридж</t>
+        </is>
+      </c>
+      <c r="O56" s="14" t="inlineStr">
+        <is>
+          <t>Бертран Рассел</t>
+        </is>
+      </c>
       <c r="P56" s="14" t="n"/>
-      <c r="Q56" s="14" t="n"/>
+      <c r="Q56" s="14" t="inlineStr">
+        <is>
+          <t>Готлоб Фреге</t>
+        </is>
+      </c>
       <c r="R56" s="14" t="n"/>
       <c r="S56" s="14" t="inlineStr">
         <is>
-          <t>композиция; теория музыки</t>
+          <t>философия языка; философия логики; философия математики</t>
         </is>
       </c>
       <c r="T56" s="14" t="inlineStr">
         <is>
-          <t>Немецкий композитор, дирижёр и музыкальный теоретик, один из крупнейших музыкантов XX века. Автор оперы «Художник Матис» и теоретических трудов по музыкальной композиции.</t>
+          <t>Австрийско-британский философ, один из самых влиятельных мыслителей XX века в философии языка. Условно разделяется на «раннего» (логический атомизм, «Логико-философский трактат», идея языка как картины мира) и «позднего» (философия обыденного языка, «Философские исследования», идея значения как употребления, языковые игры). Рецензенты считают, что «Блуждающие значения» сохраняют дух позднего Витгенштейна. Показательно, что в самой книге Уилсона фигурируют оба периода в диаметрально противоположных ролях (см. раздел «Ранний и поздний Витгенштейн в аргументации Уилсона» ниже).</t>
         </is>
       </c>
       <c r="U56" s="14" t="inlineStr">
         <is>
-          <t>- Комбинационные тоны как необходимое условие музыкального восприятия</t>
-        </is>
-      </c>
-      <c r="V56" s="14" t="n"/>
+          <t>- Поздний Витгенштейн: значение как употребление, языковые игры («Философские исследования», см. отдельную карточку filosofskie-issledovaniya-vitgenshteyna) - «Философские исследования», §18 — метафора языка как старого города (лабиринт узких улиц и площадей разных эпох плюс новые районы с регулярной планировкой) - Ранний Витгенштейн: «Логико-философский трактат» (1921) — идея Души, проецирующей значение на символы через интенцию (см. logiko-filosofsky-traktat) - (дозаполнить по мере чтения — само название книги, «Блуждающие значения», возможно, перекликается с образом «блуждания» по темам, о котором пишет Уилсон в этом же фрагменте предисловия)</t>
+        </is>
+      </c>
+      <c r="V56" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/wittgenstein/</t>
+        </is>
+      </c>
       <c r="W56" s="14" t="n"/>
       <c r="X56" s="14" t="inlineStr">
         <is>
-          <t>Уилсон цитирует Хиндемита как авторитетного музыканта, подтверждающего фундаментальную роль комбинационных тонов в музыкальном восприятии. Хиндемит заявляет: «Интервал без комбинационных тонов был бы абстрактным понятием, не имеющим бытия». Эта цитата используется для усиления аргумента о том, что музыкальное восприятие неразрывно связано с субъективными процессами в слуховом аппарате.</t>
+          <t>Уилсон в предисловии пишет, что несколько рецензентов охарактеризовали высказанные в книге взгляды как «витгенштейнианские» — и он, возможно, с этим согласен. В юности он много читал Витгенштейна под руководством своего учителя Чарльза Маркса и находит примечательным, что они с Витгенштейном часто «блуждают» по схожим темам в своих философских странствиях. В главе 1 (раздел «Смягчённый скептицизм») Витгенштейн появляется ещё раз как источник альтернативной метафоры. Разбирая, как в языке возникают локальные «карманы» нового словоупотребления рядом со старым, Уилсон сперва предлагает собственный образ («поликристаллическая» структура значения слова, зарождение новых «зёрен»-употреблений по краям старых — метафора из материаловедения, эпитаксиальный рост кристаллов), а затем прямо предлагает витгенштейновскую метафору города как альтернативу или дополнение к своей: язык — это старинный город, лабиринт узких улиц и площадей вперемешку с домами разных эпох, окружённый новыми районами с прямой, регулярной планировкой. Источник — «Философские исследования», §18 (в тексте сноска дана как «Investigations, x18», по всей видимости — опечатка). ### Ранний и поздний Витгенштейн в аргументации Уилсона В главе 3, §(ii) («Классический клей») Витгенштейн появляется в третий раз — но уже как ранний Витгенштейн периода Трактата, и в роли, прямо противоположной главе 1. Уилсон приводит его идею Души как невидимого присутствия, «оживляющего» обычные символы через акт интенционального проецирования — иллюстрируя это бытовым образом кухонной утвари на столе, которая символизирует Битву при Энтитеме (Antietam) потому, что дед рассказчика пожелал реализовать эту связь. Этот ранний Витгенштейн вводится Уилсоном как исторический представитель интенционально-обоснованной картины предикатной значимости — картины, которую Уилсон явно отграничивает от защищаемого им классического склеивания Рассела, и которая, доведённая до крайности, граничит с «оккультной». Таким образом, один и тот же философ у Уилсона фигурирует дважды в противоположных функциях: ранний Витгенштейн (гл. 3) иллюстрирует почти магическую, интенционально-волевую картину языка, которую Уилсон скорее дистанцирует от собственной позиции; поздний Витгенштейн (гл. 1, предисловие) назван важнейшим анти-классическим событием и источником дружественной, созвучной Уилсону метафоры города.</t>
         </is>
       </c>
       <c r="Y56" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 1; гл. 3</t>
         </is>
       </c>
       <c r="Z56" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_iv</t>
+          <t>chapter_1_iii; chapter_1_ix; chapter_3_ii</t>
         </is>
       </c>
       <c r="AA56" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/paul-hindemith</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/ludwig-wittgenstein</t>
         </is>
       </c>
       <c r="AB56" s="14" t="inlineStr">
@@ -6946,109 +6958,105 @@
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Жан Пиаже</t>
+          <t>Бастер Китон</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Jean Piaget</t>
+          <t>Buster Keaton</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>швейцарец</t>
+          <t>американец</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j_piaget.png</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/buster-keaton.jpg</t>
         </is>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>1896–1980</t>
+          <t>1895–1966</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>1896-08-09</t>
+          <t>1895-10-04</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>1980-09-16</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="n"/>
+          <t>1966-02-01</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>рак лёгких</t>
+        </is>
+      </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>Невшатель, Швейцария</t>
+          <t>Пикуа, Канзас, США</t>
         </is>
       </c>
       <c r="J57" s="14" t="inlineStr">
         <is>
-          <t>46.9900, 6.9300</t>
+          <t>37.9200, -95.5300</t>
         </is>
       </c>
       <c r="K57" s="14" t="inlineStr">
         <is>
-          <t>Женева, Швейцария</t>
+          <t>Вудленд-Хиллз, Лос-Анджелес, США</t>
         </is>
       </c>
       <c r="L57" s="14" t="inlineStr">
         <is>
-          <t>46.2044, 6.1432</t>
-        </is>
-      </c>
-      <c r="M57" s="14" t="inlineStr">
-        <is>
-          <t>Невшательский университет</t>
-        </is>
-      </c>
-      <c r="N57" s="14" t="inlineStr">
-        <is>
-          <t>Женевский университет; Институт Жан-Жака Руссо</t>
-        </is>
-      </c>
+          <t>34.1680, -118.6050</t>
+        </is>
+      </c>
+      <c r="M57" s="14" t="n"/>
+      <c r="N57" s="14" t="n"/>
       <c r="O57" s="14" t="n"/>
       <c r="P57" s="14" t="n"/>
       <c r="Q57" s="14" t="n"/>
-      <c r="R57" s="14" t="n"/>
+      <c r="R57" s="14" t="inlineStr">
+        <is>
+          <t>Почётный «Оскар» (1960)</t>
+        </is>
+      </c>
       <c r="S57" s="14" t="inlineStr">
         <is>
-          <t>психология развития; генетическая эпистемология</t>
+          <t>кино; комедия</t>
         </is>
       </c>
       <c r="T57" s="14" t="inlineStr">
         <is>
-          <t>Швейцарский психолог, основоположник теории когнитивного развития ребёнка — описал стадии, через которые проходит детское мышление на пути к взрослому пониманию мира, включая представления о причинности, постоянстве объектов и логических операциях.</t>
-        </is>
-      </c>
-      <c r="U57" s="14" t="inlineStr">
-        <is>
-          <t>- Не применимо — используется как имя-маркер авторитета, а не как содержательный источник</t>
-        </is>
-      </c>
+          <t>Американский комик и режиссёр немого кино, «Великий Каменное Лицо»: «Генерал», «Шерлок-младший», «Пароходный Билл-младший».</t>
+        </is>
+      </c>
+      <c r="U57" s="14" t="n"/>
       <c r="V57" s="14" t="n"/>
       <c r="W57" s="14" t="n"/>
       <c r="X57" s="14" t="inlineStr">
         <is>
-          <t>Упомянут как источник стандартной, узнаваемой мерки для оценки уровня концептуального развития — в шуточных примерах про Джона, Хьюи, Дьюи и Луи, оценивающих их понимание «радуги» через фразы вроде «не достиг требуемого Пиаже уровня понимания причинных связей с материальными объектами».</t>
+          <t>В честь фильма Китона «Шерлок-младший» (Sherlock Jr., 1924) Уилсон называет юмовские рассуждения «аргументами Шерлока-младшего» (с. 165). В фильме киномеханик во сне входит в экран, и монтаж мгновенно меняет вокруг него обстановку. Так и юмовский аргумент утверждает, что «кинематографический монтаж реального жизненного опыта» можно отредактировать любым нестандартным способом: зубчатое колесо в железном корпусе последовательно заменяется зубчатым колесом с крылышками. Мы всё равно классифицировали бы предмет в каждом кадре как «зубчатое колесо» — значит, понятие не может содержать богатый набор инференциальных ассоциаций как часть инвариантного содержания.</t>
         </is>
       </c>
       <c r="Y57" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z57" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_vi</t>
+          <t>chapter_3_vi</t>
         </is>
       </c>
       <c r="AA57" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/jean-piaget</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/buster-keaton</t>
         </is>
       </c>
       <c r="AB57" s="14" t="inlineStr">
@@ -7061,68 +7069,72 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>Васко Рончи</t>
+          <t>Пауль Хиндемит</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Vasco Ronchi</t>
+          <t>Paul Hindemith</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>итальянец</t>
+          <t>немец</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/ronchi.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/hindemith.jpg</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>1897–1988</t>
+          <t>1895–1963</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>1897-12-19</t>
+          <t>1895-11-16</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>1988-10-31</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="n"/>
+          <t>1963-12-28</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>острый панкреатит</t>
+        </is>
+      </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>Флоренция</t>
+          <t>Ханау, Германия</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>43.7696, 11.2558</t>
+          <t>50.1264, 8.9283</t>
         </is>
       </c>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>Флоренция</t>
+          <t>Франкфурт-на-Майне, Германия</t>
         </is>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>43.7696, 11.2558</t>
+          <t>50.1109, 8.6821</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>Высшая нормальная школа, Пиза</t>
+          <t>Консерватория Хоха, Франкфурт</t>
         </is>
       </c>
       <c r="N58" s="14" t="inlineStr">
         <is>
-          <t>Национальный институт оптики, Флоренция</t>
+          <t>Берлинская высшая школа музыки; Йельский университет</t>
         </is>
       </c>
       <c r="O58" s="14" t="n"/>
@@ -7131,24 +7143,24 @@
       <c r="R58" s="14" t="n"/>
       <c r="S58" s="14" t="inlineStr">
         <is>
-          <t>оптика; история оптики</t>
+          <t>композиция; теория музыки</t>
         </is>
       </c>
       <c r="T58" s="14" t="inlineStr">
         <is>
-          <t>Итальянский физик и историк науки, специалист в области оптики и теории зрения. Автор книги «Оптика: наука о зрении» (Optics: The Science of Vision).</t>
+          <t>Немецкий композитор, дирижёр и музыкальный теоретик, один из крупнейших музыкантов XX века. Автор оперы «Художник Матис» и теоретических трудов по музыкальной композиции.</t>
         </is>
       </c>
       <c r="U58" s="14" t="inlineStr">
         <is>
-          <t>- Optics: The Science of Vision (1991) — цитата о субъективной природе звука</t>
+          <t>- Комбинационные тоны как необходимое условие музыкального восприятия</t>
         </is>
       </c>
       <c r="V58" s="14" t="n"/>
       <c r="W58" s="14" t="n"/>
       <c r="X58" s="14" t="inlineStr">
         <is>
-          <t>Уилсон цитирует Рончи как пример «совершенно оголтелой» формы субъективизма, характерной для практических руководств (в отличие от философской литературы, которая обычно пытается смягчить радикальность субъективации). Рончи утверждает, что звук — это сугубо ментальный феномен, а физические вибрации существуют вне сознания; отождествление акустических колебаний со звуком ведёт к опасному недоразумению. Уилсон иронически замечает, что такой подход приводит к парадоксальному выводу: если в лесу падает дерево, звука не возникает. Этот пример служит иллюстрацией субъективистской модели музыкальных атрибутов, которую Уилсон также отвергает.</t>
+          <t>Уилсон цитирует Хиндемита как авторитетного музыканта, подтверждающего фундаментальную роль комбинационных тонов в музыкальном восприятии. Хиндемит заявляет: «Интервал без комбинационных тонов был бы абстрактным понятием, не имеющим бытия». Эта цитата используется для усиления аргумента о том, что музыкальное восприятие неразрывно связано с субъективными процессами в слуховом аппарате.</t>
         </is>
       </c>
       <c r="Y58" s="14" t="inlineStr">
@@ -7163,7 +7175,7 @@
       </c>
       <c r="AA58" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/vasco-ronchi</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/paul-hindemith</t>
         </is>
       </c>
       <c r="AB58" s="14" t="inlineStr">
@@ -7176,77 +7188,109 @@
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>Фрэнк и Энн Уорнер</t>
+          <t>Жан Пиаже</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Frank and Anne Warner</t>
+          <t>Jean Piaget</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>американцы</t>
+          <t>швейцарец</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/the_warners.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j_piaget.png</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>Фрэнк: 1903–1978; Энн: 1905–1991</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="14" t="n"/>
+          <t>1896–1980</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>1896-08-09</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>1980-09-16</t>
+        </is>
+      </c>
       <c r="H59" s="14" t="n"/>
-      <c r="I59" s="14" t="n"/>
-      <c r="J59" s="14" t="n"/>
-      <c r="K59" s="14" t="n"/>
-      <c r="L59" s="14" t="n"/>
-      <c r="M59" s="14" t="n"/>
-      <c r="N59" s="14" t="n"/>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>Невшатель, Швейцария</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>46.9900, 6.9300</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>Женева, Швейцария</t>
+        </is>
+      </c>
+      <c r="L59" s="14" t="inlineStr">
+        <is>
+          <t>46.2044, 6.1432</t>
+        </is>
+      </c>
+      <c r="M59" s="14" t="inlineStr">
+        <is>
+          <t>Невшательский университет</t>
+        </is>
+      </c>
+      <c r="N59" s="14" t="inlineStr">
+        <is>
+          <t>Женевский университет; Институт Жан-Жака Руссо</t>
+        </is>
+      </c>
       <c r="O59" s="14" t="n"/>
       <c r="P59" s="14" t="n"/>
       <c r="Q59" s="14" t="n"/>
       <c r="R59" s="14" t="n"/>
       <c r="S59" s="14" t="inlineStr">
         <is>
-          <t>фольклористика; полевые записи</t>
+          <t>психология развития; генетическая эпистемология</t>
         </is>
       </c>
       <c r="T59" s="14" t="inlineStr">
         <is>
-          <t>Американские собиратели, исполнители и исследователи традиционной народной музыки. С конца 1930-х годов Фрэнк и Энн Уорнер во время поездок по восточным районам США записывали песни и рассказы традиционных исполнителей, формируя коллекцию, насчитывающую более тысячи песен и историй. Их деятельность охватывала Аппалачи, Северную Каролину, Внешние отмели, Вирджинию, Новую Англию и север штата Нью-Йорк. Фрэнк выступал как певец и музыкант, а Энн занималась документированием материала, расшифровкой записей и подготовкой текстов. При нехватке носителей они нередко записывали только часть песни, после чего Энн восстанавливала остальной текст по стенографической записи.</t>
+          <t>Швейцарский психолог, основоположник теории когнитивного развития ребёнка — описал стадии, через которые проходит детское мышление на пути к взрослому пониманию мира, включая представления о причинности, постоянстве объектов и логических операциях.</t>
         </is>
       </c>
       <c r="U59" s="14" t="inlineStr">
         <is>
-          <t>- Anne and Frank Warner Collection — собрание полевых записей традиционной американской музыки. - Her Bright Smile Haunts Me Still, Appleseed APR CD 1035 (2000). - Полевое собирание фольклора. - Документирование традиционной музыки. - Сохранение музыкального содержания. - Исполнение как форма продолжения традиции. - Противопоставление записи и живого музыкального опыта.</t>
+          <t>- Не применимо — используется как имя-маркер авторитета, а не как содержательный источник</t>
         </is>
       </c>
       <c r="V59" s="14" t="n"/>
       <c r="W59" s="14" t="n"/>
       <c r="X59" s="14" t="inlineStr">
         <is>
-          <t>Уилсон вводит Уорнеров как собирателей 1940-х годов, чьи полевые записи становятся объектом последующего рассуждения о сохранении музыкального содержания. Непосредственно философскую позицию, связанную с этими записями, выражает Тим Эриксон в сопроводительных заметках к переизданию их полевых записей Her Bright Smile Haunts Me Still (2000). Эриксон утверждает, что ценность записанной музыки не существует вне восприятия и опыта и что надёжный способ сохранить музыку «живой» состоит в её исполнении и проживании. Таким образом, Уорнеры занимают в аргументе Уилсона особое положение: их записи представляют объект сохранения, а рассуждения Эриксона превращают этот объект в повод для критики партиципативного понимания сохранения. Уилсон противопоставляет этой позиции идею сохранения посредством записи: если музыкальное содержание уже зафиксировано на носителе, дополнительное участие исполнителя может не только поддерживать традицию, но и изменять или даже разрушать особенности первоначального исполнения.</t>
+          <t>Упомянут как источник стандартной, узнаваемой мерки для оценки уровня концептуального развития — в шуточных примерах про Джона, Хьюи, Дьюи и Луи, оценивающих их понимание «радуги» через фразы вроде «не достиг требуемого Пиаже уровня понимания причинных связей с материальными объектами».</t>
         </is>
       </c>
       <c r="Y59" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z59" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_v</t>
+          <t>chapter_1_vi</t>
         </is>
       </c>
       <c r="AA59" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/frank-and-anne-warner</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/jean-piaget</t>
         </is>
       </c>
       <c r="AB59" s="14" t="inlineStr">
@@ -7259,105 +7303,109 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Кэри Грант</t>
+          <t>Васко Рончи</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Cary Grant</t>
+          <t>Vasco Ronchi</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>британец, американец</t>
+          <t>итальянец</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/cary_grant.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/ronchi.jpg</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>1904–1986</t>
+          <t>1897–1988</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>1904-01-18</t>
+          <t>1897-12-19</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>1986-11-29</t>
-        </is>
-      </c>
-      <c r="H60" s="14" t="inlineStr">
-        <is>
-          <t>инсульт</t>
-        </is>
-      </c>
+          <t>1988-10-31</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="n"/>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>Бристоль, Англия</t>
+          <t>Флоренция</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>51.4545, -2.5879</t>
+          <t>43.7696, 11.2558</t>
         </is>
       </c>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>Дэвенпорт, Айова, США</t>
+          <t>Флоренция</t>
         </is>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>41.5236, -90.5776</t>
-        </is>
-      </c>
-      <c r="M60" s="14" t="n"/>
-      <c r="N60" s="14" t="n"/>
+          <t>43.7696, 11.2558</t>
+        </is>
+      </c>
+      <c r="M60" s="14" t="inlineStr">
+        <is>
+          <t>Высшая нормальная школа, Пиза</t>
+        </is>
+      </c>
+      <c r="N60" s="14" t="inlineStr">
+        <is>
+          <t>Национальный институт оптики, Флоренция</t>
+        </is>
+      </c>
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
       <c r="Q60" s="14" t="n"/>
-      <c r="R60" s="14" t="inlineStr">
-        <is>
-          <t>Почётный «Оскар» (1970)</t>
-        </is>
-      </c>
+      <c r="R60" s="14" t="n"/>
       <c r="S60" s="14" t="inlineStr">
         <is>
-          <t>кино</t>
+          <t>оптика; история оптики</t>
         </is>
       </c>
       <c r="T60" s="14" t="inlineStr">
         <is>
-          <t>Британско-американский киноактёр (настоящее имя — Арчибальд Александер Лич), одна из главных звёзд классического Голливуда: «Воспитание крошки», «Филадельфийская история», «Дурная слава», «К северу через северо-запад».</t>
-        </is>
-      </c>
-      <c r="U60" s="14" t="n"/>
+          <t>Итальянский физик и историк науки, специалист в области оптики и теории зрения. Автор книги «Оптика: наука о зрении» (Optics: The Science of Vision).</t>
+        </is>
+      </c>
+      <c r="U60" s="14" t="inlineStr">
+        <is>
+          <t>- Optics: The Science of Vision (1991) — цитата о субъективной природе звука</t>
+        </is>
+      </c>
       <c r="V60" s="14" t="n"/>
       <c r="W60" s="14" t="n"/>
       <c r="X60" s="14" t="inlineStr">
         <is>
-          <t>Возникает в одном примере. Уилсон показывает, что некоторые «паттерны руководства» легко подчиняются нашему сознательному контролю: речь можно подчинить алгоритму или схеме аксиом («Прибавьте „2“ к цифре, которая у вас уже есть») — или инструкции, опирающейся на непосредственное впечатление: «Помечайте знаком „Х“ любого человека, который напоминает вам Кэри Гранта». Решительное следование таким инструкциям Уилсон называет лично навязанными направленностями. Именно на них, по Уилсону, Куайн чрезмерно полагается в своей картине «правильной лингвистической навигации» (см. willard-quine).</t>
+          <t>Уилсон цитирует Рончи как пример «совершенно оголтелой» формы субъективизма, характерной для практических руководств (в отличие от философской литературы, которая обычно пытается смягчить радикальность субъективации). Рончи утверждает, что звук — это сугубо ментальный феномен, а физические вибрации существуют вне сознания; отождествление акустических колебаний со звуком ведёт к опасному недоразумению. Уилсон иронически замечает, что такой подход приводит к парадоксальному выводу: если в лесу падает дерево, звука не возникает. Этот пример служит иллюстрацией субъективистской модели музыкальных атрибутов, которую Уилсон также отвергает.</t>
         </is>
       </c>
       <c r="Y60" s="14" t="inlineStr">
         <is>
-          <t>гл. 3</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z60" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_v</t>
+          <t>chapter_2_iv</t>
         </is>
       </c>
       <c r="AA60" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/cary-grant</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/vasco-ronchi</t>
         </is>
       </c>
       <c r="AB60" s="14" t="inlineStr">
@@ -7370,113 +7418,77 @@
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>Доктор Зойс (Доктор Сьюз)</t>
+          <t>Фрэнк и Энн Уорнер</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>Dr. Seuss</t>
+          <t>Frank and Anne Warner</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>американцы</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/dr_seuss.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/the_warners.jpg</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>1904–1991</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
-        <is>
-          <t>1904-03-02</t>
-        </is>
-      </c>
-      <c r="G61" s="14" t="inlineStr">
-        <is>
-          <t>1991-09-24</t>
-        </is>
-      </c>
-      <c r="H61" s="14" t="inlineStr">
-        <is>
-          <t>рак ротовой полости</t>
-        </is>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>Спрингфилд, Массачусетс, США</t>
-        </is>
-      </c>
-      <c r="J61" s="14" t="inlineStr">
-        <is>
-          <t>42.1015, -72.5898</t>
-        </is>
-      </c>
-      <c r="K61" s="14" t="inlineStr">
-        <is>
-          <t>Ла-Холья, Калифорния, США</t>
-        </is>
-      </c>
-      <c r="L61" s="14" t="inlineStr">
-        <is>
-          <t>32.8328, -117.2713</t>
-        </is>
-      </c>
-      <c r="M61" s="14" t="inlineStr">
-        <is>
-          <t>Дартмутский колледж; Линкольн-колледж, Оксфорд</t>
-        </is>
-      </c>
+          <t>Фрэнк: 1903–1978; Энн: 1905–1991</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="n"/>
+      <c r="G61" s="14" t="n"/>
+      <c r="H61" s="14" t="n"/>
+      <c r="I61" s="14" t="n"/>
+      <c r="J61" s="14" t="n"/>
+      <c r="K61" s="14" t="n"/>
+      <c r="L61" s="14" t="n"/>
+      <c r="M61" s="14" t="n"/>
       <c r="N61" s="14" t="n"/>
       <c r="O61" s="14" t="n"/>
       <c r="P61" s="14" t="n"/>
       <c r="Q61" s="14" t="n"/>
-      <c r="R61" s="14" t="inlineStr">
-        <is>
-          <t>Специальная Пулитцеровская премия (1984)</t>
-        </is>
-      </c>
+      <c r="R61" s="14" t="n"/>
       <c r="S61" s="14" t="inlineStr">
         <is>
-          <t>детская литература; иллюстрация</t>
+          <t>фольклористика; полевые записи</t>
         </is>
       </c>
       <c r="T61" s="14" t="inlineStr">
         <is>
-          <t>Псевдоним Теодора Сьюза Гайзеля, американского детского писателя и иллюстратора, автора «The Cat in the Hat», «Green Eggs and Ham», «How the Grinch Stole Christmas!» и десятков других книг, отличающихся характерным ритмизованным, изобретательным словотворчеством. Здесь цитируется его алфавитная книга «Dr. Seuss's ABC» (1963). (Примечание по транслитерации: в русском переводе фрагмента имя передано как «доктор Зойс» — нестандартный вариант против общепринятого в русскоязычной традиции «Доктор Сьюз»; возможно, стоит унифицировать при редактуре.)</t>
+          <t>Американские собиратели, исполнители и исследователи традиционной народной музыки. С конца 1930-х годов Фрэнк и Энн Уорнер во время поездок по восточным районам США записывали песни и рассказы традиционных исполнителей, формируя коллекцию, насчитывающую более тысячи песен и историй. Их деятельность охватывала Аппалачи, Северную Каролину, Внешние отмели, Вирджинию, Новую Англию и север штата Нью-Йорк. Фрэнк выступал как певец и музыкант, а Энн занималась документированием материала, расшифровкой записей и подготовкой текстов. При нехватке носителей они нередко записывали только часть песни, после чего Энн восстанавливала остальной текст по стенографической записи.</t>
         </is>
       </c>
       <c r="U61" s="14" t="inlineStr">
         <is>
-          <t>- Dr. Seuss, Dr. Seuss's ABC (New York: Random House, 1963), 34</t>
+          <t>- Anne and Frank Warner Collection — собрание полевых записей традиционной американской музыки. - Her Bright Smile Haunts Me Still, Appleseed APR CD 1035 (2000). - Полевое собирание фольклора. - Документирование традиционной музыки. - Сохранение музыкального содержания. - Исполнение как форма продолжения традиции. - Противопоставление записи и живого музыкального опыта.</t>
         </is>
       </c>
       <c r="V61" s="14" t="n"/>
       <c r="W61" s="14" t="n"/>
       <c r="X61" s="14" t="inlineStr">
         <is>
-          <t>Использован как шутливая, но точная иллюстрация тезиса о «креативности языка»: строчка про букву «O» («Oscar's only ostrich oiled an orange owl today») — искусственное предложение, которое почти наверняка никто, кроме самого Доктора Сьюза (и производных от него комментаторов вроде самого Уилсона), никогда не произнёс бы, но которое, тем не менее, мгновенно и полностью понятно любому носителю языка. Это доводит до абсурда — и тем самым иллюстрирует — довод Джекендоффа о том, что понимание бесконечного числа новых предложений требует конечного набора полностью усвоенных примитивов.</t>
+          <t>Уилсон вводит Уорнеров как собирателей 1940-х годов, чьи полевые записи становятся объектом последующего рассуждения о сохранении музыкального содержания. Непосредственно философскую позицию, связанную с этими записями, выражает Тим Эриксон в сопроводительных заметках к переизданию их полевых записей Her Bright Smile Haunts Me Still (2000). Эриксон утверждает, что ценность записанной музыки не существует вне восприятия и опыта и что надёжный способ сохранить музыку «живой» состоит в её исполнении и проживании. Таким образом, Уорнеры занимают в аргументе Уилсона особое положение: их записи представляют объект сохранения, а рассуждения Эриксона превращают этот объект в повод для критики партиципативного понимания сохранения. Уилсон противопоставляет этой позиции идею сохранения посредством записи: если музыкальное содержание уже зафиксировано на носителе, дополнительное участие исполнителя может не только поддерживать традицию, но и изменять или даже разрушать особенности первоначального исполнения.</t>
         </is>
       </c>
       <c r="Y61" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z61" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_vi</t>
+          <t>chapter_2_v</t>
         </is>
       </c>
       <c r="AA61" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/doctor-seuss</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/frank-and-anne-warner</t>
         </is>
       </c>
       <c r="AB61" s="14" t="inlineStr">
@@ -7489,85 +7501,105 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Железный Герцог</t>
+          <t>Кэри Грант</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>The Duke of Iron</t>
+          <t>Cary Grant</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>тринидадец</t>
+          <t>британец, американец</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/duke_of_iron.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/cary_grant.jpg</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>1906–1968</t>
+          <t>1904–1986</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1904-01-18</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="H62" s="14" t="n"/>
-      <c r="I62" s="14" t="n"/>
-      <c r="J62" s="14" t="n"/>
-      <c r="K62" s="14" t="n"/>
-      <c r="L62" s="14" t="n"/>
+          <t>1986-11-29</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>инсульт</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>Бристоль, Англия</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
+        <is>
+          <t>51.4545, -2.5879</t>
+        </is>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>Дэвенпорт, Айова, США</t>
+        </is>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>41.5236, -90.5776</t>
+        </is>
+      </c>
       <c r="M62" s="14" t="n"/>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n"/>
       <c r="P62" s="14" t="n"/>
       <c r="Q62" s="14" t="n"/>
-      <c r="R62" s="14" t="n"/>
+      <c r="R62" s="14" t="inlineStr">
+        <is>
+          <t>Почётный «Оскар» (1970)</t>
+        </is>
+      </c>
       <c r="S62" s="14" t="inlineStr">
         <is>
-          <t>калипсо</t>
+          <t>кино</t>
         </is>
       </c>
       <c r="T62" s="14" t="inlineStr">
         <is>
-          <t>Настоящее имя — Сесил Андерсон (Cecil Anderson), калипсонье (исполнитель калипсо), уроженец Порт-оф-Спейна, Тринидад. В 1923 году переехал с семьёй в Нью-Йорк, где и сделал основную карьеру — один из самых популярных исполнителей калипсо в США 1930–1960-х годов, известен чёткой дикцией и умением ясно доносить английский текст до американской аудитории (в отличие от многих коллег с более выраженным креольским произношением), а также озорным, фривольным юмором в текстах. Десятимесячная резидентура в нью-йоркском Village Vanguard (1940-е), выступления в Carnegie Hall и Apollo Theater, участие в легендарном концерте «Calypso at Midnight» Алана Ломакса (Town Hall, декабрь 1946), роль в фильме «Calypso Joe» (1957) с Энджи Дикинсон. Среди самых известных вещей — «The Big Bamboo» (культовая фривольная классика жанра) и, что любопытно для этого путеводителя, собственная запись той же песни «Marry a Woman Uglier Than You» — того самого источника, вокруг авторства которого разворачивается путаница в примечании Уилсона (см. карточку roaring-lion).</t>
-        </is>
-      </c>
-      <c r="U62" s="14" t="inlineStr">
-        <is>
-          <t>- «Wide Screen» (Monogram Record M-934) — источник эпиграфа, установлено по авторской сноске</t>
-        </is>
-      </c>
+          <t>Британско-американский киноактёр (настоящее имя — Арчибальд Александер Лич), одна из главных звёзд классического Голливуда: «Воспитание крошки», «Филадельфийская история», «Дурная слава», «К северу через северо-запад».</t>
+        </is>
+      </c>
+      <c r="U62" s="14" t="n"/>
       <c r="V62" s="14" t="n"/>
       <c r="W62" s="14" t="n"/>
       <c r="X62" s="14" t="inlineStr">
         <is>
-          <t>Использован как источник эпиграфа к главе 1 («Широкий экран»/Wide Screen) — двустишие про очки и возможность видеть «любой экран, прибывший в Тринидад» (по содержанию соответствует русскому переводу; дословно не воспроизвожу — это лирика песни, а не проза Уилсона). Источник установлен точно по сноске самого автора: песня называется «Wide Screen», пластинка Monogram Record M-934. Главы книги открываются калипсо-эпиграфами, что задаёт неформальный, игривый тон изложения даже там, где обсуждаются сложные технические вопросы. Не удалось найти первоисточник всего текста песни.</t>
+          <t>Возникает в одном примере. Уилсон показывает, что некоторые «паттерны руководства» легко подчиняются нашему сознательному контролю: речь можно подчинить алгоритму или схеме аксиом («Прибавьте „2“ к цифре, которая у вас уже есть») — или инструкции, опирающейся на непосредственное впечатление: «Помечайте знаком „Х“ любого человека, который напоминает вам Кэри Гранта». Решительное следование таким инструкциям Уилсон называет лично навязанными направленностями. Именно на них, по Уилсону, Куайн чрезмерно полагается в своей картине «правильной лингвистической навигации» (см. willard-quine).</t>
         </is>
       </c>
       <c r="Y62" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z62" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_i</t>
+          <t>chapter_3_v</t>
         </is>
       </c>
       <c r="AA62" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/duke-of-iron</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/cary-grant</t>
         </is>
       </c>
       <c r="AB62" s="14" t="inlineStr">
@@ -7580,89 +7612,113 @@
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Фриц Винкель</t>
+          <t>Доктор Зойс (Доктор Сьюз)</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Fritz Winckel</t>
+          <t>Dr. Seuss</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>немец</t>
+          <t>американец</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/f_winckel.png</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/dr_seuss.jpg</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>1907-2000</t>
+          <t>1904–1991</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1904-03-02</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="H63" s="14" t="n"/>
-      <c r="I63" s="14" t="n"/>
-      <c r="J63" s="14" t="n"/>
-      <c r="K63" s="14" t="n"/>
-      <c r="L63" s="14" t="n"/>
-      <c r="M63" s="14" t="n"/>
-      <c r="N63" s="14" t="inlineStr">
-        <is>
-          <t>Технический университет Берлина</t>
-        </is>
-      </c>
+          <t>1991-09-24</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>рак ротовой полости</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>Спрингфилд, Массачусетс, США</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>42.1015, -72.5898</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>Ла-Холья, Калифорния, США</t>
+        </is>
+      </c>
+      <c r="L63" s="14" t="inlineStr">
+        <is>
+          <t>32.8328, -117.2713</t>
+        </is>
+      </c>
+      <c r="M63" s="14" t="inlineStr">
+        <is>
+          <t>Дартмутский колледж; Линкольн-колледж, Оксфорд</t>
+        </is>
+      </c>
+      <c r="N63" s="14" t="n"/>
       <c r="O63" s="14" t="n"/>
       <c r="P63" s="14" t="n"/>
       <c r="Q63" s="14" t="n"/>
-      <c r="R63" s="14" t="n"/>
+      <c r="R63" s="14" t="inlineStr">
+        <is>
+          <t>Специальная Пулитцеровская премия (1984)</t>
+        </is>
+      </c>
       <c r="S63" s="14" t="inlineStr">
         <is>
-          <t>акустика; музыкальная психоакустика</t>
+          <t>детская литература; иллюстрация</t>
         </is>
       </c>
       <c r="T63" s="14" t="inlineStr">
         <is>
-          <t>Немецкий музыковед и акустик XX века, автор книги «Музыка, звук и ощущение» (Music, Sound and Sensation, 1967), в которой исследуются физические и психологические основы музыкального восприятия.</t>
+          <t>Псевдоним Теодора Сьюза Гайзеля, американского детского писателя и иллюстратора, автора «The Cat in the Hat», «Green Eggs and Ham», «How the Grinch Stole Christmas!» и десятков других книг, отличающихся характерным ритмизованным, изобретательным словотворчеством. Здесь цитируется его алфавитная книга «Dr. Seuss's ABC» (1963). (Примечание по транслитерации: в русском переводе фрагмента имя передано как «доктор Зойс» — нестандартный вариант против общепринятого в русскоязычной традиции «Доктор Сьюз»; возможно, стоит унифицировать при редактуре.)</t>
         </is>
       </c>
       <c r="U63" s="14" t="inlineStr">
         <is>
-          <t>- Music, Sound and Sensation: A Modern Exposition (1967) — цитаты о роли комбинационных тонов и обертонов в музыкальном восприятии</t>
+          <t>- Dr. Seuss, Dr. Seuss's ABC (New York: Random House, 1963), 34</t>
         </is>
       </c>
       <c r="V63" s="14" t="n"/>
       <c r="W63" s="14" t="n"/>
       <c r="X63" s="14" t="inlineStr">
         <is>
-          <t>Уилсон цитирует Винкеля как авторитетного музыковеда, который в ироничном ключе утверждает, что математически описываемая гармония (синусоидальные волны, чистые интервалы) не вызывает музыкальных переживаний; напротив, для полноценного музыкального опыта требуются такие «несовершенства», как комбинационные тоны и обертоны. Винкель пишет: «Чистые интервалы триады простых тонов не вызывают музыкальных переживаний, а, напротив, на самом деле требуют стимулирующего компонента — по крайней мере, 7-го обертона». Это подкрепляет аргумент Уилсона о том, что музыкальные свойства укоренены в «изменчивой человеческой природе».</t>
+          <t>Использован как шутливая, но точная иллюстрация тезиса о «креативности языка»: строчка про букву «O» («Oscar's only ostrich oiled an orange owl today») — искусственное предложение, которое почти наверняка никто, кроме самого Доктора Сьюза (и производных от него комментаторов вроде самого Уилсона), никогда не произнёс бы, но которое, тем не менее, мгновенно и полностью понятно любому носителю языка. Это доводит до абсурда — и тем самым иллюстрирует — довод Джекендоффа о том, что понимание бесконечного числа новых предложений требует конечного набора полностью усвоенных примитивов.</t>
         </is>
       </c>
       <c r="Y63" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z63" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_iv</t>
+          <t>chapter_1_vi</t>
         </is>
       </c>
       <c r="AA63" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/fritz-winckel</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/doctor-seuss</t>
         </is>
       </c>
       <c r="AB63" s="14" t="inlineStr">
@@ -7675,12 +7731,12 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Могучий Лев (в оригинале — Roaring Lion, точнее «Ревущий/Рычащий Лев»)</t>
+          <t>Железный Герцог</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Roaring Lion</t>
+          <t>The Duke of Iron</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -7690,22 +7746,22 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/roaring_lion.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/duke_of_iron.jpg</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>1908–1999</t>
+          <t>1906–1968</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="H64" s="14" t="n"/>
@@ -7726,19 +7782,19 @@
       </c>
       <c r="T64" s="14" t="inlineStr">
         <is>
-          <t>Один из величайших пионеров калипсо золотого века жанра (1930–1950-е). Настоящее имя спорно документировано — сам себя называл Rafael Arias Cairi Llama de Leon, хотя долгое время в источниках фигурировало «Hubert Raphael Charles» (это, по данным современных исследований, ошибка). Сценическое имя «Roaring Lion» получил от уходящего на покой калипсонье по прозвищу Poetical Harris — за мощный, «рычащий» вокал. В 1934 году вместе с Attila the Hun стал первым калипсонье, выехавшим записываться за границу (Нью-Йорк) — тогда же выступил перед президентом США Франклином Рузвельтом в отеле Waldorf Astoria, где на вопрос о происхождении ответил «The Land of Calypso», закрепив это прозвище за Тринидадом. Автор изданной под конец жизни книги по истории жанра «Calypso from France to Trinidad: 800 Years of History» (1986).</t>
+          <t>Настоящее имя — Сесил Андерсон (Cecil Anderson), калипсонье (исполнитель калипсо), уроженец Порт-оф-Спейна, Тринидад. В 1923 году переехал с семьёй в Нью-Йорк, где и сделал основную карьеру — один из самых популярных исполнителей калипсо в США 1930–1960-х годов, известен чёткой дикцией и умением ясно доносить английский текст до американской аудитории (в отличие от многих коллег с более выраженным креольским произношением), а также озорным, фривольным юмором в текстах. Десятимесячная резидентура в нью-йоркском Village Vanguard (1940-е), выступления в Carnegie Hall и Apollo Theater, участие в легендарном концерте «Calypso at Midnight» Алана Ломакса (Town Hall, декабрь 1946), роль в фильме «Calypso Joe» (1957) с Энджи Дикинсон. Среди самых известных вещей — «The Big Bamboo» (культовая фривольная классика жанра) и, что любопытно для этого путеводителя, собственная запись той же песни «Marry a Woman Uglier Than You» — того самого источника, вокруг авторства которого разворачивается путаница в примечании Уилсона (см. карточку roaring-lion).</t>
         </is>
       </c>
       <c r="U64" s="14" t="inlineStr">
         <is>
-          <t>- «Ugly Woman» (1933/34) — источник названия книги Куайна «From a Logical Point of View» (1953)</t>
+          <t>- «Wide Screen» (Monogram Record M-934) — источник эпиграфа, установлено по авторской сноске</t>
         </is>
       </c>
       <c r="V64" s="14" t="n"/>
       <c r="W64" s="14" t="n"/>
       <c r="X64" s="14" t="inlineStr">
         <is>
-          <t>Персонаж, связанный с примечанием об ошибках в атрибуции. Уилсон поясняет: У. В. Куайн, называя свой знаменитый сборник статей «From a Logical Point of View» («С логической точки зрения», 1953), заимствовал название из строки калипсо-песни — но приписал её Гарри Белафонте, тогда как настоящий автор и первый исполнитель песни — именно этот калипсонье, который «так и не получил должного признания за свою работу». Проверено по независимым источникам: песня называется «Ugly Woman» (записана в 1933–34 гг.), содержит буквальную строку «That's from a logical point of view / Always love a woman uglier than you» — прямой источник заглавия книги Куайна. В 1957 году актёр и певец Роберт Митчем записал кавер-версию именно под названием «From a Logical Point of View» (альбом «Calypso — Is Like So...») — по всей видимости, именно эта версия и стала непосредственным источником, который слышал Куайн, а сам факт присвоения авторства Белафонте, вероятно, объясняется тем, что Белафонте был несравнимо более известен и ассоциировался с калипсо-бумом середины 1950-х в целом, тогда как ни настоящий автор, ни фактический кавер-исполнитель (Митчем) такой славы не получили.</t>
+          <t>Использован как источник эпиграфа к главе 1 («Широкий экран»/Wide Screen) — двустишие про очки и возможность видеть «любой экран, прибывший в Тринидад» (по содержанию соответствует русскому переводу; дословно не воспроизвожу — это лирика песни, а не проза Уилсона). Источник установлен точно по сноске самого автора: песня называется «Wide Screen», пластинка Monogram Record M-934. Главы книги открываются калипсо-эпиграфами, что задаёт неформальный, игривый тон изложения даже там, где обсуждаются сложные технические вопросы. Не удалось найти первоисточник всего текста песни.</t>
         </is>
       </c>
       <c r="Y64" s="14" t="inlineStr">
@@ -7753,7 +7809,7 @@
       </c>
       <c r="AA64" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/roaring-lion</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/duke-of-iron</t>
         </is>
       </c>
       <c r="AB64" s="14" t="inlineStr">
@@ -7766,125 +7822,89 @@
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>Уиллард Куайн</t>
+          <t>Фриц Винкель</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Willard Van Orman Quine</t>
+          <t>Fritz Winckel</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>немец</t>
         </is>
       </c>
       <c r="D65" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/quinewo.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/f_winckel.png</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>1908–2000</t>
+          <t>1907-2000</t>
         </is>
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>1908-06-25</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>2000-12-25</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H65" s="14" t="n"/>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>Акрон, Огайо, США</t>
-        </is>
-      </c>
-      <c r="J65" s="14" t="inlineStr">
-        <is>
-          <t>41.0814, -81.5190</t>
-        </is>
-      </c>
-      <c r="K65" s="14" t="inlineStr">
-        <is>
-          <t>Бостон, США</t>
-        </is>
-      </c>
-      <c r="L65" s="14" t="inlineStr">
-        <is>
-          <t>42.3601, -71.0589</t>
-        </is>
-      </c>
-      <c r="M65" s="14" t="inlineStr">
-        <is>
-          <t>Оберлин-колледж; Гарвардский университет</t>
-        </is>
-      </c>
+      <c r="I65" s="14" t="n"/>
+      <c r="J65" s="14" t="n"/>
+      <c r="K65" s="14" t="n"/>
+      <c r="L65" s="14" t="n"/>
+      <c r="M65" s="14" t="n"/>
       <c r="N65" s="14" t="inlineStr">
         <is>
-          <t>Гарвардский университет</t>
-        </is>
-      </c>
-      <c r="O65" s="14" t="inlineStr">
-        <is>
-          <t>Альфред Норт Уайтхед</t>
-        </is>
-      </c>
-      <c r="P65" s="14" t="inlineStr">
-        <is>
-          <t>Дэвид Льюис</t>
-        </is>
-      </c>
-      <c r="Q65" s="14" t="inlineStr">
-        <is>
-          <t>Хилари Патнэм</t>
-        </is>
-      </c>
+          <t>Технический университет Берлина</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="n"/>
+      <c r="P65" s="14" t="n"/>
+      <c r="Q65" s="14" t="n"/>
       <c r="R65" s="14" t="n"/>
       <c r="S65" s="14" t="inlineStr">
         <is>
-          <t>логика; философия языка; эпистемология</t>
+          <t>акустика; музыкальная психоакустика</t>
         </is>
       </c>
       <c r="T65" s="14" t="inlineStr">
         <is>
-          <t>Один из центральных философов-аналитиков XX века. Известен критикой различения аналитических и синтетических суждений (статья «Две догмы эмпиризма»), тезисом о неопределённости перевода и программой натурализованной эпистемологии.</t>
+          <t>Немецкий музыковед и акустик XX века, автор книги «Музыка, звук и ощущение» (Music, Sound and Sensation, 1967), в которой исследуются физические и психологические основы музыкального восприятия.</t>
         </is>
       </c>
       <c r="U65" s="14" t="inlineStr">
         <is>
-          <t>- Холизм подтверждения / тезис Дюэма–Куайна - Критика различения аналитического и синтетического («Две догмы эмпиризма», 1951) - Корабль Нойрата как образ языковой эволюции (Word and Object, 1960) — см. korabl-noyrata - Регламентация языка: максима «Приведите свои дела в простейший регламентированный порядок» (гл. 3, v)</t>
-        </is>
-      </c>
-      <c r="V65" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/quine/</t>
-        </is>
-      </c>
+          <t>- Music, Sound and Sensation: A Modern Exposition (1967) — цитаты о роли комбинационных тонов и обертонов в музыкальном восприятии</t>
+        </is>
+      </c>
+      <c r="V65" s="14" t="n"/>
       <c r="W65" s="14" t="n"/>
       <c r="X65" s="14" t="inlineStr">
         <is>
-          <t>Упомянут как один из первых, кто усомнился в основаниях классических подходов к системам понятий в науке и философии — то есть выступает как предшественник и союзник по духу основного тезиса книги, хотя и с иной, более общей постановкой вопроса. Уилсон, судя по всему, опирается на этот скептицизм как на отправную точку, чтобы затем предложить собственную, более детализированную картину того, как понятия меняются в употреблении.</t>
+          <t>Уилсон цитирует Винкеля как авторитетного музыковеда, который в ироничном ключе утверждает, что математически описываемая гармония (синусоидальные волны, чистые интервалы) не вызывает музыкальных переживаний; напротив, для полноценного музыкального опыта требуются такие «несовершенства», как комбинационные тоны и обертоны. Винкель пишет: «Чистые интервалы триады простых тонов не вызывают музыкальных переживаний, а, напротив, на самом деле требуют стимулирующего компонента — по крайней мере, 7-го обертона». Это подкрепляет аргумент Уилсона о том, что музыкальные свойства укоренены в «изменчивой человеческой природе».</t>
         </is>
       </c>
       <c r="Y65" s="14" t="inlineStr">
         <is>
-          <t>предисловие; гл. 3</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z65" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_i; chapter_3_ii; chapter_3_v; predislovie</t>
+          <t>chapter_2_iv</t>
         </is>
       </c>
       <c r="AA65" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/willard-quine</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/fritz-winckel</t>
         </is>
       </c>
       <c r="AB65" s="14" t="inlineStr">
@@ -7897,117 +7917,85 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Дж. Л. Остин</t>
+          <t>Могучий Лев (в оригинале — Roaring Lion, точнее «Ревущий/Рычащий Лев»)</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>John Langshaw Austin</t>
+          <t>Roaring Lion</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
+          <t>тринидадец</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/jlaustin.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/roaring_lion.jpg</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>1911–1960</t>
+          <t>1908–1999</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>1911-03-26</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>1960-02-08</t>
-        </is>
-      </c>
-      <c r="H66" s="14" t="inlineStr">
-        <is>
-          <t>рак лёгких</t>
-        </is>
-      </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>Ланкастер, Англия</t>
-        </is>
-      </c>
-      <c r="J66" s="14" t="inlineStr">
-        <is>
-          <t>54.0466, -2.8007</t>
-        </is>
-      </c>
-      <c r="K66" s="14" t="inlineStr">
-        <is>
-          <t>Оксфорд, Англия</t>
-        </is>
-      </c>
-      <c r="L66" s="14" t="inlineStr">
-        <is>
-          <t>51.7520, -1.2577</t>
-        </is>
-      </c>
-      <c r="M66" s="14" t="inlineStr">
-        <is>
-          <t>Баллиол-колледж, Оксфорд</t>
-        </is>
-      </c>
-      <c r="N66" s="14" t="inlineStr">
-        <is>
-          <t>Оксфордский университет</t>
-        </is>
-      </c>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="n"/>
+      <c r="I66" s="14" t="n"/>
+      <c r="J66" s="14" t="n"/>
+      <c r="K66" s="14" t="n"/>
+      <c r="L66" s="14" t="n"/>
+      <c r="M66" s="14" t="n"/>
+      <c r="N66" s="14" t="n"/>
       <c r="O66" s="14" t="n"/>
       <c r="P66" s="14" t="n"/>
       <c r="Q66" s="14" t="n"/>
       <c r="R66" s="14" t="n"/>
       <c r="S66" s="14" t="inlineStr">
         <is>
-          <t>философия обыденного языка; теория речевых актов</t>
+          <t>калипсо</t>
         </is>
       </c>
       <c r="T66" s="14" t="inlineStr">
         <is>
-          <t>Британский философ, один из основателей философии обыденного языка (ordinary language philosophy) и теории речевых актов. Автор работ «Как производить действия при помощи слов» («How to Do Things with Words») и «Чужое сознание» / «Оправдания» («A Plea for Excuses»). Известен методом пристального внимания к тому, как понятия реально используются в языке, — вместо того чтобы конструировать их значения априорно.</t>
+          <t>Один из величайших пионеров калипсо золотого века жанра (1930–1950-е). Настоящее имя спорно документировано — сам себя называл Rafael Arias Cairi Llama de Leon, хотя долгое время в источниках фигурировало «Hubert Raphael Charles» (это, по данным современных исследований, ошибка). Сценическое имя «Roaring Lion» получил от уходящего на покой калипсонье по прозвищу Poetical Harris — за мощный, «рычащий» вокал. В 1934 году вместе с Attila the Hun стал первым калипсонье, выехавшим записываться за границу (Нью-Йорк) — тогда же выступил перед президентом США Франклином Рузвельтом в отеле Waldorf Astoria, где на вопрос о происхождении ответил «The Land of Calypso», закрепив это прозвище за Тринидадом. Автор изданной под конец жизни книги по истории жанра «Calypso from France to Trinidad: 800 Years of History» (1986).</t>
         </is>
       </c>
       <c r="U66" s="14" t="inlineStr">
         <is>
-          <t>- Теория речевых актов (speech acts) — «How to Do Things with Words» - Метод анализа обыденного языка через конкретные случаи употребления - (дозаполнить по мере чтения)</t>
-        </is>
-      </c>
-      <c r="V66" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/austin-jl/</t>
-        </is>
-      </c>
+          <t>- «Ugly Woman» (1933/34) — источник названия книги Куайна «From a Logical Point of View» (1953)</t>
+        </is>
+      </c>
+      <c r="V66" s="14" t="n"/>
       <c r="W66" s="14" t="n"/>
       <c r="X66" s="14" t="inlineStr">
         <is>
-          <t>Остиновский метод — внимание к фактическому, ситуативному употреблению слов вместо абстрактных дефиниций — методологически близок общему проекту Уилсона: показать, что значения понятий формируются и «блуждают» именно в практике употребления. Возможный методологический союзник, а не оппонент.</t>
+          <t>Персонаж, связанный с примечанием об ошибках в атрибуции. Уилсон поясняет: У. В. Куайн, называя свой знаменитый сборник статей «From a Logical Point of View» («С логической точки зрения», 1953), заимствовал название из строки калипсо-песни — но приписал её Гарри Белафонте, тогда как настоящий автор и первый исполнитель песни — именно этот калипсонье, который «так и не получил должного признания за свою работу». Проверено по независимым источникам: песня называется «Ugly Woman» (записана в 1933–34 гг.), содержит буквальную строку «That's from a logical point of view / Always love a woman uglier than you» — прямой источник заглавия книги Куайна. В 1957 году актёр и певец Роберт Митчем записал кавер-версию именно под названием «From a Logical Point of View» (альбом «Calypso — Is Like So...») — по всей видимости, именно эта версия и стала непосредственным источником, который слышал Куайн, а сам факт присвоения авторства Белафонте, вероятно, объясняется тем, что Белафонте был несравнимо более известен и ассоциировался с калипсо-бумом середины 1950-х в целом, тогда как ни настоящий автор, ни фактический кавер-исполнитель (Митчем) такой славы не получили.</t>
         </is>
       </c>
       <c r="Y66" s="14" t="inlineStr">
         <is>
-          <t>гл. 1; гл. 3</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z66" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_v; chapter_3_i</t>
+          <t>chapter_1_i</t>
         </is>
       </c>
       <c r="AA66" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/j-l-austin</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/roaring-lion</t>
         </is>
       </c>
       <c r="AB66" s="14" t="inlineStr">
@@ -8020,12 +8008,12 @@
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>М. Х. Абрамс</t>
+          <t>Уиллард Куайн</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>M. H. Abrams</t>
+          <t>Willard Van Orman Quine</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
@@ -8035,94 +8023,110 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/m_abrams.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/quinewo.jpg</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>1912–2015</t>
+          <t>1908–2000</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1912-07-23</t>
+          <t>1908-06-25</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>2015-04-21</t>
+          <t>2000-12-25</t>
         </is>
       </c>
       <c r="H67" s="14" t="n"/>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>Лонг-Бранч, Нью-Джерси, США</t>
+          <t>Акрон, Огайо, США</t>
         </is>
       </c>
       <c r="J67" s="14" t="inlineStr">
         <is>
-          <t>40.3040, -73.9920</t>
+          <t>41.0814, -81.5190</t>
         </is>
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>Итака, Нью-Йорк, США</t>
+          <t>Бостон, США</t>
         </is>
       </c>
       <c r="L67" s="14" t="inlineStr">
         <is>
-          <t>42.4440, -76.5019</t>
+          <t>42.3601, -71.0589</t>
         </is>
       </c>
       <c r="M67" s="14" t="inlineStr">
         <is>
+          <t>Оберлин-колледж; Гарвардский университет</t>
+        </is>
+      </c>
+      <c r="N67" s="14" t="inlineStr">
+        <is>
           <t>Гарвардский университет</t>
         </is>
       </c>
-      <c r="N67" s="14" t="inlineStr">
-        <is>
-          <t>Корнеллский университет</t>
-        </is>
-      </c>
-      <c r="O67" s="14" t="n"/>
-      <c r="P67" s="14" t="n"/>
-      <c r="Q67" s="14" t="n"/>
+      <c r="O67" s="14" t="inlineStr">
+        <is>
+          <t>Альфред Норт Уайтхед</t>
+        </is>
+      </c>
+      <c r="P67" s="14" t="inlineStr">
+        <is>
+          <t>Дэвид Льюис</t>
+        </is>
+      </c>
+      <c r="Q67" s="14" t="inlineStr">
+        <is>
+          <t>Хилари Патнэм</t>
+        </is>
+      </c>
       <c r="R67" s="14" t="n"/>
       <c r="S67" s="14" t="inlineStr">
         <is>
-          <t>литературоведение; романтизм</t>
+          <t>логика; философия языка; эпистемология</t>
         </is>
       </c>
       <c r="T67" s="14" t="inlineStr">
         <is>
-          <t>Американский литературовед, один из крупнейших исследователей английского романтизма.</t>
+          <t>Один из центральных философов-аналитиков XX века. Известен критикой различения аналитических и синтетических суждений (статья «Две догмы эмпиризма»), тезисом о неопределённости перевода и программой натурализованной эпистемологии.</t>
         </is>
       </c>
       <c r="U67" s="14" t="inlineStr">
         <is>
-          <t>- M. H. Abrams, Natural Supernaturalism (1973), p. 375 - M. H. Abrams, The Correspondent Breeze (1984) - Романтическое восприятие - Взаимодействие ума и мира</t>
-        </is>
-      </c>
-      <c r="V67" s="14" t="n"/>
+          <t>- Холизм подтверждения / тезис Дюэма–Куайна - Критика различения аналитического и синтетического («Две догмы эмпиризма», 1951) - Корабль Нойрата как образ языковой эволюции (Word and Object, 1960) — см. korabl-noyrata - Регламентация языка: максима «Приведите свои дела в простейший регламентированный порядок» (гл. 3, v)</t>
+        </is>
+      </c>
+      <c r="V67" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/quine/</t>
+        </is>
+      </c>
       <c r="W67" s="14" t="n"/>
       <c r="X67" s="14" t="inlineStr">
         <is>
-          <t>Абрамс нужен Уилсону как историк романтической доктрины восприятия. Его формулировка показывает, что для романтического поэта жизненное положение человека зависит от того, как его ум взаимодействует с миром в акте восприятия.</t>
+          <t>Упомянут как один из первых, кто усомнился в основаниях классических подходов к системам понятий в науке и философии — то есть выступает как предшественник и союзник по духу основного тезиса книги, хотя и с иной, более общей постановкой вопроса. Уилсон, судя по всему, опирается на этот скептицизм как на отправную точку, чтобы затем предложить собственную, более детализированную картину того, как понятия меняются в употреблении.</t>
         </is>
       </c>
       <c r="Y67" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>предисловие; гл. 3</t>
         </is>
       </c>
       <c r="Z67" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_vi</t>
+          <t>chapter_3_i; chapter_3_ii; chapter_3_v; predislovie</t>
         </is>
       </c>
       <c r="AA67" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/m-h-abrams</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/willard-quine</t>
         </is>
       </c>
       <c r="AB67" s="14" t="inlineStr">
@@ -8135,113 +8139,117 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>Уилфрид Селларс</t>
+          <t>Дж. Л. Остин</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Wilfrid Sellars</t>
+          <t>John Langshaw Austin</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>британец</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/w_sellars.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/jlaustin.jpg</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>1912–1989</t>
+          <t>1911–1960</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>1912-05-20</t>
+          <t>1911-03-26</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>1989-07-02</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="n"/>
+          <t>1960-02-08</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>рак лёгких</t>
+        </is>
+      </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>Анн-Арбор, Мичиган, США</t>
+          <t>Ланкастер, Англия</t>
         </is>
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>42.2808, -83.7430</t>
+          <t>54.0466, -2.8007</t>
         </is>
       </c>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>Питтсбург, США</t>
+          <t>Оксфорд, Англия</t>
         </is>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>40.4406, -79.9959</t>
+          <t>51.7520, -1.2577</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>Мичиганский университет; Ориел-колледж, Оксфорд</t>
+          <t>Баллиол-колледж, Оксфорд</t>
         </is>
       </c>
       <c r="N68" s="14" t="inlineStr">
         <is>
-          <t>Миннесотский университет; Йельский университет; Питтсбургский университет</t>
+          <t>Оксфордский университет</t>
         </is>
       </c>
       <c r="O68" s="14" t="n"/>
       <c r="P68" s="14" t="n"/>
-      <c r="Q68" s="14" t="inlineStr">
-        <is>
-          <t>Роберт Брэндом</t>
-        </is>
-      </c>
+      <c r="Q68" s="14" t="n"/>
       <c r="R68" s="14" t="n"/>
       <c r="S68" s="14" t="inlineStr">
         <is>
-          <t>эпистемология; философия сознания; философия языка</t>
+          <t>философия обыденного языка; теория речевых актов</t>
         </is>
       </c>
       <c r="T68" s="14" t="inlineStr">
         <is>
-          <t>Американский философ, один из центральных представителей аналитической философии XX века. Известен критикой «мифа о данном» и разработкой идей о концептуальной роли языка и социальных практик.</t>
+          <t>Британский философ, один из основателей философии обыденного языка (ordinary language philosophy) и теории речевых актов. Автор работ «Как производить действия при помощи слов» («How to Do Things with Words») и «Чужое сознание» / «Оправдания» («A Plea for Excuses»). Известен методом пристального внимания к тому, как понятия реально используются в языке, — вместо того чтобы конструировать их значения априорно.</t>
         </is>
       </c>
       <c r="U68" s="14" t="inlineStr">
         <is>
-          <t>- Концептуальное мышление - Социальное посредничество - Язык - Прагматизм</t>
+          <t>- Теория речевых актов (speech acts) — «How to Do Things with Words» - Метод анализа обыденного языка через конкретные случаи употребления - (дозаполнить по мере чтения)</t>
         </is>
       </c>
       <c r="V68" s="14" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/sellars/</t>
+          <t>https://plato.stanford.edu/entries/austin-jl/</t>
         </is>
       </c>
       <c r="W68" s="14" t="n"/>
       <c r="X68" s="14" t="inlineStr">
         <is>
-          <t>Селларс появляется в обсуждении роли сообщества в формировании концептуального мышления. Он отвергает слишком простую модель, согласно которой внешний мир непосредственно порождает концептуальную систему отдельного индивида без посредничества семьи и общества. Уилсон связывает эту позицию с влиянием прагматизма, особенно Джона Дьюи, но сопротивляется превращению социального посредничества в доказательство того, что индивидуальная концептуализация не может быть связана с реальными объектами.</t>
+          <t>Остиновский метод — внимание к фактическому, ситуативному употреблению слов вместо абстрактных дефиниций — методологически близок общему проекту Уилсона: показать, что значения понятий формируются и «блуждают» именно в практике употребления. Возможный методологический союзник, а не оппонент.</t>
         </is>
       </c>
       <c r="Y68" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
-        </is>
-      </c>
-      <c r="Z68" s="14" t="n"/>
+          <t>гл. 1; гл. 3</t>
+        </is>
+      </c>
+      <c r="Z68" s="14" t="inlineStr">
+        <is>
+          <t>chapter_1_v; chapter_3_i</t>
+        </is>
+      </c>
       <c r="AA68" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/wilfrid-sellars</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/j-l-austin</t>
         </is>
       </c>
       <c r="AB68" s="14" t="inlineStr">
@@ -8254,86 +8262,94 @@
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>Вольфганг Хильдесхаймер</t>
+          <t>М. Х. Абрамс</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Wolfgang Hildesheimer</t>
+          <t>M. H. Abrams</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>немец</t>
+          <t>американец</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/hildesheimer.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/m_abrams.jpg</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>1916–1991</t>
+          <t>1912–2015</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>1916-12-09</t>
+          <t>1912-07-23</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>1991-08-21</t>
+          <t>2015-04-21</t>
         </is>
       </c>
       <c r="H69" s="14" t="n"/>
       <c r="I69" s="14" t="inlineStr">
         <is>
-          <t>Гамбург</t>
+          <t>Лонг-Бранч, Нью-Джерси, США</t>
         </is>
       </c>
       <c r="J69" s="14" t="inlineStr">
         <is>
-          <t>53.5511, 9.9937</t>
+          <t>40.3040, -73.9920</t>
         </is>
       </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>Поскьяво, Швейцария</t>
+          <t>Итака, Нью-Йорк, США</t>
         </is>
       </c>
       <c r="L69" s="14" t="inlineStr">
         <is>
-          <t>46.3245, 10.0573</t>
-        </is>
-      </c>
-      <c r="M69" s="14" t="n"/>
-      <c r="N69" s="14" t="n"/>
+          <t>42.4440, -76.5019</t>
+        </is>
+      </c>
+      <c r="M69" s="14" t="inlineStr">
+        <is>
+          <t>Гарвардский университет</t>
+        </is>
+      </c>
+      <c r="N69" s="14" t="inlineStr">
+        <is>
+          <t>Корнеллский университет</t>
+        </is>
+      </c>
       <c r="O69" s="14" t="n"/>
       <c r="P69" s="14" t="n"/>
       <c r="Q69" s="14" t="n"/>
       <c r="R69" s="14" t="n"/>
       <c r="S69" s="14" t="inlineStr">
         <is>
-          <t>проза; драматургия; биография</t>
+          <t>литературоведение; романтизм</t>
         </is>
       </c>
       <c r="T69" s="14" t="inlineStr">
         <is>
-          <t>Немецкий писатель, драматург и художник, автор биографии Моцарта (1982).</t>
+          <t>Американский литературовед, один из крупнейших исследователей английского романтизма.</t>
         </is>
       </c>
       <c r="U69" s="14" t="inlineStr">
         <is>
-          <t>- Mozart (1982), биография — цитата о полярности мажора и минора</t>
+          <t>- M. H. Abrams, Natural Supernaturalism (1973), p. 375 - M. H. Abrams, The Correspondent Breeze (1984) - Романтическое восприятие - Взаимодействие ума и мира</t>
         </is>
       </c>
       <c r="V69" s="14" t="n"/>
       <c r="W69" s="14" t="n"/>
       <c r="X69" s="14" t="inlineStr">
         <is>
-          <t>Уилсон цитирует Хильдесхаймера как пример музыковеда, который наивно принимает эмоциональный контраст мажора и минора за «чёткую полярность», подобную включению и выключению, не осознавая, что для значительной части населения земного шара это различие может проходить незамеченным. Эта цитата служит иллюстрацией старой эстетической традиции, которая абсолютизирует культурно-специфические музыкальные свойства.</t>
+          <t>Абрамс нужен Уилсону как историк романтической доктрины восприятия. Его формулировка показывает, что для романтического поэта жизненное положение человека зависит от того, как его ум взаимодействует с миром в акте восприятия.</t>
         </is>
       </c>
       <c r="Y69" s="14" t="inlineStr">
@@ -8343,12 +8359,12 @@
       </c>
       <c r="Z69" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_iv</t>
+          <t>chapter_2_vi</t>
         </is>
       </c>
       <c r="AA69" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/wolfgang-hildesheimer</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/m-h-abrams</t>
         </is>
       </c>
       <c r="AB69" s="14" t="inlineStr">
@@ -8361,12 +8377,12 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Эдвард Липпман</t>
+          <t>Уилфрид Селларс</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Edward Lippmann</t>
+          <t>Wilfrid Sellars</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -8376,59 +8392,87 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/lippmann.jpg.webp</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/w_sellars.jpg</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>1920-2010</t>
+          <t>1912–1989</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1912-05-20</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1989-07-02</t>
         </is>
       </c>
       <c r="H70" s="14" t="n"/>
-      <c r="I70" s="14" t="n"/>
-      <c r="J70" s="14" t="n"/>
-      <c r="K70" s="14" t="n"/>
-      <c r="L70" s="14" t="n"/>
-      <c r="M70" s="14" t="n"/>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>Анн-Арбор, Мичиган, США</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>42.2808, -83.7430</t>
+        </is>
+      </c>
+      <c r="K70" s="14" t="inlineStr">
+        <is>
+          <t>Питтсбург, США</t>
+        </is>
+      </c>
+      <c r="L70" s="14" t="inlineStr">
+        <is>
+          <t>40.4406, -79.9959</t>
+        </is>
+      </c>
+      <c r="M70" s="14" t="inlineStr">
+        <is>
+          <t>Мичиганский университет; Ориел-колледж, Оксфорд</t>
+        </is>
+      </c>
       <c r="N70" s="14" t="inlineStr">
         <is>
-          <t>Колумбийский университет</t>
+          <t>Миннесотский университет; Йельский университет; Питтсбургский университет</t>
         </is>
       </c>
       <c r="O70" s="14" t="n"/>
       <c r="P70" s="14" t="n"/>
-      <c r="Q70" s="14" t="n"/>
+      <c r="Q70" s="14" t="inlineStr">
+        <is>
+          <t>Роберт Брэндом</t>
+        </is>
+      </c>
       <c r="R70" s="14" t="n"/>
       <c r="S70" s="14" t="inlineStr">
         <is>
-          <t>музыковедение; музыкальная эстетика</t>
+          <t>эпистемология; философия сознания; философия языка</t>
         </is>
       </c>
       <c r="T70" s="14" t="inlineStr">
         <is>
-          <t>Американский музыковед и философ музыки. Автор работ по эстетике и теории музыки, исследовал связь музыкального восприятия с более широкими культурными и психологическими контекстами.</t>
+          <t>Американский философ, один из центральных представителей аналитической философии XX века. Известен критикой «мифа о данном» и разработкой идей о концептуальной роли языка и социальных практик.</t>
         </is>
       </c>
       <c r="U70" s="14" t="inlineStr">
         <is>
-          <t>- Musical Thought in Ancient Greece. New York: Columbia University Press. 1964. ISBN "ISBN (identifier)") 978-0231027267. - A Humanistic Philosophy of Music. New York: New York University Press. 1977. ISBN "ISBN (identifier)") 978-0814749739. - Musical Aesthetics: A Historical Reader. New York: Pendragon Press. 1986–90. (3 volumes) - A History of Western Musical Aesthetics. Lincoln: University of Nebraska Press. 1992. ISBN "ISBN (identifier)") 978-0803228634.</t>
-        </is>
-      </c>
-      <c r="V70" s="14" t="n"/>
+          <t>- Концептуальное мышление - Социальное посредничество - Язык - Прагматизм</t>
+        </is>
+      </c>
+      <c r="V70" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/sellars/</t>
+        </is>
+      </c>
       <c r="W70" s="14" t="n"/>
       <c r="X70" s="14" t="inlineStr">
         <is>
-          <t>Уилсон, вероятно, опирается на работы Липпмана (аналогично Хильдесхаймеру) для тезиса о том, что эстетическое восприятие не является чем-то неизменным. Вместе с кейсом Дарвина (charles-darwin) и примером скрипичной музыки восточного Кентукки (skripichnaya-muzyka-vostochnogo-kentukki), Липпман может служить авторитетным источником, показывающим, что наши "струны" музыкальной чувствительности "блуждают" под влиянием физиологических и культурных факторов.</t>
+          <t>Селларс появляется в обсуждении роли сообщества в формировании концептуального мышления. Он отвергает слишком простую модель, согласно которой внешний мир непосредственно порождает концептуальную систему отдельного индивида без посредничества семьи и общества. Уилсон связывает эту позицию с влиянием прагматизма, особенно Джона Дьюи, но сопротивляется превращению социального посредничества в доказательство того, что индивидуальная концептуализация не может быть связана с реальными объектами.</t>
         </is>
       </c>
       <c r="Y70" s="14" t="inlineStr">
@@ -8436,14 +8480,10 @@
           <t>гл. 2</t>
         </is>
       </c>
-      <c r="Z70" s="14" t="inlineStr">
-        <is>
-          <t>chapter_2_iv</t>
-        </is>
-      </c>
+      <c r="Z70" s="14" t="n"/>
       <c r="AA70" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/edward-lippmann</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/wilfrid-sellars</t>
         </is>
       </c>
       <c r="AB70" s="14" t="inlineStr">
@@ -8456,113 +8496,101 @@
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>Майкл Даммит</t>
+          <t>Вольфганг Хильдесхаймер</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Michael Dummett</t>
+          <t>Wolfgang Hildesheimer</t>
         </is>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
+          <t>немец</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/m_dummet.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/hildesheimer.jpg</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>1925–2011</t>
+          <t>1916–1991</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr">
         <is>
-          <t>1925-06-27</t>
+          <t>1916-12-09</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>2011-12-27</t>
+          <t>1991-08-21</t>
         </is>
       </c>
       <c r="H71" s="14" t="n"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>Лондон</t>
+          <t>Гамбург</t>
         </is>
       </c>
       <c r="J71" s="14" t="inlineStr">
         <is>
-          <t>51.5074, -0.1278</t>
+          <t>53.5511, 9.9937</t>
         </is>
       </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
-          <t>Оксфорд, Англия</t>
+          <t>Поскьяво, Швейцария</t>
         </is>
       </c>
       <c r="L71" s="14" t="inlineStr">
         <is>
-          <t>51.7520, -1.2577</t>
-        </is>
-      </c>
-      <c r="M71" s="14" t="inlineStr">
-        <is>
-          <t>Крайст-Чёрч, Оксфорд</t>
-        </is>
-      </c>
-      <c r="N71" s="14" t="inlineStr">
-        <is>
-          <t>Колледж Всех Душ, Оксфорд; Нью-колледж, Оксфорд</t>
-        </is>
-      </c>
+          <t>46.3245, 10.0573</t>
+        </is>
+      </c>
+      <c r="M71" s="14" t="n"/>
+      <c r="N71" s="14" t="n"/>
       <c r="O71" s="14" t="n"/>
       <c r="P71" s="14" t="n"/>
-      <c r="Q71" s="14" t="inlineStr">
-        <is>
-          <t>Криспин Райт</t>
-        </is>
-      </c>
+      <c r="Q71" s="14" t="n"/>
       <c r="R71" s="14" t="n"/>
       <c r="S71" s="14" t="inlineStr">
         <is>
-          <t>философия языка; философия математики; логика</t>
+          <t>проза; драматургия; биография</t>
         </is>
       </c>
       <c r="T71" s="14" t="inlineStr">
         <is>
-          <t>Британский философ, один из ведущих представителей послевоенной аналитической философии, профессор Оксфорда. Крупнейший исследователь и интерпретатор Фреге («Frege: Philosophy of Language», 1973; «Frege: Philosophy of Mathematics», 1991); разработчик семантического антиреализма — программы, согласно которой значение утверждения задаётся условиями его оправданного утверждения (assertibility), что ведёт к пересмотру классической логики в пользу интуиционистской. Известный борец с расизмом (активно участвовал в кампании против расовой дискриминации в Великобритании 1960-х).</t>
+          <t>Немецкий писатель, драматург и художник, автор биографии Моцарта (1982).</t>
         </is>
       </c>
       <c r="U71" s="14" t="inlineStr">
         <is>
-          <t>- Конкретных работ Даммита в этом фрагменте Уилсон не называет — только общее указание на его критику классической картины. Наиболее вероятные кандидаты — программные статьи по семантическому антиреализму («What is a Theory of Meaning?», 1975, 1976; «The Reality of the Past», 1969) и книга «The Logical Basis of Metaphysics» (1991). - Michael Dummett, “What is a Theory of Meaning?-II” // Truth and Meaning, Gareth Evans and John McDowell, eds. (Oxford: Oxford University Press, 1978), 137.</t>
+          <t>- Mozart (1982), биография — цитата о полярности мажора и минора</t>
         </is>
       </c>
       <c r="V71" s="14" t="n"/>
       <c r="W71" s="14" t="n"/>
       <c r="X71" s="14" t="inlineStr">
         <is>
-          <t>Упомянут в подразделе (viii) как один из трёх современных критиков klassicheskaya-kartina-kontseptsiy (вместе с Куайном и Брэндомом; см. willard-quine, robert-brandom), чья мотивация — «выделить точный способ, которым классическая картина искажает разумный взгляд на человеческие способности».</t>
+          <t>Уилсон цитирует Хильдесхаймера как пример музыковеда, который наивно принимает эмоциональный контраст мажора и минора за «чёткую полярность», подобную включению и выключению, не осознавая, что для значительной части населения земного шара это различие может проходить незамеченным. Эта цитата служит иллюстрацией старой эстетической традиции, которая абсолютизирует культурно-специфические музыкальные свойства.</t>
         </is>
       </c>
       <c r="Y71" s="14" t="inlineStr">
         <is>
-          <t>гл. 1; гл. 3</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z71" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_viii; chapter_3_iii</t>
+          <t>chapter_2_iv</t>
         </is>
       </c>
       <c r="AA71" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/michael-dummett</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/wolfgang-hildesheimer</t>
         </is>
       </c>
       <c r="AB71" s="14" t="inlineStr">
@@ -8575,12 +8603,12 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Хилари Патнэм</t>
+          <t>Эдвард Липпман</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Hilary Putnam</t>
+          <t>Edward Lippmann</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -8590,106 +8618,74 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/putnam.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/lippmann.jpg.webp</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>1926–2016</t>
+          <t>1920-2010</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>1926-07-31</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>2016-03-13</t>
-        </is>
-      </c>
-      <c r="H72" s="14" t="inlineStr">
-        <is>
-          <t>мезотелиома</t>
-        </is>
-      </c>
-      <c r="I72" s="14" t="inlineStr">
-        <is>
-          <t>Чикаго, США</t>
-        </is>
-      </c>
-      <c r="J72" s="14" t="inlineStr">
-        <is>
-          <t>41.8781, -87.6298</t>
-        </is>
-      </c>
-      <c r="K72" s="14" t="inlineStr">
-        <is>
-          <t>Арлингтон, Массачусетс, США</t>
-        </is>
-      </c>
-      <c r="L72" s="14" t="inlineStr">
-        <is>
-          <t>42.4154, -71.1565</t>
-        </is>
-      </c>
-      <c r="M72" s="14" t="inlineStr">
-        <is>
-          <t>Пенсильванский университет; Калифорнийский университет в Лос-Анджелесе</t>
-        </is>
-      </c>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="14" t="n"/>
+      <c r="L72" s="14" t="n"/>
+      <c r="M72" s="14" t="n"/>
       <c r="N72" s="14" t="inlineStr">
         <is>
-          <t>Принстонский университет; Массачусетский технологический институт; Гарвардский университет</t>
+          <t>Колумбийский университет</t>
         </is>
       </c>
       <c r="O72" s="14" t="n"/>
-      <c r="P72" s="14" t="inlineStr">
-        <is>
-          <t>Джерри Фодор</t>
-        </is>
-      </c>
-      <c r="Q72" s="14" t="inlineStr">
-        <is>
-          <t>Уиллард Куайн</t>
-        </is>
-      </c>
+      <c r="P72" s="14" t="n"/>
+      <c r="Q72" s="14" t="n"/>
       <c r="R72" s="14" t="n"/>
       <c r="S72" s="14" t="inlineStr">
         <is>
-          <t>философия языка; философия сознания; философия науки</t>
+          <t>музыковедение; музыкальная эстетика</t>
         </is>
       </c>
       <c r="T72" s="14" t="inlineStr">
         <is>
-          <t>Американский философ, один из наиболее влиятельных аналитических философов второй половины XX века. Работал в философии языка, сознания и науки; известен мысленным экспериментом «Земля-двойник» и тезисом «значение не в голове», функционализмом в философии сознания, а также сменой ряда собственных позиций на протяжении карьеры (от научного реализма к внутреннему реализму и далее к прагматическому реализму).</t>
+          <t>Американский музыковед и философ музыки. Автор работ по эстетике и теории музыки, исследовал связь музыкального восприятия с более широкими культурными и психологическими контекстами.</t>
         </is>
       </c>
       <c r="U72" s="14" t="inlineStr">
         <is>
-          <t>- Совместная работа пришлась примерно на конец 1960-х – 1976 год: Уилсон закончил бакалавриат в Университете Вашингтона в 1969-м, затем поступил в докторантуру Гарварда, где научным руководителем был Патнэм, и защитил диссертацию в 1976 году. - Работы Патнэма, которые напрямую связаны с тематикой "Блуждающих значений": 1. Putnam H. Is Semantic Possible?//Metaphilosophy, 1970, Т. 1, N 3, C. 187-201. 2. Putnam H. The Meaning of «Meaning»//Minnesota Studies in the Philosophy of Science, 1975, Т. 7, C. 131-193.</t>
+          <t>- Musical Thought in Ancient Greece. New York: Columbia University Press. 1964. ISBN "ISBN (identifier)") 978-0231027267. - A Humanistic Philosophy of Music. New York: New York University Press. 1977. ISBN "ISBN (identifier)") 978-0814749739. - Musical Aesthetics: A Historical Reader. New York: Pendragon Press. 1986–90. (3 volumes) - A History of Western Musical Aesthetics. Lincoln: University of Nebraska Press. 1992. ISBN "ISBN (identifier)") 978-0803228634.</t>
         </is>
       </c>
       <c r="V72" s="14" t="n"/>
       <c r="W72" s="14" t="n"/>
       <c r="X72" s="14" t="inlineStr">
         <is>
-          <t>Уилсон прямо пишет в предисловии, что его конкретный фокус на предикатах и понятиях вырос из его собственной дипломной (диссертационной) работы, написанной под руководством Патнэма, а также из работ Патнэма того периода.</t>
+          <t>Уилсон, вероятно, опирается на работы Липпмана (аналогично Хильдесхаймеру) для тезиса о том, что эстетическое восприятие не является чем-то неизменным. Вместе с кейсом Дарвина (charles-darwin) и примером скрипичной музыки восточного Кентукки (skripichnaya-muzyka-vostochnogo-kentukki), Липпман может служить авторитетным источником, показывающим, что наши "струны" музыкальной чувствительности "блуждают" под влиянием физиологических и культурных факторов.</t>
         </is>
       </c>
       <c r="Y72" s="14" t="inlineStr">
         <is>
-          <t>предисловие</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z72" s="14" t="inlineStr">
         <is>
-          <t>predislovie</t>
+          <t>chapter_2_iv</t>
         </is>
       </c>
       <c r="AA72" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/hilary-putnam</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/edward-lippmann</t>
         </is>
       </c>
       <c r="AB72" s="14" t="inlineStr">
@@ -8702,117 +8698,113 @@
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>Джерри Фодор</t>
+          <t>Майкл Даммит</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>Jerry Fodor</t>
+          <t>Michael Dummett</t>
         </is>
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>британец</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j-fodor.png</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/m_dummet.jpg</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>1935–2017</t>
+          <t>1925–2011</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>1935-04-22</t>
+          <t>1925-06-27</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
-        </is>
-      </c>
-      <c r="H73" s="14" t="inlineStr">
-        <is>
-          <t>болезнь Паркинсона, последствия инсульта</t>
-        </is>
-      </c>
+          <t>2011-12-27</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="n"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>Нью-Йорк, США</t>
+          <t>Лондон</t>
         </is>
       </c>
       <c r="J73" s="14" t="inlineStr">
         <is>
-          <t>40.7128, -74.0060</t>
+          <t>51.5074, -0.1278</t>
         </is>
       </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>Нью-Йорк, США</t>
+          <t>Оксфорд, Англия</t>
         </is>
       </c>
       <c r="L73" s="14" t="inlineStr">
         <is>
-          <t>40.7128, -74.0060</t>
+          <t>51.7520, -1.2577</t>
         </is>
       </c>
       <c r="M73" s="14" t="inlineStr">
         <is>
-          <t>Колумбийский колледж; Принстонский университет</t>
+          <t>Крайст-Чёрч, Оксфорд</t>
         </is>
       </c>
       <c r="N73" s="14" t="inlineStr">
         <is>
-          <t>Массачусетский технологический институт; Ратгерский университет</t>
-        </is>
-      </c>
-      <c r="O73" s="14" t="inlineStr">
-        <is>
-          <t>Хилари Патнэм</t>
-        </is>
-      </c>
+          <t>Колледж Всех Душ, Оксфорд; Нью-колледж, Оксфорд</t>
+        </is>
+      </c>
+      <c r="O73" s="14" t="n"/>
       <c r="P73" s="14" t="n"/>
-      <c r="Q73" s="14" t="n"/>
+      <c r="Q73" s="14" t="inlineStr">
+        <is>
+          <t>Криспин Райт</t>
+        </is>
+      </c>
       <c r="R73" s="14" t="n"/>
       <c r="S73" s="14" t="inlineStr">
         <is>
-          <t>философия сознания; когнитивная наука</t>
+          <t>философия языка; философия математики; логика</t>
         </is>
       </c>
       <c r="T73" s="14" t="inlineStr">
         <is>
-          <t>Американский философ и когнитивист (1935–2017), автор теории языка мысли и концептуального атомизма. Основная работа, на которую ссылается Уилсон: Concepts: Where Cognitive Science Went Wrong (Oxford UP, 1998).</t>
+          <t>Британский философ, один из ведущих представителей послевоенной аналитической философии, профессор Оксфорда. Крупнейший исследователь и интерпретатор Фреге («Frege: Philosophy of Language», 1973; «Frege: Philosophy of Mathematics», 1991); разработчик семантического антиреализма — программы, согласно которой значение утверждения задаётся условиями его оправданного утверждения (assertibility), что ведёт к пересмотру классической логики в пользу интуиционистской. Известный борец с расизмом (активно участвовал в кампании против расовой дискриминации в Великобритании 1960-х).</t>
         </is>
       </c>
       <c r="U73" s="14" t="inlineStr">
         <is>
-          <t>- J. Fodor, Concepts: Where Cognitive Science Went Wrong (Oxford UP, 1998)</t>
+          <t>- Конкретных работ Даммита в этом фрагменте Уилсон не называет — только общее указание на его критику классической картины. Наиболее вероятные кандидаты — программные статьи по семантическому антиреализму («What is a Theory of Meaning?», 1975, 1976; «The Reality of the Past», 1969) и книга «The Logical Basis of Metaphysics» (1991). - Michael Dummett, “What is a Theory of Meaning?-II” // Truth and Meaning, Gareth Evans and John McDowell, eds. (Oxford: Oxford University Press, 1978), 137.</t>
         </is>
       </c>
       <c r="V73" s="14" t="n"/>
       <c r="W73" s="14" t="n"/>
       <c r="X73" s="14" t="inlineStr">
         <is>
-          <t>Книга Фодора приводится как образец обсуждения, «сосредоточенного исключительно» на генерических примерах: «быть собакой» и «быть дверной ручкой». По мнению Уилсона, ни один из таких образцов вряд ли выявит тонкие напряжения «содержания», важные для его исследования, и такая избирательность свидетельствует об «относительной слепоте к фундаментальным вопросам».</t>
+          <t>Упомянут в подразделе (viii) как один из трёх современных критиков klassicheskaya-kartina-kontseptsiy (вместе с Куайном и Брэндомом; см. willard-quine, robert-brandom), чья мотивация — «выделить точный способ, которым классическая картина искажает разумный взгляд на человеческие способности».</t>
         </is>
       </c>
       <c r="Y73" s="14" t="inlineStr">
         <is>
-          <t>гл. 3</t>
+          <t>гл. 1; гл. 3</t>
         </is>
       </c>
       <c r="Z73" s="14" t="inlineStr">
         <is>
-          <t>chapter_3_iv</t>
+          <t>chapter_1_viii; chapter_3_iii</t>
         </is>
       </c>
       <c r="AA73" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/dzherri-fodor</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/michael-dummett</t>
         </is>
       </c>
       <c r="AB73" s="14" t="inlineStr">
@@ -8825,12 +8817,12 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Дэвид Э. Уизнант</t>
+          <t>Хилари Патнэм</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>David E. Whisnant</t>
+          <t>Hilary Putnam</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -8840,74 +8832,106 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/d-whisnant.webp</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/putnam.jpg</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>1938–2024</t>
+          <t>1926–2016</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1926-07-31</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="H74" s="14" t="n"/>
-      <c r="I74" s="14" t="n"/>
-      <c r="J74" s="14" t="n"/>
-      <c r="K74" s="14" t="n"/>
-      <c r="L74" s="14" t="n"/>
-      <c r="M74" s="14" t="n"/>
+          <t>2016-03-13</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>мезотелиома</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>Чикаго, США</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>41.8781, -87.6298</t>
+        </is>
+      </c>
+      <c r="K74" s="14" t="inlineStr">
+        <is>
+          <t>Арлингтон, Массачусетс, США</t>
+        </is>
+      </c>
+      <c r="L74" s="14" t="inlineStr">
+        <is>
+          <t>42.4154, -71.1565</t>
+        </is>
+      </c>
+      <c r="M74" s="14" t="inlineStr">
+        <is>
+          <t>Пенсильванский университет; Калифорнийский университет в Лос-Анджелесе</t>
+        </is>
+      </c>
       <c r="N74" s="14" t="inlineStr">
         <is>
-          <t>Университет Северной Каролины в Чапел-Хилле</t>
+          <t>Принстонский университет; Массачусетский технологический институт; Гарвардский университет</t>
         </is>
       </c>
       <c r="O74" s="14" t="n"/>
-      <c r="P74" s="14" t="n"/>
-      <c r="Q74" s="14" t="n"/>
+      <c r="P74" s="14" t="inlineStr">
+        <is>
+          <t>Джерри Фодор</t>
+        </is>
+      </c>
+      <c r="Q74" s="14" t="inlineStr">
+        <is>
+          <t>Уиллард Куайн</t>
+        </is>
+      </c>
       <c r="R74" s="14" t="n"/>
       <c r="S74" s="14" t="inlineStr">
         <is>
-          <t>американистика; фольклористика; культурная политика</t>
+          <t>философия языка; философия сознания; философия науки</t>
         </is>
       </c>
       <c r="T74" s="14" t="inlineStr">
         <is>
-          <t>Американский исследователь фольклора и культурной политики, автор книги All That Is Native and Fine (1983).</t>
+          <t>Американский философ, один из наиболее влиятельных аналитических философов второй половины XX века. Работал в философии языка, сознания и науки; известен мысленным экспериментом «Земля-двойник» и тезисом «значение не в голове», функционализмом в философии сознания, а также сменой ряда собственных позиций на протяжении карьеры (от научного реализма к внутреннему реализму и далее к прагматическому реализму).</t>
         </is>
       </c>
       <c r="U74" s="14" t="inlineStr">
         <is>
-          <t>- David E. Whisnant, All That Is Native and Fine (Chapel Hill: University of North Carolina Press, 1983), pp. xiii–xiv, 260–261 - Культурная «инаковость» (otherness) - Политика культуры - Сохранение и возрождение культуры - Колониальное подчинение - Освоение ресурсов - Классовое неравенство</t>
+          <t>- Совместная работа пришлась примерно на конец 1960-х – 1976 год: Уилсон закончил бакалавриат в Университете Вашингтона в 1969-м, затем поступил в докторантуру Гарварда, где научным руководителем был Патнэм, и защитил диссертацию в 1976 году. - Работы Патнэма, которые напрямую связаны с тематикой "Блуждающих значений": 1. Putnam H. Is Semantic Possible?//Metaphilosophy, 1970, Т. 1, N 3, C. 187-201. 2. Putnam H. The Meaning of «Meaning»//Minnesota Studies in the Philosophy of Science, 1975, Т. 7, C. 131-193.</t>
         </is>
       </c>
       <c r="V74" s="14" t="n"/>
       <c r="W74" s="14" t="n"/>
       <c r="X74" s="14" t="inlineStr">
         <is>
-          <t>Уизнант рассматривает фольклористские практики через проблему культурной «инаковости» и политики культуры. Его критика показывает, как слова вроде «культура», «сохранение» и «возрождение» могут скрывать более глубокие социальные отношения — колониальное подчинение, освоение ресурсов и классовое неравенство. Уилсон соглашается с рядом конкретных критических замечаний Уизнанта, но отвергает вывод о том, что вся система музыкальных классификаций безнадёжно испорчена социальными и капиталистическими «шорами».</t>
+          <t>Уилсон прямо пишет в предисловии, что его конкретный фокус на предикатах и понятиях вырос из его собственной дипломной (диссертационной) работы, написанной под руководством Патнэма, а также из работ Патнэма того периода.</t>
         </is>
       </c>
       <c r="Y74" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>предисловие</t>
         </is>
       </c>
       <c r="Z74" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_v</t>
+          <t>predislovie</t>
         </is>
       </c>
       <c r="AA74" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/david-whisnant</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/hilary-putnam</t>
         </is>
       </c>
       <c r="AB74" s="14" t="inlineStr">
@@ -8920,69 +8944,117 @@
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>Чарльз Маркс</t>
+          <t>Джерри Фодор</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>Charles E. Marks</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="n"/>
+          <t>Jerry Fodor</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>американец</t>
+        </is>
+      </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/ch_marks.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j-fodor.png</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>ок. 1940 (оценка, не подтверждено первоисточником) – 2022</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="n"/>
-      <c r="G75" s="14" t="n"/>
-      <c r="H75" s="14" t="n"/>
-      <c r="I75" s="14" t="n"/>
-      <c r="J75" s="14" t="n"/>
-      <c r="K75" s="14" t="n"/>
-      <c r="L75" s="14" t="n"/>
-      <c r="M75" s="14" t="n"/>
-      <c r="N75" s="14" t="n"/>
-      <c r="O75" s="14" t="n"/>
+          <t>1935–2017</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>1935-04-22</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>2017-11-29</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>болезнь Паркинсона, последствия инсульта</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>Нью-Йорк, США</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>40.7128, -74.0060</t>
+        </is>
+      </c>
+      <c r="K75" s="14" t="inlineStr">
+        <is>
+          <t>Нью-Йорк, США</t>
+        </is>
+      </c>
+      <c r="L75" s="14" t="inlineStr">
+        <is>
+          <t>40.7128, -74.0060</t>
+        </is>
+      </c>
+      <c r="M75" s="14" t="inlineStr">
+        <is>
+          <t>Колумбийский колледж; Принстонский университет</t>
+        </is>
+      </c>
+      <c r="N75" s="14" t="inlineStr">
+        <is>
+          <t>Массачусетский технологический институт; Ратгерский университет</t>
+        </is>
+      </c>
+      <c r="O75" s="14" t="inlineStr">
+        <is>
+          <t>Хилари Патнэм</t>
+        </is>
+      </c>
       <c r="P75" s="14" t="n"/>
       <c r="Q75" s="14" t="n"/>
       <c r="R75" s="14" t="n"/>
-      <c r="S75" s="14" t="n"/>
+      <c r="S75" s="14" t="inlineStr">
+        <is>
+          <t>философия сознания; когнитивная наука</t>
+        </is>
+      </c>
       <c r="T75" s="14" t="inlineStr">
         <is>
-          <t>Профессор философии Университета Вашингтона (Сиэтл): пришёл на факультет в 1966 году, был его деканом в 1980–1982-м, вышел на пенсию в 2003-м, умер 18 апреля 2022 года в Сиэтле (согласно некрологу Reed College). Точный год рождения в надёжных источниках не указан . Б. Аспирантуру проходил в Корнеллском университете (поступил в 1962-м, защитился только в 1972-м), до этого учился в Рид-колледже под руководством Марвина Левича и Хьюго Бедо, где занимался этикой. В Корнелле переключился на философию сознания — под влиянием состава факультета (Сидни Шумейкер, Кит Доннеллан, Норман Малкольм, Дэвид Сакс). Преподавал философию сознания и историю философии; любимым дидактическим приёмом было разбирать со студентами эксперименты Сперри и Газзаниги на пациентах с рассечённым мозолистым телом как повод для философских головоломок о сознании.</t>
+          <t>Американский философ и когнитивист (1935–2017), автор теории языка мысли и концептуального атомизма. Основная работа, на которую ссылается Уилсон: Concepts: Where Cognitive Science Went Wrong (Oxford UP, 1998).</t>
         </is>
       </c>
       <c r="U75" s="14" t="inlineStr">
         <is>
-          <t>- Прямых работ Маркса, на которые бы ссылался Уилсон, не выявлено — роль чисто педагогическая/личная, не библиографическая - Собственная область Маркса — философия сознания (в частности, философские следствия экспериментов на пациентах с расщеплённым мозгом)</t>
+          <t>- J. Fodor, Concepts: Where Cognitive Science Went Wrong (Oxford UP, 1998)</t>
         </is>
       </c>
       <c r="V75" s="14" t="n"/>
       <c r="W75" s="14" t="n"/>
       <c r="X75" s="14" t="inlineStr">
         <is>
-          <t>Не философский источник содержания, а личный учитель на раннем этапе: Уилсон пишет в предисловии, что в молодости много читал Витгенштейна «под умелым руководством» (able tutelage) Чарльза Маркса, и находит примечательным, что сам он с Витгенштейном часто «блуждают по схожим темам» в философских странствиях (см. карточку ludwig-wittgenstein). Поскольку Маркс пришёл в Университет Вашингтона в 1966 году, а Уилсон получил там бакалавриат в 1969-м, речь, судя по всему, идёт именно об университетском (не аспирантском) периоде — то есть Маркс был для Уилсона учителем-бакалаврского уровня, предшествовавшим гарвардскому научному руководству Патнэма (см. hilary-putnam). Специализация самого Маркса — философия сознания, а не история аналитической философии языка; собственно витгенштейноведом он, судя по всему, не был. Зато среди его учителей в Корнелле был Норман Малкольм — один из ближайших личных учеников и друзей самого Витгенштейна в Кембридже, автор мемуарной книги о нём. Если Маркс действительно перенял интерес к Витгенштейну через Малкольма (что напрямую источниками не подтверждено, только через совпадение по месту и времени учёбы), то перед нами двухступенчатая личная передача: Витгенштейн → Малкольм (личный ученик) → Маркс (аспирант в Корнелле в те же годы) → Уилсон (студент, читающий Витгенштейна под руководством Маркса). Это интересная гипотеза, требующая специально исследования.</t>
+          <t>Книга Фодора приводится как образец обсуждения, «сосредоточенного исключительно» на генерических примерах: «быть собакой» и «быть дверной ручкой». По мнению Уилсона, ни один из таких образцов вряд ли выявит тонкие напряжения «содержания», важные для его исследования, и такая избирательность свидетельствует об «относительной слепоте к фундаментальным вопросам».</t>
         </is>
       </c>
       <c r="Y75" s="14" t="inlineStr">
         <is>
-          <t>предисловие</t>
+          <t>гл. 3</t>
         </is>
       </c>
       <c r="Z75" s="14" t="inlineStr">
         <is>
-          <t>predislovie</t>
+          <t>chapter_3_iv</t>
         </is>
       </c>
       <c r="AA75" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/charles-marks</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/dzherri-fodor</t>
         </is>
       </c>
       <c r="AB75" s="14" t="inlineStr">
@@ -8995,12 +9067,12 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>Пол Дж. Нахин</t>
+          <t>Дэвид Э. Уизнант</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>Paul J. Nahin</t>
+          <t>David E. Whisnant</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -9010,33 +9082,33 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/nahin.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/d-whisnant.webp</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1938–2024</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>1940-11-26</t>
-        </is>
-      </c>
-      <c r="G76" s="14" t="n"/>
+          <t>1938</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="H76" s="14" t="n"/>
       <c r="I76" s="14" t="n"/>
       <c r="J76" s="14" t="n"/>
       <c r="K76" s="14" t="n"/>
       <c r="L76" s="14" t="n"/>
-      <c r="M76" s="14" t="inlineStr">
-        <is>
-          <t>Стэнфордский университет; Калифорнийский технологический институт; Калифорнийский университет в Ирвайне</t>
-        </is>
-      </c>
+      <c r="M76" s="14" t="n"/>
       <c r="N76" s="14" t="inlineStr">
         <is>
-          <t>Университет Нью-Гэмпшира</t>
+          <t>Университет Северной Каролины в Чапел-Хилле</t>
         </is>
       </c>
       <c r="O76" s="14" t="n"/>
@@ -9045,39 +9117,39 @@
       <c r="R76" s="14" t="n"/>
       <c r="S76" s="14" t="inlineStr">
         <is>
-          <t>электротехника; история науки; популяризация математики</t>
+          <t>американистика; фольклористика; культурная политика</t>
         </is>
       </c>
       <c r="T76" s="14" t="inlineStr">
         <is>
-          <t>Родился 26 ноября 1940 года в Калифорнии, закончил школу в 1958-м, а затем получил степень бакалавра в Стэнфорде (1962), магистра — в Калтехе (1963) и докторскую степень — в Университете Калифорнии в Ирвайне (1972), всё — по электротехнике. До перехода в академию несколько лет проработал инженером-разработчиком цифровой логики и радиолокационных систем в аэрокосмической отрасли Южной Калифорнии. Преподавал в Харви Мадд Колледже, Университете Вирджинии и Военно-морской аспирантуре в Монтерее, а с 2004 года — почётный профессор электротехники Университета Нью-Гэмпшира. Помимо биографии Хевисайда, написал научно-популярные биографии Джорджа Буля и Клода Шеннона (совместную — под названием «The Logician and the Engineer»), ряд книг по истории математических констант и понятий (формула Эйлера, дзета-функция Римана, мнимая единица), а также несколько книг о физике и философских парадоксах путешествий во времени. Также опубликовал около двух десятков научно-фантастических рассказов в журналах Analog, Omni и Twilight Zone. В 1979 году получил первую премию Harry Rowe Mimno от IEEE, а в 2017-м — премию Chandler Davis за выдающийся научно-популярный стиль изложения математики.</t>
+          <t>Американский исследователь фольклора и культурной политики, автор книги All That Is Native and Fine (1983).</t>
         </is>
       </c>
       <c r="U76" s="14" t="inlineStr">
         <is>
-          <t>1. Nahin P.J. Oliver Heaviside: The Life, Work, and Times of an Electrical Genius of the Victorian Age : A Johns Hopkins paperback. – Johns Hopkins University Press, 2002.</t>
+          <t>- David E. Whisnant, All That Is Native and Fine (Chapel Hill: University of North Carolina Press, 1983), pp. xiii–xiv, 260–261 - Культурная «инаковость» (otherness) - Политика культуры - Сохранение и возрождение культуры - Колониальное подчинение - Освоение ресурсов - Классовое неравенство</t>
         </is>
       </c>
       <c r="V76" s="14" t="n"/>
       <c r="W76" s="14" t="n"/>
       <c r="X76" s="14" t="inlineStr">
         <is>
-          <t>Уилсон уделяет особое внимание биографии Хевисайда, написанной Полом Нахином как исторического источника при описании конфликта Хевисайда с академическим математическим сообществом</t>
+          <t>Уизнант рассматривает фольклористские практики через проблему культурной «инаковости» и политики культуры. Его критика показывает, как слова вроде «культура», «сохранение» и «возрождение» могут скрывать более глубокие социальные отношения — колониальное подчинение, освоение ресурсов и классовое неравенство. Уилсон соглашается с рядом конкретных критических замечаний Уизнанта, но отвергает вывод о том, что вся система музыкальных классификаций безнадёжно испорчена социальными и капиталистическими «шорами».</t>
         </is>
       </c>
       <c r="Y76" s="14" t="inlineStr">
         <is>
-          <t>предисловие</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z76" s="14" t="inlineStr">
         <is>
-          <t>predislovie</t>
+          <t>chapter_2_v</t>
         </is>
       </c>
       <c r="AA76" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/p-j-nahin</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/david-whisnant</t>
         </is>
       </c>
       <c r="AB76" s="14" t="inlineStr">
@@ -9090,125 +9162,69 @@
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>Дэвид Льюис</t>
+          <t>Чарльз Маркс</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>David Lewis</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>американец</t>
-        </is>
-      </c>
+          <t>Charles E. Marks</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="n"/>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/d_lewis.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/ch_marks.jpg</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>1941–2001</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
-        <is>
-          <t>1941-09-28</t>
-        </is>
-      </c>
-      <c r="G77" s="14" t="inlineStr">
-        <is>
-          <t>2001-10-14</t>
-        </is>
-      </c>
-      <c r="H77" s="14" t="inlineStr">
-        <is>
-          <t>осложнения сахарного диабета</t>
-        </is>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
-        <is>
-          <t>Оберлин, Огайо, США</t>
-        </is>
-      </c>
-      <c r="J77" s="14" t="inlineStr">
-        <is>
-          <t>41.2939, -82.2174</t>
-        </is>
-      </c>
-      <c r="K77" s="14" t="inlineStr">
-        <is>
-          <t>Принстон, Нью-Джерси, США</t>
-        </is>
-      </c>
-      <c r="L77" s="14" t="inlineStr">
-        <is>
-          <t>40.3573, -74.6672</t>
-        </is>
-      </c>
-      <c r="M77" s="14" t="inlineStr">
-        <is>
-          <t>Суортмор-колледж; Гарвардский университет</t>
-        </is>
-      </c>
-      <c r="N77" s="14" t="inlineStr">
-        <is>
-          <t>Калифорнийский университет в Лос-Анджелесе; Принстонский университет</t>
-        </is>
-      </c>
-      <c r="O77" s="14" t="inlineStr">
-        <is>
-          <t>Уиллард Куайн</t>
-        </is>
-      </c>
-      <c r="P77" s="14" t="inlineStr">
-        <is>
-          <t>Роберт Брэндом</t>
-        </is>
-      </c>
+          <t>ок. 1940 (оценка, не подтверждено первоисточником) – 2022</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="n"/>
+      <c r="G77" s="14" t="n"/>
+      <c r="H77" s="14" t="n"/>
+      <c r="I77" s="14" t="n"/>
+      <c r="J77" s="14" t="n"/>
+      <c r="K77" s="14" t="n"/>
+      <c r="L77" s="14" t="n"/>
+      <c r="M77" s="14" t="n"/>
+      <c r="N77" s="14" t="n"/>
+      <c r="O77" s="14" t="n"/>
+      <c r="P77" s="14" t="n"/>
       <c r="Q77" s="14" t="n"/>
       <c r="R77" s="14" t="n"/>
-      <c r="S77" s="14" t="inlineStr">
-        <is>
-          <t>метафизика; философия языка; модальная логика</t>
-        </is>
-      </c>
+      <c r="S77" s="14" t="n"/>
       <c r="T77" s="14" t="inlineStr">
         <is>
-          <t>Американский философ, один из самых влиятельных аналитических метафизиков второй половины XX века. Профессор Принстонского университета, ученик Куайна. Известен доктриной модального реализма — тезисом, что все логически возможные миры существуют реально, наравне с нашим (главное изложение: «On the Plurality of Worlds», 1986); работами в философии сознания (функционализм), философии науки, теории каузальности (каузальность через контрфактуалы), теории игр и конвенций языка («Convention», 1969).</t>
+          <t>Профессор философии Университета Вашингтона (Сиэтл): пришёл на факультет в 1966 году, был его деканом в 1980–1982-м, вышел на пенсию в 2003-м, умер 18 апреля 2022 года в Сиэтле (согласно некрологу Reed College). Точный год рождения в надёжных источниках не указан . Б. Аспирантуру проходил в Корнеллском университете (поступил в 1962-м, защитился только в 1972-м), до этого учился в Рид-колледже под руководством Марвина Левича и Хьюго Бедо, где занимался этикой. В Корнелле переключился на философию сознания — под влиянием состава факультета (Сидни Шумейкер, Кит Доннеллан, Норман Малкольм, Дэвид Сакс). Преподавал философию сознания и историю философии; любимым дидактическим приёмом было разбирать со студентами эксперименты Сперри и Газзаниги на пациентах с рассечённым мозолистым телом как повод для философских головоломок о сознании.</t>
         </is>
       </c>
       <c r="U77" s="14" t="inlineStr">
         <is>
-          <t>- В (viii) конкретных работ не назвал — только общее указание, что Льюис укладывается в классическую картину. Обещанная точка сверки — приложение к главе 3.</t>
-        </is>
-      </c>
-      <c r="V77" s="14" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/david-lewis/</t>
-        </is>
-      </c>
+          <t>- Прямых работ Маркса, на которые бы ссылался Уилсон, не выявлено — роль чисто педагогическая/личная, не библиографическая - Собственная область Маркса — философия сознания (в частности, философские следствия экспериментов на пациентах с расщеплённым мозгом)</t>
+        </is>
+      </c>
+      <c r="V77" s="14" t="n"/>
       <c r="W77" s="14" t="n"/>
       <c r="X77" s="14" t="inlineStr">
         <is>
-          <t>Упомянут в подразделе (viii) как редкий пример современного философа, чей взгляд на концепции Уилсон расценивает как «полностью классический по качеству» — то есть как «тонкую настройку Рассела» (bertrand-russell) в рамках klassicheskaya-kartina-kontseptsiy. Уилсон прямо отмечает, что использовал некоторые идеи Льюиса в приложении к главе 3 (там, где систематизирует тезисы классической картины). В отличие от Куайна , Даммита и Брэндома, Льюис представлен как более утончённый продолжатель.</t>
+          <t>Не философский источник содержания, а личный учитель на раннем этапе: Уилсон пишет в предисловии, что в молодости много читал Витгенштейна «под умелым руководством» (able tutelage) Чарльза Маркса, и находит примечательным, что сам он с Витгенштейном часто «блуждают по схожим темам» в философских странствиях (см. карточку ludwig-wittgenstein). Поскольку Маркс пришёл в Университет Вашингтона в 1966 году, а Уилсон получил там бакалавриат в 1969-м, речь, судя по всему, идёт именно об университетском (не аспирантском) периоде — то есть Маркс был для Уилсона учителем-бакалаврского уровня, предшествовавшим гарвардскому научному руководству Патнэма (см. hilary-putnam). Специализация самого Маркса — философия сознания, а не история аналитической философии языка; собственно витгенштейноведом он, судя по всему, не был. Зато среди его учителей в Корнелле был Норман Малкольм — один из ближайших личных учеников и друзей самого Витгенштейна в Кембридже, автор мемуарной книги о нём. Если Маркс действительно перенял интерес к Витгенштейну через Малкольма (что напрямую источниками не подтверждено, только через совпадение по месту и времени учёбы), то перед нами двухступенчатая личная передача: Витгенштейн → Малкольм (личный ученик) → Маркс (аспирант в Корнелле в те же годы) → Уилсон (студент, читающий Витгенштейна под руководством Маркса). Это интересная гипотеза, требующая специально исследования.</t>
         </is>
       </c>
       <c r="Y77" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>предисловие</t>
         </is>
       </c>
       <c r="Z77" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_viii</t>
+          <t>predislovie</t>
         </is>
       </c>
       <c r="AA77" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/david-lewis</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/charles-marks</t>
         </is>
       </c>
       <c r="AB77" s="14" t="inlineStr">
@@ -9221,32 +9237,32 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Криспин Райт</t>
+          <t>Пол Дж. Нахин</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Crispin Wright</t>
+          <t>Paul J. Nahin</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>британец</t>
+          <t>американец</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/c_wright.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/nahin.jpg</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>1942–</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1940-11-26</t>
         </is>
       </c>
       <c r="G78" s="14" t="n"/>
@@ -9257,53 +9273,53 @@
       <c r="L78" s="14" t="n"/>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>Тринити-колледж, Кембридж; Оксфордский университет</t>
+          <t>Стэнфордский университет; Калифорнийский технологический институт; Калифорнийский университет в Ирвайне</t>
         </is>
       </c>
       <c r="N78" s="14" t="inlineStr">
         <is>
-          <t>Сент-Эндрюсский университет; Нью-Йоркский университет; Университет Стерлинга</t>
+          <t>Университет Нью-Гэмпшира</t>
         </is>
       </c>
       <c r="O78" s="14" t="n"/>
       <c r="P78" s="14" t="n"/>
-      <c r="Q78" s="14" t="inlineStr">
-        <is>
-          <t>Майкл Даммит</t>
-        </is>
-      </c>
+      <c r="Q78" s="14" t="n"/>
       <c r="R78" s="14" t="n"/>
       <c r="S78" s="14" t="inlineStr">
         <is>
-          <t>философия языка; философия математики; эпистемология</t>
+          <t>электротехника; история науки; популяризация математики</t>
         </is>
       </c>
       <c r="T78" s="14" t="inlineStr">
         <is>
-          <t>Британский аналитический философ, известный работами по проблемам истины, реализму, антиреализму и философии языка.</t>
+          <t>Родился 26 ноября 1940 года в Калифорнии, закончил школу в 1958-м, а затем получил степень бакалавра в Стэнфорде (1962), магистра — в Калтехе (1963) и докторскую степень — в Университете Калифорнии в Ирвайне (1972), всё — по электротехнике. До перехода в академию несколько лет проработал инженером-разработчиком цифровой логики и радиолокационных систем в аэрокосмической отрасли Южной Калифорнии. Преподавал в Харви Мадд Колледже, Университете Вирджинии и Военно-морской аспирантуре в Монтерее, а с 2004 года — почётный профессор электротехники Университета Нью-Гэмпшира. Помимо биографии Хевисайда, написал научно-популярные биографии Джорджа Буля и Клода Шеннона (совместную — под названием «The Logician and the Engineer»), ряд книг по истории математических констант и понятий (формула Эйлера, дзета-функция Римана, мнимая единица), а также несколько книг о физике и философских парадоксах путешествий во времени. Также опубликовал около двух десятков научно-фантастических рассказов в журналах Analog, Omni и Twilight Zone. В 1979 году получил первую премию Harry Rowe Mimno от IEEE, а в 2017-м — премию Chandler Davis за выдающийся научно-популярный стиль изложения математики.</t>
         </is>
       </c>
       <c r="U78" s="14" t="inlineStr">
         <is>
-          <t>- Crispin Wright, Truth and Objectivity (1992) - Объективность - Истина - Корреспонденция - Антиреализм</t>
+          <t>1. Nahin P.J. Oliver Heaviside: The Life, Work, and Times of an Electrical Genius of the Victorian Age : A Johns Hopkins paperback. – Johns Hopkins University Press, 2002.</t>
         </is>
       </c>
       <c r="V78" s="14" t="n"/>
       <c r="W78" s="14" t="n"/>
       <c r="X78" s="14" t="inlineStr">
         <is>
-          <t>Уилсон приводит проект Райта в Truth and Objectivity как пример более мягкой попытки сохранить понятие объективности после отказа от наивной модели прямого соответствия слова и мира. Он подчёркивает, что точные мотивы Райта ему не вполне ясны.</t>
+          <t>Уилсон уделяет особое внимание биографии Хевисайда, написанной Полом Нахином как исторического источника при описании конфликта Хевисайда с академическим математическим сообществом</t>
         </is>
       </c>
       <c r="Y78" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
-        </is>
-      </c>
-      <c r="Z78" s="14" t="n"/>
+          <t>предисловие</t>
+        </is>
+      </c>
+      <c r="Z78" s="14" t="inlineStr">
+        <is>
+          <t>predislovie</t>
+        </is>
+      </c>
       <c r="AA78" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/crispin-wright</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/p-j-nahin</t>
         </is>
       </c>
       <c r="AB78" s="14" t="inlineStr">
@@ -9316,97 +9332,125 @@
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>Фрэнк Джексон</t>
+          <t>Дэвид Льюис</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Frank Jackson</t>
+          <t>David Lewis</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>австралиец</t>
+          <t>американец</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/jackson.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/d_lewis.jpg</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>1943–</t>
+          <t>1941–2001</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>1943-08-31</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="n"/>
-      <c r="H79" s="14" t="n"/>
+          <t>1941-09-28</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>2001-10-14</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>осложнения сахарного диабета</t>
+        </is>
+      </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>Мельбурн, Австралия</t>
+          <t>Оберлин, Огайо, США</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
         <is>
-          <t>-37.8136, 144.9631</t>
-        </is>
-      </c>
-      <c r="K79" s="14" t="n"/>
-      <c r="L79" s="14" t="n"/>
+          <t>41.2939, -82.2174</t>
+        </is>
+      </c>
+      <c r="K79" s="14" t="inlineStr">
+        <is>
+          <t>Принстон, Нью-Джерси, США</t>
+        </is>
+      </c>
+      <c r="L79" s="14" t="inlineStr">
+        <is>
+          <t>40.3573, -74.6672</t>
+        </is>
+      </c>
       <c r="M79" s="14" t="inlineStr">
         <is>
-          <t>Мельбурнский университет; Университет Ла Троба</t>
+          <t>Суортмор-колледж; Гарвардский университет</t>
         </is>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
-          <t>Австралийский национальный университет</t>
-        </is>
-      </c>
-      <c r="O79" s="14" t="n"/>
-      <c r="P79" s="14" t="n"/>
+          <t>Калифорнийский университет в Лос-Анджелесе; Принстонский университет</t>
+        </is>
+      </c>
+      <c r="O79" s="14" t="inlineStr">
+        <is>
+          <t>Уиллард Куайн</t>
+        </is>
+      </c>
+      <c r="P79" s="14" t="inlineStr">
+        <is>
+          <t>Роберт Брэндом</t>
+        </is>
+      </c>
       <c r="Q79" s="14" t="n"/>
       <c r="R79" s="14" t="n"/>
       <c r="S79" s="14" t="inlineStr">
         <is>
-          <t>философия сознания; метафизика</t>
+          <t>метафизика; философия языка; модальная логика</t>
         </is>
       </c>
       <c r="T79" s="14" t="inlineStr">
         <is>
-          <t>Австралийский философ, профессор Принстонского и Австралийского национального университетов. Известен аргументом «комнаты Мэри» (knowledge argument) против физикализма, работами по философии сознания, квалиа и метафизике. Автор книги «От метафизики к этике» (From Metaphysics to Ethics, 1998).</t>
+          <t>Американский философ, один из самых влиятельных аналитических метафизиков второй половины XX века. Профессор Принстонского университета, ученик Куайна. Известен доктриной модального реализма — тезисом, что все логически возможные миры существуют реально, наравне с нашим (главное изложение: «On the Plurality of Worlds», 1986); работами в философии сознания (функционализм), философии науки, теории каузальности (каузальность через контрфактуалы), теории игр и конвенций языка («Convention», 1969).</t>
         </is>
       </c>
       <c r="U79" s="14" t="inlineStr">
         <is>
-          <t>- «Проблемы локальности» (locality problems) — вопросы о том, где (в какой сфере) атрибут получает своё основное распространение</t>
-        </is>
-      </c>
-      <c r="V79" s="14" t="n"/>
+          <t>- В (viii) конкретных работ не назвал — только общее указание, что Льюис укладывается в классическую картину. Обещанная точка сверки — приложение к главе 3.</t>
+        </is>
+      </c>
+      <c r="V79" s="14" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/david-lewis/</t>
+        </is>
+      </c>
       <c r="W79" s="14" t="n"/>
       <c r="X79" s="14" t="inlineStr">
         <is>
-          <t>Уилсон упоминает Джексона в контексте обсуждения субъективистских моделей музыкальных атрибутов. Он ссылается на джексоновский термин «проблемы локальности» (locality problems), которым тот обозначает вопросы о том, в какой сфере (физической или ментальной) атрибут получает своё основное распространение. Уилсон использует это понятие, чтобы охарактеризовать субъективистскую позицию, согласно которой музыкальные свойства типа «выражение печали» должны быть локализованы в ментальной сфере.</t>
+          <t>Упомянут в подразделе (viii) как редкий пример современного философа, чей взгляд на концепции Уилсон расценивает как «полностью классический по качеству» — то есть как «тонкую настройку Рассела» (bertrand-russell) в рамках klassicheskaya-kartina-kontseptsiy. Уилсон прямо отмечает, что использовал некоторые идеи Льюиса в приложении к главе 3 (там, где систематизирует тезисы классической картины). В отличие от Куайна , Даммита и Брэндома, Льюис представлен как более утончённый продолжатель.</t>
         </is>
       </c>
       <c r="Y79" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z79" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_iv</t>
+          <t>chapter_1_viii</t>
         </is>
       </c>
       <c r="AA79" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/frank-jackson</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/david-lewis</t>
         </is>
       </c>
       <c r="AB79" s="14" t="inlineStr">
@@ -9419,32 +9463,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Джефф Тодд Титон</t>
+          <t>Криспин Райт</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Jeff Todd Titon</t>
+          <t>Crispin Wright</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>британец</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j_titon.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/c_wright.jpg</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>1943–</t>
+          <t>1942–</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="G80" s="14" t="n"/>
@@ -9453,51 +9497,55 @@
       <c r="J80" s="14" t="n"/>
       <c r="K80" s="14" t="n"/>
       <c r="L80" s="14" t="n"/>
-      <c r="M80" s="14" t="n"/>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>Тринити-колледж, Кембридж; Оксфордский университет</t>
+        </is>
+      </c>
       <c r="N80" s="14" t="inlineStr">
         <is>
-          <t>Брауновский университет</t>
+          <t>Сент-Эндрюсский университет; Нью-Йоркский университет; Университет Стерлинга</t>
         </is>
       </c>
       <c r="O80" s="14" t="n"/>
       <c r="P80" s="14" t="n"/>
-      <c r="Q80" s="14" t="n"/>
+      <c r="Q80" s="14" t="inlineStr">
+        <is>
+          <t>Майкл Даммит</t>
+        </is>
+      </c>
       <c r="R80" s="14" t="n"/>
       <c r="S80" s="14" t="inlineStr">
         <is>
-          <t>этномузыкология; фольклористика</t>
+          <t>философия языка; философия математики; эпистемология</t>
         </is>
       </c>
       <c r="T80" s="14" t="inlineStr">
         <is>
-          <t>Американский этномузыковед и фольклорист. В рассматриваемом Уилсоном контексте Титон защищает такой вариант этномузыкологии, в котором главное место занимает понимание жизненного опыта людей, создающих музыку, а не его естественно-научное объяснение.</t>
+          <t>Британский аналитический философ, известный работами по проблемам истины, реализму, антиреализму и философии языка.</t>
         </is>
       </c>
       <c r="U80" s="14" t="inlineStr">
         <is>
-          <t>- Jeff Todd Titon, “Reconstructing the Blues” // Neil V. Rosenberg, ed., Transforming Tradition (1993), p. 238 - Jeff Todd Titon, “Knowing Fieldwork” // G. F. Barz and T. J. Cooley, eds., Shadows in the Field, pp. 87–100 - Понимание вместо объяснения - Музыка как социально сконструированный культурный феномен - Совместное музицирование и полевое участие - Субъективный музыкальный опыт</t>
+          <t>- Crispin Wright, Truth and Objectivity (1992) - Объективность - Истина - Корреспонденция - Антиреализм</t>
         </is>
       </c>
       <c r="V80" s="14" t="n"/>
       <c r="W80" s="14" t="n"/>
       <c r="X80" s="14" t="inlineStr">
         <is>
-          <t>Титон предлагает философское обоснование собственных этномузыкологических практик. Он рассматривает музыку как социально сконструированный культурный феномен и подчёркивает значение непосредственного музыкального опыта, совместного музицирования и полевой работы. Уилсон интерпретирует эту позицию как движение к субъективизму и отмечает в ней «сильный привкус» партиципативного идеализма. В дальнейшем критика Титона связывается с вопросом о том, может ли внутренний музыкальный опыт служить основанием публичного гуманитарного знания.</t>
+          <t>Уилсон приводит проект Райта в Truth and Objectivity как пример более мягкой попытки сохранить понятие объективности после отказа от наивной модели прямого соответствия слова и мира. Он подчёркивает, что точные мотивы Райта ему не вполне ясны.</t>
         </is>
       </c>
       <c r="Y80" s="14" t="inlineStr">
         <is>
-          <t>гл. 2; гл. 3</t>
-        </is>
-      </c>
-      <c r="Z80" s="14" t="inlineStr">
-        <is>
-          <t>chapter_2_v; chapter_3_iv</t>
-        </is>
-      </c>
+          <t>гл. 2</t>
+        </is>
+      </c>
+      <c r="Z80" s="14" t="n"/>
       <c r="AA80" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/jeff-todd-titon</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/crispin-wright</t>
         </is>
       </c>
       <c r="AB80" s="14" t="inlineStr">
@@ -9510,48 +9558,56 @@
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>Рэй Джекендофф</t>
+          <t>Фрэнк Джексон</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Ray Jackendoff</t>
+          <t>Frank Jackson</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>американец</t>
+          <t>австралиец</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/r_jackendoff.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/jackson.jpg</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>р. 1945</t>
+          <t>1943–</t>
         </is>
       </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1943-08-31</t>
         </is>
       </c>
       <c r="G81" s="14" t="n"/>
       <c r="H81" s="14" t="n"/>
-      <c r="I81" s="14" t="n"/>
-      <c r="J81" s="14" t="n"/>
+      <c r="I81" s="14" t="inlineStr">
+        <is>
+          <t>Мельбурн, Австралия</t>
+        </is>
+      </c>
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>-37.8136, 144.9631</t>
+        </is>
+      </c>
       <c r="K81" s="14" t="n"/>
       <c r="L81" s="14" t="n"/>
       <c r="M81" s="14" t="inlineStr">
         <is>
-          <t>Суортмор-колледж; Массачусетский технологический институт</t>
+          <t>Мельбурнский университет; Университет Ла Троба</t>
         </is>
       </c>
       <c r="N81" s="14" t="inlineStr">
         <is>
-          <t>Брандейский университет; Университет Тафтса</t>
+          <t>Австралийский национальный университет</t>
         </is>
       </c>
       <c r="O81" s="14" t="n"/>
@@ -9560,39 +9616,39 @@
       <c r="R81" s="14" t="n"/>
       <c r="S81" s="14" t="inlineStr">
         <is>
-          <t>лингвистика; семантика; когнитивная наука; музыкальное познание</t>
+          <t>философия сознания; метафизика</t>
         </is>
       </c>
       <c r="T81" s="14" t="inlineStr">
         <is>
-          <t>Американский лингвист, один из ведущих специалистов по семантике и когнитивной лингвистике, работал над теорией концептуальной семантики (Conceptual Semantics) — альтернативой чисто формальным подходам к значению, связывающей языковую семантику со структурами мышления в целом. Долгое время работал в Университете Брандейса и Университете Тафтса.</t>
+          <t>Австралийский философ, профессор Принстонского и Австралийского национального университетов. Известен аргументом «комнаты Мэри» (knowledge argument) против физикализма, работами по философии сознания, квалиа и метафизике. Автор книги «От метафизики к этике» (From Metaphysics to Ethics, 1998).</t>
         </is>
       </c>
       <c r="U81" s="14" t="inlineStr">
         <is>
-          <t>- Ray Jackendoff, "What is a Concept that a Person May Grasp It?" // Eric Margolis and Stephen Laurence, eds., Concepts (Cambridge, Mass.: MIT Press, 1999), 307</t>
+          <t>- «Проблемы локальности» (locality problems) — вопросы о том, где (в какой сфере) атрибут получает своё основное распространение</t>
         </is>
       </c>
       <c r="V81" s="14" t="n"/>
       <c r="W81" s="14" t="n"/>
       <c r="X81" s="14" t="inlineStr">
         <is>
-          <t>Процитирован (по статье «What is a Concept that a Person May Grasp It?», 1999) как представитель влиятельного лингвистического аргумента в пользу семантической завершённости: раз говорящие способны понимать бесконечное количество ранее не встречавшихся предложений («креативность языка»), то в основе этого должен лежать конечный набор полностью усвоенных «ментальных примитивов» и принципов их композиции — а базовыми единицами этого набора являются лексические концепции, выражаемые словами. Уилсон приводит эту цитату не для того, чтобы опровергнуть лингвистику как таковую, а чтобы показать, откуда происходит философская привлекательность тезиса о семантической завершённости, который сам он оспаривает.</t>
+          <t>Уилсон упоминает Джексона в контексте обсуждения субъективистских моделей музыкальных атрибутов. Он ссылается на джексоновский термин «проблемы локальности» (locality problems), которым тот обозначает вопросы о том, в какой сфере (физической или ментальной) атрибут получает своё основное распространение. Уилсон использует это понятие, чтобы охарактеризовать субъективистскую позицию, согласно которой музыкальные свойства типа «выражение печали» должны быть локализованы в ментальной сфере.</t>
         </is>
       </c>
       <c r="Y81" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 2</t>
         </is>
       </c>
       <c r="Z81" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_vi</t>
+          <t>chapter_2_iv</t>
         </is>
       </c>
       <c r="AA81" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/ray-jackendoff</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/frank-jackson</t>
         </is>
       </c>
       <c r="AB81" s="14" t="inlineStr">
@@ -9605,12 +9661,12 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>Роберт Брэндом</t>
+          <t>Джефф Тодд Титон</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Robert Brandom</t>
+          <t>Jeff Todd Titon</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -9620,17 +9676,17 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/r_brandom.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/j_titon.jpg</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>р. 1950</t>
+          <t>1943–</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="G82" s="14" t="n"/>
@@ -9639,63 +9695,51 @@
       <c r="J82" s="14" t="n"/>
       <c r="K82" s="14" t="n"/>
       <c r="L82" s="14" t="n"/>
-      <c r="M82" s="14" t="inlineStr">
-        <is>
-          <t>Йельский университет; Принстонский университет</t>
-        </is>
-      </c>
+      <c r="M82" s="14" t="n"/>
       <c r="N82" s="14" t="inlineStr">
         <is>
-          <t>Питтсбургский университет</t>
-        </is>
-      </c>
-      <c r="O82" s="14" t="inlineStr">
-        <is>
-          <t>Дэвид Льюис</t>
-        </is>
-      </c>
+          <t>Брауновский университет</t>
+        </is>
+      </c>
+      <c r="O82" s="14" t="n"/>
       <c r="P82" s="14" t="n"/>
-      <c r="Q82" s="14" t="inlineStr">
-        <is>
-          <t>Уилфрид Селларс</t>
-        </is>
-      </c>
+      <c r="Q82" s="14" t="n"/>
       <c r="R82" s="14" t="n"/>
       <c r="S82" s="14" t="inlineStr">
         <is>
-          <t>философия языка; инференциализм; прагматизм</t>
+          <t>этномузыкология; фольклористика</t>
         </is>
       </c>
       <c r="T82" s="14" t="inlineStr">
         <is>
-          <t>Американский философ, коллега Уилсона по кафедре философии Питтсбургского университета (Distinguished Professor). Ученик Ричарда Рорти. Наиболее известен программой инференциализма — теорией значения, согласно которой содержание понятий задаётся не отношением к миру (как в референциальных теориях), а сетью инференциальных обязательств: понимать значение утверждения — это уметь пользоваться им в игре «давания и требования оснований» (giving and asking for reasons). Главное изложение — фундаментальная монография «Making It Explicit» (1994); более доступная версия — «Articulating Reasons» (2000). Работает также над Гегелем («A Spirit of Trust», 2019).</t>
+          <t>Американский этномузыковед и фольклорист. В рассматриваемом Уилсоном контексте Титон защищает такой вариант этномузыкологии, в котором главное место занимает понимание жизненного опыта людей, создающих музыку, а не его естественно-научное объяснение.</t>
         </is>
       </c>
       <c r="U82" s="14" t="inlineStr">
         <is>
-          <t>- Конкретных работ Брэндома в этом фрагменте Уилсон не называет — только общее указание на его критику классической картины. Наиболее вероятные кандидаты — «Making It Explicit» (Cambridge, Mass.: Harvard University Press, 1994) и «Articulating Reasons» (2000).</t>
+          <t>- Jeff Todd Titon, “Reconstructing the Blues” // Neil V. Rosenberg, ed., Transforming Tradition (1993), p. 238 - Jeff Todd Titon, “Knowing Fieldwork” // G. F. Barz and T. J. Cooley, eds., Shadows in the Field, pp. 87–100 - Понимание вместо объяснения - Музыка как социально сконструированный культурный феномен - Совместное музицирование и полевое участие - Субъективный музыкальный опыт</t>
         </is>
       </c>
       <c r="V82" s="14" t="n"/>
       <c r="W82" s="14" t="n"/>
       <c r="X82" s="14" t="inlineStr">
         <is>
-          <t>Упомянут в подразделе (viii) как один из трёх современных критиков klassicheskaya-kartina-kontseptsiy (вместе с Куайном и Даммитом; см. willard-quine, michael-dummett), чьи «варьирующиеся диагностики» Уилсон не разделяет, но чью общую цель — изолировать точный способ, которым классическая картина искажает разумный взгляд на человеческие способности — он полностью разделяет. Книга Уилсона названа его собственной попыткой довести до конца похожий проект.</t>
+          <t>Титон предлагает философское обоснование собственных этномузыкологических практик. Он рассматривает музыку как социально сконструированный культурный феномен и подчёркивает значение непосредственного музыкального опыта, совместного музицирования и полевой работы. Уилсон интерпретирует эту позицию как движение к субъективизму и отмечает в ней «сильный привкус» партиципативного идеализма. В дальнейшем критика Титона связывается с вопросом о том, может ли внутренний музыкальный опыт служить основанием публичного гуманитарного знания.</t>
         </is>
       </c>
       <c r="Y82" s="14" t="inlineStr">
         <is>
-          <t>гл. 1</t>
+          <t>гл. 2; гл. 3</t>
         </is>
       </c>
       <c r="Z82" s="14" t="inlineStr">
         <is>
-          <t>chapter_1_viii</t>
+          <t>chapter_2_v; chapter_3_iv; chapter_3_vii</t>
         </is>
       </c>
       <c r="AA82" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-brandom</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/jeff-todd-titon</t>
         </is>
       </c>
       <c r="AB82" s="14" t="inlineStr">
@@ -9708,12 +9752,12 @@
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>Тим Эриксон</t>
+          <t>Рэй Джекендофф</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Tim Erikson</t>
+          <t>Ray Jackendoff</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr">
@@ -9723,62 +9767,74 @@
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/t_erikson.webp</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/r_jackendoff.jpg</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>1966–</t>
-        </is>
-      </c>
-      <c r="F83" s="14" t="n"/>
+          <t>р. 1945</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
       <c r="G83" s="14" t="n"/>
       <c r="H83" s="14" t="n"/>
       <c r="I83" s="14" t="n"/>
       <c r="J83" s="14" t="n"/>
       <c r="K83" s="14" t="n"/>
       <c r="L83" s="14" t="n"/>
-      <c r="M83" s="14" t="n"/>
-      <c r="N83" s="14" t="n"/>
+      <c r="M83" s="14" t="inlineStr">
+        <is>
+          <t>Суортмор-колледж; Массачусетский технологический институт</t>
+        </is>
+      </c>
+      <c r="N83" s="14" t="inlineStr">
+        <is>
+          <t>Брандейский университет; Университет Тафтса</t>
+        </is>
+      </c>
       <c r="O83" s="14" t="n"/>
       <c r="P83" s="14" t="n"/>
       <c r="Q83" s="14" t="n"/>
       <c r="R83" s="14" t="n"/>
       <c r="S83" s="14" t="inlineStr">
         <is>
-          <t>народная музыка; скрипка</t>
+          <t>лингвистика; семантика; когнитивная наука; музыкальное познание</t>
         </is>
       </c>
       <c r="T83" s="14" t="inlineStr">
         <is>
-          <t>Музыкант и исследователь, автор заметок к записи Her Bright Smile Haunts Me Still (Appleseed APR CD 1035, 2000), посвящённой песням Чарли Уорнерса (Warners).</t>
+          <t>Американский лингвист, один из ведущих специалистов по семантике и когнитивной лингвистике, работал над теорией концептуальной семантики (Conceptual Semantics) — альтернативой чисто формальным подходам к значению, связывающей языковую семантику со структурами мышления в целом. Долгое время работал в Университете Брандейса и Университете Тафтса.</t>
         </is>
       </c>
       <c r="U83" s="14" t="inlineStr">
         <is>
-          <t>- Tim Erikson, заметки к Her Bright Smile Haunts Me Still, Appleseed APR CD 1035 (2000) - Сохранение через исполнение - Музыкальный опыт - Партиципативность - Напряжение между сохранением и реконструкцией</t>
+          <t>- Ray Jackendoff, "What is a Concept that a Person May Grasp It?" // Eric Margolis and Stephen Laurence, eds., Concepts (Cambridge, Mass.: MIT Press, 1999), 307</t>
         </is>
       </c>
       <c r="V83" s="14" t="n"/>
       <c r="W83" s="14" t="n"/>
       <c r="X83" s="14" t="inlineStr">
         <is>
-          <t>Эриксон служит практическим примером партиципативного подхода к сохранению музыки. В его рассуждении ценность музыкальной записи не существует независимо от восприятия и опыта: надёжное сохранение требует «жить» музыкой и исполнять её. Сам Эриксон участвует в исполнении песен Уорнерса. Уилсон, однако, считает, что подобное участие способно не только сохранить, но и исказить исходный музыкальный материал, уничтожая тонкие детали, которые могли бы быть важны будущим слушателям.</t>
+          <t>Процитирован (по статье «What is a Concept that a Person May Grasp It?», 1999) как представитель влиятельного лингвистического аргумента в пользу семантической завершённости: раз говорящие способны понимать бесконечное количество ранее не встречавшихся предложений («креативность языка»), то в основе этого должен лежать конечный набор полностью усвоенных «ментальных примитивов» и принципов их композиции — а базовыми единицами этого набора являются лексические концепции, выражаемые словами. Уилсон приводит эту цитату не для того, чтобы опровергнуть лингвистику как таковую, а чтобы показать, откуда происходит философская привлекательность тезиса о семантической завершённости, который сам он оспаривает.</t>
         </is>
       </c>
       <c r="Y83" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z83" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_v</t>
+          <t>chapter_1_vi</t>
         </is>
       </c>
       <c r="AA83" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/tim-erikson</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/ray-jackendoff</t>
         </is>
       </c>
       <c r="AB83" s="14" t="inlineStr">
@@ -9791,12 +9847,12 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>Тимоти Дж. Кули</t>
+          <t>Роберт Брэндом</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Timothy J. Cooley</t>
+          <t>Robert Brandom</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -9806,66 +9862,82 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/t_cooley.jpg</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/r_brandom.jpg</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>не установлено</t>
-        </is>
-      </c>
-      <c r="F84" s="14" t="n"/>
+          <t>р. 1950</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
       <c r="G84" s="14" t="n"/>
       <c r="H84" s="14" t="n"/>
       <c r="I84" s="14" t="n"/>
       <c r="J84" s="14" t="n"/>
       <c r="K84" s="14" t="n"/>
       <c r="L84" s="14" t="n"/>
-      <c r="M84" s="14" t="n"/>
+      <c r="M84" s="14" t="inlineStr">
+        <is>
+          <t>Йельский университет; Принстонский университет</t>
+        </is>
+      </c>
       <c r="N84" s="14" t="inlineStr">
         <is>
-          <t>Калифорнийский университет в Санта-Барбаре</t>
-        </is>
-      </c>
-      <c r="O84" s="14" t="n"/>
+          <t>Питтсбургский университет</t>
+        </is>
+      </c>
+      <c r="O84" s="14" t="inlineStr">
+        <is>
+          <t>Дэвид Льюис</t>
+        </is>
+      </c>
       <c r="P84" s="14" t="n"/>
-      <c r="Q84" s="14" t="n"/>
+      <c r="Q84" s="14" t="inlineStr">
+        <is>
+          <t>Уилфрид Селларс</t>
+        </is>
+      </c>
       <c r="R84" s="14" t="n"/>
       <c r="S84" s="14" t="inlineStr">
         <is>
-          <t>этномузыкология</t>
+          <t>философия языка; инференциализм; прагматизм</t>
         </is>
       </c>
       <c r="T84" s="14" t="inlineStr">
         <is>
-          <t>Американский этномузыковед, редактор и автор работ по полевой этномузыкологии. В данном фрагменте Уилсон обращается прежде всего к его введению в сборник Shadows in the Field.</t>
+          <t>Американский философ, коллега Уилсона по кафедре философии Питтсбургского университета (Distinguished Professor). Ученик Ричарда Рорти. Наиболее известен программой инференциализма — теорией значения, согласно которой содержание понятий задаётся не отношением к миру (как в референциальных теориях), а сетью инференциальных обязательств: понимать значение утверждения — это уметь пользоваться им в игре «давания и требования оснований» (giving and asking for reasons). Главное изложение — фундаментальная монография «Making It Explicit» (1994); более доступная версия — «Articulating Reasons» (2000). Работает также над Гегелем («A Spirit of Trust», 2019).</t>
         </is>
       </c>
       <c r="U84" s="14" t="inlineStr">
         <is>
-          <t>- Timothy J. Cooley, “Casting Shadows in the Field: An Introduction” // G. F. Barz and T. J. Cooley, eds., Shadows in the Field (1997), p. 11 - Проблема объективности - Кризис научной/интеллектуальной гегемонии - Интерпретирующие сообщества - Семантический холизм - Политическая нагруженность классификаций</t>
+          <t>- Конкретных работ Брэндома в этом фрагменте Уилсон не называет — только общее указание на его критику классической картины. Наиболее вероятные кандидаты — «Making It Explicit» (Cambridge, Mass.: Harvard University Press, 1994) и «Articulating Reasons» (2000).</t>
         </is>
       </c>
       <c r="V84" s="14" t="n"/>
       <c r="W84" s="14" t="n"/>
       <c r="X84" s="14" t="inlineStr">
         <is>
-          <t>Кули вводит проблему объективности этномузыкологического знания на фоне кризиса западной интеллектуальной и научной гегемонии. Уилсон связывает эти сомнения с более широкой логикой холизма: если значение и классификация зависят от сети социальных и культурных отношений, возникает вопрос о возможности объективного описания музыки. В предельной форме такая логика превращает даже обозначение произведения как «народной песни» в потенциально политический акт.</t>
+          <t>Упомянут в подразделе (viii) как один из трёх современных критиков klassicheskaya-kartina-kontseptsiy (вместе с Куайном и Даммитом; см. willard-quine, michael-dummett), чьи «варьирующиеся диагностики» Уилсон не разделяет, но чью общую цель — изолировать точный способ, которым классическая картина искажает разумный взгляд на человеческие способности — он полностью разделяет. Книга Уилсона названа его собственной попыткой довести до конца похожий проект.</t>
         </is>
       </c>
       <c r="Y84" s="14" t="inlineStr">
         <is>
-          <t>гл. 2</t>
+          <t>гл. 1</t>
         </is>
       </c>
       <c r="Z84" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_v</t>
+          <t>chapter_1_viii</t>
         </is>
       </c>
       <c r="AA84" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/timothy-cooley</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/robert-brandom</t>
         </is>
       </c>
       <c r="AB84" s="14" t="inlineStr">
@@ -9878,25 +9950,29 @@
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Фолькер Шерлисс</t>
+          <t>Тим Эриксон</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Volker Scherliess</t>
+          <t>Tim Erikson</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>немец</t>
+          <t>американец</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/v_scherliess.jpg</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="n"/>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/t_erikson.webp</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>1966–</t>
+        </is>
+      </c>
       <c r="F85" s="14" t="n"/>
       <c r="G85" s="14" t="n"/>
       <c r="H85" s="14" t="n"/>
@@ -9912,20 +9988,24 @@
       <c r="R85" s="14" t="n"/>
       <c r="S85" s="14" t="inlineStr">
         <is>
-          <t>музыковедение</t>
+          <t>народная музыка; скрипка</t>
         </is>
       </c>
       <c r="T85" s="14" t="inlineStr">
         <is>
-          <t>Немецкий музыковед, автор комментария к записи симфоний №40 и №41 Моцарта в исполнении Венского филармонического оркестра под управлением Леонарда Бернстайна (Deutsche Grammophon, 1984).</t>
-        </is>
-      </c>
-      <c r="U85" s="14" t="n"/>
+          <t>Музыкант и исследователь, автор заметок к записи Her Bright Smile Haunts Me Still (Appleseed APR CD 1035, 2000), посвящённой песням Чарли Уорнерса (Warners).</t>
+        </is>
+      </c>
+      <c r="U85" s="14" t="inlineStr">
+        <is>
+          <t>- Tim Erikson, заметки к Her Bright Smile Haunts Me Still, Appleseed APR CD 1035 (2000) - Сохранение через исполнение - Музыкальный опыт - Партиципативность - Напряжение между сохранением и реконструкцией</t>
+        </is>
+      </c>
       <c r="V85" s="14" t="n"/>
       <c r="W85" s="14" t="n"/>
       <c r="X85" s="14" t="inlineStr">
         <is>
-          <t>Цитируется по поводу исторической изменчивости восприятия Симфонии №40: Шуман слышал в ней «Греческую грацию», другой автор интерпретировал её в духе итальянской оперы-буфф, тогда как современные слушатели (и сам Уилсон) склонны воспринимать её мрачный, драматический пафос — трагедию, скорбь, отчаяние.</t>
+          <t>Эриксон служит практическим примером партиципативного подхода к сохранению музыки. В его рассуждении ценность музыкальной записи не существует независимо от восприятия и опыта: надёжное сохранение требует «жить» музыкой и исполнять её. Сам Эриксон участвует в исполнении песен Уорнерса. Уилсон, однако, считает, что подобное участие способно не только сохранить, но и исказить исходный музыкальный материал, уничтожая тонкие детали, которые могли бы быть важны будущим слушателям.</t>
         </is>
       </c>
       <c r="Y85" s="14" t="inlineStr">
@@ -9935,12 +10015,12 @@
       </c>
       <c r="Z85" s="14" t="inlineStr">
         <is>
-          <t>chapter_2_i</t>
+          <t>chapter_2_v</t>
         </is>
       </c>
       <c r="AA85" s="14" t="inlineStr">
         <is>
-          <t>https://kagort.github.io/wand_sign_navigator/03-people/volker-scherliess</t>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/tim-erikson</t>
         </is>
       </c>
       <c r="AB85" s="14" t="inlineStr">
@@ -9950,8 +10030,170 @@
       </c>
       <c r="AC85" s="14" t="n"/>
     </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>Тимоти Дж. Кули</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>Timothy J. Cooley</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>американец</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/t_cooley.jpg</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="n"/>
+      <c r="G86" s="14" t="n"/>
+      <c r="H86" s="14" t="n"/>
+      <c r="I86" s="14" t="n"/>
+      <c r="J86" s="14" t="n"/>
+      <c r="K86" s="14" t="n"/>
+      <c r="L86" s="14" t="n"/>
+      <c r="M86" s="14" t="n"/>
+      <c r="N86" s="14" t="inlineStr">
+        <is>
+          <t>Калифорнийский университет в Санта-Барбаре</t>
+        </is>
+      </c>
+      <c r="O86" s="14" t="n"/>
+      <c r="P86" s="14" t="n"/>
+      <c r="Q86" s="14" t="n"/>
+      <c r="R86" s="14" t="n"/>
+      <c r="S86" s="14" t="inlineStr">
+        <is>
+          <t>этномузыкология</t>
+        </is>
+      </c>
+      <c r="T86" s="14" t="inlineStr">
+        <is>
+          <t>Американский этномузыковед, редактор и автор работ по полевой этномузыкологии. В данном фрагменте Уилсон обращается прежде всего к его введению в сборник Shadows in the Field.</t>
+        </is>
+      </c>
+      <c r="U86" s="14" t="inlineStr">
+        <is>
+          <t>- Timothy J. Cooley, “Casting Shadows in the Field: An Introduction” // G. F. Barz and T. J. Cooley, eds., Shadows in the Field (1997), p. 11 - Проблема объективности - Кризис научной/интеллектуальной гегемонии - Интерпретирующие сообщества - Семантический холизм - Политическая нагруженность классификаций</t>
+        </is>
+      </c>
+      <c r="V86" s="14" t="n"/>
+      <c r="W86" s="14" t="n"/>
+      <c r="X86" s="14" t="inlineStr">
+        <is>
+          <t>Кули вводит проблему объективности этномузыкологического знания на фоне кризиса западной интеллектуальной и научной гегемонии. Уилсон связывает эти сомнения с более широкой логикой холизма: если значение и классификация зависят от сети социальных и культурных отношений, возникает вопрос о возможности объективного описания музыки. В предельной форме такая логика превращает даже обозначение произведения как «народной песни» в потенциально политический акт.</t>
+        </is>
+      </c>
+      <c r="Y86" s="14" t="inlineStr">
+        <is>
+          <t>гл. 2</t>
+        </is>
+      </c>
+      <c r="Z86" s="14" t="inlineStr">
+        <is>
+          <t>chapter_2_v</t>
+        </is>
+      </c>
+      <c r="AA86" s="14" t="inlineStr">
+        <is>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/timothy-cooley</t>
+        </is>
+      </c>
+      <c r="AB86" s="14" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="AC86" s="14" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Фолькер Шерлисс</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>Volker Scherliess</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>немец</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/assets/v_scherliess.jpg</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="n"/>
+      <c r="F87" s="14" t="n"/>
+      <c r="G87" s="14" t="n"/>
+      <c r="H87" s="14" t="n"/>
+      <c r="I87" s="14" t="n"/>
+      <c r="J87" s="14" t="n"/>
+      <c r="K87" s="14" t="n"/>
+      <c r="L87" s="14" t="n"/>
+      <c r="M87" s="14" t="n"/>
+      <c r="N87" s="14" t="n"/>
+      <c r="O87" s="14" t="n"/>
+      <c r="P87" s="14" t="n"/>
+      <c r="Q87" s="14" t="n"/>
+      <c r="R87" s="14" t="n"/>
+      <c r="S87" s="14" t="inlineStr">
+        <is>
+          <t>музыковедение</t>
+        </is>
+      </c>
+      <c r="T87" s="14" t="inlineStr">
+        <is>
+          <t>Немецкий музыковед, автор комментария к записи симфоний №40 и №41 Моцарта в исполнении Венского филармонического оркестра под управлением Леонарда Бернстайна (Deutsche Grammophon, 1984).</t>
+        </is>
+      </c>
+      <c r="U87" s="14" t="n"/>
+      <c r="V87" s="14" t="n"/>
+      <c r="W87" s="14" t="n"/>
+      <c r="X87" s="14" t="inlineStr">
+        <is>
+          <t>Цитируется по поводу исторической изменчивости восприятия Симфонии №40: Шуман слышал в ней «Греческую грацию», другой автор интерпретировал её в духе итальянской оперы-буфф, тогда как современные слушатели (и сам Уилсон) склонны воспринимать её мрачный, драматический пафос — трагедию, скорбь, отчаяние.</t>
+        </is>
+      </c>
+      <c r="Y87" s="14" t="inlineStr">
+        <is>
+          <t>гл. 2</t>
+        </is>
+      </c>
+      <c r="Z87" s="14" t="inlineStr">
+        <is>
+          <t>chapter_2_i</t>
+        </is>
+      </c>
+      <c r="AA87" s="14" t="inlineStr">
+        <is>
+          <t>https://kagort.github.io/wand_sign_navigator/03-people/volker-scherliess</t>
+        </is>
+      </c>
+      <c r="AB87" s="14" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="AC87" s="14" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:AC85"/>
+  <autoFilter ref="A3:AC87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
